--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,118 +489,99 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFQ- Impact Assessment Of The Water Quality Programme (Arsenic, Iron, Fluo...</t>
+          <t>RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and ...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Centre For Microfinance And Livelihood (Cml) An Associate Organization Tata Trusts | Kamrup, Nalbari &amp; Dhalai / North Tripura, Assam, Tripura
-RFQ- Impact Assessment Of The Water Quality Programme (Arsenic, Iron, Fluoride &amp; Bacterial Removal Units) In Assam And Tripura, Centre For Microfinance And L ... Read More</t>
+          <t>Lords Education and Health Society (LEHS) | India
+RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and Enterprise Wireless Access Points, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tende ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• 4. Scope of Work &amp; Coverage
-The assessment will cover a sample of 40 villages, constituting approximately 20% of the total 200 programme villages across Assam
-and Tripura, as detailed below:
-State District(s) Villages Covered IA Sample (20%)
-Assam – Kamrup – Villages Covered: 90 – IA Sample (20%): 18
-Assam – Nalbari – Villages Covered: 50 – IA Sample (20%): 10
-Tripura – Dhalai / North Tripura – Villages Covered: 60 – IA Sample (20%): 12
-Total Villages Covered- 200 and IA Sample- 40
-The final list of sample villages will be shared by CML in consultation with the selected agency, ensuring representation across technology types
-(ARP/IRP/Fluoride/Bacterial units), districts, and years of installation.
-5. Methodology
-The assessment is expected to adopt a mixed -methods approach, drawing on both qualitative and quantitative tools, including at minimum:
-Group Discussions (GDs) with beneficiary communities/Water User Committees in each sample village;
-Interpersonal communication and informal interactions with community members, Jal Mitra (Pump operators) and frontline
-functionaries; and
-Individual household interviews/surveys to capture quantifiable indicators of adoption, usage, and behaviour change.
-Bidders are encouraged to propose an appropriate sampling framework, survey tools and analytical approach in their technical
-proposal, in line with the objectives and scope outlined above.
-6. Deliverables
-Inception note, including finalised methodology, sampling plan and data collection tools;
-Cleaned primary data sets (quantitative and qualitative);
-A detailed Impact Assessment Report, covering findings against each objective and clear, actionable recommendations; and
-A summary PowerPoint presentation of key findings and recommendations, for presentation to CML and its partners.
-7. Timeline
-Milestone Indicative Timeline
-Issue of RFQ 1 September 2026
-Last date for submission of quotations 12 September 2026
-Selection &amp; award of assignment By 15 September 2026
-Field data collection (GDs, interviews, KIIs) Third week of Sept – 15 October 2026
-Submission of draft report &amp; PPT Within 5 working days of field completion
-Submission of final report &amp; PPT (post feedback) Within 5 working days of CML's comments
-8. Estimated Budget &amp; Payment Schedule
-Total Budget: INR 8,00,000 (Rupees Eight Lakh only), inclusive of GST, covering all professional fees, field travel, logistics and reporting costs
-Payment Schedule
-:
-On award / mobilisation – 30% – Trigger: Signing of agreement &amp; submission of field plan
-On completion of field work – 40% – Trigger: Submission of raw data &amp; field summary
-On acceptance of final report &amp; PPT 30% Submission of final report and presentation,incorporating CML's feedback
-• 9. Eligibility Criteria for Bidding Agencies
-Registered organisation/firm (Society, Trust, Section 8 Company, or Consultancy) with at least 3 years of experience in conducting social/development impact assessments, preferably in WASH, water security or public health;
-Demonstrated field experience in Assam and/or Tripura, or the wider Northeast region, will be preferred;
-Proven capability in qualitative and quantitative research methods, including GDs, KIIs and household surveys; and
-Valid PAN and GST registration, including MSME (if applicable)
-10. Composition of the Proposed Team
-Bidders must field a multi-disciplinary team, with, at minimum, the composition below. Detailed CVs of all proposed key personnel, along with
-their specific role on this assignment, must be submitted with the Technical Proposal; this will be a key input to CML’s evaluation of proposals.
-Proposed Team Composition (continued):
-Team Leader / Research Lead 1 10+ years WASH/public health impact assessments; mixed -methods
-Expertise continued: research design; report writing &amp; presentation
-Water Quality / WASH Technical Specialist – No. Required: 1 – Minimum Experience: 7+ years
-Expertise: Water quality &amp; water security programmes; drinking water treatment technologies
-Expertise continued: Water quality &amp; water security programmes; drinking water
-Expertise continued: treatment technologies (ARP/IRP/Fluoride/Bacterial removal
-Expertise continued: units), preferable to be a civil engineer or environmental
-engineer
-Social Scientist / Behaviour Change Specialist – No. Required: 1 – Minimum Experience: 7+ years
-Expertise: Community mobilisation, behaviour change communication,
-Expertise continued: gender &amp; social inclusion
-Statistician / Data Analyst – No. Required: 1 – Minimum Experience: 5+ years – Expertise: Quantitative survey design, sampling, statistical analysis and
-Expertise continued: data management
-Proposed Team Composition (continued):
-Field Researchers/Enumerators – No. Required: 6–8 (as required) – Minimum Experience: 4+ years – Expertise: Household surveys, GDs and KIIs; working proficiency in Expertise continued: Assamese/Bengali or relevant local dialects
-Bidders may propose an alternate but equivalent team structure, provided the combined expertise and experience levels above are demonstrably met; any such
-deviation should be clearly justified in the Technical Proposal.
-11. Submission Requirements
-Technical Proposal — organisational profile, relevant past experience/references, proposed methodology, sampling approach, team composition &amp; CVs, and work plan;
-Financial Proposal — itemized budget in INR, inclusive of GST, in a separate sealed document/file; and
-Statutory documents — PAN, GST registration certificate, and registration certificate of the organisation.
-Proposals should be submitted by email to
-procurement@cmlnortheast.com
-on or before 12 September 2026, 5:00 PM IST,
-with the subject line “RFQ Response – Water Quality Programme Impact Assessment ( CML/HR/6687/2026)”.
-For queries, please contact- Mr. Rituparno Chanda, M-8013068581
-Also need to send the quotation including other details in CML Office address-
-To, Executive Director, Centre for Microfinance and Livelihood,
-An Associate of Tata Trusts, 5th Floor Divine Plaza,
-Dispur Supermarket, Guwahati- 781006, M-8013068581
-12. General Terms &amp; Conditions
-The quotation shall remain valid for a minimum of 60 days from the last date of submission;
-All costs quoted must be inclusive of applicable taxes (GST) and shall not be revised during the assignment period;
-The selected agency shall ensure that field investigators are trained on ethical research conduct, informed consent, and
-child/community safeguarding norms while engaging with respondents;
-All primary data, tools and reports developed under this assignment shall remain the property of CML; and
-CML reserves the right to accept or reject any or all quotations, in part or in full, without assigning any reason.
-Annexure: Financial Proposal Format
-Financial Proposal Format:
-Professional fees (research team) – Unit: Lump sum
-Field travel &amp; logistics – Unit: Lump sum
-Data collection, transcription &amp; analysis Lump sum
-Report writing &amp; PPT preparation Lump sum
-GST @ applicable rate
-Total – inclusive of GST
-For more information, please visit our website :
-https://cmlnortheast.com/Tenders
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303512</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>RFP - English Annotation of Student Voice Recordings from Gujarat</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Gujarat
+RFP - English Annotation of Student Voice Recordings from Gujarat, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login ... Read More</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>• Submission Details
+All proposals to this RFP must be received no later than
+&lt;September 13th&gt;
+.
+The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP:
+English Transcriptions of Student Voice Recordings of Reading - Gujarat (Name of the partner)
+.
+Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below.
 • Job Email ID:
-Procurement(at)cmlnortheast.com
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP - Gujarat Data Annotation I Grades 3-8 English RFP.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-12 Sep 2026
+13 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -657,54 +638,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -735,72 +716,22 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>12-09-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303133</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and ...</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | India
-RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and Enterprise Wireless Access Points, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tende ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>13-09-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303512</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303219</t>
         </is>
       </c>
     </row>
@@ -912,54 +843,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1001,7 +932,7 @@
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -1018,44 +949,81 @@
       <c r="B5" s="1" t="inlineStr"/>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>RFP - English Annotation of Student Voice Recordings from Gujarat</t>
+          <t>RFP - for Hiring Data Collection Enumerators/Agency for Noida, Gurugram an...</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lords Education and Health Society (LEHS) | Gujarat
-RFP - English Annotation of Student Voice Recordings from Gujarat, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+          <t>MAMTA Health Institute for Mother and Child (MAMTA) | Uttar Pradesh, Haryana
+RFP - for Hiring Data Collection Enumerators/Agency for Noida, Gurugram and Mirzapur, Uttar Pradesh, MAMTA Health Institute for Mother and Child (MAMTA)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login ... Read More</t>
+Value Membershi ... Read More</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>• Submission Details
-All proposals to this RFP must be received no later than
-&lt;September 13th&gt;
-.
-The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP:
-English Transcriptions of Student Voice Recordings of Reading - Gujarat (Name of the partner)
-.
-Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
-For detailed information, please check the complete version of the RFP attached below.
+          <t>• Scope of Work
+Visit assigned government school’s/project locations in Noida, Gurugram and Mirzapur as per the approved field plan.
+Collect data using project-approved questionnaires, checklists, digital forms or other data-collection tools.
+Conduct interviews/discussions with relevant respondents such as teachers, school staff, students and other project stakeholders, as instructed.
+Record school-level information related to STEM education activities, participation, infrastructure, use of STEM resources and implementation progress, as applicable to the approved tools.
+Verify collected information for completeness, consistency and accuracy before submission.
+Capture photographs or supporting documentation only where specifically authorized under the project protocol and with due regard to consent and safeguarding requirements.
+Maintain daily field records and submit completed forms/data within the timelines communicated by the project team.
+Report data-quality issues, respondent concerns, school-level challenges or deviations from the field plan to the assigned supervisor.
+Maintain confidentiality of all project information, respondent information and collected data.
+Perform other reasonable field data-collection and documentation activities directly related to the assignment.
+Expected Deliverables
+Completed and quality-checked data-collection forms for all assigned schools/respondents.
+Daily/periodic field progress updates as required by the project team.
+Verified supporting documentation and field notes, where applicable.
+Submission of all assigned data and records within the agreed one-month assignment period.
+Final field completion report/summary as per the format provided by the project team.
+• Eligibility Criteria
+Minimum educational qualification: 12th Pass. Graduates are also eligible and may be preferred.
+Minimum age: 18 years as on the date of engagement.
+Good communication skills and ability to interact respectfully with school personnel, teachers and students.
+Basic ability to use smartphones/tablets/computers and digital data-collection applications.
+Ability to read and write Hindi; working knowledge of English will be an advantage.
+Willingness and ability to travel to assigned schools within the designated project locations.
+Prior experience in field surveys, data collection, education projects, school visits, research or community-based work will be an advantage.
+Candidates must be available for the full one-month engagement period.
+Required Skills and Competencies
+Attention to detail and accuracy in recording information.
+Good interpersonal and communication skills.
+Ability to follow structured questionnaires and field protocols.
+Basic digital literacy and data-entry skills.
+Punctuality, professionalism and ability to work independently in the field.
+Commitment to confidentiality, ethical data collection and responsible conduct with children and school communities.
+Duration and Place of Engagement
+The engagement will be for one month. Enumerators may be deployed across Noida, Gurugram and Mirzapur based on project requirements. Exact school allocation, field schedule and reporting arrangements will be communicated by the project team.
+• Selection Process
+• Screening of applications against the eligibility criteria.
+Shortlisting based on qualification, relevant experience, communication skills and availability.
+Interview/interaction and, where required, a short practical/data-collection assessment.
+Final selection and engagement subject to project requirements and satisfactory verification of submitted information.
+• Application/Proposal Submission Requirements
+Updated CV/profile and Educational qualification details and supporting certificates
+Aadhar card, PAN card, Bank detail
+• Terms and Conditions
+The engagement is temporary and limited to the specified one-month assignment unless extended in writing.
+Selection and deployment will depend on project requirements and availability of suitable candidates.
+Submission of Application
+Interested candidates/agencies may submit their application/CV to email
+rfp@mamtahimc.in
+. Suggested subject line: “Application for Data Collection Enumerator –Location]”. By 13
+th
+September 2026 for any clarification contact at
+rfp@mamtahimc.in
+by 11
+th
+September 2026.
 • Job Email ID:
-rfp.lehs(at)wadhwaniai.org
-Download Attachment:
-RFP - Gujarat Data Annotation I Grades 3-8 English RFP.pdf
+rfp(at)mamtahimc.in
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1117,54 +1085,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1197,7 +1165,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Governance, Safety</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -1206,11 +1174,11 @@
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303219</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303525</t>
         </is>
       </c>
     </row>
@@ -1310,54 +1278,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1399,7 +1367,7 @@
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -1599,54 +1567,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1688,7 +1656,7 @@
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -1705,504 +1673,10 @@
       <c r="B8" s="1" t="inlineStr"/>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>RFP - Hindi Annotation of Student Voice Recordings from Bihar</t>
+          <t>RFP-ERP, CRM, People Management Software Solution</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | Bihar
-RFP - Hindi Annotation of Student Voice Recordings from Bihar, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Regi ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>• Submission Details
-All proposals to this RFP must be received no later than
-&lt;September 13th&gt;
-.
-The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP:
-Hindi Transcriptions of Student Voice Recordings of Reading - Bihar (Name of the partner)
-.
-Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
-For detailed information, please check the complete version of the RFP attached below
-• Job Email ID:
-rfp.lehs(at)wadhwaniai.org
-Download Attachment:
-RFP - Bihar Data Annotation I Grades 1-8 Hindi RFP.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-13 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
-Apply by:
-20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>13-09-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303221</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Hiring Data Collection Enumerators/Agency for Noida, Gurugram an...</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | Uttar Pradesh, Haryana
-RFP - for Hiring Data Collection Enumerators/Agency for Noida, Gurugram and Mirzapur, Uttar Pradesh, MAMTA Health Institute for Mother and Child (MAMTA)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membershi ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-Visit assigned government school’s/project locations in Noida, Gurugram and Mirzapur as per the approved field plan.
-Collect data using project-approved questionnaires, checklists, digital forms or other data-collection tools.
-Conduct interviews/discussions with relevant respondents such as teachers, school staff, students and other project stakeholders, as instructed.
-Record school-level information related to STEM education activities, participation, infrastructure, use of STEM resources and implementation progress, as applicable to the approved tools.
-Verify collected information for completeness, consistency and accuracy before submission.
-Capture photographs or supporting documentation only where specifically authorized under the project protocol and with due regard to consent and safeguarding requirements.
-Maintain daily field records and submit completed forms/data within the timelines communicated by the project team.
-Report data-quality issues, respondent concerns, school-level challenges or deviations from the field plan to the assigned supervisor.
-Maintain confidentiality of all project information, respondent information and collected data.
-Perform other reasonable field data-collection and documentation activities directly related to the assignment.
-Expected Deliverables
-Completed and quality-checked data-collection forms for all assigned schools/respondents.
-Daily/periodic field progress updates as required by the project team.
-Verified supporting documentation and field notes, where applicable.
-Submission of all assigned data and records within the agreed one-month assignment period.
-Final field completion report/summary as per the format provided by the project team.
-• Eligibility Criteria
-Minimum educational qualification: 12th Pass. Graduates are also eligible and may be preferred.
-Minimum age: 18 years as on the date of engagement.
-Good communication skills and ability to interact respectfully with school personnel, teachers and students.
-Basic ability to use smartphones/tablets/computers and digital data-collection applications.
-Ability to read and write Hindi; working knowledge of English will be an advantage.
-Willingness and ability to travel to assigned schools within the designated project locations.
-Prior experience in field surveys, data collection, education projects, school visits, research or community-based work will be an advantage.
-Candidates must be available for the full one-month engagement period.
-Required Skills and Competencies
-Attention to detail and accuracy in recording information.
-Good interpersonal and communication skills.
-Ability to follow structured questionnaires and field protocols.
-Basic digital literacy and data-entry skills.
-Punctuality, professionalism and ability to work independently in the field.
-Commitment to confidentiality, ethical data collection and responsible conduct with children and school communities.
-Duration and Place of Engagement
-The engagement will be for one month. Enumerators may be deployed across Noida, Gurugram and Mirzapur based on project requirements. Exact school allocation, field schedule and reporting arrangements will be communicated by the project team.
-• Selection Process
-• Screening of applications against the eligibility criteria.
-Shortlisting based on qualification, relevant experience, communication skills and availability.
-Interview/interaction and, where required, a short practical/data-collection assessment.
-Final selection and engagement subject to project requirements and satisfactory verification of submitted information.
-• Application/Proposal Submission Requirements
-Updated CV/profile and Educational qualification details and supporting certificates
-Aadhar card, PAN card, Bank detail
-• Terms and Conditions
-The engagement is temporary and limited to the specified one-month assignment unless extended in writing.
-Selection and deployment will depend on project requirements and availability of suitable candidates.
-Submission of Application
-Interested candidates/agencies may submit their application/CV to email
-rfp@mamtahimc.in
-. Suggested subject line: “Application for Data Collection Enumerator –Location]”. By 13
-th
-September 2026 for any clarification contact at
-rfp@mamtahimc.in
-by 11
-th
-September 2026.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-13 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
-Apply by:
-20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Safety</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>13-09-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303525</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Stanley 1913 Creators Fund 2027 – $50,000 Grants for Early-Stage Nonprofits</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Stanley 1913 is a global lifestyle brand built around a long history of invention and practical design. Through theStanley 1913 Creators Fund, the company supports emerging nonprofit leaders and organisations developing innovative approaches to community challenges. The Fund reflects Stanley 1913’s ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>The Fund is intended forearly-stage nonprofit organisationsand emerging leaders developing innovative solutions to community challenges. Applicants should demonstrate a clear idea, meaningful community connection and potential for positive impact. The programme is not limited to a single sector, allowing organisations working across different social and community issues to apply. Stanley 1913’s previous grantees demonstrate the breadth of eligible causes, including youth development, water access, food security, environmental initiatives and economic empowerment. Applicants should review the current application guidelines carefully for the specific organisational, geographic and legal requirements applicable to the 2027 funding cycle.</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/stanley-1913-creators-fund-2027-50000-grants-for-early-stage-nonprofits/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>RFP-ERP, CRM, People Management Software Solution</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>HelpAge India | India
 RFP-ERP, CRM, People Management Software Solution, HelpAge India() | DevNetJobsIndia
@@ -2227,7 +1701,7 @@
 RFP-ERP, CR ... Read More</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• The agency shall bear all costs associated with the preparation and submission of bid.
 The agency must have PAN (Permanent Account Number) and registered with GST and the document for the same is to be attached.
@@ -2401,54 +1875,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2479,14 +1953,311 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302971</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hindi Annotation of Student Voice Recordings from Bihar</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Bihar
+RFP - Hindi Annotation of Student Voice Recordings from Bihar, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regi ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• Submission Details
+All proposals to this RFP must be received no later than
+&lt;September 13th&gt;
+.
+The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP:
+Hindi Transcriptions of Student Voice Recordings of Reading - Bihar (Name of the partner)
+.
+Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below
+• Job Email ID:
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP - Bihar Data Annotation I Grades 1-8 Hindi RFP.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+13 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Head of People &amp; Culture
+(Value Members only)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Researcher
+(Value Members only)
+Location:
+Punjab
+Apply by:
+20 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303221</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Stanley 1913 Creators Fund 2027 – $50,000 Grants for Early-Stage Nonprofits</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Stanley 1913 is a global lifestyle brand built around a long history of invention and practical design. Through theStanley 1913 Creators Fund, the company supports emerging nonprofit leaders and organisations developing innovative approaches to community challenges. The Fund reflects Stanley 1913’s ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The Fund is intended forearly-stage nonprofit organisationsand emerging leaders developing innovative solutions to community challenges. Applicants should demonstrate a clear idea, meaningful community connection and potential for positive impact. The programme is not limited to a single sector, allowing organisations working across different social and community issues to apply. Stanley 1913’s previous grantees demonstrate the breadth of eligible causes, including youth development, water access, food security, environmental initiatives and economic empowerment. Applicants should review the current application guidelines carefully for the specific organisational, geographic and legal requirements applicable to the 2027 funding cycle.</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/stanley-1913-creators-fund-2027-50000-grants-for-early-stage-nonprofits/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Rolex Explorers Club Grant 2027</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>The Explorers Clubis an international not-for-profit organization founded in 1904 to advance scientific exploration, field research and the preservation of the instinct to explore. Its global membership includes scientists, researchers and explorers working across disciplines such as oceanography, a ... Read More</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>TheRolex Explorers Club Grantsupports young explorers conducting fieldwork that addresses anovel scientific, environmental or historical question. The programme is designed to help researchers undertake original field science capable of generating significant new understanding or impact. Awards areUS$10,000and can support fieldwork across disciplines including ecology, wildlife, botany, archaeology, earth sciences, marine and freshwater research, geography and paleontology. Applicants must present a clear scientific rationale, original research and a strong fieldwork component. The 2027 field-season application cycle is currently open, with submissions due14 September 2026 at 6:00 PM ET.</t>
+        </is>
+      </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="H11" s="1" t="n">
@@ -2494,7 +2265,7 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302971</t>
+          <t>https://andpurpose.world/rolex-explorers-club-grant-2027/</t>
         </is>
       </c>
     </row>
@@ -2511,22 +2282,22 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Exhibition Publication Grants</t>
+          <t>Fair Water Action Fund for Water Justice and Water Security</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ThePaul Mellon Centre for Studies in British Artis an internationally recognised research institution dedicated to advancing the understanding of British art, architecture, and visual culture. Through grants, fellowships, publications, and collaborative initiatives, the Centre supports innovative re ... Read More</t>
+          <t>Water Witness Internationalis a global organization working to improve water security, water governance and climate resilience while promoting fairness and accountability in water management. The organization works with communities, civil society groups, researchers, journalists and other partners t ... Read More</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Applications are open toorganisations, institutions, non-profit organisations, and international organisationsproducing publications connected to exhibitions or displays on British art, visual culture, or architecture. Collaborative applications involving multiple organisations are encouraged, provided roles and responsibilities are clearly defined. Eligible projects include exhibition catalogues, research publications, and practice-based research outputs that contribute new knowledge to British art studies. Applicants must submit a detailed project description, publication plan, realistic budget, and referee information through the official application system. Proposals should demonstrate strong research quality, clear audience engagement, and practical plans for publication and dissemination.</t>
+          <t>The Fair Water Action Fund is open to applicants working in theGlobal South, particularly in countries experiencing physical and economic water scarcity. Eligible applicants may includecivil society organizations, media organizations, coalitions and networks, investigative journalists, individual researchers and research institutions. Applicants should demonstrate a clear connection between their proposed work and water justice, water security, accountability or systemic change. Strong applications should address practical water challenges and show how the proposed work can contribute to improved governance, equitable access to water, stronger accountability or policy change. Initiatives may address water, sanitation, drought, floods, pollution, water conflicts, climate impacts or related governance challenges.</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -2535,11 +2306,11 @@
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-exhibition-publication-grants/</t>
+          <t>https://andpurpose.world/fair-water-action-fund-for-water-justice-and-water-security/</t>
         </is>
       </c>
     </row>
@@ -2556,17 +2327,17 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Fair Water Action Fund for Water Justice and Water Security</t>
+          <t>Call for Proposals: Community Grants Program (Canada)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Water Witness Internationalis a global organization working to improve water security, water governance and climate resilience while promoting fairness and accountability in water management. The organization works with communities, civil society groups, researchers, journalists and other partners t ... Read More</t>
+          <t>Community Foundation of Southeastern Alberta (CFSEA) TheCommunity Foundation of Southeastern Alberta (CFSEA)is a community-focused philanthropic organization that works to strengthen communities across Southeastern Alberta. Through grantmaking, partnerships and local research, CFSEA supports initiat ... Read More</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>The Fair Water Action Fund is open to applicants working in theGlobal South, particularly in countries experiencing physical and economic water scarcity. Eligible applicants may includecivil society organizations, media organizations, coalitions and networks, investigative journalists, individual researchers and research institutions. Applicants should demonstrate a clear connection between their proposed work and water justice, water security, accountability or systemic change. Strong applications should address practical water challenges and show how the proposed work can contribute to improved governance, equitable access to water, stronger accountability or policy change. Initiatives may address water, sanitation, drought, floods, pollution, water conflicts, climate impacts or related governance challenges.</t>
+          <t>Eligible applicants must provide services inSoutheastern Albertaand meet CFSEA’s organizational requirements. Potential applicants includeregistered charities, municipalities, school divisions, qualified donees and eligible nonprofit organizations working in partnership with a qualified donee. Registered nonprofit societies in Alberta may also apply directly where they meet the programme’s requirements, including the applicable five-year good-standing requirement. Applicants should have no outstanding final reports from previous CFSEA Community Grants. Proposed projects must address a demonstrated community need, align with one or more funding priorities, benefit Southeastern Alberta communities and have achievable objectives and measurable outcomes. Political activities, religious activities, debt repayment and projects outside the region are not eligible.</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -2580,72 +2351,27 @@
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/fair-water-action-fund-for-water-justice-and-water-security/</t>
+          <t>https://andpurpose.world/call-for-proposals-community-grants-program-canada/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Call for Proposals: Community Grants Program (Canada)</t>
+          <t>RFP - Engagement of Banking Partner(s) for Employee Benefits Fund</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Community Foundation of Southeastern Alberta (CFSEA) TheCommunity Foundation of Southeastern Alberta (CFSEA)is a community-focused philanthropic organization that works to strengthen communities across Southeastern Alberta. Through grantmaking, partnerships and local research, CFSEA supports initiat ... Read More</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants must provide services inSoutheastern Albertaand meet CFSEA’s organizational requirements. Potential applicants includeregistered charities, municipalities, school divisions, qualified donees and eligible nonprofit organizations working in partnership with a qualified donee. Registered nonprofit societies in Alberta may also apply directly where they meet the programme’s requirements, including the applicable five-year good-standing requirement. Applicants should have no outstanding final reports from previous CFSEA Community Grants. Proposed projects must address a demonstrated community need, align with one or more funding priorities, benefit Southeastern Alberta communities and have achievable objectives and measurable outcomes. Political activities, religious activities, debt repayment and projects outside the region are not eligible.</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>14 September 2026</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/call-for-proposals-community-grants-program-canada/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Engagement of Banking Partner(s) for Employee Benefits Fund</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 RFP - Engagement of Banking Partner(s) for Employee Benefits Fund, Coalition for Disaster Resilient Infrastructure (CDRI)() | DevNetJobsIndia
@@ -2661,7 +2387,7 @@
 E ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>• 3.Scope of Work
 The selected Bank(s) shall provide banking, cash and liquidity management, treasury advisory, investment execution and related reporting services for the Employee Benefits Fund, including but not limited to:
@@ -2755,54 +2481,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2833,22 +2559,67 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>14-09-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302418</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Applications Open for Exhibition Publication Grants</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>ThePaul Mellon Centre for Studies in British Artis an internationally recognised research institution dedicated to advancing the understanding of British art, architecture, and visual culture. Through grants, fellowships, publications, and collaborative initiatives, the Centre supports innovative re ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Applications are open toorganisations, institutions, non-profit organisations, and international organisationsproducing publications connected to exhibitions or displays on British art, visual culture, or architecture. Collaborative applications involving multiple organisations are encouraged, provided roles and responsibilities are clearly defined. Eligible projects include exhibition catalogues, research publications, and practice-based research outputs that contribute new knowledge to British art studies. Applicants must submit a detailed project description, publication plan, realistic budget, and referee information through the official application system. Proposals should demonstrate strong research quality, clear audience engagement, and practical plans for publication and dissemination.</t>
+        </is>
+      </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302418</t>
+          <t>https://andpurpose.world/applications-open-for-exhibition-publication-grants/</t>
         </is>
       </c>
     </row>
@@ -2946,54 +2717,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3035,7 +2806,7 @@
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -3046,61 +2817,16 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Rolex Explorers Club Grant 2027</t>
+          <t>RFP - Individual Consultant / Firm Engagement: TN Energy Audits</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>The Explorers Clubis an international not-for-profit organization founded in 1904 to advance scientific exploration, field research and the preservation of the instinct to explore. Its global membership includes scientists, researchers and explorers working across disciplines such as oceanography, a ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>TheRolex Explorers Club Grantsupports young explorers conducting fieldwork that addresses anovel scientific, environmental or historical question. The programme is designed to help researchers undertake original field science capable of generating significant new understanding or impact. Awards areUS$10,000and can support fieldwork across disciplines including ecology, wildlife, botany, archaeology, earth sciences, marine and freshwater research, geography and paleontology. Applicants must present a clear scientific rationale, original research and a strong fieldwork component. The 2027 field-season application cycle is currently open, with submissions due14 September 2026 at 6:00 PM ET.</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>14 September 2026</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/rolex-explorers-club-grant-2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Individual Consultant / Firm Engagement: TN Energy Audits</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>World Resources Institute India (WRI India) | Tamil Nadu
 RFP - Individual Consultant / Firm Engagement: TN Energy Audits, World Resources Institute India (WRI India)() | DevNetJobsIndia
@@ -3118,7 +2844,7 @@
 L ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>• Accordingly, IRT seeks to engage a qualified and certified energy auditing firm or energy auditor (consultant) to undertake comprehensive energy audits, collect and analyse technical data, develop evidence-based recommendations, and prepare detailed technical reports and implementation guidance in accordance with the scope of work outlined in this Terms of Reference.
 2.         Objectives of the Consultancy
@@ -3211,54 +2937,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3289,38 +3015,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Climate</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>15-09-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303143</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - Speaker Attribution Data Annotation of ORF Voice Recordings</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS) | India
 RFP - Speaker Attribution Data Annotation of ORF Voice Recordings, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
@@ -3339,7 +3065,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• PROPOSAL SUBMISSION GUIDELINES
 Your proposal must include:
@@ -3452,54 +3178,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3530,22 +3256,67 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>SURE! Invest 2026 Funding Program (Austria)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>TheClimate and Energy Fund (Austria)supports projects that accelerate climate action, sustainable development and environmental resilience across the country. Working with regional authorities and communities, the Fund finances innovative initiatives that address climate change, improve energy effic ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>TheSURE! Invest 2026 Funding Programis open to eligibleKLAR! (Climate Change Adaptation Model Regions)andKEM (Climate and Energy Model Regions)that are in the implementation phase. Regions where KLAR! and KEM programmes overlap must coordinate with KLAR! management before submitting a KEM application. Applicants must contributeat least 25%of project costs through regional funding. Only one application may be submitted per eligible region under this funding call. Projects should address genuine climate adaptation challenges and follow principles of environmental sustainability, social inclusion and long-term climate resilience.</t>
+        </is>
+      </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>Governance, Learning, Safety</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303101</t>
+          <t>https://andpurpose.world/sure-invest-2026-funding-program-austria/</t>
         </is>
       </c>
     </row>
@@ -3689,54 +3460,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3778,7 +3549,7 @@
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -3903,54 +3674,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3992,7 +3763,7 @@
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -4013,22 +3784,22 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>SURE! Invest 2026 Funding Program (Austria)</t>
+          <t>Mahila Krishi Shakti Puraskar 2026 – JSW Foundation–MSSRF National Award for Women in Agriculture</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>TheClimate and Energy Fund (Austria)supports projects that accelerate climate action, sustainable development and environmental resilience across the country. Working with regional authorities and communities, the Fund finances innovative initiatives that address climate change, improve energy effic ... Read More</t>
+          <t>M. S. Swaminathan Research Foundation (MSSRF) in collaboration with JSW Foundation TheM. S. Swaminathan Research Foundation (MSSRF)is an Indian organisation focused on pro-poor, pro-women and pro-nature development, with longstanding work in agriculture, nutrition, biodiversity, ecology and rural co ... Read More</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>TheSURE! Invest 2026 Funding Programis open to eligibleKLAR! (Climate Change Adaptation Model Regions)andKEM (Climate and Energy Model Regions)that are in the implementation phase. Regions where KLAR! and KEM programmes overlap must coordinate with KLAR! management before submitting a KEM application. Applicants must contributeat least 25%of project costs through regional funding. Only one application may be submitted per eligible region under this funding call. Projects should address genuine climate adaptation challenges and follow principles of environmental sustainability, social inclusion and long-term climate resilience.</t>
+          <t>The application deadline is 15 September 2026</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -4037,11 +3808,11 @@
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/sure-invest-2026-funding-program-austria/</t>
+          <t>https://andpurpose.world/mahila-krishi-shakti-puraskar-2026-jsw-foundation-mssrf-national-award-for-women-in-agriculture/</t>
         </is>
       </c>
     </row>
@@ -4058,17 +3829,17 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Mahila Krishi Shakti Puraskar 2026 – JSW Foundation–MSSRF National Award for Women in Agriculture</t>
+          <t>CFAs: Strengthening the Role of Women’s Rights Organisations for Implementation of Gender Equality (Zimbabwe)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>M. S. Swaminathan Research Foundation (MSSRF) in collaboration with JSW Foundation TheM. S. Swaminathan Research Foundation (MSSRF)is an Indian organisation focused on pro-poor, pro-women and pro-nature development, with longstanding work in agriculture, nutrition, biodiversity, ecology and rural co ... Read More</t>
+          <t>TheEuropean Commissionsupports programmes that promote human rights, gender equality, democratic governance and sustainable development worldwide. Through its external funding initiatives, the Commission partners with civil society organisations, non-governmental organisations and public institution ... Read More</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 15 September 2026</t>
+          <t>TheWomen’s Rights Organisations Grant Zimbabwe 2026is open tonon-profit organisations, NGOs, women’s rights organisations and eligible international organisationsestablished in Zimbabwe, an EU Member State or another eligible NDICI-GE country. Applicants may apply individually or with co-applicants and affiliated entities. Projects must be implemented in Zimbabwe and adopt gender-transformative and rights-based approaches. Applicants must meet all European Commission eligibility requirements and demonstrate the operational and financial capacity to manage large-scale grant projects. Registration in the required EU systems is mandatory before submission.</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -4082,11 +3853,11 @@
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/mahila-krishi-shakti-puraskar-2026-jsw-foundation-mssrf-national-award-for-women-in-agriculture/</t>
+          <t>https://andpurpose.world/cfas-strengthening-the-role-of-womens-rights-organisations-for-implementation-of-gender-equality-zimbabwe/</t>
         </is>
       </c>
     </row>
@@ -4103,17 +3874,17 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Translation Funding Programme Grants for German-Language Literature</t>
+          <t>India Fund</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TheGoethe-Institutis the cultural institute of the Federal Republic of Germany with a global network dedicated to promoting German language and international cultural cooperation. It provides cultural and educational programmes that encourage intercultural dialogue, cultural participation and intern ... Read More</t>
+          <t>ThePaul Hamlyn Foundation (PHF)is a UK-based independent grant-making foundation established in 1987. The Foundation works towards a just future where everyone, particularly young people, can realise their potential and enjoy fulfilling and creative lives. Its strategic priorities include investing ... Read More</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>The programme is open tointernational professional publishersthat wish to translate German-language books. Applicants must have documented experience publishing quality literature and maintain professional distribution channels.Translators and authors cannot apply directlyfor this translation subsidy. The translation must be made directly from theoriginal German text, and the work must have been published in printed form by a publisher in a German-speaking country. The applicant publisher must provide the required rights and translation contracts and demonstrate the quality of its publishing programme and previous translations. The translation mustnot go to print before the funding agreement has been signed.</t>
+          <t>Confirm that your organisation is an eligible Indian NGO with FCRA registration and operates locally within the communities it serves. Develop a community-centred proposal demonstrating how disadvantaged communities will participate in designing and leading change. Explain the intended systemic impact, organisational capacity-building approach, environmental considerations and commitment to gender equality. Prepare the required organisational and project information and submit the application through the Paul Hamlyn Foundation’s official India Fund process before the deadline.</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -4127,11 +3898,11 @@
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/translation-funding-programme-grants-for-german-language-literature/</t>
+          <t>https://andpurpose.world/india-fund/</t>
         </is>
       </c>
     </row>
@@ -4148,22 +3919,22 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>CFAs: Strengthening the Role of Women’s Rights Organisations for Implementation of Gender Equality (Zimbabwe)</t>
+          <t>Translation Funding Programme Grants for German-Language Literature</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>TheEuropean Commissionsupports programmes that promote human rights, gender equality, democratic governance and sustainable development worldwide. Through its external funding initiatives, the Commission partners with civil society organisations, non-governmental organisations and public institution ... Read More</t>
+          <t>TheGoethe-Institutis the cultural institute of the Federal Republic of Germany with a global network dedicated to promoting German language and international cultural cooperation. It provides cultural and educational programmes that encourage intercultural dialogue, cultural participation and intern ... Read More</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>TheWomen’s Rights Organisations Grant Zimbabwe 2026is open tonon-profit organisations, NGOs, women’s rights organisations and eligible international organisationsestablished in Zimbabwe, an EU Member State or another eligible NDICI-GE country. Applicants may apply individually or with co-applicants and affiliated entities. Projects must be implemented in Zimbabwe and adopt gender-transformative and rights-based approaches. Applicants must meet all European Commission eligibility requirements and demonstrate the operational and financial capacity to manage large-scale grant projects. Registration in the required EU systems is mandatory before submission.</t>
+          <t>The programme is open tointernational professional publishersthat wish to translate German-language books. Applicants must have documented experience publishing quality literature and maintain professional distribution channels.Translators and authors cannot apply directlyfor this translation subsidy. The translation must be made directly from theoriginal German text, and the work must have been published in printed form by a publisher in a German-speaking country. The applicant publisher must provide the required rights and translation contracts and demonstrate the quality of its publishing programme and previous translations. The translation mustnot go to print before the funding agreement has been signed.</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
@@ -4172,11 +3943,11 @@
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/cfas-strengthening-the-role-of-womens-rights-organisations-for-implementation-of-gender-equality-zimbabwe/</t>
+          <t>https://andpurpose.world/translation-funding-programme-grants-for-german-language-literature/</t>
         </is>
       </c>
     </row>
@@ -4193,17 +3964,17 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for GEF SGP CSO Challenge Program 2026</t>
+          <t>2026 Call for Proposals: Mountains ADAPT Small Grants</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Global Environment Facility (GEF) Small Grants Programme (SGP), implemented through IUCN and RTI International TheGlobal Environment Facility Small Grants Programme (GEF SGP)supports locally led environmental action by civil society and community-based organisations. Established in 1992, the program ... Read More</t>
+          <t>TheUnited Nations Environment Programme (UNEP)is the United Nations system’s leading global environmental authority. It works to set the environmental agenda, promote coherent implementation of the environmental dimension of sustainable development and strengthen international action on environmenta ... Read More</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Applicants should first review the official programme eligibility requirements and select the relevant regional call. For the current call, organisations in Africa, Latin America &amp; the Caribbean, and Asia-Pacific &amp; Oceania can submit proposals online in English, French or Spanish. The application should demonstrate the existing solution’s environmental results, scalability, innovation, theory of change, partnerships, sustainability and financial viability. Applications are submitted through the online grants portal before the stated regional deadline.</t>
+          <t>Complete the official Mountains ADAPT application form and provide information about your organization, previous experience, the mountain climate challenge being addressed, proposed nature-based solution, beneficiaries and expected community benefits. Upload the organization’s valid registration certificate. The proposal should demonstrate community ownership, gender and youth inclusion, feasibility, sustainability and environmental safeguards. Applications can be submitted in English and, depending on location, Armenian, Azerbaijani, French, Georgian or Kiswahili. Submit before the deadline. UNEP – UN Environment Programme</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -4217,11 +3988,11 @@
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-gef-sgp-cso-challenge-program-2026/</t>
+          <t>https://andpurpose.world/2026-call-for-proposals-mountains-adapt-small-grants/</t>
         </is>
       </c>
     </row>
@@ -4238,17 +4009,17 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>India Fund</t>
+          <t>Applications Invited for GEF SGP CSO Challenge Program 2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ThePaul Hamlyn Foundation (PHF)is a UK-based independent grant-making foundation established in 1987. The Foundation works towards a just future where everyone, particularly young people, can realise their potential and enjoy fulfilling and creative lives. Its strategic priorities include investing ... Read More</t>
+          <t>Global Environment Facility (GEF) Small Grants Programme (SGP), implemented through IUCN and RTI International TheGlobal Environment Facility Small Grants Programme (GEF SGP)supports locally led environmental action by civil society and community-based organisations. Established in 1992, the program ... Read More</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Confirm that your organisation is an eligible Indian NGO with FCRA registration and operates locally within the communities it serves. Develop a community-centred proposal demonstrating how disadvantaged communities will participate in designing and leading change. Explain the intended systemic impact, organisational capacity-building approach, environmental considerations and commitment to gender equality. Prepare the required organisational and project information and submit the application through the Paul Hamlyn Foundation’s official India Fund process before the deadline.</t>
+          <t>Applicants should first review the official programme eligibility requirements and select the relevant regional call. For the current call, organisations in Africa, Latin America &amp; the Caribbean, and Asia-Pacific &amp; Oceania can submit proposals online in English, French or Spanish. The application should demonstrate the existing solution’s environmental results, scalability, innovation, theory of change, partnerships, sustainability and financial viability. Applications are submitted through the online grants portal before the stated regional deadline.</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -4262,554 +4033,27 @@
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/india-fund/</t>
+          <t>https://andpurpose.world/applications-invited-for-gef-sgp-cso-challenge-program-2026/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>2026 Call for Proposals: Mountains ADAPT Small Grants</t>
+          <t>RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-...</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>TheUnited Nations Environment Programme (UNEP)is the United Nations system’s leading global environmental authority. It works to set the environmental agenda, promote coherent implementation of the environmental dimension of sustainable development and strengthen international action on environmenta ... Read More</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Complete the official Mountains ADAPT application form and provide information about your organization, previous experience, the mountain climate challenge being addressed, proposed nature-based solution, beneficiaries and expected community benefits. Upload the organization’s valid registration certificate. The proposal should demonstrate community ownership, gender and youth inclusion, feasibility, sustainability and environmental safeguards. Applications can be submitted in English and, depending on location, Armenian, Azerbaijani, French, Georgian or Kiswahili. Submit before the deadline. UNEP – UN Environment Programme</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>15 September 2026</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/2026-call-for-proposals-mountains-adapt-small-grants/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>Master Composter Training to Strengthen Composting Practices in Ukrainian Communities</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>TheZero Waste Academyis a learning platform focused on sharing practical knowledge and approaches related to waste prevention, resource efficiency and circular economy practices. Through educational programmes, the platform connects participants with experts and practical experiences that can be ada ... Read More</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>The programme is open to participants fromUkrainewho are interested in composting and bio-waste management. Eligible participants can include Ukrainian communities, civil society organisations, institutions, community initiatives and individuals. People with existing composting experience as well as those planning to introduce composting at home, within an organisation or at community level can participate. Applicants do not necessarily need to already operate a composting programme. The course is suitable for people who want to gain practical knowledge and apply composting and circular-economy approaches within their communities or organisations.</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>16 September 2026</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/master-composter-training-to-strengthen-composting-practices-in-ukrainian-communities/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Standardisation and Development of Community Training Modules and Fa...</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-ToR - Standardisation and Development of Community Training Modules and Facilitator Manuals for WASH-Secure Communities, WaterAid India() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-| ... Read More</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>• Evaluation Criteria
-Selection will follow a
-Quality and Cost Based Selection (QCBS)
-process.
-Technical Evaluation (80 Marks)
-Criteria
-Marks
-Understanding   of assignment
-15
-Methodology   and technical approach
-20
-Relevant   organisational experience
-15
-Experience of   proposed team members
-20
-Quality of   previous work samples
-10
-Total   Technical Score
-80
-Only bidders scoring
-60 marks or above
-in the technical evaluation will qualify for financial evaluation.
-Financial Evaluation (20 Marks)
-The lowest evaluated financial proposal will receive the maximum score of 20, while other proposals will be scored proportionately.
-Final Score
-Final Score = Technical Score (80%) + Financial Score (20%)
-The consultant/agency obtaining the highest combined score will be recommended for award.
-Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
-th
-September by 5:30 pm
-For detailed information, please check the complete version of the ToR attached below.
-• Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
-Download Attachment:
-TOR for Standardisation of Modules.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-16 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
-Apply by:
-20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303298</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Development of WaterAid India's Hygiene Framework, Community Facilit...</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-ToR - Development of WaterAid India's Hygiene Framework, Community Facilitator Toolkit, Hygiene Booklet and Hygiene Calendar, WaterAid India() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Log ... Read More</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>• Evaluation Criteria
-Criteria
-Weight
-Understanding   of assignment
-20%
-Proposed   methodology
-25%
-Relevant   organisational experience
-20%
-Team   composition and expertise
-20%
-Financial   proposal
-15%
-Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
-th
-September by 5:30 pm
-For detailed information, please check the complete version of the ToR attached below.
-• Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
-Download Attachment:
-TOR for Hygiene Tool kit and framework.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-16 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
-Apply by:
-20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303297</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-...</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>WaterAid India | Bhadrak, Odisha, Unnao, Uttar Pradesh
 RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-Change Affected Vulnerable Communities”, WaterAid India(Bhadrak, Odisha, Unnao) | DevNetJobsIndia
@@ -4823,7 +4067,7 @@
 RFPs ... Read More</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Pre-bid Queries:
 By 15 September 2026
@@ -4972,54 +4216,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5050,14 +4294,541 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303358</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Master Composter Training to Strengthen Composting Practices in Ukrainian Communities</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>TheZero Waste Academyis a learning platform focused on sharing practical knowledge and approaches related to waste prevention, resource efficiency and circular economy practices. Through educational programmes, the platform connects participants with experts and practical experiences that can be ada ... Read More</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>The programme is open to participants fromUkrainewho are interested in composting and bio-waste management. Eligible participants can include Ukrainian communities, civil society organisations, institutions, community initiatives and individuals. People with existing composting experience as well as those planning to introduce composting at home, within an organisation or at community level can participate. Applicants do not necessarily need to already operate a composting programme. The course is suitable for people who want to gain practical knowledge and apply composting and circular-economy approaches within their communities or organisations.</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>16 September 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/master-composter-training-to-strengthen-composting-practices-in-ukrainian-communities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Standardisation and Development of Community Training Modules and Fa...</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | India
+ToR - Standardisation and Development of Community Training Modules and Facilitator Manuals for WASH-Secure Communities, WaterAid India() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+| ... Read More</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>• Evaluation Criteria
+Selection will follow a
+Quality and Cost Based Selection (QCBS)
+process.
+Technical Evaluation (80 Marks)
+Criteria
+Marks
+Understanding   of assignment
+15
+Methodology   and technical approach
+20
+Relevant   organisational experience
+15
+Experience of   proposed team members
+20
+Quality of   previous work samples
+10
+Total   Technical Score
+80
+Only bidders scoring
+60 marks or above
+in the technical evaluation will qualify for financial evaluation.
+Financial Evaluation (20 Marks)
+The lowest evaluated financial proposal will receive the maximum score of 20, while other proposals will be scored proportionately.
+Final Score
+Final Score = Technical Score (80%) + Financial Score (20%)
+The consultant/agency obtaining the highest combined score will be recommended for award.
+Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
+th
+September by 5:30 pm
+For detailed information, please check the complete version of the ToR attached below.
+• Job Email ID:
+WAIP2P-Delhi(at)wateraid.org
+Download Attachment:
+TOR for Standardisation of Modules.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+16 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Head of People &amp; Culture
+(Value Members only)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Researcher
+(Value Members only)
+Location:
+Punjab
+Apply by:
+20 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303298</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Development of WaterAid India's Hygiene Framework, Community Facilit...</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | India
+ToR - Development of WaterAid India's Hygiene Framework, Community Facilitator Toolkit, Hygiene Booklet and Hygiene Calendar, WaterAid India() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Log ... Read More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>• Evaluation Criteria
+Criteria
+Weight
+Understanding   of assignment
+20%
+Proposed   methodology
+25%
+Relevant   organisational experience
+20%
+Team   composition and expertise
+20%
+Financial   proposal
+15%
+Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
+th
+September by 5:30 pm
+For detailed information, please check the complete version of the ToR attached below.
+• Job Email ID:
+WAIP2P-Delhi(at)wateraid.org
+Download Attachment:
+TOR for Hygiene Tool kit and framework.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+16 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Head of People &amp; Culture
+(Value Members only)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Researcher
+(Value Members only)
+Location:
+Punjab
+Apply by:
+20 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303297</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for SVRI Research Grant 2027 – Data to Evidence Grant</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>TheSexual Violence Research Initiative (SVRI)is a global organisation dedicated to strengthening research on violence against women, child sexual violence and other forms of gender-based violence, particularly in low- and middle-income countries. SVRI supports locally led, ethically rigorous and act ... Read More</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>The lead applicant must be based at anLMIC-based university, research institution or NGO. Independent consultants and individuals without institutional affiliation, as well as applicants affiliated with for-profit companies, are not eligible. The proposed dataset must have been ethically sourced, and applicants must have the necessary permission and approval to access and analyse it. The lead applicant cannot currently hold another active SVRI research grant or have previously received an SVRI grant. However, an institution whose previous SVRI grant has ended may apply. Applicants must be based in a country classified as low-, lower-middle- or upper-middle-income under the applicable World Bank classification.</t>
+        </is>
+      </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Climate, Governance, Learning</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>17 September 2026</t>
         </is>
       </c>
       <c r="H32" s="1" t="n">
@@ -5065,7 +4836,7 @@
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303358</t>
+          <t>https://andpurpose.world/applications-invited-for-svri-research-grant-2027-data-to-evidence-grant/</t>
         </is>
       </c>
     </row>
@@ -5235,54 +5006,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5324,7 +5095,7 @@
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
@@ -5345,17 +5116,17 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for SVRI Research Grant 2027 – Data to Evidence Grant</t>
+          <t>Nominations Open for Italian Bilateral Scientific Cooperation Award (US)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>TheSexual Violence Research Initiative (SVRI)is a global organisation dedicated to strengthening research on violence against women, child sexual violence and other forms of gender-based violence, particularly in low- and middle-income countries. SVRI supports locally led, ethically rigorous and act ... Read More</t>
+          <t>Italian Ministry of Foreign Affairs and International Cooperation (MAECI) TheItalian Ministry of Foreign Affairs and International Cooperation (MAECI)is responsible for Italy’s foreign relations and international cooperation. The Ministry works to strengthen Italy’s diplomatic, cultural, economic an ... Read More</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>The lead applicant must be based at anLMIC-based university, research institution or NGO. Independent consultants and individuals without institutional affiliation, as well as applicants affiliated with for-profit companies, are not eligible. The proposed dataset must have been ethically sourced, and applicants must have the necessary permission and approval to access and analyse it. The lead applicant cannot currently hold another active SVRI research grant or have previously received an SVRI grant. However, an institution whose previous SVRI grant has ended may apply. Applicants must be based in a country classified as low-, lower-middle- or upper-middle-income under the applicable World Bank classification.</t>
+          <t>The application deadline is 18 September 2026</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -5365,7 +5136,7 @@
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>17 September 2026</t>
+          <t>18 September 2026</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
@@ -5373,7 +5144,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-svri-research-grant-2027-data-to-evidence-grant/</t>
+          <t>https://andpurpose.world/nominations-open-for-italian-bilateral-scientific-cooperation-award-us/</t>
         </is>
       </c>
     </row>
@@ -5390,22 +5161,22 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Nominations Open for Italian Bilateral Scientific Cooperation Award (US)</t>
+          <t>Applications Invited for the Wellcome Prize for Mental Health Science with Nature</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Italian Ministry of Foreign Affairs and International Cooperation (MAECI) TheItalian Ministry of Foreign Affairs and International Cooperation (MAECI)is responsible for Italy’s foreign relations and international cooperation. The Ministry works to strengthen Italy’s diplomatic, cultural, economic an ... Read More</t>
+          <t>Wellcomeis a global charitable foundation supporting science to solve urgent health challenges. Its work includes discovery research into life, health and wellbeing, with mental health among its major global priorities.Natureis an international scientific publication known for publishing rigorous re ... Read More</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 18 September 2026</t>
+          <t>Research teams should select a lead applicant and complete the official online application form. Applications are open for self-submission, so formal nomination is not required. Applicants should demonstrate the intervention’s novelty, scientific credibility, measurable clinical benefit and potential for adoption. Teams should also explain how the intervention was developed and provide evidence supporting its clinical effectiveness. The application must be complete and submitted online by the official closing time.</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -5414,11 +5185,11 @@
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/nominations-open-for-italian-bilateral-scientific-cooperation-award-us/</t>
+          <t>https://andpurpose.world/applications-invited-for-the-wellcome-prize-for-mental-health-science-with-nature/</t>
         </is>
       </c>
     </row>
@@ -5435,22 +5206,22 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>WFP SDS Microgrant Programme 2026: Apply for Up to $5,000 in Farmer Grants</t>
+          <t>Call for Proposals: Labour Service Organisations Training Vulnerable Workers (South Africa)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TheUnited Nations World Food Programme (WFP)is a leading humanitarian organization working worldwide to combat hunger, strengthen food security, and support vulnerable communities. For this initiative, WFP is partnering with the NGOSouthern Development Strategy (SDS)to provide targeted financial ass ... Read More</t>
+          <t>TheSouth African Department of Employment and Labouris a national government department responsible for promoting decent employment, protecting workers’ rights and supporting fair and safe labour practices across South Africa. Its responsibilities include administering and implementing labour legisl ... Read More</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>TheWFP SDS Microgrant Programmeprovides financial assistance to farmers and small-scale producers in Ukraine who are already engaged in agricultural production or related activities. Theseagricultural grantsare designed to help existing enterprises recover, strengthen production, purchase essential equipment or materials, and contribute to sustainable community development. Eligible activities include crop cultivation, livestock production, beekeeping, food processing, and fish farming. Microgrants are available at three levels US$1,500, US$3,000, and US$5,000. The final amount is determined by a selection committee after reviewing the application and, for shortlisted applicants, conducting a verification visit.</t>
+          <t>The application deadline is 18 September 2026</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Agriculture &amp; Rural</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
@@ -5459,11 +5230,11 @@
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/https-andpurpose-world-wfp-sds-microgrant-programme-2026/</t>
+          <t>https://andpurpose.world/call-for-proposals-labour-service-organisations-training-vulnerable-workers-south-africa/</t>
         </is>
       </c>
     </row>
@@ -5480,22 +5251,22 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Call for Proposals: Labour Service Organisations Training Vulnerable Workers (South Africa)</t>
+          <t>WFP SDS Microgrant Programme 2026: Apply for Up to $5,000 in Farmer Grants</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>TheSouth African Department of Employment and Labouris a national government department responsible for promoting decent employment, protecting workers’ rights and supporting fair and safe labour practices across South Africa. Its responsibilities include administering and implementing labour legisl ... Read More</t>
+          <t>TheUnited Nations World Food Programme (WFP)is a leading humanitarian organization working worldwide to combat hunger, strengthen food security, and support vulnerable communities. For this initiative, WFP is partnering with the NGOSouthern Development Strategy (SDS)to provide targeted financial ass ... Read More</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 18 September 2026</t>
+          <t>TheWFP SDS Microgrant Programmeprovides financial assistance to farmers and small-scale producers in Ukraine who are already engaged in agricultural production or related activities. Theseagricultural grantsare designed to help existing enterprises recover, strengthen production, purchase essential equipment or materials, and contribute to sustainable community development. Eligible activities include crop cultivation, livestock production, beekeeping, food processing, and fish farming. Microgrants are available at three levels US$1,500, US$3,000, and US$5,000. The final amount is determined by a selection committee after reviewing the application and, for shortlisted applicants, conducting a verification visit.</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Agriculture &amp; Rural</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -5504,56 +5275,200 @@
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/call-for-proposals-labour-service-organisations-training-vulnerable-workers-south-africa/</t>
+          <t>https://andpurpose.world/https-andpurpose-world-wfp-sds-microgrant-programme-2026/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for the Wellcome Prize for Mental Health Science with Nature</t>
+          <t>ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquife...</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Wellcomeis a global charitable foundation supporting science to solve urgent health challenges. Its work includes discovery research into life, health and wellbeing, with mental health among its major global priorities.Natureis an international scientific publication known for publishing rigorous re ... Read More</t>
+          <t>Development Support Centre (DSC) | India
+ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquifer Study Using Participatory Approaches for Natural Resource, Watershed..., Development Support Centre (DSC)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broad ... Read More</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Research teams should select a lead applicant and complete the official online application form. Applications are open for self-submission, so formal nomination is not required. Applicants should demonstrate the intervention’s novelty, scientific credibility, measurable clinical benefit and potential for adoption. Teams should also explain how the intervention was developed and provide evidence supporting its clinical effectiveness. The application must be complete and submitted online by the official closing time.</t>
+          <t>• Job Email ID:
+cpc.dsc(at)gmail.com
+Download Attachment:
+DSC-Geohydrology Study ToR.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+20 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Head of People &amp; Culture
+(Value Members only)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Researcher
+(Value Members only)
+Location:
+Punjab
+Apply by:
+20 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>18 September 2026</t>
+          <t>20-09-2026</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-the-wellcome-prize-for-mental-health-science-with-nature/</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303378</t>
         </is>
       </c>
     </row>
@@ -5703,54 +5618,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5792,7 +5707,7 @@
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
@@ -5809,33 +5724,54 @@
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquife...</t>
+          <t>RFP - Procurement of IT Equipment and Accessories</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Development Support Centre (DSC) | India
-ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquifer Study Using Participatory Approaches for Natural Resource, Watershed..., Development Support Centre (DSC)() | DevNetJobsIndia
+          <t>India HIV/AIDS Alliance (Alliance India) | India
+RFP - Procurement of IT Equipment and Accessories, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broad ... Read More</t>
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseeker ... Read More</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>• Job Email ID:
-cpc.dsc(at)gmail.com
+          <t>• Interested bidders meeting the preliminary examination and technical evaluation criteria are invited to submit Financial Proposals in accordance with the requirements outlined in this Request for Proposal (RFP).
+2. About India HIV/AIDS Alliance
+India HIV/AIDS Alliance (Alliance India) is a leading non-government organization dedicated to strengthening India's response to HIV/AIDS, public health, and community systems. Through partnerships with government agencies, civil society organizations, community-based organizations, donors, and development partners, Alliance India works to improve equitable access to quality healthcare services for vulnerable and key populations.
+Alliance India implements programmes across multiple states through technical assistance, capacity building, advocacy, research, procurement support, and programme management while maintaining the highest standards of governance, transparency, and financial accountability
+3. Objective of the Procurement
+The objective of this procurement is to identify one or more technically qualified and financially capable suppliers for the supply of high-quality IT equipment and accessories to support programme implementation across multiple locations in India.
+4. Submission Process
+Proposals shall be submitted electronically to
+procurement1@allianceindia.org
+on or before the deadline mentioned in this RFP.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+procurement1(at)allianceindia.org
 Download Attachment:
-DSC-Geohydrology Study ToR.pdf
+RFP_Procurement_of_IT_Equipment.doc
+Download Attachment:
+IHAA_IT Equipment_Corrigendum-1.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-20 Sep 2026
+21 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -5892,54 +5828,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5972,12 +5908,12 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Safety</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>20-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
@@ -5985,26 +5921,71 @@
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303378</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303414</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Submit Applications for Homelessness Prevention Grants (UK)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge City Councilis the local authority responsible for delivering public services and supporting communities across Cambridge, United Kingdom. The Council works with voluntary, community, and partner organisations to address local challenges including homelessness, rough sleeping, housing inse ... Read More</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Applications are open tovoluntary and community organisationsworking to prevent or relieve homelessness and rough sleeping in Cambridge. Applicants should have appropriate governance arrangements, financial controls, and the organisational capacity to manage public funding responsibly. Projects must benefit people in Cambridge and directly contribute to homelessness prevention or relief. Applicants should demonstrate a clear understanding of local homelessness needs, explain why funding is required, and show how activities and outcomes will be monitored and measured. The Council may also require supporting documents such as accounts, organisational budgets, governing documents, insurance certificates, risk assessments, and relevant organisational policies.</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>22 September 2026</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/submit-applications-for-homelessness-prevention-grants-uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Procurement of IT Equipment and Accessories</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | India
-RFP - Procurement of IT Equipment and Accessories, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
+      <c r="B42" s="1" t="inlineStr"/>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
+RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -6013,39 +5994,32 @@
 Value Membership
 Broadcast Resume
 RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>• Interested bidders meeting the preliminary examination and technical evaluation criteria are invited to submit Financial Proposals in accordance with the requirements outlined in this Request for Proposal (RFP).
-2. About India HIV/AIDS Alliance
-India HIV/AIDS Alliance (Alliance India) is a leading non-government organization dedicated to strengthening India's response to HIV/AIDS, public health, and community systems. Through partnerships with government agencies, civil society organizations, community-based organizations, donors, and development partners, Alliance India works to improve equitable access to quality healthcare services for vulnerable and key populations.
-Alliance India implements programmes across multiple states through technical assistance, capacity building, advocacy, research, procurement support, and programme management while maintaining the highest standards of governance, transparency, and financial accountability
-3. Objective of the Procurement
-The objective of this procurement is to identify one or more technically qualified and financially capable suppliers for the supply of high-quality IT equipment and accessories to support programme implementation across multiple locations in India.
-4. Submission Process
-Proposals shall be submitted electronically to
-procurement1@allianceindia.org
-on or before the deadline mentioned in this RFP.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-procurement1(at)allianceindia.org
+Se ... Read More</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>• SCOPE OF WORK
+• The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
+TAF will facilitate access to the baseline survey tool, the January 2025 baseline report, the deidentified baseline dataset, and government permissions; these materials, along with any other tools and de-identified datasets, will be shared only with the selected study partner. The study partner will be responsible for adapting the instruments, and for fielding, analysing, and reporting the endline round.
+Key deliverables
+will include an inception report, IRB approval documentation, cleaned quantitative and qualitative datasets, a draft endline report, a final endline report, and a presentation of findings to TAF (see Annex 1, Section VI).
+SUBMISSION
+All proposals and queries should be sent to
+TAF_MnE@antarafoundation.org
+and cc to
+puneet.naithani@antarafoundation.org
+with the subject line
+"Damoh Endline Evaluation proposal || Organisation name".
+Queries will be accepted until the deadline stated on the cover page; responses to queries (RFQ) will be shared with all prospective applicants by the date indicated.
+For detailed information, please check the complete version of the RFP attached below
 Download Attachment:
-RFP_Procurement_of_IT_Equipment.doc
-Download Attachment:
-IHAA_IT Equipment_Corrigendum-1.doc
+Damoh_Endline_RFP_TAF.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-21 Sep 2026
+25 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -6102,54 +6076,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6180,331 +6154,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303414</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Submit Applications for Homelessness Prevention Grants (UK)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Cambridge City Councilis the local authority responsible for delivering public services and supporting communities across Cambridge, United Kingdom. The Council works with voluntary, community, and partner organisations to address local challenges including homelessness, rough sleeping, housing inse ... Read More</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Applications are open tovoluntary and community organisationsworking to prevent or relieve homelessness and rough sleeping in Cambridge. Applicants should have appropriate governance arrangements, financial controls, and the organisational capacity to manage public funding responsibly. Projects must benefit people in Cambridge and directly contribute to homelessness prevention or relief. Applicants should demonstrate a clear understanding of local homelessness needs, explain why funding is required, and show how activities and outcomes will be monitored and measured. The Council may also require supporting documents such as accounts, organisational budgets, governing documents, insurance certificates, risk assessments, and relevant organisational policies.</t>
-        </is>
-      </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>22 September 2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/submit-applications-for-homelessness-prevention-grants-uk/</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
+          <t>RFP - Empanelment of development &amp; implementation partners for CSR, commu...</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>25 September 2026</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I43" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
-RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Se ... Read More</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>• SCOPE OF WORK
-• The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
-TAF will facilitate access to the baseline survey tool, the January 2025 baseline report, the deidentified baseline dataset, and government permissions; these materials, along with any other tools and de-identified datasets, will be shared only with the selected study partner. The study partner will be responsible for adapting the instruments, and for fielding, analysing, and reporting the endline round.
-Key deliverables
-will include an inception report, IRB approval documentation, cleaned quantitative and qualitative datasets, a draft endline report, a final endline report, and a presentation of findings to TAF (see Annex 1, Section VI).
-SUBMISSION
-All proposals and queries should be sent to
-TAF_MnE@antarafoundation.org
-and cc to
-puneet.naithani@antarafoundation.org
-with the subject line
-"Damoh Endline Evaluation proposal || Organisation name".
-Queries will be accepted until the deadline stated on the cover page; responses to queries (RFQ) will be shared with all prospective applicants by the date indicated.
-For detailed information, please check the complete version of the RFP attached below
-Download Attachment:
-Damoh_Endline_RFP_TAF.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-25 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
-Apply by:
-20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Empanelment of development &amp; implementation partners for CSR, commu...</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>AROH Foundation | India
 RFP - Empanelment of development &amp; implementation partners  for CSR, community development &amp; infrastructure projects across India, AROH Foundation() | DevNetJobsIndia
@@ -6521,7 +6202,7 @@
 Jobseeke ... Read More</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>• 1. INTRODUCTION AND BACKGROUND
 AROH Foundation invites proposals from experienced, technically competent and financially sound development agencies, implementation partners, contractors, service providers and vendors for empanelment to undertake CSR, community development, infrastructure, renewable energy, water conservation, natural resource management and allied
@@ -6683,54 +6364,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6761,38 +6442,83 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>25-09-2026</t>
         </is>
       </c>
-      <c r="H45" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I45" s="1" t="inlineStr">
+      <c r="H43" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302836</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>25 September 2026</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr"/>
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>RFP - for Final Evaluation of Support Micro/Small entrepreneurs among part...</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe e.V | India
 RFP - for Final Evaluation of Support Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans, Deutsche Welthungerhilfe e.V() | DevNetJobsIndia
@@ -6807,7 +6533,7 @@
 Searc ... Read More</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION ANDCONTEXT
 Country:
@@ -6916,54 +6642,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Optometrist
-Doctors For You (DFY)
-Location:
-Maharashtra
-Apply by:
-12 Oct 2026
-Project Manager
+Head of People &amp; Culture
 (Value Members only)
 Location:
-Gujarat
+Delhi
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Shree Amar Sanskar Kalyan Kendra (Sanskar)
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Associate Project Coordinator
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+20 Sep 2026
+Project Coordinator
+SADHANA (Society for Action in Disability and Hea...
+Location:
+Odisha
+Apply by:
+20 Sep 2026
+Outreach Worker
+Social Awareness Institution (SAI)
+Location:
+Odisha
+Apply by:
+16 Sep 2026
+Communications Manager
+(Value Members only)
+Location:
+Delhi
+Apply by:
+18 Sep 2026
+Birsa Village Coordinator
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
 Apply by:
 24 Sep 2026
-Field Executive
-Participatory Learning and Action Network Foundat...
-Location:
-Gujarat
-Apply by:
-09 Oct 2026
-Farm Supervisor
-Jagran Jan Vikas Samiti (JJVS), Udaipur
-Location:
-Rajasthan
+Researcher
+(Value Members only)
+Location:
+Punjab
 Apply by:
 20 Sep 2026
-Senior Manager: Organisation Development, People ...
-(Value Members only)
-Location:
-Delhi
-Apply by:
-07 Oct 2026
-Superintendent
-Behala Keertika
-Location:
-West Bengal
-Apply by:
-20 Sep 2026
-Youth Employment Facilitator
-ETASHA Society
-Location:
-Haryana
-Apply by:
-09 Oct 2026
-Auxiliary Nursing and Midwifery
-Priyanshi TI Narmadapuram
-Location:
-Madhya Pradesh
-Apply by:
-25 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6994,14 +6720,59 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 29 September 2026</t>
+        </is>
+      </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
@@ -7009,7 +6780,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
+          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
         </is>
       </c>
     </row>
@@ -7026,17 +6797,17 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 29 September 2026</t>
+          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
@@ -7050,11 +6821,11 @@
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
+          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
         </is>
       </c>
     </row>
@@ -7071,27 +6842,27 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+          <t>The application deadline is30 September 2026</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>29 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
@@ -7099,7 +6870,7 @@
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
         </is>
       </c>
     </row>
@@ -7116,22 +6887,22 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
+          <t>Joint Research Groups in the UK – Scheme 3</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
+          <t>TheLondon Mathematical Society (LMS)is the UK’s leading learned society dedicated to promoting and advancing mathematical knowledge. It supports researchers, educators and institutions through research funding, conferences, publications and professional development opportunities. The Society encoura ... Read More</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is30 September 2026</t>
+          <t>TheJoint Research Groups Grant UK 2026is open to mathematicians based in theUnited Kingdom, Isle of Man and Channel Islandswho are part of a collaborative research group. Each research group must include participants fromat least three different locations, with at leasttwo participating institutions located in the UK, Isle of Man or Channel Islands. International collaborators may also participate. Applications must be submitted by a nominated grant holder responsible for managing the funding. PhD students cannot apply as grant holders. Non-members of the London Mathematical Society must obtain support from an LMS member before applying.</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
@@ -7140,11 +6911,11 @@
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
+          <t>https://andpurpose.world/joint-research-groups-in-the-uk-scheme-3/</t>
         </is>
       </c>
     </row>
@@ -7161,17 +6932,17 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Joint Research Groups in the UK – Scheme 3</t>
+          <t>Giving Joy Microgrant 2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TheLondon Mathematical Society (LMS)is the UK’s leading learned society dedicated to promoting and advancing mathematical knowledge. It supports researchers, educators and institutions through research funding, conferences, publications and professional development opportunities. The Society encoura ... Read More</t>
+          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>TheJoint Research Groups Grant UK 2026is open to mathematicians based in theUnited Kingdom, Isle of Man and Channel Islandswho are part of a collaborative research group. Each research group must include participants fromat least three different locations, with at leasttwo participating institutions located in the UK, Isle of Man or Channel Islands. International collaborators may also participate. Applications must be submitted by a nominated grant holder responsible for managing the funding. PhD students cannot apply as grant holders. Non-members of the London Mathematical Society must obtain support from an LMS member before applying.</t>
+          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -7185,11 +6956,11 @@
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/joint-research-groups-in-the-uk-scheme-3/</t>
+          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
         </is>
       </c>
     </row>
@@ -7206,17 +6977,17 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Giving Joy Microgrant 2026</t>
+          <t>Applications Open for Green Box Artist in Residency Program</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
+          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
+          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -7230,11 +7001,11 @@
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
+          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
         </is>
       </c>
     </row>
@@ -7251,35 +7022,35 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Green Box Artist in Residency Program</t>
+          <t>RFAs: Expanding Global Health Security Through Local Partnerships (Ethiopia)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
+          <t>U.S. Centers for Disease Control and Prevention (CDC) TheU.S. Centers for Disease Control and Prevention (CDC)is a leading public health agency dedicated to protecting communities from health threats through research, disease prevention, surveillance, and emergency response. Working closely with gov ... Read More</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
+          <t>Review the official funding announcement and verify your organization’s eligibility. Prepare a technical proposal aligned with one or more program priorities, including implementation plans, monitoring strategies, and a realistic budget. Demonstrate organizational capacity, sustainable partnerships, and measurable public health outcomes. Submit the completed application with all required supporting documents through the official application system before the closing deadline.</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>02 October 2026</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
+          <t>https://andpurpose.world/rfas-expanding-global-health-security-through-local-partnerships-ethiopia/</t>
         </is>
       </c>
     </row>
@@ -7296,35 +7067,35 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>RFAs: Expanding Global Health Security Through Local Partnerships (Ethiopia)</t>
+          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U.S. Centers for Disease Control and Prevention (CDC) TheU.S. Centers for Disease Control and Prevention (CDC)is a leading public health agency dedicated to protecting communities from health threats through research, disease prevention, surveillance, and emergency response. Working closely with gov ... Read More</t>
+          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Review the official funding announcement and verify your organization’s eligibility. Prepare a technical proposal aligned with one or more program priorities, including implementation plans, monitoring strategies, and a realistic budget. Demonstrate organizational capacity, sustainable partnerships, and measurable public health outcomes. Submit the completed application with all required supporting documents through the official application system before the closing deadline.</t>
+          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>02 October 2026</t>
+          <t>6 October 2026</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/rfas-expanding-global-health-security-through-local-partnerships-ethiopia/</t>
+          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
         </is>
       </c>
     </row>
@@ -7341,35 +7112,35 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+          <t>Funding Opportunity for Civil Society Organisations to Countering Disinformation in Poland</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+          <t>TheEEA Civil Society Fundsupports civil society organisations working to strengthen democracy, human rights, public participation, and social inclusion across eligible European countries. Through targeted funding programmes, the Fund empowers non-profit organisations to address emerging societal cha ... Read More</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+          <t>Eligible organisations should prepare a proposal outlining the disinformation challenge, project objectives, planned activities, expected outcomes, implementation strategy, organisational experience, and budget. Applications should demonstrate measurable impact, sustainability, and community benefit. Ensure all legal and eligibility requirements are met before submitting the proposal according to the programme guidelines before the closing date.</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>06 October 2026</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
+          <t>https://andpurpose.world/funding-opportunity-for-civil-society-organisations-to-countering-disinformation-in-poland/</t>
         </is>
       </c>
     </row>
@@ -7386,17 +7157,17 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Funding Opportunity for Civil Society Organisations to Countering Disinformation in Poland</t>
+          <t>Apply Now: Small Scale Projects PART-B on Institutional Capacity (Greece, Italy)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>TheEEA Civil Society Fundsupports civil society organisations working to strengthen democracy, human rights, public participation, and social inclusion across eligible European countries. Through targeted funding programmes, the Fund empowers non-profit organisations to address emerging societal cha ... Read More</t>
+          <t>TheInterreg VI-A Greece–Italy 2021–2027 Programmeis a European Territorial Cooperation initiative funded by the European Union to strengthen collaboration between Greece and Italy. The programme promotes sustainable regional development by supporting joint actions that improve governance, innovation ... Read More</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should prepare a proposal outlining the disinformation challenge, project objectives, planned activities, expected outcomes, implementation strategy, organisational experience, and budget. Applications should demonstrate measurable impact, sustainability, and community benefit. Ensure all legal and eligibility requirements are met before submitting the proposal according to the programme guidelines before the closing date.</t>
+          <t>Eligible applicants includeregional public authorities, local public authorities, bodies governed by public law, non-profit organisations established under private law, and European Groupings of Territorial Cooperation (EGTCs). Applicants must operate within one of the six eligible programme regions across Greece and Italy. Proposed projects should align withSpecific Objectives 6.1 or 6.4, demonstrate clear cross-border cooperation, and contribute to strengthening institutional capacity, governance, or territorial development. Applications must include strong partnerships between Greek and Italian organisations, measurable project outcomes, a realistic implementation plan, and compliance with all programme eligibility and documentation requirements.</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -7406,15 +7177,15 @@
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>06 October 2026</t>
+          <t>09 October 2026</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/funding-opportunity-for-civil-society-organisations-to-countering-disinformation-in-poland/</t>
+          <t>https://andpurpose.world/apply-now-small-scale-projects-part-b-on-institutional-capacity-greece-italy/</t>
         </is>
       </c>
     </row>
@@ -7431,17 +7202,17 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>Apply Now: Small Scale Projects PART-B on Institutional Capacity (Greece, Italy)</t>
+          <t>Applications Open for Realization of Short Animation Grant</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>TheInterreg VI-A Greece–Italy 2021–2027 Programmeis a European Territorial Cooperation initiative funded by the European Union to strengthen collaboration between Greece and Italy. The programme promotes sustainable regional development by supporting joint actions that improve governance, innovation ... Read More</t>
+          <t>TheNetherlands Film Fundis the national agency responsible for supporting professional film production and film-related activities in the Netherlands. The Fund provides financial contributions for film development, production, distribution, and other activities within the Dutch film sector. It suppo ... Read More</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants includeregional public authorities, local public authorities, bodies governed by public law, non-profit organisations established under private law, and European Groupings of Territorial Cooperation (EGTCs). Applicants must operate within one of the six eligible programme regions across Greece and Italy. Proposed projects should align withSpecific Objectives 6.1 or 6.4, demonstrate clear cross-border cooperation, and contribute to strengthening institutional capacity, governance, or territorial development. Applications must include strong partnerships between Greek and Italian organisations, measurable project outcomes, a realistic implementation plan, and compliance with all programme eligibility and documentation requirements.</t>
+          <t>Applications are open to eligibleindependent production companiesthat are legal entities and have been established for at least two years in the Netherlands, an EU member state, EEA country, or Switzerland. The company must continuously produce and exploit films or other audiovisual productions. For films up to 10 minutes, the producer must have experience as the majority producer responsible for realizing and releasing at least one qualifying independent film. For films from 10 minutes onward, the producer must have experience with at least two qualifying independent animation productions. The producer cannot also be the film’s director or screenwriter.</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -7451,15 +7222,15 @@
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>09 October 2026</t>
+          <t>13 October 2026</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-small-scale-projects-part-b-on-institutional-capacity-greece-italy/</t>
+          <t>https://andpurpose.world/applications-open-for-realization-of-short-animation-grant/</t>
         </is>
       </c>
     </row>
@@ -7476,17 +7247,17 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Realization of Short Animation Grant</t>
+          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TheNetherlands Film Fundis the national agency responsible for supporting professional film production and film-related activities in the Netherlands. The Fund provides financial contributions for film development, production, distribution, and other activities within the Dutch film sector. It suppo ... Read More</t>
+          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Applications are open to eligibleindependent production companiesthat are legal entities and have been established for at least two years in the Netherlands, an EU member state, EEA country, or Switzerland. The company must continuously produce and exploit films or other audiovisual productions. For films up to 10 minutes, the producer must have experience as the majority producer responsible for realizing and releasing at least one qualifying independent film. For films from 10 minutes onward, the producer must have experience with at least two qualifying independent animation productions. The producer cannot also be the film’s director or screenwriter.</t>
+          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -7500,11 +7271,11 @@
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-realization-of-short-animation-grant/</t>
+          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -7521,17 +7292,17 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
+          <t>Applications Invited for WUN Research Development Fund 2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
+          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
+          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -7541,15 +7312,15 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>13 October 2026</t>
+          <t>15 October 2026</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -7566,17 +7337,17 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for WUN Research Development Fund 2026</t>
+          <t>Applications Open for Commercialisation of Creative Industries Research Grant (UK)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
+          <t>TheArts and Humanities Research Council (AHRC)is part of UK Research and Innovation (UKRI) and funds outstanding research across arts and humanities disciplines. AHRC supports projects that encourage innovation, collaboration, knowledge exchange, and economic growth by connecting universities, resea ... Read More</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
+          <t>Applications are open toeligible UK universitiesand organisations that meetUK Research and Innovation (UKRI)eligibility requirements. The lead applicant must demonstrate experience managing multi-stakeholder partnerships, commercialising creative industries research, and coordinating sector-wide collaborations. Partnerships should include organisations experienced in research commercialisation as well as investors or investment-focused organisations with a strong track record in the creative industries. Applicants should possess expertise in innovation, governance, entrepreneurship, intellectual property, and stakeholder engagement. A detailed project plan, evidence-based methodology, partner commitment letters, and compliance with relevant UKRI requirements are expected as part of the application.</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -7590,11 +7361,11 @@
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
+          <t>https://andpurpose.world/applications-open-for-commercialisation-of-creative-industries-research-grant-uk/</t>
         </is>
       </c>
     </row>
@@ -7611,17 +7382,17 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Commercialisation of Creative Industries Research Grant (UK)</t>
+          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>TheArts and Humanities Research Council (AHRC)is part of UK Research and Innovation (UKRI) and funds outstanding research across arts and humanities disciplines. AHRC supports projects that encourage innovation, collaboration, knowledge exchange, and economic growth by connecting universities, resea ... Read More</t>
+          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Applications are open toeligible UK universitiesand organisations that meetUK Research and Innovation (UKRI)eligibility requirements. The lead applicant must demonstrate experience managing multi-stakeholder partnerships, commercialising creative industries research, and coordinating sector-wide collaborations. Partnerships should include organisations experienced in research commercialisation as well as investors or investment-focused organisations with a strong track record in the creative industries. Applicants should possess expertise in innovation, governance, entrepreneurship, intellectual property, and stakeholder engagement. A detailed project plan, evidence-based methodology, partner commitment letters, and compliance with relevant UKRI requirements are expected as part of the application.</t>
+          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -7635,11 +7406,11 @@
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-commercialisation-of-creative-industries-research-grant-uk/</t>
+          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
         </is>
       </c>
     </row>
@@ -7656,27 +7427,27 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
+          <t>Request for Applications: Research in Health Systems (South Africa)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
+          <t>TheSouth African Medical Research Council (SAMRC)is a national research organisation dedicated to improving health and quality of life through research, innovation and technology transfer. SAMRC supports health and medical research across South Africa and works with academic institutions, researcher ... Read More</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
+          <t>The opportunity is open to eligible researchers employed by recognised South African research institutions whose primary purpose includes research and postgraduate training. Eligible host institutions includeSouth African public universities, public research entities, science councils, national facilities and other recognised research institutions. The Principal Investigator must be aSouth African citizen or permanent residentand employed by an eligible institution. NGOs, nonprofit organisations and private companies whose primary purpose is not research and postgraduate training cannot apply as lead applicants, although they may participate as collaborators where permitted. International organisations and researchers may also collaborate where allowed. Applicants must demonstrate appropriate research capacity, institutional support, scientific expertise and implementation potential.</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>15 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
@@ -7684,7 +7455,7 @@
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
+          <t>https://andpurpose.world/request-for-applications-research-in-health-systems-south-africa/</t>
         </is>
       </c>
     </row>
@@ -7701,22 +7472,22 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Request for Applications: Research in Health Systems (South Africa)</t>
+          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TheSouth African Medical Research Council (SAMRC)is a national research organisation dedicated to improving health and quality of life through research, innovation and technology transfer. SAMRC supports health and medical research across South Africa and works with academic institutions, researcher ... Read More</t>
+          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>The opportunity is open to eligible researchers employed by recognised South African research institutions whose primary purpose includes research and postgraduate training. Eligible host institutions includeSouth African public universities, public research entities, science councils, national facilities and other recognised research institutions. The Principal Investigator must be aSouth African citizen or permanent residentand employed by an eligible institution. NGOs, nonprofit organisations and private companies whose primary purpose is not research and postgraduate training cannot apply as lead applicants, although they may participate as collaborators where permitted. International organisations and researchers may also collaborate where allowed. Applicants must demonstrate appropriate research capacity, institutional support, scientific expertise and implementation potential.</t>
+          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
@@ -7725,11 +7496,11 @@
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/request-for-applications-research-in-health-systems-south-africa/</t>
+          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
         </is>
       </c>
     </row>
@@ -7746,35 +7517,35 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
+          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
+          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
         </is>
       </c>
     </row>
@@ -7791,17 +7562,17 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
+          <t>RFPs: Sheldon Danziger Pipeline Grant Program (US)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
+          <t>TheRussell Sage Foundation (RSF)is a leading American research foundation dedicated to improving the understanding of social, economic, and behavioral issues through high-quality social science research. It funds investigator-led studies that generate evidence to address public policy challenges and ... Read More</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
+          <t>Applications are open toAssistant Professors, Adjunct Assistant Professors, and Lecturerswho meet the programme’s eligibility requirements. Applicants must not have previously received an RSF research grant, excluding Dissertation Research Grants. There are no nationality or institutional location restrictions, making the programme accessible to eligible scholars worldwide. Applications from researchers who are underrepresented in the social sciences or employed at under-resourced universities are strongly encouraged. Postdoctoral fellows cannot serve as Principal Investigators but may participate as research assistants. Full Professors and Associate Professors may join as Co-Principal Investigators but are not eligible for salary or conference travel support.</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -7811,7 +7582,7 @@
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>21 October 2026</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
@@ -7819,7 +7590,7 @@
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
+          <t>https://andpurpose.world/rfps-sheldon-danziger-pipeline-grant-program-us/</t>
         </is>
       </c>
     </row>
@@ -7836,17 +7607,17 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>RFPs: Sheldon Danziger Pipeline Grant Program (US)</t>
+          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>TheRussell Sage Foundation (RSF)is a leading American research foundation dedicated to improving the understanding of social, economic, and behavioral issues through high-quality social science research. It funds investigator-led studies that generate evidence to address public policy challenges and ... Read More</t>
+          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Applications are open toAssistant Professors, Adjunct Assistant Professors, and Lecturerswho meet the programme’s eligibility requirements. Applicants must not have previously received an RSF research grant, excluding Dissertation Research Grants. There are no nationality or institutional location restrictions, making the programme accessible to eligible scholars worldwide. Applications from researchers who are underrepresented in the social sciences or employed at under-resourced universities are strongly encouraged. Postdoctoral fellows cannot serve as Principal Investigators but may participate as research assistants. Full Professors and Associate Professors may join as Co-Principal Investigators but are not eligible for salary or conference travel support.</t>
+          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -7856,15 +7627,15 @@
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>21 October 2026</t>
+          <t>26 October 2026</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/rfps-sheldon-danziger-pipeline-grant-program-us/</t>
+          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
         </is>
       </c>
     </row>
@@ -7881,17 +7652,17 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
+          <t>Applications Open for Core Research Grant Program (US)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
+          <t>TheFoundation for Scholarly Researchsupports high-quality academic research that advances knowledge and addresses important global challenges. Through its research funding programmes, the foundation encourages investigator-led projects across diverse disciplines while promoting innovation, collabora ... Read More</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
+          <t>The programme is open toPrincipal Investigators (PIs)andCo-Principal Investigators (Co-PIs)from anywhere in the world. Applicants are generally expected to hold a doctoral degree. However, exceptional candidates without a doctorate may also apply if they demonstrate a distinguished academic or professional background and proven ability to conduct high-quality, peer-reviewed scholarly research. There are no nationality or institutional location restrictions, making the programme accessible to eligible researchers globally. Applicants should submit proposals that align with the foundation’s research priorities and demonstrate strong research methodology, academic significance, and the capacity to successfully complete the proposed project.</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -7901,15 +7672,15 @@
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>26 October 2026</t>
+          <t>28 October 2026</t>
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
+          <t>https://andpurpose.world/applications-open-for-core-research-grant-program-us/</t>
         </is>
       </c>
     </row>
@@ -7926,17 +7697,17 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Core Research Grant Program (US)</t>
+          <t>Whitley Award 2027</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>TheFoundation for Scholarly Researchsupports high-quality academic research that advances knowledge and addresses important global challenges. Through its research funding programmes, the foundation encourages investigator-led projects across diverse disciplines while promoting innovation, collabora ... Read More</t>
+          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>The programme is open toPrincipal Investigators (PIs)andCo-Principal Investigators (Co-PIs)from anywhere in the world. Applicants are generally expected to hold a doctoral degree. However, exceptional candidates without a doctorate may also apply if they demonstrate a distinguished academic or professional background and proven ability to conduct high-quality, peer-reviewed scholarly research. There are no nationality or institutional location restrictions, making the programme accessible to eligible researchers globally. Applicants should submit proposals that align with the foundation’s research priorities and demonstrate strong research methodology, academic significance, and the capacity to successfully complete the proposed project.</t>
+          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -7946,15 +7717,15 @@
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>28 October 2026</t>
+          <t>30 October 2026</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-core-research-grant-program-us/</t>
+          <t>https://andpurpose.world/whitley-award-2027/</t>
         </is>
       </c>
     </row>
@@ -7971,35 +7742,35 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Whitley Award 2027</t>
+          <t>National Indian Health Outreach and Education Program 2026</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
+          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
+          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>30 October 2026</t>
+          <t>2 November 2026</t>
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/whitley-award-2027/</t>
+          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
         </is>
       </c>
     </row>
@@ -8016,35 +7787,35 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>National Indian Health Outreach and Education Program 2026</t>
+          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
+          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
+          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>2 November 2026</t>
+          <t>4 November 2026</t>
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
         </is>
       </c>
     </row>
@@ -8061,27 +7832,27 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
+          <t>CFAs: U.S. Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
+          <t>TheCenters for Disease Control and Prevention (CDC)is a U.S. public health agency responsible for protecting communities from diseases, health threats, and other public health risks. The agency conducts research, develops evidence-based guidance, monitors health trends, and supports public health pr ... Read More</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
+          <t>TheTravel Health Research Grants 2026opportunity supports initiatives that improve health protection for U.S. residents traveling internationally. The program focuses on four connected areas: travel preparation information, health information collection and surveillance, research into emerging health threats, and travel medicine education for primary care providers. Projects may use electronic medical records, websites, mobile applications, and other digital health technologies to collect information before, during, and after international travel. The estimated total program funding isUS$5 million, with individual awards ranging fromUS$750,000 to US$1 million. The initiative aims to strengthen evidence-based travel health information and public health research.</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>4 November 2026</t>
+          <t>05 November 2026</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
@@ -8089,7 +7860,7 @@
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
+          <t>https://andpurpose.world/cfas-u-s-travelers-health-research-surveillance-communication-and-outreach-network/</t>
         </is>
       </c>
     </row>
@@ -8106,27 +7877,27 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>CFAs: U.S. Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
+          <t>Applications Invited for World Food Day Poster Contest 2026</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>TheCenters for Disease Control and Prevention (CDC)is a U.S. public health agency responsible for protecting communities from diseases, health threats, and other public health risks. The agency conducts research, develops evidence-based guidance, monitors health trends, and supports public health pr ... Read More</t>
+          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>TheTravel Health Research Grants 2026opportunity supports initiatives that improve health protection for U.S. residents traveling internationally. The program focuses on four connected areas: travel preparation information, health information collection and surveillance, research into emerging health threats, and travel medicine education for primary care providers. Projects may use electronic medical records, websites, mobile applications, and other digital health technologies to collect information before, during, and after international travel. The estimated total program funding isUS$5 million, with individual awards ranging fromUS$750,000 to US$1 million. The initiative aims to strengthen evidence-based travel health information and public health research.</t>
+          <t>The application deadline is 6 November 2026</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>05 November 2026</t>
+          <t>6 November 2026</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
@@ -8134,7 +7905,7 @@
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/cfas-u-s-travelers-health-research-surveillance-communication-and-outreach-network/</t>
+          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
         </is>
       </c>
     </row>
@@ -8151,17 +7922,17 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for World Food Day Poster Contest 2026</t>
+          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
+          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 6 November 2026</t>
+          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
@@ -8171,15 +7942,15 @@
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>6 November 2026</t>
+          <t>9 November 2026</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
+          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
         </is>
       </c>
     </row>
@@ -8196,17 +7967,17 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
+          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
+          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
+          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
@@ -8216,15 +7987,15 @@
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>9 November 2026</t>
+          <t>15 November 2026</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
+          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
         </is>
       </c>
     </row>
@@ -8241,17 +8012,17 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
+          <t>Apply Now for Skills Development Grants for Creative Industries in Toronto</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
+          <t>TheCity of Torontois Canada’s largest municipal government and supports initiatives that strengthen the city’s economy, communities, culture, and workforce. Through its creative industries funding programs, the City supports film, television, music, and creative technology sectors. Its funding initi ... Read More</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
+          <t>Applications are open to eligibleCanadian not-for-profit and charitable organizations, urban off-reserve Indigenous-led organizations, and community centres that are part of the Association of Community Centres. Applicants must be located in Toronto or deliver the proposed funded services to Toronto-based individuals or entities. Organizations must not owe money to the City of Toronto or be in default of existing City agreements. Projects should focus on practical workforce development, employment readiness, and technical skills connected to Toronto’s creative industries. Eligible initiatives may include training in post-production, VFX, animation, digital workflows, trades, crafts, and other high-demand technical roles.</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
@@ -8265,11 +8036,11 @@
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
+          <t>https://andpurpose.world/apply-now-for-skills-development-grants-for-creative-industries-in-toronto/</t>
         </is>
       </c>
     </row>
@@ -8286,17 +8057,17 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for Skills Development Grants for Creative Industries in Toronto</t>
+          <t>Applications Open for CRI Technology Impact Award Grant</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>TheCity of Torontois Canada’s largest municipal government and supports initiatives that strengthen the city’s economy, communities, culture, and workforce. Through its creative industries funding programs, the City supports film, television, music, and creative technology sectors. Its funding initi ... Read More</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Applications are open to eligibleCanadian not-for-profit and charitable organizations, urban off-reserve Indigenous-led organizations, and community centres that are part of the Association of Community Centres. Applicants must be located in Toronto or deliver the proposed funded services to Toronto-based individuals or entities. Organizations must not owe money to the City of Toronto or be in default of existing City agreements. Projects should focus on practical workforce development, employment readiness, and technical skills connected to Toronto’s creative industries. Eligible initiatives may include training in post-production, VFX, animation, digital workflows, trades, crafts, and other high-demand technical roles.</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
@@ -8306,7 +8077,7 @@
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>15 November 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
@@ -8314,7 +8085,7 @@
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-skills-development-grants-for-creative-industries-in-toronto/</t>
+          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
         </is>
       </c>
     </row>
@@ -8331,17 +8102,17 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for CRI Technology Impact Award Grant</t>
+          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
+          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
+          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
@@ -8355,11 +8126,11 @@
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
+          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
         </is>
       </c>
     </row>
@@ -8376,17 +8147,17 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
+          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
+          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
+          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
@@ -8396,15 +8167,15 @@
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
+          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
         </is>
       </c>
     </row>
@@ -8421,17 +8192,17 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
+          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
+          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
+          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
@@ -8445,11 +8216,11 @@
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
+          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
         </is>
       </c>
     </row>
@@ -8466,17 +8237,17 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
+          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
+          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
+          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
@@ -8490,11 +8261,11 @@
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
+          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
         </is>
       </c>
     </row>
@@ -8511,22 +8282,22 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
+          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
+          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
+          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
@@ -8535,11 +8306,11 @@
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
+          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
         </is>
       </c>
     </row>
@@ -8556,35 +8327,35 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
+          <t>Collections Stewardship Program Grant – National Endowment for the Humanities</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
+          <t>TheNational Endowment for the Humanities (NEH)is an independent federal agency of the United States that supports research, education, preservation and public programs in the humanities. Through its Division of Collections &amp; Infrastructure, NEH supports organizations working to preserve physical and ... Read More</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
+          <t>TheNEH Collections Stewardship Programprovides funding for projects that preserve and improve access to physical and digital collections important to humanities research, teaching and public engagement. Supported activities include conservation, preservation planning, collection storage and care, archival arrangement and description, cataloguing, digitization, transcription, indexing, digital preservation and enhancement of established digital humanities resources. The program can also support preservation services and education or training for students and professionals working with humanities collections. Awards range from$50,000 to $500,000, with single organizations eligible for up to $350,000 and consortium applications eligible for up to $500,000.</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>15 December 2026</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
+          <t>https://andpurpose.world/collections-stewardship-program-grant-national-endowment-for-the-humanities/</t>
         </is>
       </c>
     </row>
@@ -8601,17 +8372,17 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Collections Stewardship Program Grant – National Endowment for the Humanities</t>
+          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>TheNational Endowment for the Humanities (NEH)is an independent federal agency of the United States that supports research, education, preservation and public programs in the humanities. Through its Division of Collections &amp; Infrastructure, NEH supports organizations working to preserve physical and ... Read More</t>
+          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>TheNEH Collections Stewardship Programprovides funding for projects that preserve and improve access to physical and digital collections important to humanities research, teaching and public engagement. Supported activities include conservation, preservation planning, collection storage and care, archival arrangement and description, cataloguing, digitization, transcription, indexing, digital preservation and enhancement of established digital humanities resources. The program can also support preservation services and education or training for students and professionals working with humanities collections. Awards range from$50,000 to $500,000, with single organizations eligible for up to $350,000 and consortium applications eligible for up to $500,000.</t>
+          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
@@ -8621,15 +8392,15 @@
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>15 December 2026</t>
+          <t>20 December 2026</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/collections-stewardship-program-grant-national-endowment-for-the-humanities/</t>
+          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -8646,35 +8417,35 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
+          <t>Travel Grant Competition for Women/Feminist Organizations (Ukraine) 2026</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
+          <t>TheUkrainian Women’s Fund (UWF)is a leading grant-making organization dedicated to advancing women’s rights, gender equality and feminist leadership across Ukraine. Through strategic funding and capacity-building initiatives, UWF supports women’s rights organizations, activists and networks working ... Read More</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
+          <t>TheTravel Grant for Women Organizations Ukraine 2026is open to women’s rights activists, feminist leaders, representatives of women’s human rights organizations and members of women’s networks working in Ukraine. Eligible organizations must be officially registered in Ukraine, operate independently of political parties and government institutions, and focus on women’s rights protection or gender equality promotion. Professional women’s associations may apply if they follow feminist principles and actively support women’s rights. Individual activists or experts may receive fundingup to two times per year. Applicants should clearly demonstrate their contribution to Ukraine’s women’s movement.</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>20 December 2026</t>
+          <t>31 December 2026</t>
         </is>
       </c>
       <c r="H83" s="1" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
+          <t>https://andpurpose.world/travel-grant-competition-for-women-feminist-organizations-ukraine-2026/</t>
         </is>
       </c>
     </row>
@@ -8691,35 +8462,35 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Travel Grant Competition for Women/Feminist Organizations (Ukraine) 2026</t>
+          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>TheUkrainian Women’s Fund (UWF)is a leading grant-making organization dedicated to advancing women’s rights, gender equality and feminist leadership across Ukraine. Through strategic funding and capacity-building initiatives, UWF supports women’s rights organizations, activists and networks working ... Read More</t>
+          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>TheTravel Grant for Women Organizations Ukraine 2026is open to women’s rights activists, feminist leaders, representatives of women’s human rights organizations and members of women’s networks working in Ukraine. Eligible organizations must be officially registered in Ukraine, operate independently of political parties and government institutions, and focus on women’s rights protection or gender equality promotion. Professional women’s associations may apply if they follow feminist principles and actively support women’s rights. Individual activists or experts may receive fundingup to two times per year. Applicants should clearly demonstrate their contribution to Ukraine’s women’s movement.</t>
+          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>31 December 2026</t>
+          <t>14 January 2027</t>
         </is>
       </c>
       <c r="H84" s="1" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/travel-grant-competition-for-women-feminist-organizations-ukraine-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
         </is>
       </c>
     </row>
@@ -8736,27 +8507,27 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
+          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
+          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
+          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>14 January 2027</t>
+          <t>15 January 2027</t>
         </is>
       </c>
       <c r="H85" s="1" t="n">
@@ -8764,7 +8535,7 @@
       </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
+          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
         </is>
       </c>
     </row>
@@ -8781,80 +8552,62 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
+          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
+          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
+          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>15 January 2027</t>
+          <t>15 February 2027</t>
         </is>
       </c>
       <c r="H86" s="1" t="n">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
+          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
-        </is>
-      </c>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>15 February 2027</t>
-        </is>
-      </c>
-      <c r="H87" s="1" t="n">
-        <v>156</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr"/>
+      <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8620,7 @@
       <c r="B88" s="1" t="inlineStr"/>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -8881,7 +8634,7 @@
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8647,8 @@
       <c r="B89" s="1" t="inlineStr"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
+          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
+                    here</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -8908,7 +8662,7 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -8921,22 +8675,21 @@
       <c r="B90" s="1" t="inlineStr"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
-                    here</t>
+          <t>RFP for Women Entrepreneurship Programme - Click here</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -8949,21 +8702,21 @@
       <c r="B91" s="1" t="inlineStr"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>RFP for Women Entrepreneurship Programme - Click here</t>
+          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8729,8 @@
       <c r="B92" s="1" t="inlineStr"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+                    here</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -8990,7 +8744,7 @@
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
         </is>
       </c>
     </row>
@@ -9003,7 +8757,8 @@
       <c r="B93" s="1" t="inlineStr"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+          <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
+                India Pvt. Ltd - Click here | Click
                     here</t>
         </is>
       </c>
@@ -9011,14 +8766,14 @@
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -9031,23 +8786,21 @@
       <c r="B94" s="1" t="inlineStr"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
-                India Pvt. Ltd - Click here | Click
-                    here</t>
+          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
         </is>
       </c>
     </row>
@@ -9060,21 +8813,21 @@
       <c r="B95" s="1" t="inlineStr"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
+          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
         </is>
       </c>
     </row>
@@ -9087,21 +8840,21 @@
       <c r="B96" s="1" t="inlineStr"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
+          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
         </is>
       </c>
     </row>
@@ -9114,21 +8867,21 @@
       <c r="B97" s="1" t="inlineStr"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
+          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
         </is>
       </c>
     </row>
@@ -9141,7 +8894,8 @@
       <c r="B98" s="1" t="inlineStr"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
+          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
+                    here</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -9155,7 +8909,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
         </is>
       </c>
     </row>
@@ -9168,22 +8922,21 @@
       <c r="B99" s="1" t="inlineStr"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
-                    here</t>
+          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
         </is>
       </c>
     </row>
@@ -9196,7 +8949,7 @@
       <c r="B100" s="1" t="inlineStr"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -9210,7 +8963,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
@@ -9223,21 +8976,21 @@
       <c r="B101" s="1" t="inlineStr"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -9250,21 +9003,21 @@
       <c r="B102" s="1" t="inlineStr"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -9277,21 +9030,21 @@
       <c r="B103" s="1" t="inlineStr"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -9304,21 +9057,21 @@
       <c r="B104" s="1" t="inlineStr"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9084,7 @@
       <c r="B105" s="1" t="inlineStr"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -9345,7 +9098,7 @@
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9111,7 @@
       <c r="B106" s="1" t="inlineStr"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -9372,7 +9125,7 @@
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9138,7 @@
       <c r="B107" s="1" t="inlineStr"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -9399,7 +9152,7 @@
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -9412,21 +9165,22 @@
       <c r="B108" s="1" t="inlineStr"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
+                education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -9439,8 +9193,7 @@
       <c r="B109" s="1" t="inlineStr"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
-                education in STEM courses - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -9454,7 +9207,7 @@
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9220,7 @@
       <c r="B110" s="1" t="inlineStr"/>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -9481,7 +9234,7 @@
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -9494,21 +9247,22 @@
       <c r="B111" s="1" t="inlineStr"/>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
+                and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -9521,22 +9275,22 @@
       <c r="B112" s="1" t="inlineStr"/>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
-                and Financial Management - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
+                    here</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -9549,8 +9303,8 @@
       <c r="B113" s="1" t="inlineStr"/>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
-                    here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
@@ -9564,7 +9318,7 @@
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9332,7 @@
       <c r="C114" s="1" t="inlineStr">
         <is>
           <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -9592,7 +9346,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -9605,8 +9359,7 @@
       <c r="B115" s="1" t="inlineStr"/>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -9620,7 +9373,7 @@
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9386,7 @@
       <c r="B116" s="1" t="inlineStr"/>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -9647,7 +9400,7 @@
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -9660,21 +9413,21 @@
       <c r="B117" s="1" t="inlineStr"/>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr"/>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -9687,34 +9440,38 @@
       <c r="B118" s="1" t="inlineStr"/>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
@@ -9724,11 +9481,15 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr"/>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>31st Aug, 2026</t>
+        </is>
+      </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
         </is>
       </c>
     </row>
@@ -9745,25 +9506,25 @@
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
+          <t>Senior Programme Officer - Uday</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>31st Aug, 2026</t>
+          <t>15th Aug, 2026</t>
         </is>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9541,7 @@
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>Senior Programme Officer - Uday</t>
+          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -9792,13 +9553,13 @@
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>15th Aug, 2026</t>
+          <t>29th Jun, 2026</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
         </is>
       </c>
     </row>
@@ -9815,25 +9576,25 @@
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>29th Jun, 2026</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9611,7 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
@@ -9868,7 +9629,7 @@
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -9885,25 +9646,25 @@
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -9920,25 +9681,25 @@
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -9955,25 +9716,25 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -9990,25 +9751,25 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -10025,924 +9786,25 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr"/>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
           <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr"/>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="1" t="inlineStr"/>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr"/>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="1" t="inlineStr"/>
-      <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="1" t="inlineStr"/>
-      <c r="G132" s="1" t="inlineStr"/>
-      <c r="H132" s="1" t="inlineStr"/>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr"/>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="1" t="inlineStr"/>
-      <c r="G133" s="1" t="inlineStr"/>
-      <c r="H133" s="1" t="inlineStr"/>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="1" t="inlineStr"/>
-      <c r="G134" s="1" t="inlineStr"/>
-      <c r="H134" s="1" t="inlineStr"/>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>UHI_RFP_Formatted_10072026.pdf</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="1" t="inlineStr"/>
-      <c r="G135" s="1" t="inlineStr"/>
-      <c r="H135" s="1" t="inlineStr"/>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-9590033.pdf</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="1" t="inlineStr"/>
-      <c r="G136" s="1" t="inlineStr"/>
-      <c r="H136" s="1" t="inlineStr"/>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="1" t="inlineStr"/>
-      <c r="G137" s="1" t="inlineStr"/>
-      <c r="H137" s="1" t="inlineStr"/>
-      <c r="I137" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="1" t="inlineStr"/>
-      <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr"/>
-      <c r="I138" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B139" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr">
-        <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr"/>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="1" t="inlineStr"/>
-      <c r="G139" s="1" t="inlineStr"/>
-      <c r="H139" s="1" t="inlineStr"/>
-      <c r="I139" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP_CORRIGENDUM%20I_150726.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>05.06.2026_EOI-RFP_Kedarnath and Amarnath Yatra.pdf</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr"/>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="1" t="inlineStr"/>
-      <c r="G140" s="1" t="inlineStr"/>
-      <c r="H140" s="1" t="inlineStr"/>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/05.06.2026_EOI-RFP_Kedarnath%20and%20Amarnath%20Yatra.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>SOP_Kedarnath and Amarnath_corrigendum_1.pdf</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr"/>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="1" t="inlineStr"/>
-      <c r="G141" s="1" t="inlineStr"/>
-      <c r="H141" s="1" t="inlineStr"/>
-      <c r="I141" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP_Kedarnath%20and%20Amarnath_corrigendum_1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>SOP-Kedarnath Amarnath_PRe-bid queries.pdf</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr"/>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="1" t="inlineStr"/>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
-      <c r="I142" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP-Kedarnath%20Amarnath_PRe-bid%20queries.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>EOI FOR CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS UNDER COMPONENT 2.pdf</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr"/>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="1" t="inlineStr"/>
-      <c r="G143" s="1" t="inlineStr"/>
-      <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS%20UNDER%20COMPONENT%202.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>Extension_of_Dates_.pdf</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="1" t="inlineStr"/>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension_of_Dates_.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum_Transversal_Experts.pdf</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr"/>
-      <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_Transversal_Experts.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>Reply_to_Pre-bid_queries_transversal_expert.pdf</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply_to_Pre-bid_queries_transversal_expert.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr">
-        <is>
-          <t>Extension of Dates.pdf</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="1" t="inlineStr"/>
-      <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension%20of%20Dates_1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B148" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C148" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-9271299.pdf</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="1" t="inlineStr"/>
-      <c r="G148" s="1" t="inlineStr"/>
-      <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9271299.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B149" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C149" s="1" t="inlineStr">
-        <is>
-          <t>Reply to pre-bid queries.pdf</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr"/>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="1" t="inlineStr"/>
-      <c r="G149" s="1" t="inlineStr"/>
-      <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20pre-bid%20queries_0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B150" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum - I.pdf</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="2" t="inlineStr"/>
-      <c r="F150" s="1" t="inlineStr"/>
-      <c r="G150" s="1" t="inlineStr"/>
-      <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20I_1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B151" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr">
-        <is>
-          <t>Draft RFP UHI_4.pdf</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="1" t="inlineStr"/>
-      <c r="G151" s="1" t="inlineStr"/>
-      <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Draft%20RFP%20UHI_4.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-9289662.pdf</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="1" t="inlineStr"/>
-      <c r="G152" s="1" t="inlineStr"/>
-      <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9289662.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B153" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C153" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum_USI.pdf</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
-      <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="1" t="inlineStr"/>
-      <c r="G153" s="1" t="inlineStr"/>
-      <c r="H153" s="1" t="inlineStr"/>
-      <c r="I153" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_USI.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C154" s="1" t="inlineStr">
-        <is>
-          <t>EMPANELMENT OF AGENCIES FOR PREPARATION OF INTEGRATED STATE URBAN CLIMATE ACTION PLANS AND CONTEXTUALISED CITY CLIMATE ACTION PLANS UNDER COMPONENT 2 OF CITIIS 2.0.pdf</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="2" t="inlineStr"/>
-      <c r="F154" s="1" t="inlineStr"/>
-      <c r="G154" s="1" t="inlineStr"/>
-      <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/EMPANELMENT%20OF%20AGENCIES%20FOR%20PREPARATION%20OF%20INTEGRATED%20STATE%20URBAN%20CLIMATE%20ACTION%20PLANS%20AND%20CONTEXTUALISED%20CITY%20CLIMATE%20ACTION%20PLANS%20UNDER%20COMPONENT%202%20OF%20CITIIS%202.0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B155" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C155" s="1" t="inlineStr">
-        <is>
-          <t>Extension_of_Dates_citiis.pdf</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="1" t="inlineStr"/>
-      <c r="G155" s="1" t="inlineStr"/>
-      <c r="H155" s="1" t="inlineStr"/>
-      <c r="I155" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension_of_Dates_citiis.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B156" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C156" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum - I.pdf</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
-      <c r="E156" s="2" t="inlineStr"/>
-      <c r="F156" s="1" t="inlineStr"/>
-      <c r="G156" s="1" t="inlineStr"/>
-      <c r="H156" s="1" t="inlineStr"/>
-      <c r="I156" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20I_0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B157" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="inlineStr">
-        <is>
-          <t>Reply to Pre-bid Queries.pdf</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr"/>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="1" t="inlineStr"/>
-      <c r="G157" s="1" t="inlineStr"/>
-      <c r="H157" s="1" t="inlineStr"/>
-      <c r="I157" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-bid%20Queries_0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B158" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C158" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum - II.pdf</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="2" t="inlineStr"/>
-      <c r="F158" s="1" t="inlineStr"/>
-      <c r="G158" s="1" t="inlineStr"/>
-      <c r="H158" s="1" t="inlineStr"/>
-      <c r="I158" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20II.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B159" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="inlineStr">
-        <is>
-          <t>Extension of Dates.pdf</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="1" t="inlineStr"/>
-      <c r="G159" s="1" t="inlineStr"/>
-      <c r="H159" s="1" t="inlineStr"/>
-      <c r="I159" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension%20of%20Dates_0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B160" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C160" s="1" t="inlineStr">
-        <is>
-          <t>Reply to Pre-bid Queries -II.pdf</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr"/>
-      <c r="E160" s="2" t="inlineStr"/>
-      <c r="F160" s="1" t="inlineStr"/>
-      <c r="G160" s="1" t="inlineStr"/>
-      <c r="H160" s="1" t="inlineStr"/>
-      <c r="I160" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-bid%20Queries%20-II.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr">
-        <is>
-          <t>Tech Form 10 JV Format.pdf</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr"/>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="1" t="inlineStr"/>
-      <c r="G161" s="1" t="inlineStr"/>
-      <c r="H161" s="1" t="inlineStr"/>
-      <c r="I161" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Tech%20Form%2010%20JV%20Format.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -483,183 +483,37 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFQ - Well-Based Piped Drinking Water Supply Scheme - Kandawani</t>
+          <t>Translation Funding Programme Grants for German-Language Literature</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>WaterAid India | Kandawani , Samnapur, District Dindori, Madhya Pradesh
-RFQ - Well-Based Piped Drinking Water Supply Scheme - Kandawani, WaterAid India(Kandawani , Samnapur, District Dindori) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search J ... Read More</t>
+          <t>TheGoethe-Institutis the cultural institute of the Federal Republic of Germany with a global network dedicated to promoting German language and international cultural cooperation. It provides cultural and educational programmes that encourage intercultural dialogue, cultural participation and intern ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• Job Email ID:
-WAIProcurementMP(at)wateraid.org
-Download Attachment:
-RFQ-Khandwani.xls
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-14 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Center Manager
-(Value Members only)
-Location:
-Delhi
-Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
-Location:
-Gujarat
-Apply by:
-11 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
+          <t>The programme is open tointernational professional publishersthat wish to translate German-language books. Applicants must have documented experience publishing quality literature and maintain professional distribution channels.Translators and authors cannot apply directlyfor this translation subsidy. The translation must be made directly from theoriginal German text, and the work must have been published in printed form by a publisher in a German-speaking country. The applicant publisher must provide the required rights and translation contracts and demonstrate the quality of its publishing programme and previous translations. The translation mustnot go to print before the funding agreement has been signed.</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -667,218 +521,44 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303484</t>
+          <t>https://andpurpose.world/translation-funding-programme-grants-for-german-language-literature/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>RFP - Engagement of Banking Partner(s) for Employee Benefits Fund</t>
+          <t>Applications Invited for GEF SGP CSO Challenge Program 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-RFP - Engagement of Banking Partner(s) for Employee Benefits Fund, Coalition for Disaster Resilient Infrastructure (CDRI)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-E ... Read More</t>
+          <t>Global Environment Facility (GEF) Small Grants Programme (SGP), implemented through IUCN and RTI International TheGlobal Environment Facility Small Grants Programme (GEF SGP)supports locally led environmental action by civil society and community-based organisations. Established in 1992, the program ... Read More</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• 3.Scope of Work
-The selected Bank(s) shall provide banking, cash and liquidity management, treasury advisory, investment execution and related reporting services for the Employee Benefits Fund, including but not limited to:
-a) Account Management
-The Bank(s) shall establish and maintain dedicated bank accounts in INR and USD for the management of employee benefit funds.
-The Bank(s) shall facilitate secure electronic banking, payment processing, maker-checker workflows, authorized signatory management, transaction monitoring and other relevant institutional banking services required for the operation of the Fund.
-b) Cash and Liquidity Management
-The Bank(s) shall provide appropriate cash and liquidity management solutions that seek to optimize returns on surplus balances while ensuring sufficient liquidity to meet employee benefit obligations.
-The Bank(s) may propose suitable products such as fixed deposits, auto-sweep facilities, flexi deposits or equivalent banking solutions, subject to CDRI's approval and applicable laws and regulations.
-The Bank(s) shall provide advice on appropriate deposit tenures and maturity planning based on CDRI's anticipated cash-flow requirements.
-c) Investment Advisory
-The Bank(s) shall provide professional treasury and investment advisory services to support prudent investment and liquidity management of the Employee Benefits Fund, including recommendations on suitable investment options, deposit tenures, prevailing interest rate trends, diversification, maturity planning, and cash-flow optimization.
-The Bank(s) shall clearly explain the key features, risks, liquidity considerations and expected returns associated with all recommended investment options.
-Investment recommendations shall remain advisory in nature, and all investment decisions shall be subject to CDRI's prior approval.
-d) Investment Execution and Treasury Support
-The Bank(s) shall execute investment instructions issued by CDRI and facilitate investment placements, renewals, maturity management, premature withdrawals, where applicable, and other related treasury services.
-The Bank(s) shall provide timely information on upcoming maturities and assist CDRI in taking informed decisions regarding renewal, withdrawal or reinvestment of funds.
-e) Reporting
-The Bank(s) shall provide periodic account statements and management reports relating to the Employee Benefits Fund, including account balances, investment balances, accrued/earned interest, maturity schedules, applicable rates/returns, and such other information as may be reasonably required by CDRI for financial management, reconciliation and oversight.
-The Bank(s) shall also provide transaction confirmations and investment/maturity-related information on a timely basis.
-The bidders are requested to submit their proposals through email to
-tender.projects@cdri.world
-by 23:59 hrs (IST) on
-14 September 2026
-.
-Responses received after the stipulated time or not in accordance with the requirements will be summarily rejected.
-Please ensure that your proposal is sent ONLY to the ABOVE-MENTIONED email ID before the closing date &amp; time. Proposals sent/copied to any other email ID (other than above) OR received after the bid closing date &amp; time (mentioned above) will not be entertained.
-For detailed information, please check the complete version of the RFP attached below
-• Job Email ID:
-tender.projects(at)cdri.world
-Download Attachment:
-RFP_CDRI_Engagement of Banking Partner(s) for Employee Benefits Fund.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-14 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Center Manager
-(Value Members only)
-Location:
-Delhi
-Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
-Location:
-Gujarat
-Apply by:
-11 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
+          <t>Applicants should first review the official programme eligibility requirements and select the relevant regional call. For the current call, organisations in Africa, Latin America &amp; the Caribbean, and Asia-Pacific &amp; Oceania can submit proposals online in English, French or Spanish. The application should demonstrate the existing solution’s environmental results, scalability, innovation, theory of change, partnerships, sustainability and financial viability. Applications are submitted through the online grants portal before the stated regional deadline.</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>14-09-2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
@@ -886,7 +566,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302418</t>
+          <t>https://andpurpose.world/applications-invited-for-gef-sgp-cso-challenge-program-2026/</t>
         </is>
       </c>
     </row>
@@ -903,17 +583,17 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Rolex Explorers Club Grant 2027</t>
+          <t>2026 Call for Proposals: Mountains ADAPT Small Grants</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The Explorers Clubis an international not-for-profit organization founded in 1904 to advance scientific exploration, field research and the preservation of the instinct to explore. Its global membership includes scientists, researchers and explorers working across disciplines such as oceanography, a ... Read More</t>
+          <t>TheUnited Nations Environment Programme (UNEP)is the United Nations system’s leading global environmental authority. It works to set the environmental agenda, promote coherent implementation of the environmental dimension of sustainable development and strengthen international action on environmenta ... Read More</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>TheRolex Explorers Club Grantsupports young explorers conducting fieldwork that addresses anovel scientific, environmental or historical question. The programme is designed to help researchers undertake original field science capable of generating significant new understanding or impact. Awards areUS$10,000and can support fieldwork across disciplines including ecology, wildlife, botany, archaeology, earth sciences, marine and freshwater research, geography and paleontology. Applicants must present a clear scientific rationale, original research and a strong fieldwork component. The 2027 field-season application cycle is currently open, with submissions due14 September 2026 at 6:00 PM ET.</t>
+          <t>Complete the official Mountains ADAPT application form and provide information about your organization, previous experience, the mountain climate challenge being addressed, proposed nature-based solution, beneficiaries and expected community benefits. Upload the organization’s valid registration certificate. The proposal should demonstrate community ownership, gender and youth inclusion, feasibility, sustainability and environmental safeguards. Applications can be submitted in English and, depending on location, Armenian, Azerbaijani, French, Georgian or Kiswahili. Submit before the deadline. UNEP – UN Environment Programme</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -923,7 +603,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="H4" s="1" t="n">
@@ -931,7 +611,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/rolex-explorers-club-grant-2027/</t>
+          <t>https://andpurpose.world/2026-call-for-proposals-mountains-adapt-small-grants/</t>
         </is>
       </c>
     </row>
@@ -948,27 +628,27 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Exhibition Publication Grants</t>
+          <t>India Fund</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ThePaul Mellon Centre for Studies in British Artis an internationally recognised research institution dedicated to advancing the understanding of British art, architecture, and visual culture. Through grants, fellowships, publications, and collaborative initiatives, the Centre supports innovative re ... Read More</t>
+          <t>ThePaul Hamlyn Foundation (PHF)is a UK-based independent grant-making foundation established in 1987. The Foundation works towards a just future where everyone, particularly young people, can realise their potential and enjoy fulfilling and creative lives. Its strategic priorities include investing ... Read More</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Applications are open toorganisations, institutions, non-profit organisations, and international organisationsproducing publications connected to exhibitions or displays on British art, visual culture, or architecture. Collaborative applications involving multiple organisations are encouraged, provided roles and responsibilities are clearly defined. Eligible projects include exhibition catalogues, research publications, and practice-based research outputs that contribute new knowledge to British art studies. Applicants must submit a detailed project description, publication plan, realistic budget, and referee information through the official application system. Proposals should demonstrate strong research quality, clear audience engagement, and practical plans for publication and dissemination.</t>
+          <t>Confirm that your organisation is an eligible Indian NGO with FCRA registration and operates locally within the communities it serves. Develop a community-centred proposal demonstrating how disadvantaged communities will participate in designing and leading change. Explain the intended systemic impact, organisational capacity-building approach, environmental considerations and commitment to gender equality. Prepare the required organisational and project information and submit the application through the Paul Hamlyn Foundation’s official India Fund process before the deadline.</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="H5" s="1" t="n">
@@ -976,7 +656,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-exhibition-publication-grants/</t>
+          <t>https://andpurpose.world/india-fund/</t>
         </is>
       </c>
     </row>
@@ -993,27 +673,27 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Fair Water Action Fund for Water Justice and Water Security</t>
+          <t>Mahila Krishi Shakti Puraskar 2026 – JSW Foundation–MSSRF National Award for Women in Agriculture</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Water Witness Internationalis a global organization working to improve water security, water governance and climate resilience while promoting fairness and accountability in water management. The organization works with communities, civil society groups, researchers, journalists and other partners t ... Read More</t>
+          <t>M. S. Swaminathan Research Foundation (MSSRF) in collaboration with JSW Foundation TheM. S. Swaminathan Research Foundation (MSSRF)is an Indian organisation focused on pro-poor, pro-women and pro-nature development, with longstanding work in agriculture, nutrition, biodiversity, ecology and rural co ... Read More</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>The Fair Water Action Fund is open to applicants working in theGlobal South, particularly in countries experiencing physical and economic water scarcity. Eligible applicants may includecivil society organizations, media organizations, coalitions and networks, investigative journalists, individual researchers and research institutions. Applicants should demonstrate a clear connection between their proposed work and water justice, water security, accountability or systemic change. Strong applications should address practical water challenges and show how the proposed work can contribute to improved governance, equitable access to water, stronger accountability or policy change. Initiatives may address water, sanitation, drought, floods, pollution, water conflicts, climate impacts or related governance challenges.</t>
+          <t>The application deadline is 15 September 2026</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>15 September 2026</t>
         </is>
       </c>
       <c r="H6" s="1" t="n">
@@ -1021,709 +701,23 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/fair-water-action-fund-for-water-justice-and-water-security/</t>
+          <t>https://andpurpose.world/mahila-krishi-shakti-puraskar-2026-jsw-foundation-mssrf-national-award-for-women-in-agriculture/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Call for Proposals: Community Grants Program (Canada)</t>
+          <t>RFP – Hiring of an Agency to Conduct an Endline Assessment of THR and PM-P...</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Community Foundation of Southeastern Alberta (CFSEA) TheCommunity Foundation of Southeastern Alberta (CFSEA)is a community-focused philanthropic organization that works to strengthen communities across Southeastern Alberta. Through grantmaking, partnerships and local research, CFSEA supports initiat ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants must provide services inSoutheastern Albertaand meet CFSEA’s organizational requirements. Potential applicants includeregistered charities, municipalities, school divisions, qualified donees and eligible nonprofit organizations working in partnership with a qualified donee. Registered nonprofit societies in Alberta may also apply directly where they meet the programme’s requirements, including the applicable five-year good-standing requirement. Applicants should have no outstanding final reports from previous CFSEA Community Grants. Proposed projects must address a demonstrated community need, align with one or more funding priorities, benefit Southeastern Alberta communities and have achievable objectives and measurable outcomes. Political activities, religious activities, debt repayment and projects outside the region are not eligible.</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>14 September 2026</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/call-for-proposals-community-grants-program-canada/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Speaker Attribution Data Annotation of ORF Voice Recordings</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | India
-RFP - Speaker Attribution Data Annotation of ORF Voice Recordings, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-| ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>• PROPOSAL SUBMISSION GUIDELINES
-Your proposal must include:
-1. Technical Proposal
-• Understanding of Scope, Deliverables, and Problem Statement: Demonstrate understanding of the problem we are solving with these annotations, the full scope of work, and the expected deliverables.
-Process and Tools
-• Annotator selection criteria
-Equipment and listening environment standards
-Annotator training process: how annotators are trained to understand each type of annotation and the differences between them
-Annotation tooling used
-How annotator fatigue is managed
-How annotation quality is defined and what mechanisms are used to monitor annotation quality continuously during the project.
-How underperforming annotators are identified and addressed
-Team Composition and Qualifications: Details of the team assigned to this project, their relevant experience, and role allocation.
-Quality Assurance Mechanisms:
-Remediation process: what happens when annotation accuracy falls below acceptable levels, including the process for how affected data is re-annotated.
-Reporting cadence: how frequently the partner will communicate with us during the engagement (daily, weekly, or milestone-based).
-Reporting content: what specific metrics or summaries will be shared with us on a regular basis (e.g., annotation throughput, flagged files, annotator performance summaries) and in the pilot and final reports.
-Data Policy: partners must describe their data handling policy with respect to our data, including storage location, access controls, retention period, deletion process upon project completion, and any subcontracting or third-party access to the data.
-2. Financial Proposal
-Detailed cost breakdown
-Schedule of Payments Linked to Milestones Achieved Applicable taxes and contingencies
-• 3. Organizational Profile o Relevant project experience o Sample of similar work
-4. Signed NDA: Partners are expected to download and update the Organisation Name, registration no., Address in the NDA
-here
-, provide Authorised Signatory and attach signed NDA with your proposal. Without Signed NDA, Proposal will be invalidated.
-5. Annotation of Sample Audios: Partners are provided with a sample set of audio files via
-Google Drive
-. Along with their proposals, they must return completed annotations for this sample set as part of their proposal, following the definitions provided above. The format for the annotations is provided in the Annotation Format section. Without Sample annotations in required format, Proposal will be invalidated.
-• Sample Evaluation Criteria
-Partners are required to submit completed annotations for the sample audio set provided. These annotations will be evaluated on annotation accuracy annotations calculated against golden ground truth prepared internally. This measures how closely the partner's annotations align with the expected annotators, and is an indicator of how well annotators have understood and applied the metric definitions and score descriptors.
-Criteria for Application
-Applicants must meet the following criteria.
-Mandatory:
-Demonstrated team capacity to annotate audio clips based on metrics
-Clear and demonstrable quality check process
-Submission of evaluation samples (Proposal without sample annotations will be rejected)
-Preferred:
-Prior experience in annotating multilingual audio data, including languages such as Gujarati, Hindi, English, Odia, Telugu, etc.
-• Submission Details
-All proposals to this RFP must be received no later than
-&lt;Sept 15th&gt;.
-The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP: Speaker Attribution Data Annotation of ORF Voice Recordings
-Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
-For detailed information, please check the complete version of the RFP attached below
-• Job Email ID:
-rfp.lehs(at)wadhwaniai.org
-Download Attachment:
-RFP - Speaker Attribution Data Annotation - Pan India.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Center Manager
-(Value Members only)
-Location:
-Delhi
-Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
-Location:
-Gujarat
-Apply by:
-11 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303101</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Individual Consultant / Firm Engagement: TN Energy Audits</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>World Resources Institute India (WRI India) | Tamil Nadu
-RFP - Individual Consultant / Firm Engagement: TN Energy Audits, World Resources Institute India (WRI India)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-L ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Accordingly, IRT seeks to engage a qualified and certified energy auditing firm or energy auditor (consultant) to undertake comprehensive energy audits, collect and analyse technical data, develop evidence-based recommendations, and prepare detailed technical reports and implementation guidance in accordance with the scope of work outlined in this Terms of Reference.
-2.         Objectives of the Consultancy
-Undertake comprehensive energy audits of the identified public healthcare facilities to assess existing energy consumption patterns, electrical infrastructure, power quality, and the energy performance of major medical and non-medical equipment, establishing a robust baseline for energy management.
-Identify and evaluate energy conservation and energy efficiency opportunities through detailed technical analysis, including equipment-level performance assessment, load profiling, critical and non-critical load segregation, cost-benefit analysis, and recommendations for operational improvements, efficient technologies, and renewable energy integration where feasible.
-Develop actionable technical outputs including facility-wise energy audit reports, actionable suggestions with technical specifications, guidance documents, and walkthrough audit tools to support evidence-based planning, future energy planning, and replication of energy audits across healthcare facilities.
-• 3.         Scope of Work
-A.         Energy Audit of healthcare facilities –
-A detailed energy audit will be conducted at each facility to understand existing energy consumption patterns across various building end-use applications such as lighting, air-conditioning, medical use, hot water, etc., at total of 20 healthcare facilities in Tamil Nadu.
-4.         Required Qualifications and Experience
-The consultant/consulting firm should meet the following minimum qualifications and experience requirements:
-Educational Qualification
-Lead Energy Auditor shall possess a Bachelors degree or higher in Electrical Engineering, Energy Engineering, Mechanical Engineering, or a related discipline. Additional qualifications in Energy Management, Renewable Energy, or Energy Efficiency will be preferred.
-Accredited Energy Auditor (AEA) or Certified Energy Auditor (CEA) registered with the Bureau of Energy Efficiency (BEE), Government of India
-The audit team should comprise suitably qualified engineers and technical professionals with relevant educational backgrounds.
-Professional Experience:
-Minimum three (3) years of demonstrated experience in conducting detailed energy audits of commercial, institutional, industrial, or public sector facilities.
-Experience in conducting energy audits of healthcare facilities will be highly desirable.
-Technical Expertise:
-Demonstrated expertise in energy auditing, electrical load assessment, power quality analysis, electrical distribution systems, energy performance analysis, and identification of energy conservation and energy efficiency measures.
-Experience in analysing the energy performance of electrical and medical equipment, developing energy performance indicators, conducting cost-benefit analysis, and preparing technically sound recommendations for energy efficiency and renewable energy integration.
-Familiarity with relevant Bureau of Energy Efficiency (BEE) guidelines, applicable Indian Standards, and best practices in energy auditing.
-Deadline
-: 15th September 2026 Expression of interest:
-All expressions of interest, questions and proposals in response to this RFP must be received via email to the contact below by September 15, 2026
-Amittosh.Pandey@wri.org
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-Amittosh.Pandey(at)wri.org
-Download Attachment:
-RFP - TN Energy Audits.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Center Manager
-(Value Members only)
-Location:
-Delhi
-Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
-Location:
-Gujarat
-Apply by:
-11 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>15-09-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303143</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>2026 Call for Proposals: Mountains ADAPT Small Grants</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>TheUnited Nations Environment Programme (UNEP)is the United Nations system’s leading global environmental authority. It works to set the environmental agenda, promote coherent implementation of the environmental dimension of sustainable development and strengthen international action on environmenta ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Complete the official Mountains ADAPT application form and provide information about your organization, previous experience, the mountain climate challenge being addressed, proposed nature-based solution, beneficiaries and expected community benefits. Upload the organization’s valid registration certificate. The proposal should demonstrate community ownership, gender and youth inclusion, feasibility, sustainability and environmental safeguards. Applications can be submitted in English and, depending on location, Armenian, Azerbaijani, French, Georgian or Kiswahili. Submit before the deadline. UNEP – UN Environment Programme</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>15 September 2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/2026-call-for-proposals-mountains-adapt-small-grants/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>CFAs: Strengthening the Role of Women’s Rights Organisations for Implementation of Gender Equality (Zimbabwe)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>TheEuropean Commissionsupports programmes that promote human rights, gender equality, democratic governance and sustainable development worldwide. Through its external funding initiatives, the Commission partners with civil society organisations, non-governmental organisations and public institution ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>TheWomen’s Rights Organisations Grant Zimbabwe 2026is open tonon-profit organisations, NGOs, women’s rights organisations and eligible international organisationsestablished in Zimbabwe, an EU Member State or another eligible NDICI-GE country. Applicants may apply individually or with co-applicants and affiliated entities. Projects must be implemented in Zimbabwe and adopt gender-transformative and rights-based approaches. Applicants must meet all European Commission eligibility requirements and demonstrate the operational and financial capacity to manage large-scale grant projects. Registration in the required EU systems is mandatory before submission.</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Women &amp; Gender</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>15 September 2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/cfas-strengthening-the-role-of-womens-rights-organisations-for-implementation-of-gender-equality-zimbabwe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for GEF SGP CSO Challenge Program 2026</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Global Environment Facility (GEF) Small Grants Programme (SGP), implemented through IUCN and RTI International TheGlobal Environment Facility Small Grants Programme (GEF SGP)supports locally led environmental action by civil society and community-based organisations. Established in 1992, the program ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should first review the official programme eligibility requirements and select the relevant regional call. For the current call, organisations in Africa, Latin America &amp; the Caribbean, and Asia-Pacific &amp; Oceania can submit proposals online in English, French or Spanish. The application should demonstrate the existing solution’s environmental results, scalability, innovation, theory of change, partnerships, sustainability and financial viability. Applications are submitted through the online grants portal before the stated regional deadline.</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>15 September 2026</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-gef-sgp-cso-challenge-program-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Mahila Krishi Shakti Puraskar 2026 – JSW Foundation–MSSRF National Award for Women in Agriculture</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>M. S. Swaminathan Research Foundation (MSSRF) in collaboration with JSW Foundation TheM. S. Swaminathan Research Foundation (MSSRF)is an Indian organisation focused on pro-poor, pro-women and pro-nature development, with longstanding work in agriculture, nutrition, biodiversity, ecology and rural co ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 15 September 2026</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Women &amp; Gender</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>15 September 2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/mahila-krishi-shakti-puraskar-2026-jsw-foundation-mssrf-national-award-for-women-in-agriculture/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>RFP – Hiring of an Agency to Conduct an Endline Assessment of THR and PM-P...</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Global Health Strategies Institute (GHSi) | Delhi, Andhra Pradesh, Rajasthan
 RFP – Hiring of an Agency to Conduct an Endline Assessment of THR and PM-POSHAN across Three Districts of AP and Four Districts of Rajasthan, Global Health Strategies Institute (GHSi)() | DevNetJobsIndia
@@ -1731,7 +725,7 @@
 Login ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 • Interested organizations may submit a proposed plan as per their strengths and expertise. Proposals should also be drafted based on the SOW detailed above. Applicants are requested to share their proposals along with a duly filled-in Budget Costing Excel sheet as per the below-mentioned submission details and deadlines.
@@ -1828,54 +822,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1906,38 +900,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>15-09-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302569</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>RFQ - Project -Towards Resilient Futures: Sustainable &amp; Holistic Developme...</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Partnering Hope Into Action Foundation (PHIA) | Ladakh
 RFQ - Project -Towards Resilient Futures: Sustainable &amp; Holistic Development of Tribal Communities in the Nubra Region, Ladakh, Partnering Hope Into Action Foundation (PHIA)() | DevNetJobsIndia
@@ -1949,7 +943,7 @@
 Value Membership ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• 1. Scope of Work &amp; Deliverables
 I
@@ -2065,54 +1059,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2143,131 +1137,86 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>15-09-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303030</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>Translation Funding Programme Grants for German-Language Literature</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>TheGoethe-Institutis the cultural institute of the Federal Republic of Germany with a global network dedicated to promoting German language and international cultural cooperation. It provides cultural and educational programmes that encourage intercultural dialogue, cultural participation and intern ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The programme is open tointernational professional publishersthat wish to translate German-language books. Applicants must have documented experience publishing quality literature and maintain professional distribution channels.Translators and authors cannot apply directlyfor this translation subsidy. The translation must be made directly from theoriginal German text, and the work must have been published in printed form by a publisher in a German-speaking country. The applicant publisher must provide the required rights and translation contracts and demonstrate the quality of its publishing programme and previous translations. The translation mustnot go to print before the funding agreement has been signed.</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>CFAs: Strengthening the Role of Women’s Rights Organisations for Implementation of Gender Equality (Zimbabwe)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>TheEuropean Commissionsupports programmes that promote human rights, gender equality, democratic governance and sustainable development worldwide. Through its external funding initiatives, the Commission partners with civil society organisations, non-governmental organisations and public institution ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>TheWomen’s Rights Organisations Grant Zimbabwe 2026is open tonon-profit organisations, NGOs, women’s rights organisations and eligible international organisationsestablished in Zimbabwe, an EU Member State or another eligible NDICI-GE country. Applicants may apply individually or with co-applicants and affiliated entities. Projects must be implemented in Zimbabwe and adopt gender-transformative and rights-based approaches. Applicants must meet all European Commission eligibility requirements and demonstrate the operational and financial capacity to manage large-scale grant projects. Registration in the required EU systems is mandatory before submission.</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Women &amp; Gender</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>15 September 2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/translation-funding-programme-grants-for-german-language-literature/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>India Fund</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>ThePaul Hamlyn Foundation (PHF)is a UK-based independent grant-making foundation established in 1987. The Foundation works towards a just future where everyone, particularly young people, can realise their potential and enjoy fulfilling and creative lives. Its strategic priorities include investing ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Confirm that your organisation is an eligible Indian NGO with FCRA registration and operates locally within the communities it serves. Develop a community-centred proposal demonstrating how disadvantaged communities will participate in designing and leading change. Explain the intended systemic impact, organisational capacity-building approach, environmental considerations and commitment to gender equality. Prepare the required organisational and project information and submit the application through the Paul Hamlyn Foundation’s official India Fund process before the deadline.</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>15 September 2026</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/india-fund/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/cfas-strengthening-the-role-of-womens-rights-organisations-for-implementation-of-gender-equality-zimbabwe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Development of WaterAid India's Hygiene Framework, Community Facilit...</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-ToR - Development of WaterAid India's Hygiene Framework, Community Facilitator Toolkit, Hygiene Booklet and Hygiene Calendar, WaterAid India() | DevNetJobsIndia
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Speaker Attribution Data Annotation of ORF Voice Recordings</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | India
+RFP - Speaker Attribution Data Annotation of ORF Voice Recordings, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -2279,37 +1228,67 @@
 Search Jobs
 Events
 Jobseekers:
-Log ... Read More</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>• Evaluation Criteria
-Criteria
-Weight
-Understanding   of assignment
-20%
-Proposed   methodology
-25%
-Relevant   organisational experience
-20%
-Team   composition and expertise
-20%
-Financial   proposal
-15%
-Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
-th
-September by 5:30 pm
-For detailed information, please check the complete version of the ToR attached below.
+Login
+| ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• PROPOSAL SUBMISSION GUIDELINES
+Your proposal must include:
+1. Technical Proposal
+• Understanding of Scope, Deliverables, and Problem Statement: Demonstrate understanding of the problem we are solving with these annotations, the full scope of work, and the expected deliverables.
+Process and Tools
+• Annotator selection criteria
+Equipment and listening environment standards
+Annotator training process: how annotators are trained to understand each type of annotation and the differences between them
+Annotation tooling used
+How annotator fatigue is managed
+How annotation quality is defined and what mechanisms are used to monitor annotation quality continuously during the project.
+How underperforming annotators are identified and addressed
+Team Composition and Qualifications: Details of the team assigned to this project, their relevant experience, and role allocation.
+Quality Assurance Mechanisms:
+Remediation process: what happens when annotation accuracy falls below acceptable levels, including the process for how affected data is re-annotated.
+Reporting cadence: how frequently the partner will communicate with us during the engagement (daily, weekly, or milestone-based).
+Reporting content: what specific metrics or summaries will be shared with us on a regular basis (e.g., annotation throughput, flagged files, annotator performance summaries) and in the pilot and final reports.
+Data Policy: partners must describe their data handling policy with respect to our data, including storage location, access controls, retention period, deletion process upon project completion, and any subcontracting or third-party access to the data.
+2. Financial Proposal
+Detailed cost breakdown
+Schedule of Payments Linked to Milestones Achieved Applicable taxes and contingencies
+• 3. Organizational Profile o Relevant project experience o Sample of similar work
+4. Signed NDA: Partners are expected to download and update the Organisation Name, registration no., Address in the NDA
+here
+, provide Authorised Signatory and attach signed NDA with your proposal. Without Signed NDA, Proposal will be invalidated.
+5. Annotation of Sample Audios: Partners are provided with a sample set of audio files via
+Google Drive
+. Along with their proposals, they must return completed annotations for this sample set as part of their proposal, following the definitions provided above. The format for the annotations is provided in the Annotation Format section. Without Sample annotations in required format, Proposal will be invalidated.
+• Sample Evaluation Criteria
+Partners are required to submit completed annotations for the sample audio set provided. These annotations will be evaluated on annotation accuracy annotations calculated against golden ground truth prepared internally. This measures how closely the partner's annotations align with the expected annotators, and is an indicator of how well annotators have understood and applied the metric definitions and score descriptors.
+Criteria for Application
+Applicants must meet the following criteria.
+Mandatory:
+Demonstrated team capacity to annotate audio clips based on metrics
+Clear and demonstrable quality check process
+Submission of evaluation samples (Proposal without sample annotations will be rejected)
+Preferred:
+Prior experience in annotating multilingual audio data, including languages such as Gujarati, Hindi, English, Odia, Telugu, etc.
+• Submission Details
+All proposals to this RFP must be received no later than
+&lt;Sept 15th&gt;.
+The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP: Speaker Attribution Data Annotation of ORF Voice Recordings
+Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below
 • Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
+rfp.lehs(at)wadhwaniai.org
 Download Attachment:
-TOR for Hygiene Tool kit and framework.doc
+RFP - Speaker Attribution Data Annotation - Pan India.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-16 Sep 2026
+15 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -2366,54 +1345,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2444,38 +1423,570 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>15-09-2026</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and ...</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | India
+RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and Enterprise Wireless Access Points, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tende ... Read More</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303512</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Standardisation and Development of Community Training Modules and Fa...</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | India
+ToR - Standardisation and Development of Community Training Modules and Facilitator Manuals for WASH-Secure Communities, WaterAid India() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+| ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• Evaluation Criteria
+Selection will follow a
+Quality and Cost Based Selection (QCBS)
+process.
+Technical Evaluation (80 Marks)
+Criteria
+Marks
+Understanding   of assignment
+15
+Methodology   and technical approach
+20
+Relevant   organisational experience
+15
+Experience of   proposed team members
+20
+Quality of   previous work samples
+10
+Total   Technical Score
+80
+Only bidders scoring
+60 marks or above
+in the technical evaluation will qualify for financial evaluation.
+Financial Evaluation (20 Marks)
+The lowest evaluated financial proposal will receive the maximum score of 20, while other proposals will be scored proportionately.
+Final Score
+Final Score = Technical Score (80%) + Financial Score (20%)
+The consultant/agency obtaining the highest combined score will be recommended for award.
+Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
+th
+September by 5:30 pm
+For detailed information, please check the complete version of the ToR attached below.
+• Job Email ID:
+WAIP2P-Delhi(at)wateraid.org
+Download Attachment:
+TOR for Standardisation of Modules.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+16 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>16-09-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303298</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Development of WaterAid India's Hygiene Framework, Community Facilit...</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | India
+ToR - Development of WaterAid India's Hygiene Framework, Community Facilitator Toolkit, Hygiene Booklet and Hygiene Calendar, WaterAid India() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Log ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• Evaluation Criteria
+Criteria
+Weight
+Understanding   of assignment
+20%
+Proposed   methodology
+25%
+Relevant   organisational experience
+20%
+Team   composition and expertise
+20%
+Financial   proposal
+15%
+Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
+th
+September by 5:30 pm
+For detailed information, please check the complete version of the ToR attached below.
+• Job Email ID:
+WAIP2P-Delhi(at)wateraid.org
+Download Attachment:
+TOR for Hygiene Tool kit and framework.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+16 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303297</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Master Composter Training to Strengthen Composting Practices in Ukrainian Communities</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>TheZero Waste Academyis a learning platform focused on sharing practical knowledge and approaches related to waste prevention, resource efficiency and circular economy practices. Through educational programmes, the platform connects participants with experts and practical experiences that can be ada ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The programme is open to participants fromUkrainewho are interested in composting and bio-waste management. Eligible participants can include Ukrainian communities, civil society organisations, institutions, community initiatives and individuals. People with existing composting experience as well as those planning to introduce composting at home, within an organisation or at community level can participate. Applicants do not necessarily need to already operate a composting programme. The course is suitable for people who want to gain practical knowledge and apply composting and circular-economy approaches within their communities or organisations.</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>16 September 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/master-composter-training-to-strengthen-composting-practices-in-ukrainian-communities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-...</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>WaterAid India | Bhadrak, Odisha, Unnao, Uttar Pradesh
 RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-Change Affected Vulnerable Communities”, WaterAid India(Bhadrak, Odisha, Unnao) | DevNetJobsIndia
@@ -2489,7 +2000,7 @@
 RFPs ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>• Pre-bid Queries:
 By 15 September 2026
@@ -2638,54 +2149,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2716,309 +2227,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Climate, Governance, Learning</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>16-09-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303358</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Master Composter Training to Strengthen Composting Practices in Ukrainian Communities</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>TheZero Waste Academyis a learning platform focused on sharing practical knowledge and approaches related to waste prevention, resource efficiency and circular economy practices. Through educational programmes, the platform connects participants with experts and practical experiences that can be ada ... Read More</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>The programme is open to participants fromUkrainewho are interested in composting and bio-waste management. Eligible participants can include Ukrainian communities, civil society organisations, institutions, community initiatives and individuals. People with existing composting experience as well as those planning to introduce composting at home, within an organisation or at community level can participate. Applicants do not necessarily need to already operate a composting programme. The course is suitable for people who want to gain practical knowledge and apply composting and circular-economy approaches within their communities or organisations.</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>16 September 2026</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/master-composter-training-to-strengthen-composting-practices-in-ukrainian-communities/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Standardisation and Development of Community Training Modules and Fa...</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-ToR - Standardisation and Development of Community Training Modules and Facilitator Manuals for WASH-Secure Communities, WaterAid India() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-| ... Read More</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>• Evaluation Criteria
-Selection will follow a
-Quality and Cost Based Selection (QCBS)
-process.
-Technical Evaluation (80 Marks)
-Criteria
-Marks
-Understanding   of assignment
-15
-Methodology   and technical approach
-20
-Relevant   organisational experience
-15
-Experience of   proposed team members
-20
-Quality of   previous work samples
-10
-Total   Technical Score
-80
-Only bidders scoring
-60 marks or above
-in the technical evaluation will qualify for financial evaluation.
-Financial Evaluation (20 Marks)
-The lowest evaluated financial proposal will receive the maximum score of 20, while other proposals will be scored proportionately.
-Final Score
-Final Score = Technical Score (80%) + Financial Score (20%)
-The consultant/agency obtaining the highest combined score will be recommended for award.
-Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
-th
-September by 5:30 pm
-For detailed information, please check the complete version of the ToR attached below.
-• Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
-Download Attachment:
-TOR for Standardisation of Modules.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-16 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Center Manager
-(Value Members only)
-Location:
-Delhi
-Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
-Location:
-Gujarat
-Apply by:
-11 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303298</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>SoW for Hiring an External Agency for Orientation and Capacity Building</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | Jharkhand
 SoW for Hiring an External Agency for Orientation and Capacity Building, Room to Read India() | DevNetJobsIndia
@@ -3040,7 +2280,7 @@
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SoW)
 for
@@ -3172,54 +2412,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3250,286 +2490,294 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>17-09-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303276</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for SVRI Research Grant 2027 – Data to Evidence Grant</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>TheSexual Violence Research Initiative (SVRI)is a global organisation dedicated to strengthening research on violence against women, child sexual violence and other forms of gender-based violence, particularly in low- and middle-income countries. SVRI supports locally led, ethically rigorous and act ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The lead applicant must be based at anLMIC-based university, research institution or NGO. Independent consultants and individuals without institutional affiliation, as well as applicants affiliated with for-profit companies, are not eligible. The proposed dataset must have been ethically sourced, and applicants must have the necessary permission and approval to access and analyse it. The lead applicant cannot currently hold another active SVRI research grant or have previously received an SVRI grant. However, an institution whose previous SVRI grant has ended may apply. Applicants must be based in a country classified as low-, lower-middle- or upper-middle-income under the applicable World Bank classification.</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>17 September 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-invited-for-svri-research-grant-2027-data-to-evidence-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>WFP SDS Microgrant Programme 2026: Apply for Up to $5,000 in Farmer Grants</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>TheUnited Nations World Food Programme (WFP)is a leading humanitarian organization working worldwide to combat hunger, strengthen food security, and support vulnerable communities. For this initiative, WFP is partnering with the NGOSouthern Development Strategy (SDS)to provide targeted financial ass ... Read More</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>TheWFP SDS Microgrant Programmeprovides financial assistance to farmers and small-scale producers in Ukraine who are already engaged in agricultural production or related activities. Theseagricultural grantsare designed to help existing enterprises recover, strengthen production, purchase essential equipment or materials, and contribute to sustainable community development. Eligible activities include crop cultivation, livestock production, beekeeping, food processing, and fish farming. Microgrants are available at three levels US$1,500, US$3,000, and US$5,000. The final amount is determined by a selection committee after reviewing the application and, for shortlisted applicants, conducting a verification visit.</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Rural</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>18 September 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303276</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/https-andpurpose-world-wfp-sds-microgrant-programme-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for SVRI Research Grant 2027 – Data to Evidence Grant</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>TheSexual Violence Research Initiative (SVRI)is a global organisation dedicated to strengthening research on violence against women, child sexual violence and other forms of gender-based violence, particularly in low- and middle-income countries. SVRI supports locally led, ethically rigorous and act ... Read More</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>The lead applicant must be based at anLMIC-based university, research institution or NGO. Independent consultants and individuals without institutional affiliation, as well as applicants affiliated with for-profit companies, are not eligible. The proposed dataset must have been ethically sourced, and applicants must have the necessary permission and approval to access and analyse it. The lead applicant cannot currently hold another active SVRI research grant or have previously received an SVRI grant. However, an institution whose previous SVRI grant has ended may apply. Applicants must be based in a country classified as low-, lower-middle- or upper-middle-income under the applicable World Bank classification.</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for the Wellcome Prize for Mental Health Science with Nature</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Wellcomeis a global charitable foundation supporting science to solve urgent health challenges. Its work includes discovery research into life, health and wellbeing, with mental health among its major global priorities.Natureis an international scientific publication known for publishing rigorous re ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Research teams should select a lead applicant and complete the official online application form. Applications are open for self-submission, so formal nomination is not required. Applicants should demonstrate the intervention’s novelty, scientific credibility, measurable clinical benefit and potential for adoption. Teams should also explain how the intervention was developed and provide evidence supporting its clinical effectiveness. The application must be complete and submitted online by the official closing time.</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>18 September 2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-invited-for-the-wellcome-prize-for-mental-health-science-with-nature/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Call for Proposals: Labour Service Organisations Training Vulnerable Workers (South Africa)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>TheSouth African Department of Employment and Labouris a national government department responsible for promoting decent employment, protecting workers’ rights and supporting fair and safe labour practices across South Africa. Its responsibilities include administering and implementing labour legisl ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 18 September 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>18 September 2026</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/call-for-proposals-labour-service-organisations-training-vulnerable-workers-south-africa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Nominations Open for Italian Bilateral Scientific Cooperation Award (US)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Italian Ministry of Foreign Affairs and International Cooperation (MAECI) TheItalian Ministry of Foreign Affairs and International Cooperation (MAECI)is responsible for Italy’s foreign relations and international cooperation. The Ministry works to strengthen Italy’s diplomatic, cultural, economic an ... Read More</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 18 September 2026</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>17 September 2026</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="n">
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>18 September 2026</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-svri-research-grant-2027-data-to-evidence-grant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Nominations Open for Italian Bilateral Scientific Cooperation Award (US)</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Italian Ministry of Foreign Affairs and International Cooperation (MAECI) TheItalian Ministry of Foreign Affairs and International Cooperation (MAECI)is responsible for Italy’s foreign relations and international cooperation. The Ministry works to strengthen Italy’s diplomatic, cultural, economic an ... Read More</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 18 September 2026</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>18 September 2026</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://andpurpose.world/nominations-open-for-italian-bilateral-scientific-cooperation-award-us/</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>Call for Proposals: Labour Service Organisations Training Vulnerable Workers (South Africa)</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>TheSouth African Department of Employment and Labouris a national government department responsible for promoting decent employment, protecting workers’ rights and supporting fair and safe labour practices across South Africa. Its responsibilities include administering and implementing labour legisl ... Read More</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 18 September 2026</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>18 September 2026</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/call-for-proposals-labour-service-organisations-training-vulnerable-workers-south-africa/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>WFP SDS Microgrant Programme 2026: Apply for Up to $5,000 in Farmer Grants</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>TheUnited Nations World Food Programme (WFP)is a leading humanitarian organization working worldwide to combat hunger, strengthen food security, and support vulnerable communities. For this initiative, WFP is partnering with the NGOSouthern Development Strategy (SDS)to provide targeted financial ass ... Read More</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>TheWFP SDS Microgrant Programmeprovides financial assistance to farmers and small-scale producers in Ukraine who are already engaged in agricultural production or related activities. Theseagricultural grantsare designed to help existing enterprises recover, strengthen production, purchase essential equipment or materials, and contribute to sustainable community development. Eligible activities include crop cultivation, livestock production, beekeeping, food processing, and fish farming. Microgrants are available at three levels US$1,500, US$3,000, and US$5,000. The final amount is determined by a selection committee after reviewing the application and, for shortlisted applicants, conducting a verification visit.</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>Agriculture &amp; Rural</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>18 September 2026</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/https-andpurpose-world-wfp-sds-microgrant-programme-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for the Wellcome Prize for Mental Health Science with Nature</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Wellcomeis a global charitable foundation supporting science to solve urgent health challenges. Its work includes discovery research into life, health and wellbeing, with mental health among its major global priorities.Natureis an international scientific publication known for publishing rigorous re ... Read More</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Research teams should select a lead applicant and complete the official online application form. Applications are open for self-submission, so formal nomination is not required. Applicants should demonstrate the intervention’s novelty, scientific credibility, measurable clinical benefit and potential for adoption. Teams should also explain how the intervention was developed and provide evidence supporting its clinical effectiveness. The application must be complete and submitted online by the official closing time.</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>18 September 2026</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-the-wellcome-prize-for-mental-health-science-with-nature/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquife...</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Development Support Centre (DSC) | India
-ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquifer Study Using Participatory Approaches for Natural Resource, Watershed..., Development Support Centre (DSC)() | DevNetJobsIndia
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>RFQ - Spring and Dugwell Based Piped Water Supply Scheme (PWSS)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | Jagatpur, Dindori, Madhya Pradesh
+RFQ - Spring and Dugwell Based Piped Water Supply Scheme (PWSS), WaterAid India(Jagatpur, Dindori) | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broad ... Read More</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jo ... Read More</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
-cpc.dsc(at)gmail.com
+WAIProcurementMP(at)wateraid.org
 Download Attachment:
-DSC-Geohydrology Study ToR.pdf
+RFQ format-Jagatpur.xls
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-20 Sep 2026
+19 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3586,54 +2834,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3664,38 +2912,258 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>19-09-2026</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303719</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Individual Consultant / Firm Engagement: TN Energy Audits</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>World Resources Institute India (WRI India) | Tamil Nadu
+RFP - Individual Consultant / Firm Engagement: TN Energy Audits, World Resources Institute India (WRI India)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+L ... Read More</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>• Accordingly, IRT seeks to engage a qualified and certified energy auditing firm or energy auditor (consultant) to undertake comprehensive energy audits, collect and analyse technical data, develop evidence-based recommendations, and prepare detailed technical reports and implementation guidance in accordance with the scope of work outlined in this Terms of Reference.
+2.         Objectives of the Consultancy
+Undertake comprehensive energy audits of the identified public healthcare facilities to assess existing energy consumption patterns, electrical infrastructure, power quality, and the energy performance of major medical and non-medical equipment, establishing a robust baseline for energy management.
+Identify and evaluate energy conservation and energy efficiency opportunities through detailed technical analysis, including equipment-level performance assessment, load profiling, critical and non-critical load segregation, cost-benefit analysis, and recommendations for operational improvements, efficient technologies, and renewable energy integration where feasible.
+Develop actionable technical outputs including facility-wise energy audit reports, actionable suggestions with technical specifications, guidance documents, and walkthrough audit tools to support evidence-based planning, future energy planning, and replication of energy audits across healthcare facilities.
+• 3.         Scope of Work
+A.         Energy Audit of healthcare facilities –
+A detailed energy audit will be conducted at each facility to understand existing energy consumption patterns across various building end-use applications such as lighting, air-conditioning, medical use, hot water, etc., at total of 20 healthcare facilities in Tamil Nadu.
+4.         Required Qualifications and Experience
+The consultant/consulting firm should meet the following minimum qualifications and experience requirements:
+Educational Qualification
+Lead Energy Auditor shall possess a Bachelors degree or higher in Electrical Engineering, Energy Engineering, Mechanical Engineering, or a related discipline. Additional qualifications in Energy Management, Renewable Energy, or Energy Efficiency will be preferred.
+Accredited Energy Auditor (AEA) or Certified Energy Auditor (CEA) registered with the Bureau of Energy Efficiency (BEE), Government of India
+The audit team should comprise suitably qualified engineers and technical professionals with relevant educational backgrounds.
+Professional Experience:
+Minimum three (3) years of demonstrated experience in conducting detailed energy audits of commercial, institutional, industrial, or public sector facilities.
+Experience in conducting energy audits of healthcare facilities will be highly desirable.
+Technical Expertise:
+Demonstrated expertise in energy auditing, electrical load assessment, power quality analysis, electrical distribution systems, energy performance analysis, and identification of energy conservation and energy efficiency measures.
+Experience in analysing the energy performance of electrical and medical equipment, developing energy performance indicators, conducting cost-benefit analysis, and preparing technically sound recommendations for energy efficiency and renewable energy integration.
+Familiarity with relevant Bureau of Energy Efficiency (BEE) guidelines, applicable Indian Standards, and best practices in energy auditing.
+Deadline
+: 20th September 2026 Expression of interest:
+All expressions of interest, questions and proposals in response to this RFP must be received via email to the contact below by September 20, 2026
+Amittosh.Pandey@wri.org
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+Amittosh.Pandey(at)wri.org
+Download Attachment:
+RFP - TN Energy Audits.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+20 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>20-09-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303378</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303143</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>RFP - Website Transition, Hosting, Maintenance, Support and Redesign Servi...</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Plan India | India
 RFP - Website Transition, Hosting, Maintenance, Support and Redesign Services, Plan India() | DevNetJobsIndia
@@ -3718,7 +3186,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• Bid Submission Deadline: PM 20th September 2026
 • How to apply: send proposals to
@@ -3829,54 +3297,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3907,82 +3375,61 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>20-09-2026</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303530</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Procurement of IT Equipment and Accessories</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | India
-RFP - Procurement of IT Equipment and Accessories, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquife...</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Development Support Centre (DSC) | India
+ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquifer Study Using Participatory Approaches for Natural Resource, Watershed..., Development Support Centre (DSC)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>• Interested bidders meeting the preliminary examination and technical evaluation criteria are invited to submit Financial Proposals in accordance with the requirements outlined in this Request for Proposal (RFP).
-2. About India HIV/AIDS Alliance
-India HIV/AIDS Alliance (Alliance India) is a leading non-government organization dedicated to strengthening India's response to HIV/AIDS, public health, and community systems. Through partnerships with government agencies, civil society organizations, community-based organizations, donors, and development partners, Alliance India works to improve equitable access to quality healthcare services for vulnerable and key populations.
-Alliance India implements programmes across multiple states through technical assistance, capacity building, advocacy, research, procurement support, and programme management while maintaining the highest standards of governance, transparency, and financial accountability
-3. Objective of the Procurement
-The objective of this procurement is to identify one or more technically qualified and financially capable suppliers for the supply of high-quality IT equipment and accessories to support programme implementation across multiple locations in India.
-4. Submission Process
-Proposals shall be submitted electronically to
-procurement1@allianceindia.org
-on or before the deadline mentioned in this RFP.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-procurement1(at)allianceindia.org
+Broad ... Read More</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+cpc.dsc(at)gmail.com
 Download Attachment:
-RFP_Procurement_of_IT_Equipment.doc
-Download Attachment:
-IHAA_IT Equipment_Corrigendum-1.doc
+DSC-Geohydrology Study ToR.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-21 Sep 2026
+20 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -4039,54 +3486,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4117,83 +3564,741 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303378</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Procurement of IT Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | India
+RFP - Procurement of IT Equipment and Accessories, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>• Interested bidders meeting the preliminary examination and technical evaluation criteria are invited to submit Financial Proposals in accordance with the requirements outlined in this Request for Proposal (RFP).
+2. About India HIV/AIDS Alliance
+India HIV/AIDS Alliance (Alliance India) is a leading non-government organization dedicated to strengthening India's response to HIV/AIDS, public health, and community systems. Through partnerships with government agencies, civil society organizations, community-based organizations, donors, and development partners, Alliance India works to improve equitable access to quality healthcare services for vulnerable and key populations.
+Alliance India implements programmes across multiple states through technical assistance, capacity building, advocacy, research, procurement support, and programme management while maintaining the highest standards of governance, transparency, and financial accountability
+3. Objective of the Procurement
+The objective of this procurement is to identify one or more technically qualified and financially capable suppliers for the supply of high-quality IT equipment and accessories to support programme implementation across multiple locations in India.
+4. Submission Process
+Proposals shall be submitted electronically to
+procurement1@allianceindia.org
+on or before the deadline mentioned in this RFP.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+procurement1(at)allianceindia.org
+Download Attachment:
+RFP_Procurement_of_IT_Equipment.doc
+Download Attachment:
+IHAA_IT Equipment_Corrigendum-1.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+21 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>21-09-2026</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303414</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>Submit Applications for Homelessness Prevention Grants (UK)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge City Councilis the local authority responsible for delivering public services and supporting communities across Cambridge, United Kingdom. The Council works with voluntary, community, and partner organisations to address local challenges including homelessness, rough sleeping, housing inse ... Read More</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Applications are open tovoluntary and community organisationsworking to prevent or relieve homelessness and rough sleeping in Cambridge. Applicants should have appropriate governance arrangements, financial controls, and the organisational capacity to manage public funding responsibly. Projects must benefit people in Cambridge and directly contribute to homelessness prevention or relief. Applicants should demonstrate a clear understanding of local homelessness needs, explain why funding is required, and show how activities and outcomes will be monitored and measured. The Council may also require supporting documents such as accounts, organisational budgets, governing documents, insurance certificates, risk assessments, and relevant organisational policies.</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>22 September 2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303414</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Submit Applications for Homelessness Prevention Grants (UK)</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Cambridge City Councilis the local authority responsible for delivering public services and supporting communities across Cambridge, United Kingdom. The Council works with voluntary, community, and partner organisations to address local challenges including homelessness, rough sleeping, housing inse ... Read More</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Applications are open tovoluntary and community organisationsworking to prevent or relieve homelessness and rough sleeping in Cambridge. Applicants should have appropriate governance arrangements, financial controls, and the organisational capacity to manage public funding responsibly. Projects must benefit people in Cambridge and directly contribute to homelessness prevention or relief. Applicants should demonstrate a clear understanding of local homelessness needs, explain why funding is required, and show how activities and outcomes will be monitored and measured. The Council may also require supporting documents such as accounts, organisational budgets, governing documents, insurance certificates, risk assessments, and relevant organisational policies.</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>22 September 2026</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/submit-applications-for-homelessness-prevention-grants-uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Knowledge and Learning Partner</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Digital Green India | India
+RFP - Knowledge and Learning Partner, Digital Green India() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Register
+Job ID:
+303695
+RFP - Knowle ... Read More</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+Legal status:
+The bidder must be a for-profit commercial entity duly incorporated/registered under applicable Indian laws. The bidder must hold all applicable statutory registrations, licences and tax registrations required for carrying out the activities under this TOR
+Consortium bids:
+Consortium bids shall not be permitted where any consortium member is an NGO, society, charitable trust, Section 8 company or other not-for-profit entity. All consortium members must meet the legal-status requirements above and the consortium arrangement must not result in any transfer of foreign contribution by DGI to another association/person in contravention of applicable FCRA provision.
+Conflict of interest:
+Bidders must disclose any existing financial, governance, or advisory relationship with Core Council members or competing alliances that could constitute a conflict of interest.
+Exclusions:
+As this engagement will be funded from foreign contribution and is structured as a procurement of professional/programme services, the engagement is not intended to constitute a grant, sub-grant, sub-award or transfer of foreign contribution. Accordingly, entities established or operating as non-profit organisations, including NGOs, societies, charitable trusts, Section 8 companies or other not-for-profit entities, will not be eligible to participate as bidders.
+4.
+Submission Requirements
+Interested
+parties are requested to submit:
+A technical proposal describing the proposed approach to each of the four workstreams, staffing plan, and relevant prior experience;
+A financial proposal covering the three-year engagement period, with an indicative annual breakdown;
+CVs of key personnel proposed for the engagement;
+References or examples of comparable prior engagements.
+A statement of proposed team composition, base location, and language capabilities relevant to the initiative geographies.
+DGI
+will evaluate submissions against the required experience and qualifications set out in Section 4, and against the overall fit of the proposed approach with the initiative's objectives and workstreams.
+Proposal submission deadline
+:
+September 23rd 2026.
+Email ID for proposal submission
+:
+dgtindiaprocurement@digitalgreentrust.org
+Budget ceiling
+• : The budget is not being disclosed at this stage. Bidders are requested to submit a detailed financial proposal based on the scope of work, deliverables, timelines, and requirements specified in this RFP.
+PS
+: Bidders should be asked to hold their financial proposal valid for fifteen (15) days from the submission deadline.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+dgtindiaprocurement(at)digitalgreentrust.org
+Download Attachment:
+AgriNext_Alliance_TOR_Knowledge_Partner_Sep 10 2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+23 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/submit-applications-for-homelessness-prevention-grants-uk/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303695</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Development of Sports Ground with Multi Game Court in CGIC ,Tikri,Va...</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Plan India | Tikri,Varanasi, Uttar Pradesh
+RFP - Development of Sports Ground with Multi Game Court in CGIC ,Tikri,Varanasi ,UP, Plan India(Tikri,Varanasi) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regis ... Read More</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>• Bid Submission Deadline:
+25
+th
+September 2026.
+• How to apply : send proposal to Plan India in the Big /one envelope:
+• Bid Submission Address *
+only sealed bids with subject line
+a) Technical Proposal (in BOQ attached along with the Documents )
+b) Financial Proposal
+Procurement Department
+Plan International (India Chapter)
+1, Zamrudpur Community Centre, Kailash Colony
+New Delhi – 110048
+Email for Clarifications:
+procurement@planindia.org
+• Plan India reserves the rights to alter the terms &amp; conditions and alteration on Scope of Work.
+Plan India reserves the right to accept/ reject the quotation without assigning the reason whatsoever.
+Issued By
+Plan International (India Chapter)
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+RFP -Developing Sports Ground Tikri -Varanasi -UP ..doc
+Download Attachment:
+BOQ-Tikri School Multisport Game Court (1).xls
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+25 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303760</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>RFP - Empanelment of development &amp; implementation partners for CSR, commu...</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>AROH Foundation | India
 RFP - Empanelment of development &amp; implementation partners  for CSR, community development &amp; infrastructure projects across India, AROH Foundation() | DevNetJobsIndia
@@ -4210,7 +4315,7 @@
 Jobseeke ... Read More</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>• 1. INTRODUCTION AND BACKGROUND
 AROH Foundation invites proposals from experienced, technically competent and financially sound development agencies, implementation partners, contractors, service providers and vendors for empanelment to undertake CSR, community development, infrastructure, renewable energy, water conservation, natural resource management and allied
@@ -4372,54 +4477,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4450,38 +4555,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>25-09-2026</t>
         </is>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
+      <c r="H30" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302836</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
 RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
@@ -4496,7 +4601,7 @@
 Se ... Read More</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>• SCOPE OF WORK
 • The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
@@ -4575,54 +4680,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4653,6 +4758,302 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>25 September 2026</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Proj...</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Aga Khan Foundation (India) | Bihar
+RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Project Dhenu Dhara – Foraging pathways to improving livestock health and dairy , Aga Khan Foundation (India)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Re ... Read More</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>• Bidders may alter or withdraw their bids by written notification prior to the stated deadline for submission of bids. No bids may be altered after this deadline. Withdrawals must be unconditional and will end all participation in the bid procedure.
+6. Opening of bid
+The bid will be opened by the Aga Khan Foundation within
+15 days
+from the deadline for the submission of the bid.
+Any attempt by a bidder to influence the evaluation committee in the process of examination, clarification, evaluation and comparison of bids, to obtain information on how the procedure is progressing or to influence the contracting authority in its decision concerning the award of the contract will result in immediate rejection of its bid.
+• 7. Submission of bids
+The bid has to be submitted in the prescribed format on or before
+Monday,
+28
+th
+September
+202
+6
+by 5 p.m.
+Indian
+Standard Time to
+akfindia.helpdesk@akdn.org
+Technical and financial proposals should be
+submitted simultaneously, but in separate emails
+, with the RFP reference and the clear description of the proposal (technical or financial) by the date and time stipulated in this document. If the emails and email attachments are not marked as instructed, AKF will assume no responsibility for the misplacement or premature opening of the proposals submitted.
+Both email text bodies should indicate the name and address of the bidder and the description of the proposal (technical or financial). The technical email should not contain any pricing information, nor should the financial email contain any component of the technical proposal.
+Technical proposals should be submitted in one (1) email accompanied by the forms prescribed in this
+RFP, clearly marked as “technical proposal”
+- in the email subject line and corresponding attachment should read: (RFP Reference No.)
+–
+(name of bidder)
+–
+TECHNICAL PROPOSAL
+The technical proposal should not contain any details of the financial proposal / budget.
+Any financial information contained in the technical proposal will invalidate the proposal.
+Financial proposals should be submitted in one (1) email with the email subject line as ‘FINANCIAL PROPOSAL’ and corresponding email attachment should read: (RFP Reference No.) –
+(name of bidder)
+–
+FINANCIAL PROPOSAL.
+The
+Financial Proposal should contain the budget in a password protected file (excel and/or pdf), which can be opened only with the password. The bidder should not mention any financial amounts in the email text body, or the password.
+Passwords should be made available only at a later date, when requested for by AKF.
+Proposals should be received by the date, time and means of submission stipulated in this RFP. Bidders are responsible for ensuring that AKF receives their proposal by the due date and time. Proposals received by AKF after the due date and time may be rejected. When receiving proposals by email (as is required for the RFP), the receipt time stamp shall be the date and time when the submission has been received in the dedicated AKF inbox. AKF shall not be responsible for any delays caused by network problems, etc. It is the sole responsibility of bidders to ensure that their proposal is received by AKF in the dedicated inbox on or before the prescribed RFP deadline.
+Proposals following a Consortium Model for undertaking the given assignment are encouraged to
+apply
+.
+8. Request for Clarification
+All questions regarding the preparation of proposals must be submitted in writing (by e-mail) to
+akfindia.helpdesk@akdn.org
+by
+Thursday
+,
+24
+th
+September
+202
+6
+. Responses will be provided to all interested organizations by
+Friday,
+25
+th
+September
+202
+6
+, through email. Aga Khan Foundation is under no obligation to consider or respond to questions that are not received in a timely manner.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+akfindia.helpdesk(at)akdn.org
+Download Attachment:
+RFP_Dhenu Dhara Project Baseline.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+28 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
@@ -4660,76 +5061,31 @@
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303730</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
+          <t>RFP - for Final Evaluation of Support Micro/Small entrepreneurs among part...</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>25 September 2026</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Final Evaluation of Support Micro/Small entrepreneurs among part...</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe e.V | India
 RFP - for Final Evaluation of Support Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans, Deutsche Welthungerhilfe e.V() | DevNetJobsIndia
@@ -4744,7 +5100,7 @@
 Searc ... Read More</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION ANDCONTEXT
 Country:
@@ -4853,54 +5209,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Center Manager
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
 (Value Members only)
 Location:
 Delhi
 Apply by:
-20 Sep 2026
-Monitoring and Evaluation cum Accountant
-Centre of Technology and Entrepreneurship Develop...
-Location:
-Uttar Pradesh
-Apply by:
-27 Sep 2026
-Individual Consultant / Agency: Video Editor
-(Value Members only)
-Location:
-Delhi
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
 Apply by:
 30 Sep 2026
-Counsellor - Meri Trustline
-RATI Foundation for Social Change
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Assistant
-(Value Members only)
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Community Outreach Worker for Men and Boys (Men O...
-Shakti Shalini
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-Portfolio Lead, Banking
-(Value Members only)
-Location:
-Tamil Nadu
-Apply by:
-21 Sep 2026
-Soft Skill Trainer
-Pahal Nurturing Lives
+Site-In-Charge -  Mundra
+Plan India
 Location:
 Gujarat
 Apply by:
-11 Oct 2026
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4931,14 +5287,59 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+        </is>
+      </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -4946,7 +5347,7 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
+          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
         </is>
       </c>
     </row>
@@ -4963,17 +5364,17 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+          <t>The application deadline is 29 September 2026</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -4987,11 +5388,11 @@
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
         </is>
       </c>
     </row>
@@ -5008,17 +5409,17 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+          <t>Applications Open for Green Box Artist in Residency Program</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 29 September 2026</t>
+          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -5028,7 +5429,7 @@
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>29 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
@@ -5036,7 +5437,7 @@
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
+          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5478,7 @@
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
@@ -5098,22 +5499,22 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Green Box Artist in Residency Program</t>
+          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
+          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
+          <t>The application deadline is30 September 2026</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
@@ -5122,11 +5523,11 @@
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
+          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
         </is>
       </c>
     </row>
@@ -5143,27 +5544,27 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
+          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
+          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is30 September 2026</t>
+          <t>The application deadline is 01 October 2026</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>01 October 2026</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
@@ -5171,7 +5572,7 @@
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
+          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
         </is>
       </c>
     </row>
@@ -5188,27 +5589,27 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
+          <t>RFAs: Expanding Global Health Security Through Local Partnerships (Ethiopia)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
+          <t>U.S. Centers for Disease Control and Prevention (CDC) TheU.S. Centers for Disease Control and Prevention (CDC)is a leading public health agency dedicated to protecting communities from health threats through research, disease prevention, surveillance, and emergency response. Working closely with gov ... Read More</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 01 October 2026</t>
+          <t>Review the official funding announcement and verify your organization’s eligibility. Prepare a technical proposal aligned with one or more program priorities, including implementation plans, monitoring strategies, and a realistic budget. Demonstrate organizational capacity, sustainable partnerships, and measurable public health outcomes. Submit the completed application with all required supporting documents through the official application system before the closing deadline.</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>01 October 2026</t>
+          <t>02 October 2026</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
@@ -5216,52 +5617,198 @@
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
+          <t>https://andpurpose.world/rfas-expanding-global-health-security-through-local-partnerships-ethiopia/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>RFAs: Expanding Global Health Security Through Local Partnerships (Ethiopia)</t>
+          <t>RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme i...</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U.S. Centers for Disease Control and Prevention (CDC) TheU.S. Centers for Disease Control and Prevention (CDC)is a leading public health agency dedicated to protecting communities from health threats through research, disease prevention, surveillance, and emergency response. Working closely with gov ... Read More</t>
+          <t>World Resources Institute India (WRI India) | Karnataka
+RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme in Karnataka, World Resources Institute India (WRI India)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs ... Read More</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Review the official funding announcement and verify your organization’s eligibility. Prepare a technical proposal aligned with one or more program priorities, including implementation plans, monitoring strategies, and a realistic budget. Demonstrate organizational capacity, sustainable partnerships, and measurable public health outcomes. Submit the completed application with all required supporting documents through the official application system before the closing deadline.</t>
+          <t>• Job Email ID:
+Aprajita.Verma(at)wri.org
+Download Attachment:
+RFP- EV Skilling Programme in Karnataka.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Oct 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Communications Officer
+The Adventist Development and Relief Agency (ADRA...
+Location:
+Haryana
+Apply by:
+30 Sep 2026
+State Consultant – Public Finance for Children (P...
+Inductus Limited
+Location:
+Bihar
+Apply by:
+20 Sep 2026
+Consultant, Founder's Office
+(Value Members only)
+Location:
+Delhi
+Apply by:
+28 Sep 2026
+Veterinary Consultant
+Gramin Samaj Kalyan Vikas Manch
+Location:
+Jharkhand
+Apply by:
+24 Sep 2026
+Multiple Vacancies
+Manbhum Ananda Ashram Nityananda Trust (MANT)
+Location:
+West Bengal, Jharkhand
+Apply by:
+30 Sep 2026
+Site-In-Charge -  Mundra
+Plan India
+Location:
+Gujarat
+Apply by:
+15 Oct 2026
+Site-In-Charge
+Plan India
+Location:
+Maharashtra, Karnataka
+Apply by:
+15 Oct 2026
+Site Manager
+Plan India
+Location:
+India
+Apply by:
+15 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Learning, Safety</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>02 October 2026</t>
+          <t>05-10-2026</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/rfas-expanding-global-health-security-through-local-partnerships-ethiopia/</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
         </is>
       </c>
     </row>
@@ -5278,35 +5825,35 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+          <t>Funding Opportunity for Civil Society Organisations to Countering Disinformation in Poland</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+          <t>TheEEA Civil Society Fundsupports civil society organisations working to strengthen democracy, human rights, public participation, and social inclusion across eligible European countries. Through targeted funding programmes, the Fund empowers non-profit organisations to address emerging societal cha ... Read More</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+          <t>Eligible organisations should prepare a proposal outlining the disinformation challenge, project objectives, planned activities, expected outcomes, implementation strategy, organisational experience, and budget. Applications should demonstrate measurable impact, sustainability, and community benefit. Ensure all legal and eligibility requirements are met before submitting the proposal according to the programme guidelines before the closing date.</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>06 October 2026</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
+          <t>https://andpurpose.world/funding-opportunity-for-civil-society-organisations-to-countering-disinformation-in-poland/</t>
         </is>
       </c>
     </row>
@@ -5323,35 +5870,35 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Funding Opportunity for Civil Society Organisations to Countering Disinformation in Poland</t>
+          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>TheEEA Civil Society Fundsupports civil society organisations working to strengthen democracy, human rights, public participation, and social inclusion across eligible European countries. Through targeted funding programmes, the Fund empowers non-profit organisations to address emerging societal cha ... Read More</t>
+          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should prepare a proposal outlining the disinformation challenge, project objectives, planned activities, expected outcomes, implementation strategy, organisational experience, and budget. Applications should demonstrate measurable impact, sustainability, and community benefit. Ensure all legal and eligibility requirements are met before submitting the proposal according to the programme guidelines before the closing date.</t>
+          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>06 October 2026</t>
+          <t>6 October 2026</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/funding-opportunity-for-civil-society-organisations-to-countering-disinformation-in-poland/</t>
+          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5939,7 @@
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
@@ -5437,7 +5984,7 @@
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
@@ -5482,7 +6029,7 @@
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
@@ -5503,17 +6050,17 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Realization of Short Animation Grant</t>
+          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TheNetherlands Film Fundis the national agency responsible for supporting professional film production and film-related activities in the Netherlands. The Fund provides financial contributions for film development, production, distribution, and other activities within the Dutch film sector. It suppo ... Read More</t>
+          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Applications are open to eligibleindependent production companiesthat are legal entities and have been established for at least two years in the Netherlands, an EU member state, EEA country, or Switzerland. The company must continuously produce and exploit films or other audiovisual productions. For films up to 10 minutes, the producer must have experience as the majority producer responsible for realizing and releasing at least one qualifying independent film. For films from 10 minutes onward, the producer must have experience with at least two qualifying independent animation productions. The producer cannot also be the film’s director or screenwriter.</t>
+          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -5527,11 +6074,11 @@
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-realization-of-short-animation-grant/</t>
+          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -5548,17 +6095,17 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
+          <t>Applications Open for Realization of Short Animation Grant</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
+          <t>TheNetherlands Film Fundis the national agency responsible for supporting professional film production and film-related activities in the Netherlands. The Fund provides financial contributions for film development, production, distribution, and other activities within the Dutch film sector. It suppo ... Read More</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
+          <t>Applications are open to eligibleindependent production companiesthat are legal entities and have been established for at least two years in the Netherlands, an EU member state, EEA country, or Switzerland. The company must continuously produce and exploit films or other audiovisual productions. For films up to 10 minutes, the producer must have experience as the majority producer responsible for realizing and releasing at least one qualifying independent film. For films from 10 minutes onward, the producer must have experience with at least two qualifying independent animation productions. The producer cannot also be the film’s director or screenwriter.</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -5572,11 +6119,11 @@
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
+          <t>https://andpurpose.world/applications-open-for-realization-of-short-animation-grant/</t>
         </is>
       </c>
     </row>
@@ -5593,17 +6140,17 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Commercialisation of Creative Industries Research Grant (UK)</t>
+          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TheArts and Humanities Research Council (AHRC)is part of UK Research and Innovation (UKRI) and funds outstanding research across arts and humanities disciplines. AHRC supports projects that encourage innovation, collaboration, knowledge exchange, and economic growth by connecting universities, resea ... Read More</t>
+          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Applications are open toeligible UK universitiesand organisations that meetUK Research and Innovation (UKRI)eligibility requirements. The lead applicant must demonstrate experience managing multi-stakeholder partnerships, commercialising creative industries research, and coordinating sector-wide collaborations. Partnerships should include organisations experienced in research commercialisation as well as investors or investment-focused organisations with a strong track record in the creative industries. Applicants should possess expertise in innovation, governance, entrepreneurship, intellectual property, and stakeholder engagement. A detailed project plan, evidence-based methodology, partner commitment letters, and compliance with relevant UKRI requirements are expected as part of the application.</t>
+          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -5617,11 +6164,11 @@
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-commercialisation-of-creative-industries-research-grant-uk/</t>
+          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
         </is>
       </c>
     </row>
@@ -5638,17 +6185,17 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
+          <t>Applications Invited for WUN Research Development Fund 2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
+          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
+          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -5662,11 +6209,11 @@
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -5683,27 +6230,27 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for WUN Research Development Fund 2026</t>
+          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
+          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
+          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>15 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
@@ -5711,7 +6258,7 @@
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
         </is>
       </c>
     </row>
@@ -5752,7 +6299,7 @@
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
@@ -5797,7 +6344,7 @@
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
@@ -5818,35 +6365,35 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
+          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
+          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
+          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
+          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
         </is>
       </c>
     </row>
@@ -5887,7 +6434,7 @@
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
@@ -5908,17 +6455,17 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>RFPs: Sheldon Danziger Pipeline Grant Program (US)</t>
+          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TheRussell Sage Foundation (RSF)is a leading American research foundation dedicated to improving the understanding of social, economic, and behavioral issues through high-quality social science research. It funds investigator-led studies that generate evidence to address public policy challenges and ... Read More</t>
+          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Applications are open toAssistant Professors, Adjunct Assistant Professors, and Lecturerswho meet the programme’s eligibility requirements. Applicants must not have previously received an RSF research grant, excluding Dissertation Research Grants. There are no nationality or institutional location restrictions, making the programme accessible to eligible scholars worldwide. Applications from researchers who are underrepresented in the social sciences or employed at under-resourced universities are strongly encouraged. Postdoctoral fellows cannot serve as Principal Investigators but may participate as research assistants. Full Professors and Associate Professors may join as Co-Principal Investigators but are not eligible for salary or conference travel support.</t>
+          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -5928,15 +6475,15 @@
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>21 October 2026</t>
+          <t>26 October 2026</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/rfps-sheldon-danziger-pipeline-grant-program-us/</t>
+          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
         </is>
       </c>
     </row>
@@ -5953,17 +6500,17 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
+          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
+          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
+          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -5973,15 +6520,15 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>26 October 2026</t>
+          <t>28 October 2026</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
+          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
         </is>
       </c>
     </row>
@@ -5998,17 +6545,17 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Core Research Grant Program (US)</t>
+          <t>Whitley Award 2027</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>TheFoundation for Scholarly Researchsupports high-quality academic research that advances knowledge and addresses important global challenges. Through its research funding programmes, the foundation encourages investigator-led projects across diverse disciplines while promoting innovation, collabora ... Read More</t>
+          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>The programme is open toPrincipal Investigators (PIs)andCo-Principal Investigators (Co-PIs)from anywhere in the world. Applicants are generally expected to hold a doctoral degree. However, exceptional candidates without a doctorate may also apply if they demonstrate a distinguished academic or professional background and proven ability to conduct high-quality, peer-reviewed scholarly research. There are no nationality or institutional location restrictions, making the programme accessible to eligible researchers globally. Applicants should submit proposals that align with the foundation’s research priorities and demonstrate strong research methodology, academic significance, and the capacity to successfully complete the proposed project.</t>
+          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -6018,15 +6565,15 @@
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>28 October 2026</t>
+          <t>30 October 2026</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-core-research-grant-program-us/</t>
+          <t>https://andpurpose.world/whitley-award-2027/</t>
         </is>
       </c>
     </row>
@@ -6043,35 +6590,35 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Whitley Award 2027</t>
+          <t>National Indian Health Outreach and Education Program 2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
+          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
+          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>30 October 2026</t>
+          <t>2 November 2026</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/whitley-award-2027/</t>
+          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
         </is>
       </c>
     </row>
@@ -6088,35 +6635,35 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>National Indian Health Outreach and Education Program 2026</t>
+          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
+          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
+          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>2 November 2026</t>
+          <t>4 November 2026</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
         </is>
       </c>
     </row>
@@ -6133,27 +6680,27 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
+          <t>CFAs: U.S. Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
+          <t>TheCenters for Disease Control and Prevention (CDC)is a U.S. public health agency responsible for protecting communities from diseases, health threats, and other public health risks. The agency conducts research, develops evidence-based guidance, monitors health trends, and supports public health pr ... Read More</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
+          <t>TheTravel Health Research Grants 2026opportunity supports initiatives that improve health protection for U.S. residents traveling internationally. The program focuses on four connected areas: travel preparation information, health information collection and surveillance, research into emerging health threats, and travel medicine education for primary care providers. Projects may use electronic medical records, websites, mobile applications, and other digital health technologies to collect information before, during, and after international travel. The estimated total program funding isUS$5 million, with individual awards ranging fromUS$750,000 to US$1 million. The initiative aims to strengthen evidence-based travel health information and public health research.</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>4 November 2026</t>
+          <t>05 November 2026</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
@@ -6161,7 +6708,7 @@
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
+          <t>https://andpurpose.world/cfas-u-s-travelers-health-research-surveillance-communication-and-outreach-network/</t>
         </is>
       </c>
     </row>
@@ -6178,27 +6725,27 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>CFAs: U.S. Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
+          <t>Applications Invited for World Food Day Poster Contest 2026</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>TheCenters for Disease Control and Prevention (CDC)is a U.S. public health agency responsible for protecting communities from diseases, health threats, and other public health risks. The agency conducts research, develops evidence-based guidance, monitors health trends, and supports public health pr ... Read More</t>
+          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>TheTravel Health Research Grants 2026opportunity supports initiatives that improve health protection for U.S. residents traveling internationally. The program focuses on four connected areas: travel preparation information, health information collection and surveillance, research into emerging health threats, and travel medicine education for primary care providers. Projects may use electronic medical records, websites, mobile applications, and other digital health technologies to collect information before, during, and after international travel. The estimated total program funding isUS$5 million, with individual awards ranging fromUS$750,000 to US$1 million. The initiative aims to strengthen evidence-based travel health information and public health research.</t>
+          <t>The application deadline is 6 November 2026</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>05 November 2026</t>
+          <t>6 November 2026</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
@@ -6206,7 +6753,7 @@
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/cfas-u-s-travelers-health-research-surveillance-communication-and-outreach-network/</t>
+          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6770,17 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for World Food Day Poster Contest 2026</t>
+          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
+          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 6 November 2026</t>
+          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -6243,15 +6790,15 @@
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>6 November 2026</t>
+          <t>9 November 2026</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
+          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
         </is>
       </c>
     </row>
@@ -6268,17 +6815,17 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
+          <t>Apply Now for Skills Development Grants for Creative Industries in Toronto</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
+          <t>TheCity of Torontois Canada’s largest municipal government and supports initiatives that strengthen the city’s economy, communities, culture, and workforce. Through its creative industries funding programs, the City supports film, television, music, and creative technology sectors. Its funding initi ... Read More</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
+          <t>Applications are open to eligibleCanadian not-for-profit and charitable organizations, urban off-reserve Indigenous-led organizations, and community centres that are part of the Association of Community Centres. Applicants must be located in Toronto or deliver the proposed funded services to Toronto-based individuals or entities. Organizations must not owe money to the City of Toronto or be in default of existing City agreements. Projects should focus on practical workforce development, employment readiness, and technical skills connected to Toronto’s creative industries. Eligible initiatives may include training in post-production, VFX, animation, digital workflows, trades, crafts, and other high-demand technical roles.</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -6288,15 +6835,15 @@
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>9 November 2026</t>
+          <t>15 November 2026</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
+          <t>https://andpurpose.world/apply-now-for-skills-development-grants-for-creative-industries-in-toronto/</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6884,7 @@
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
@@ -6358,17 +6905,17 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for Skills Development Grants for Creative Industries in Toronto</t>
+          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>TheCity of Torontois Canada’s largest municipal government and supports initiatives that strengthen the city’s economy, communities, culture, and workforce. Through its creative industries funding programs, the City supports film, television, music, and creative technology sectors. Its funding initi ... Read More</t>
+          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Applications are open to eligibleCanadian not-for-profit and charitable organizations, urban off-reserve Indigenous-led organizations, and community centres that are part of the Association of Community Centres. Applicants must be located in Toronto or deliver the proposed funded services to Toronto-based individuals or entities. Organizations must not owe money to the City of Toronto or be in default of existing City agreements. Projects should focus on practical workforce development, employment readiness, and technical skills connected to Toronto’s creative industries. Eligible initiatives may include training in post-production, VFX, animation, digital workflows, trades, crafts, and other high-demand technical roles.</t>
+          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -6378,7 +6925,7 @@
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>15 November 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
@@ -6386,7 +6933,7 @@
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-skills-development-grants-for-creative-industries-in-toronto/</t>
+          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
         </is>
       </c>
     </row>
@@ -6403,17 +6950,17 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
+          <t>Applications Open for CRI Technology Impact Award Grant</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -6427,11 +6974,11 @@
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
+          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
         </is>
       </c>
     </row>
@@ -6448,17 +6995,17 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for CRI Technology Impact Award Grant</t>
+          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
+          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
+          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -6472,11 +7019,11 @@
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
+          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
         </is>
       </c>
     </row>
@@ -6493,22 +7040,22 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
+          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
+          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
+          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
@@ -6517,11 +7064,11 @@
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
+          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
         </is>
       </c>
     </row>
@@ -6538,22 +7085,22 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
+          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
+          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
+          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
@@ -6562,11 +7109,11 @@
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
+          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
         </is>
       </c>
     </row>
@@ -6607,7 +7154,7 @@
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
@@ -6652,7 +7199,7 @@
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
@@ -6697,7 +7244,7 @@
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
@@ -6742,7 +7289,7 @@
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
@@ -6787,7 +7334,7 @@
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
@@ -6832,7 +7379,7 @@
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
@@ -6877,7 +7424,7 @@
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
@@ -6922,7 +7469,7 @@
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
@@ -6933,54 +7480,90 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
+        </is>
+      </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>8 March 2027</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>174</v>
+      </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
+          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B81" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr"/>
+          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
+        </is>
+      </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>30 June 2027</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>288</v>
+      </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
+          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
         </is>
       </c>
     </row>
@@ -6993,7 +7576,7 @@
       <c r="B82" s="1" t="inlineStr"/>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
+          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -7007,7 +7590,7 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -7020,8 +7603,7 @@
       <c r="B83" s="1" t="inlineStr"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
-                    here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -7035,7 +7617,7 @@
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -7048,21 +7630,21 @@
       <c r="B84" s="1" t="inlineStr"/>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>RFP for Women Entrepreneurship Programme - Click here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -7075,21 +7657,22 @@
       <c r="B85" s="1" t="inlineStr"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
+                    here</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -7102,22 +7685,21 @@
       <c r="B86" s="1" t="inlineStr"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
-                    here</t>
+          <t>RFP for Women Entrepreneurship Programme - Click here</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -7129,66 +7711,67 @@
       </c>
       <c r="B87" s="1" t="inlineStr"/>
       <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr"/>
+      <c r="H87" s="1" t="inlineStr"/>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr"/>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+                    here</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr"/>
+      <c r="H88" s="1" t="inlineStr"/>
+      <c r="I88" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr"/>
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
                 India Pvt. Ltd - Click here | Click
                     here</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
-        </is>
-      </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="1" t="inlineStr">
@@ -7200,7 +7783,7 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7796,7 @@
       <c r="B90" s="1" t="inlineStr"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
+          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -7227,7 +7810,7 @@
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7823,7 @@
       <c r="B91" s="1" t="inlineStr"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
+          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -7254,7 +7837,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
         </is>
       </c>
     </row>
@@ -7267,22 +7850,21 @@
       <c r="B92" s="1" t="inlineStr"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
-                    here</t>
+          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
         </is>
       </c>
     </row>
@@ -7295,21 +7877,21 @@
       <c r="B93" s="1" t="inlineStr"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
+          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
         </is>
       </c>
     </row>
@@ -7322,21 +7904,22 @@
       <c r="B94" s="1" t="inlineStr"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
+                    here</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7349,21 +7932,21 @@
       <c r="B95" s="1" t="inlineStr"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7959,7 @@
       <c r="B96" s="1" t="inlineStr"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -7390,7 +7973,7 @@
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7986,7 @@
       <c r="B97" s="1" t="inlineStr"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -7417,7 +8000,7 @@
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7430,7 +8013,7 @@
       <c r="B98" s="1" t="inlineStr"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -7444,7 +8027,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7457,21 +8040,21 @@
       <c r="B99" s="1" t="inlineStr"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7484,7 +8067,7 @@
       <c r="B100" s="1" t="inlineStr"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -7498,7 +8081,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -7511,7 +8094,7 @@
       <c r="B101" s="1" t="inlineStr"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
@@ -7525,7 +8108,7 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7538,22 +8121,21 @@
       <c r="B102" s="1" t="inlineStr"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
-                education in STEM courses - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -7566,21 +8148,21 @@
       <c r="B103" s="1" t="inlineStr"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7593,7 +8175,8 @@
       <c r="B104" s="1" t="inlineStr"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
+                education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -7607,7 +8190,7 @@
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -7620,22 +8203,21 @@
       <c r="B105" s="1" t="inlineStr"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
-                and Financial Management - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -7648,8 +8230,7 @@
       <c r="B106" s="1" t="inlineStr"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
-                    here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -7663,7 +8244,7 @@
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7676,22 +8257,22 @@
       <c r="B107" s="1" t="inlineStr"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
+                and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -7704,8 +8285,8 @@
       <c r="B108" s="1" t="inlineStr"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
+                    here</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
@@ -7719,7 +8300,7 @@
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -7732,7 +8313,8 @@
       <c r="B109" s="1" t="inlineStr"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -7746,7 +8328,7 @@
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -7759,7 +8341,8 @@
       <c r="B110" s="1" t="inlineStr"/>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -7773,7 +8356,7 @@
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -7786,21 +8369,21 @@
       <c r="B111" s="1" t="inlineStr"/>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -7813,7 +8396,7 @@
       <c r="B112" s="1" t="inlineStr"/>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -7827,77 +8410,61 @@
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr"/>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>31st Aug, 2026</t>
-        </is>
-      </c>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr"/>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>Senior Programme Officer - Uday</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>15th Aug, 2026</t>
-        </is>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
@@ -7914,25 +8481,25 @@
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>29th Jun, 2026</t>
+          <t>31st Aug, 2026</t>
         </is>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
         </is>
       </c>
     </row>
@@ -7949,25 +8516,25 @@
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>Senior Programme Officer - Uday</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>15th Aug, 2026</t>
         </is>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -7984,25 +8551,25 @@
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>29th Jun, 2026</t>
         </is>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
         </is>
       </c>
     </row>
@@ -8019,25 +8586,25 @@
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
@@ -8054,25 +8621,25 @@
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -8089,25 +8656,25 @@
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8691,7 @@
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -8136,13 +8703,13 @@
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -8159,79 +8726,95 @@
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>15th May, 2025</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="1" t="inlineStr"/>
-      <c r="G123" s="1" t="inlineStr"/>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>21st May, 2025</t>
+        </is>
+      </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="1" t="inlineStr"/>
-      <c r="G124" s="1" t="inlineStr"/>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8831,7 @@
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
+          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
@@ -8258,7 +8841,7 @@
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8858,7 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
+          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
@@ -8285,7 +8868,7 @@
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8885,7 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
+          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
@@ -8312,7 +8895,7 @@
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8912,7 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>UHI_RFP_Formatted_10072026.pdf</t>
+          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
@@ -8339,7 +8922,7 @@
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8939,7 @@
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9590033.pdf</t>
+          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
@@ -8366,7 +8949,7 @@
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8966,7 @@
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
+          <t>UHI_RFP_Formatted_10072026.pdf</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
@@ -8393,7 +8976,7 @@
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8993,7 @@
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
+          <t>GeM-Bidding-9590033.pdf</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
@@ -8420,7 +9003,7 @@
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
         </is>
       </c>
     </row>
@@ -8437,7 +9020,7 @@
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
+          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
@@ -8447,7 +9030,7 @@
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP_CORRIGENDUM%20I_150726.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -8464,7 +9047,7 @@
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>05.06.2026_EOI-RFP_Kedarnath and Amarnath Yatra.pdf</t>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
@@ -8474,7 +9057,7 @@
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/05.06.2026_EOI-RFP_Kedarnath%20and%20Amarnath%20Yatra.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
         </is>
       </c>
     </row>
@@ -8491,7 +9074,7 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>SOP_Kedarnath and Amarnath_corrigendum_1.pdf</t>
+          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
@@ -8501,7 +9084,7 @@
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP_Kedarnath%20and%20Amarnath_corrigendum_1.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP_CORRIGENDUM%20I_150726.pdf</t>
         </is>
       </c>
     </row>
@@ -8518,7 +9101,7 @@
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>SOP-Kedarnath Amarnath_PRe-bid queries.pdf</t>
+          <t>05.06.2026_EOI-RFP_Kedarnath and Amarnath Yatra.pdf</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
@@ -8528,7 +9111,7 @@
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP-Kedarnath%20Amarnath_PRe-bid%20queries.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/05.06.2026_EOI-RFP_Kedarnath%20and%20Amarnath%20Yatra.pdf</t>
         </is>
       </c>
     </row>
@@ -8545,7 +9128,7 @@
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>EOI FOR CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS UNDER COMPONENT 2.pdf</t>
+          <t>SOP_Kedarnath and Amarnath_corrigendum_1.pdf</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
@@ -8555,7 +9138,7 @@
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS%20UNDER%20COMPONENT%202.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/SOP_Kedarnath%20and%20Amarnath_corrigendum_1.pdf</t>
         </is>
       </c>
     </row>
@@ -8572,7 +9155,7 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Extension_of_Dates_.pdf</t>
+          <t>SOP-Kedarnath Amarnath_PRe-bid queries.pdf</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
@@ -8582,7 +9165,7 @@
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension_of_Dates_.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/SOP-Kedarnath%20Amarnath_PRe-bid%20queries.pdf</t>
         </is>
       </c>
     </row>
@@ -8599,7 +9182,7 @@
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum_Transversal_Experts.pdf</t>
+          <t>EOI FOR CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS UNDER COMPONENT 2.pdf</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
@@ -8609,7 +9192,7 @@
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_Transversal_Experts.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS%20UNDER%20COMPONENT%202.pdf</t>
         </is>
       </c>
     </row>
@@ -8626,7 +9209,7 @@
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Reply_to_Pre-bid_queries_transversal_expert.pdf</t>
+          <t>Extension_of_Dates_.pdf</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
@@ -8636,7 +9219,7 @@
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply_to_Pre-bid_queries_transversal_expert.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Extension_of_Dates_.pdf</t>
         </is>
       </c>
     </row>
@@ -8653,7 +9236,7 @@
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Extension of Dates.pdf</t>
+          <t>Corrigendum_Transversal_Experts.pdf</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -8663,7 +9246,7 @@
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension%20of%20Dates_1.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum_Transversal_Experts.pdf</t>
         </is>
       </c>
     </row>
@@ -8680,7 +9263,7 @@
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9271299.pdf</t>
+          <t>Reply_to_Pre-bid_queries_transversal_expert.pdf</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -8690,7 +9273,7 @@
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9271299.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Reply_to_Pre-bid_queries_transversal_expert.pdf</t>
         </is>
       </c>
     </row>
@@ -8707,7 +9290,7 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Reply to pre-bid queries.pdf</t>
+          <t>Extension of Dates.pdf</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -8717,7 +9300,7 @@
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20pre-bid%20queries_0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Extension%20of%20Dates_1.pdf</t>
         </is>
       </c>
     </row>
@@ -8734,7 +9317,7 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum - I.pdf</t>
+          <t>GeM-Bidding-9271299.pdf</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -8744,7 +9327,7 @@
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20I_1.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9271299.pdf</t>
         </is>
       </c>
     </row>
@@ -8761,7 +9344,7 @@
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>Draft RFP UHI_4.pdf</t>
+          <t>Reply to pre-bid queries.pdf</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -8771,7 +9354,7 @@
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Draft%20RFP%20UHI_4.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20pre-bid%20queries_0.pdf</t>
         </is>
       </c>
     </row>
@@ -8788,7 +9371,7 @@
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9289662.pdf</t>
+          <t>Corrigendum - I.pdf</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -8798,7 +9381,7 @@
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9289662.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20I_1.pdf</t>
         </is>
       </c>
     </row>
@@ -8815,7 +9398,7 @@
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum_USI.pdf</t>
+          <t>Draft RFP UHI_4.pdf</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -8825,7 +9408,7 @@
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_USI.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Draft%20RFP%20UHI_4.pdf</t>
         </is>
       </c>
     </row>
@@ -8842,7 +9425,7 @@
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>EMPANELMENT OF AGENCIES FOR PREPARATION OF INTEGRATED STATE URBAN CLIMATE ACTION PLANS AND CONTEXTUALISED CITY CLIMATE ACTION PLANS UNDER COMPONENT 2 OF CITIIS 2.0.pdf</t>
+          <t>GeM-Bidding-9289662.pdf</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -8852,7 +9435,7 @@
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EMPANELMENT%20OF%20AGENCIES%20FOR%20PREPARATION%20OF%20INTEGRATED%20STATE%20URBAN%20CLIMATE%20ACTION%20PLANS%20AND%20CONTEXTUALISED%20CITY%20CLIMATE%20ACTION%20PLANS%20UNDER%20COMPONENT%202%20OF%20CITIIS%202.0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9289662.pdf</t>
         </is>
       </c>
     </row>
@@ -8869,7 +9452,7 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Extension_of_Dates_citiis.pdf</t>
+          <t>Corrigendum_USI.pdf</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -8879,7 +9462,7 @@
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension_of_Dates_citiis.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum_USI.pdf</t>
         </is>
       </c>
     </row>
@@ -8896,7 +9479,7 @@
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum - I.pdf</t>
+          <t>EMPANELMENT OF AGENCIES FOR PREPARATION OF INTEGRATED STATE URBAN CLIMATE ACTION PLANS AND CONTEXTUALISED CITY CLIMATE ACTION PLANS UNDER COMPONENT 2 OF CITIIS 2.0.pdf</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
@@ -8906,7 +9489,7 @@
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20I_0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/EMPANELMENT%20OF%20AGENCIES%20FOR%20PREPARATION%20OF%20INTEGRATED%20STATE%20URBAN%20CLIMATE%20ACTION%20PLANS%20AND%20CONTEXTUALISED%20CITY%20CLIMATE%20ACTION%20PLANS%20UNDER%20COMPONENT%202%20OF%20CITIIS%202.0.pdf</t>
         </is>
       </c>
     </row>
@@ -8923,7 +9506,7 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>Reply to Pre-bid Queries.pdf</t>
+          <t>Extension_of_Dates_citiis.pdf</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr"/>
@@ -8933,7 +9516,7 @@
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-bid%20Queries_0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Extension_of_Dates_citiis.pdf</t>
         </is>
       </c>
     </row>
@@ -8950,7 +9533,7 @@
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum - II.pdf</t>
+          <t>Corrigendum - I.pdf</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr"/>
@@ -8960,7 +9543,7 @@
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20II.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20I_0.pdf</t>
         </is>
       </c>
     </row>
@@ -8977,7 +9560,7 @@
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>Extension of Dates.pdf</t>
+          <t>Reply to Pre-bid Queries.pdf</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr"/>
@@ -8987,7 +9570,7 @@
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Extension%20of%20Dates_0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-bid%20Queries_0.pdf</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9587,7 @@
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>Reply to Pre-bid Queries -II.pdf</t>
+          <t>Corrigendum - II.pdf</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr"/>
@@ -9014,7 +9597,7 @@
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-bid%20Queries%20-II.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%20-%20II.pdf</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9614,7 @@
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>Tech Form 10 JV Format.pdf</t>
+          <t>Extension of Dates.pdf</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr"/>
@@ -9041,6 +9624,60 @@
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr">
         <is>
+          <t>https://niua.in/sites/default/files/tenders/Extension%20of%20Dates_0.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Reply to Pre-bid Queries -II.pdf</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="1" t="inlineStr"/>
+      <c r="G155" s="1" t="inlineStr"/>
+      <c r="H155" s="1" t="inlineStr"/>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-bid%20Queries%20-II.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>Tech Form 10 JV Format.pdf</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="1" t="inlineStr"/>
+      <c r="G156" s="1" t="inlineStr"/>
+      <c r="H156" s="1" t="inlineStr"/>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
           <t>https://niua.in/sites/default/files/tenders/Tech%20Form%2010%20JV%20Format.pdf</t>
         </is>
       </c>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,895 +489,10 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and ...</t>
+          <t>SoW for Hiring an External Agency for Orientation and Capacity Building</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | India
-RFP - For Provision, Deployment &amp; Support of Next-Generation Firewall and Enterprise Wireless Access Points, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tende ... Read More</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303512</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-...</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Bhadrak, Odisha, Unnao, Uttar Pradesh
-RFP - Endline Evaluation of “Demonstrating Change in the Lives of Climate-Change Affected Vulnerable Communities”, WaterAid India(Bhadrak, Odisha, Unnao) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Pre-bid Queries:
-By 15 September 2026
-Last Date for Submission of Proposal:
-16 September 2026
-Expected Agency Selection and Onboarding:
-By 25 September 2026
-About WaterAid India
-Jal Seva Charitable Foundation (JSCF) is registered in India as a not-for-profit company under Chapter 8 of the Companies Act, 2013. JSCF, is an associate member of the WaterAid federation and uses the brand name ‘WaterAid’ in India.
-WaterAid India seeks to improve the quality of life of 5,000,000 households – with a special emphasis on the vulnerable by 2029 through the provision of climate-resilient and sustainable WASH services via demonstration, institution strengthening, and the effective utilization of public resources. We work in rural and urban areas and seek to deepen our resence in states we operate in and to work in small towns. Thanks to our amazing supporters, we have reached millions of people with these three essentials – clean water, decent toilets, and good hygiene – enabling communities to unlock their potential to break free from the cycle of poverty and to change lives for good.
-We will not stop. Not until clean water, decent toilets and good hygiene are a normal part of everyday life for everyone, everywhere.
-WaterAid India’s (WAI) country office is based in New Delhi with State Offices in Bengaluru, Bhopal, Bhubaneswar, Hyderabad, Lucknow, Patna, Kolkata and Raipur. We currently have a presence in ten states in the country.
-WAI’s Programme focus in the next five years is on ensuring access to safe and assured drinking water in the households, as well as safely managed sanitation at both the household and habitation level. Further, we seek to ensure that anganwadis, schools and health care facilities have adequate and appropriate water, sanitation and hygiene infrastructure. Finally, we seek to create integrated water and sanitation solutions in small towns. In all these efforts, ensuring climate resilience of infrastructure and systems is critical. We seek to do this through demonstration and the provision of technical and knowledge support to governments at all levels who can facilitate adoption on scale. Implementation is primarily through our own field teams.
-Further details about WAI can be accessed at
-https://www.wateraid.org/in/
-Background of the Assignment
-WaterAid India has been implementing the project
-“Demonstrating Change in the Lives of Climate-Change Affected Vulnerable Communities”
-in Bhadrak district of Odisha and Unnao district of Uttar Pradesh.
-The project, being implemented from October 2023 to September 2026, focuses on demonstrating and strengthening climate-resilient Water, Sanitation and Hygiene (WASH) approaches in geographies affected by different climate vulnerabilities. The programme covers
-10 Gram Panchayats and 36 villages across the two states.
-As the project approaches completion, WaterAid India invites proposals from
-experienced and qualified agencies
-to undertake an independent endline evaluation.
-Purpose of the Assignment
-The endline evaluation will assess the extent to which the project has achieved its intended outcomes and contributed to sustainable improvements in WASH services, practices, systems and institutional capacities.
-The evaluation is expected to examine the
-relevance, coherence, effectiveness, efficiency, impact and sustainability
-of the interventions and assess changes against available baseline information. It will also generate evidence on what worked, what did not, sustainability of the demonstrated approaches, and opportunities for replication and scale.
-• Broad Scope of Work
-The selected agency will undertake an independent endline evaluation covering the project locations in
-Bhadrak, Odisha and Unnao, Uttar Pradesh
-.
-The assignment will involve a mixed-method assessment drawing on quantitative and qualitative approaches. This is expected to include household surveys, assessment of WASH facilities and infrastructure, knowledge/practice assessments, key informant interviews, focus group discussions, review of relevant project and institutional records, and analysis of available water-quality information.
-The agency will be expected to undertake appropriate sampling, develop/finalise study tools in consultation with WaterAid India, manage field data collection and quality assurance, analyse quantitative and qualitative data, compare relevant findings with the baseline, and develop clear evidence-based conclusions and recommendations.
-• The detailed Terms of Reference (TOR), attached with this advertisement, provides the complete scope of the assignment, evaluation questions, endline indicators, methodology, sampling expectations, deliverables, timelines and selection criteria. Applicants are requested to review the TOR carefully before submitting their proposals.
-Key Deliverables
-The selected agency will be responsible for delivering an inception report and study design, finalised data-collection tools, tabulation and analysis plan, clean/raw and process datasets, draft evaluation report, and a final endline evaluation report along with presentation of the findings.
-The detailed requirements and timelines for each deliverable are provided in the attached TOR.
-• Who Can Apply
-WaterAid India invites applications from
-agencies with demonstrated experience in monitoring, evaluation, research, surveys and assessment assignments
-, preferably with substantial experience in the WASH and development sectors.
-Applicants should have the technical and field capacity to undertake a multi-state evaluation involving quantitative and qualitative research and should be able to deploy suitably qualified personnel within the required timeframe.
-Proposal Submission
-Interested agencies should submit
-separate Technical and Financial Proposals
-.
-The Technical Proposal should demonstrate the agency's understanding of the assignment and include the proposed approach and methodology, sampling approach, work plan and timeline, proposed team structure and CVs of key personnel, organisational experience, and examples of relevant assignments. Documentary evidence supporting relevant organisational experience should be provided.
-The Financial Proposal should clearly present the professional fees and all other costs associated with completing the assignment, including fieldwork, travel, data collection, analysis, reporting and applicable taxes, as relevant.
-Applicants are strongly advised to refer to the
-attached detailed TOR
-while preparing both the Technical and Financial Proposals.
-• Selection Process
-The agency will be selected through a
-Quality and Cost Based Selection (QCBS)
-process. The Technical Proposal will carry
-70% weightage
-and the Financial Proposal
-30% weightage
-. Only agencies obtaining the minimum qualifying technical score will proceed to financial evaluation.
-Shortlisted agencies may be invited to make a presentation of their proposal and interact with the evaluation committee as part of the technical assessment.
-• Detailed technical and financial evaluation criteria are provided in the attached TOR.
-Important Dates
-• Pre-bid queries:
-By
-15 September 2026
-Last date for submission of proposals:
-By
-16 September 2026
-Agency selection and onboarding:
-By
-25 September 2026
-Submission of Proposal
-• All pre-bid queries and completed proposals should be submitted by email to:
-waiprocurementorissa@wateraid.org
-Email Subject:
-“RFP – Endline Evaluation of Demonstrating Change in the Lives of Climate-Change Affected Vulnerable Communities”
-The application should contain both the
-Technical Proposal and Financial Proposal
-, along with the supporting documents specified in the TOR.
-Both the technical and financial proposals must be in the letterhead of the organisation and should be addressed to Jal Seva Charitable Foundation.
-Incomplete proposals or proposals received after 16
-th
-September 2026 will not be considered. WaterAid India reserves the right to seek clarification or additional information from applicants during the evaluation process.
-Download Attachment:
-TOR endline evaluation.docx
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-16 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303358</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Standardisation and Development of Community Training Modules and Fa...</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-ToR - Standardisation and Development of Community Training Modules and Facilitator Manuals for WASH-Secure Communities, WaterAid India() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-| ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• Evaluation Criteria
-Selection will follow a
-Quality and Cost Based Selection (QCBS)
-process.
-Technical Evaluation (80 Marks)
-Criteria
-Marks
-Understanding   of assignment
-15
-Methodology   and technical approach
-20
-Relevant   organisational experience
-15
-Experience of   proposed team members
-20
-Quality of   previous work samples
-10
-Total   Technical Score
-80
-Only bidders scoring
-60 marks or above
-in the technical evaluation will qualify for financial evaluation.
-Financial Evaluation (20 Marks)
-The lowest evaluated financial proposal will receive the maximum score of 20, while other proposals will be scored proportionately.
-Final Score
-Final Score = Technical Score (80%) + Financial Score (20%)
-The consultant/agency obtaining the highest combined score will be recommended for award.
-Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
-th
-September by 5:30 pm
-For detailed information, please check the complete version of the ToR attached below.
-• Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
-Download Attachment:
-TOR for Standardisation of Modules.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-16 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303298</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Development of WaterAid India's Hygiene Framework, Community Facilit...</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-ToR - Development of WaterAid India's Hygiene Framework, Community Facilitator Toolkit, Hygiene Booklet and Hygiene Calendar, WaterAid India() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Log ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• Evaluation Criteria
-Criteria
-Weight
-Understanding   of assignment
-20%
-Proposed   methodology
-25%
-Relevant   organisational experience
-20%
-Team   composition and expertise
-20%
-Financial   proposal
-15%
-Proposal Submission Timeline- Submit Technical and Financial Proposals by 16
-th
-September by 5:30 pm
-For detailed information, please check the complete version of the ToR attached below.
-• Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
-Download Attachment:
-TOR for Hygiene Tool kit and framework.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-16 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>16-09-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303297</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Master Composter Training to Strengthen Composting Practices in Ukrainian Communities</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>TheZero Waste Academyis a learning platform focused on sharing practical knowledge and approaches related to waste prevention, resource efficiency and circular economy practices. Through educational programmes, the platform connects participants with experts and practical experiences that can be ada ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>The programme is open to participants fromUkrainewho are interested in composting and bio-waste management. Eligible participants can include Ukrainian communities, civil society organisations, institutions, community initiatives and individuals. People with existing composting experience as well as those planning to introduce composting at home, within an organisation or at community level can participate. Applicants do not necessarily need to already operate a composting programme. The course is suitable for people who want to gain practical knowledge and apply composting and circular-economy approaches within their communities or organisations.</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>16 September 2026</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/master-composter-training-to-strengthen-composting-practices-in-ukrainian-communities/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for SVRI Research Grant 2027 – Data to Evidence Grant</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>TheSexual Violence Research Initiative (SVRI)is a global organisation dedicated to strengthening research on violence against women, child sexual violence and other forms of gender-based violence, particularly in low- and middle-income countries. SVRI supports locally led, ethically rigorous and act ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>The lead applicant must be based at anLMIC-based university, research institution or NGO. Independent consultants and individuals without institutional affiliation, as well as applicants affiliated with for-profit companies, are not eligible. The proposed dataset must have been ethically sourced, and applicants must have the necessary permission and approval to access and analyse it. The lead applicant cannot currently hold another active SVRI research grant or have previously received an SVRI grant. However, an institution whose previous SVRI grant has ended may apply. Applicants must be based in a country classified as low-, lower-middle- or upper-middle-income under the applicable World Bank classification.</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>17 September 2026</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-svri-research-grant-2027-data-to-evidence-grant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>SoW for Hiring an External Agency for Orientation and Capacity Building</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | Jharkhand
 SoW for Hiring an External Agency for Orientation and Capacity Building, Room to Read India() | DevNetJobsIndia
@@ -1399,7 +514,7 @@
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SoW)
 for
@@ -1480,6 +595,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -1516,12 +637,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -1543,54 +658,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1621,218 +736,263 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>17-09-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303276</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for SVRI Research Grant 2027 – Data to Evidence Grant</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>TheSexual Violence Research Initiative (SVRI)is a global organisation dedicated to strengthening research on violence against women, child sexual violence and other forms of gender-based violence, particularly in low- and middle-income countries. SVRI supports locally led, ethically rigorous and act ... Read More</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The lead applicant must be based at anLMIC-based university, research institution or NGO. Independent consultants and individuals without institutional affiliation, as well as applicants affiliated with for-profit companies, are not eligible. The proposed dataset must have been ethically sourced, and applicants must have the necessary permission and approval to access and analyse it. The lead applicant cannot currently hold another active SVRI research grant or have previously received an SVRI grant. However, an institution whose previous SVRI grant has ended may apply. Applicants must be based in a country classified as low-, lower-middle- or upper-middle-income under the applicable World Bank classification.</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>17 September 2026</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-invited-for-svri-research-grant-2027-data-to-evidence-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>WFP SDS Microgrant Programme 2026: Apply for Up to $5,000 in Farmer Grants</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>TheUnited Nations World Food Programme (WFP)is a leading humanitarian organization working worldwide to combat hunger, strengthen food security, and support vulnerable communities. For this initiative, WFP is partnering with the NGOSouthern Development Strategy (SDS)to provide targeted financial ass ... Read More</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TheWFP SDS Microgrant Programmeprovides financial assistance to farmers and small-scale producers in Ukraine who are already engaged in agricultural production or related activities. Theseagricultural grantsare designed to help existing enterprises recover, strengthen production, purchase essential equipment or materials, and contribute to sustainable community development. Eligible activities include crop cultivation, livestock production, beekeeping, food processing, and fish farming. Microgrants are available at three levels US$1,500, US$3,000, and US$5,000. The final amount is determined by a selection committee after reviewing the application and, for shortlisted applicants, conducting a verification visit.</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Agriculture &amp; Rural</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>18 September 2026</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303276</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/https-andpurpose-world-wfp-sds-microgrant-programme-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Applications Invited for the Wellcome Prize for Mental Health Science with Nature</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Wellcomeis a global charitable foundation supporting science to solve urgent health challenges. Its work includes discovery research into life, health and wellbeing, with mental health among its major global priorities.Natureis an international scientific publication known for publishing rigorous re ... Read More</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Research teams should select a lead applicant and complete the official online application form. Applications are open for self-submission, so formal nomination is not required. Applicants should demonstrate the intervention’s novelty, scientific credibility, measurable clinical benefit and potential for adoption. Teams should also explain how the intervention was developed and provide evidence supporting its clinical effectiveness. The application must be complete and submitted online by the official closing time.</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>18 September 2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>https://andpurpose.world/applications-invited-for-the-wellcome-prize-for-mental-health-science-with-nature/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Nominations Open for Italian Bilateral Scientific Cooperation Award (US)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Italian Ministry of Foreign Affairs and International Cooperation (MAECI) TheItalian Ministry of Foreign Affairs and International Cooperation (MAECI)is responsible for Italy’s foreign relations and international cooperation. The Ministry works to strengthen Italy’s diplomatic, cultural, economic an ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>The application deadline is 18 September 2026</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>18 September 2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>https://andpurpose.world/nominations-open-for-italian-bilateral-scientific-cooperation-award-us/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Call for Proposals: Labour Service Organisations Training Vulnerable Workers (South Africa)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>TheSouth African Department of Employment and Labouris a national government department responsible for promoting decent employment, protecting workers’ rights and supporting fair and safe labour practices across South Africa. Its responsibilities include administering and implementing labour legisl ... Read More</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>The application deadline is 18 September 2026</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>18 September 2026</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://andpurpose.world/call-for-proposals-labour-service-organisations-training-vulnerable-workers-south-africa/</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>WFP SDS Microgrant Programme 2026: Apply for Up to $5,000 in Farmer Grants</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>TheUnited Nations World Food Programme (WFP)is a leading humanitarian organization working worldwide to combat hunger, strengthen food security, and support vulnerable communities. For this initiative, WFP is partnering with the NGOSouthern Development Strategy (SDS)to provide targeted financial ass ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>TheWFP SDS Microgrant Programmeprovides financial assistance to farmers and small-scale producers in Ukraine who are already engaged in agricultural production or related activities. Theseagricultural grantsare designed to help existing enterprises recover, strengthen production, purchase essential equipment or materials, and contribute to sustainable community development. Eligible activities include crop cultivation, livestock production, beekeeping, food processing, and fish farming. Microgrants are available at three levels US$1,500, US$3,000, and US$5,000. The final amount is determined by a selection committee after reviewing the application and, for shortlisted applicants, conducting a verification visit.</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Agriculture &amp; Rural</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>18 September 2026</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/https-andpurpose-world-wfp-sds-microgrant-programme-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>RFQ - Spring and Dugwell Based Piped Water Supply Scheme (PWSS)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>WaterAid India | Jagatpur, Dindori, Madhya Pradesh
 RFQ - Spring and Dugwell Based Piped Water Supply Scheme (PWSS), WaterAid India(Jagatpur, Dindori) | DevNetJobsIndia
@@ -1853,7 +1013,7 @@
 Jo ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 WAIProcurementMP(at)wateraid.org
@@ -1869,6 +1029,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -1905,12 +1071,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -1932,54 +1092,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2010,38 +1170,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>19-09-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303719</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RFP - Website Transition, Hosting, Maintenance, Support and Redesign Servi...</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Plan India | India
 RFP - Website Transition, Hosting, Maintenance, Support and Redesign Services, Plan India() | DevNetJobsIndia
@@ -2064,7 +1224,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>• Bid Submission Deadline: PM 20th September 2026
 • How to apply: send proposals to
@@ -2124,6 +1284,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -2160,12 +1326,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -2187,54 +1347,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2265,38 +1425,239 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>20-09-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303530</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquife...</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Development Support Centre (DSC) | India
+ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquifer Study Using Participatory Approaches for Natural Resource, Watershed..., Development Support Centre (DSC)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broad ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+cpc.dsc(at)gmail.com
+Download Attachment:
+DSC-Geohydrology Study ToR.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+20 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
+India HIV/AIDS Alliance (Alliance India)
+Location:
+Manipur
+Apply by:
+27 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303378</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RFP - Individual Consultant / Firm Engagement: TN Energy Audits</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>World Resources Institute India (WRI India) | Tamil Nadu
 RFP - Individual Consultant / Firm Engagement: TN Energy Audits, World Resources Institute India (WRI India)() | DevNetJobsIndia
@@ -2314,7 +1675,7 @@
 L ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Accordingly, IRT seeks to engage a qualified and certified energy auditing firm or energy auditor (consultant) to undertake comprehensive energy audits, collect and analyse technical data, develop evidence-based recommendations, and prepare detailed technical reports and implementation guidance in accordance with the scope of work outlined in this Terms of Reference.
 2.         Objectives of the Consultancy
@@ -2356,6 +1717,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -2392,12 +1759,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -2419,54 +1780,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2497,66 +1858,93 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Climate</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>20-09-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303143</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquife...</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Development Support Centre (DSC) | India
-ToR - Hiring of Technical Consultant/Agency for Hydrogeological and Aquifer Study Using Participatory Approaches for Natural Resource, Watershed..., Development Support Centre (DSC)() | DevNetJobsIndia
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Procurement of IT Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | India
+RFP - Procurement of IT Equipment and Accessories, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broad ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-cpc.dsc(at)gmail.com
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• Interested bidders meeting the preliminary examination and technical evaluation criteria are invited to submit Financial Proposals in accordance with the requirements outlined in this Request for Proposal (RFP).
+2. About India HIV/AIDS Alliance
+India HIV/AIDS Alliance (Alliance India) is a leading non-government organization dedicated to strengthening India's response to HIV/AIDS, public health, and community systems. Through partnerships with government agencies, civil society organizations, community-based organizations, donors, and development partners, Alliance India works to improve equitable access to quality healthcare services for vulnerable and key populations.
+Alliance India implements programmes across multiple states through technical assistance, capacity building, advocacy, research, procurement support, and programme management while maintaining the highest standards of governance, transparency, and financial accountability
+3. Objective of the Procurement
+The objective of this procurement is to identify one or more technically qualified and financially capable suppliers for the supply of high-quality IT equipment and accessories to support programme implementation across multiple locations in India.
+4. Submission Process
+Proposals shall be submitted electronically to
+procurement1@allianceindia.org
+on or before the deadline mentioned in this RFP.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+procurement1(at)allianceindia.org
 Download Attachment:
-DSC-Geohydrology Study ToR.pdf
+RFP_Procurement_of_IT_Equipment.doc
+Download Attachment:
+Corrigendum No. 1 &amp; 2.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-20 Sep 2026
+21 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -2593,12 +1981,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -2620,54 +2002,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2698,521 +2080,83 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>20-09-2026</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>21-09-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303378</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303414</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Submit Applications for Homelessness Prevention Grants (UK)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge City Councilis the local authority responsible for delivering public services and supporting communities across Cambridge, United Kingdom. The Council works with voluntary, community, and partner organisations to address local challenges including homelessness, rough sleeping, housing inse ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Applications are open tovoluntary and community organisationsworking to prevent or relieve homelessness and rough sleeping in Cambridge. Applicants should have appropriate governance arrangements, financial controls, and the organisational capacity to manage public funding responsibly. Projects must benefit people in Cambridge and directly contribute to homelessness prevention or relief. Applicants should demonstrate a clear understanding of local homelessness needs, explain why funding is required, and show how activities and outcomes will be monitored and measured. The Council may also require supporting documents such as accounts, organisational budgets, governing documents, insurance certificates, risk assessments, and relevant organisational policies.</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>22 September 2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/submit-applications-for-homelessness-prevention-grants-uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Procurement of IT Equipment and Accessories</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | India
-RFP - Procurement of IT Equipment and Accessories, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>• Interested bidders meeting the preliminary examination and technical evaluation criteria are invited to submit Financial Proposals in accordance with the requirements outlined in this Request for Proposal (RFP).
-2. About India HIV/AIDS Alliance
-India HIV/AIDS Alliance (Alliance India) is a leading non-government organization dedicated to strengthening India's response to HIV/AIDS, public health, and community systems. Through partnerships with government agencies, civil society organizations, community-based organizations, donors, and development partners, Alliance India works to improve equitable access to quality healthcare services for vulnerable and key populations.
-Alliance India implements programmes across multiple states through technical assistance, capacity building, advocacy, research, procurement support, and programme management while maintaining the highest standards of governance, transparency, and financial accountability
-3. Objective of the Procurement
-The objective of this procurement is to identify one or more technically qualified and financially capable suppliers for the supply of high-quality IT equipment and accessories to support programme implementation across multiple locations in India.
-4. Submission Process
-Proposals shall be submitted electronically to
-procurement1@allianceindia.org
-on or before the deadline mentioned in this RFP.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-procurement1(at)allianceindia.org
-Download Attachment:
-RFP_Procurement_of_IT_Equipment.doc
-Download Attachment:
-Corrigendum No. 1 &amp; 2.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-21 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303414</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>Submit Applications for Homelessness Prevention Grants (UK)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Cambridge City Councilis the local authority responsible for delivering public services and supporting communities across Cambridge, United Kingdom. The Council works with voluntary, community, and partner organisations to address local challenges including homelessness, rough sleeping, housing inse ... Read More</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Applications are open tovoluntary and community organisationsworking to prevent or relieve homelessness and rough sleeping in Cambridge. Applicants should have appropriate governance arrangements, financial controls, and the organisational capacity to manage public funding responsibly. Projects must benefit people in Cambridge and directly contribute to homelessness prevention or relief. Applicants should demonstrate a clear understanding of local homelessness needs, explain why funding is required, and show how activities and outcomes will be monitored and measured. The Council may also require supporting documents such as accounts, organisational budgets, governing documents, insurance certificates, risk assessments, and relevant organisational policies.</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>22 September 2026</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/submit-applications-for-homelessness-prevention-grants-uk/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>RPF-for Development of a Module on Social Media Marketing, Customer Engage...</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>People’s Rural Education Movement (PREM) | Odisha
-RPF-for Development of a Module on Social Media Marketing, Customer Engagement and Business Strategy for (WSHG) Members of Mission Shakti, People’s Rural Education Movement (PREM)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membershi ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-The assignment will comprise the following stages.
-4.1
-Review and Design of the Module
-The agency shall:
-Review the existing Social Media Training Module and Social Media Skilling Framework.
-Map existing competencies against the proposed business and marketing competencies to ensure complementarity and avoid duplication.
-Identify key gaps and barriers in translating social media presence and engagement into business outcomes.
-Develop the overall framework, learning architecture and outline for the second module.
-Ensure relevance to WSHG members with varying levels of digital literacy and enterprise experience.
-Submission Instructions:
-The Agency should have to submit Technical Proposal (must include supporting documents to justify the Required Criteria for the Bidder) and Financial Proposal (In the provided Template only) in separate email to
-procurement.prem@gmail.com
-with the Mandatory Subject line of the e-mail as e.g. “Technical Proposal–Bidder Name- RFP NO/RFP/2026/004- "Development of a Module on Social Media Marketing" by 23rd Sep 2026, 23:59 Hrs.
-Note: Technical &amp; Financial Proposal to be submitted in separate email.
-• # Bids that do not contain the correct email subject line, contain Technical &amp; Financial Proposal in a single email, Any Financial Quote in the Technical proposal or submission of bid post to the above timelines may not be considered for further processing.
-# Any Bid submitted will be regarded as an offer by the bidder and does not constitute or imply the acceptance of any quotation by PREM. PREM is under no obligation to award a contract to any bidder as a result of this RFP.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-PREM-RFQ_Module on Social Media Marketing-MS (1) (1).doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-23 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303781</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>RFP - Knowledge and Learning Partner</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Digital Green India | India
 RFP - Knowledge and Learning Partner, Digital Green India() | DevNetJobsIndia
@@ -3237,7 +2181,7 @@
 RFP - Knowle ... Read More</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Legal status:
@@ -3284,6 +2228,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -3320,12 +2270,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -3347,54 +2291,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3425,22 +2369,989 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303695</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Apply for DBT BioCARe Programme 2026–27 for Women Researchers</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>The Department of Biotechnology (DBT), under the Ministry of Science and Technology, Government of India, supports research, innovation and human-resource development in biotechnology and allied scientific disciplines. DBT works to strengthen India’s biotechnology ecosystem by funding research, deve ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The Department of Biotechnology (DBT), under the Ministry of Science and Technology, Government of India, supports research, innovation and human-resource development in biotechnology and allied scientific disciplines. DBT works to strengthen India’s biotechnology ecosystem by funding research, developing scientific talent and encouraging technological applications in areas relevant to health, agriculture, environment and industry. Through programmes such as BioCARe, the department also seeks to improve participation of women researchers in scientific research careers. The DBT BioCARe Programme provides opportunities for eligible women researchers to develop independent research projects and strengthen their careers in biotechnology, life sciences and related interdisciplinary fields.</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Women &amp; Gender</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>23 September 2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-dbt-biocare-programme-2026-27-for-women-researchers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>RPF-for Development of a Module on Social Media Marketing, Customer Engage...</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>People’s Rural Education Movement (PREM) | Odisha
+RPF-for Development of a Module on Social Media Marketing, Customer Engagement and Business Strategy for (WSHG) Members of Mission Shakti, People’s Rural Education Movement (PREM)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membershi ... Read More</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>• Scope of Work
+The assignment will comprise the following stages.
+4.1
+Review and Design of the Module
+The agency shall:
+Review the existing Social Media Training Module and Social Media Skilling Framework.
+Map existing competencies against the proposed business and marketing competencies to ensure complementarity and avoid duplication.
+Identify key gaps and barriers in translating social media presence and engagement into business outcomes.
+Develop the overall framework, learning architecture and outline for the second module.
+Ensure relevance to WSHG members with varying levels of digital literacy and enterprise experience.
+Submission Instructions:
+The Agency should have to submit Technical Proposal (must include supporting documents to justify the Required Criteria for the Bidder) and Financial Proposal (In the provided Template only) in separate email to
+procurement.prem@gmail.com
+with the Mandatory Subject line of the e-mail as e.g. “Technical Proposal–Bidder Name- RFP NO/RFP/2026/004- "Development of a Module on Social Media Marketing" by 23rd Sep 2026, 23:59 Hrs.
+Note: Technical &amp; Financial Proposal to be submitted in separate email.
+• # Bids that do not contain the correct email subject line, contain Technical &amp; Financial Proposal in a single email, Any Financial Quote in the Technical proposal or submission of bid post to the above timelines may not be considered for further processing.
+# Any Bid submitted will be regarded as an offer by the bidder and does not constitute or imply the acceptance of any quotation by PREM. PREM is under no obligation to award a contract to any bidder as a result of this RFP.
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+PREM-RFQ_Module on Social Media Marketing-MS (1) (1).doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+23 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
+India HIV/AIDS Alliance (Alliance India)
+Location:
+Manipur
+Apply by:
+27 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303781</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Digital Commerce, Brand Identity &amp; Social Media Enablement — Bhoomga...</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Development Support Centre (DSC) | Dantewada, Chhattisgarh
+RFP - Digital Commerce, Brand Identity &amp; Social Media Enablement — Bhoomgaadi Organic Farmers Producer Company Ltd, Dantewada, Chhattisgarh, Development Support Centre (DSC)(Dantewada) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Val ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• 2. Eligibility
+—
+pass/fail gate
+Valid GST registration and a registered office address anywhere in India, with documentary proof. There is no state restriction on who may apply.
+Minimum 3 years in digital marketing, branding or e-commerce enablement, with a portfolio — mandatory.
+At least one live e-commerce website built or managed by the applicant (URL), and three published reels (links).
+Named individuals who will do the work, with CVs. Hindi essential; Halbi or Gondi an advantage. FPO, agri or organic experience preferred, not mandatory. Applicants able to reach Dantewada easily, or with a presence in Chhattisgarh or a nearby state, get additional preference at evaluation — but this is a preference, not a condition. DSC wants a compact, agile team, not a large agency.
+• How to Apply
+One email, all attachments, by the deadline. Incomplete submissions may be rejected without correspondence.
+Profile with GST certificate and registered office proof. (2) Portfolio — at least one live e-commerce URL and three reel links. (3) Methodology and execution plan, including the approach to field visits and to farmer, Millet Sisters and ecopreneur stories. (4) CVs of the people who will do the work. (5) Financial proposal as a separate document, workstream-wise, field visit cost shown separately, with the inclusions and exclusions statement. (6) Proposed monthly targets for the two accountable measures in Section 8. (7) Signed acceptance of the mandatory conditions in Section 4.
+Submissions
+dscmiraclemillet@gmail.com
+(cc:
+dsc@dscindia.org
+)
+Subject line
+RFP Response –   Digital Marketing – Dantewada, Chhattisgarh
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+DSC_RFP_Digital_Marketing_Dantewada.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+25 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
+India HIV/AIDS Alliance (Alliance India)
+Location:
+Manipur
+Apply by:
+27 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303818</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>25 September 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
+RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Se ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• SCOPE OF WORK
+• The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
+TAF will facilitate access to the baseline survey tool, the January 2025 baseline report, the deidentified baseline dataset, and government permissions; these materials, along with any other tools and de-identified datasets, will be shared only with the selected study partner. The study partner will be responsible for adapting the instruments, and for fielding, analysing, and reporting the endline round.
+Key deliverables
+will include an inception report, IRB approval documentation, cleaned quantitative and qualitative datasets, a draft endline report, a final endline report, and a presentation of findings to TAF (see Annex 1, Section VI).
+SUBMISSION
+All proposals and queries should be sent to
+TAF_MnE@antarafoundation.org
+and cc to
+puneet.naithani@antarafoundation.org
+with the subject line
+"Damoh Endline Evaluation proposal || Organisation name".
+Queries will be accepted until the deadline stated on the cover page; responses to queries (RFQ) will be shared with all prospective applicants by the date indicated.
+For detailed information, please check the complete version of the RFP attached below
+Download Attachment:
+Damoh_Endline_RFP_TAF.pdf
+Download Attachment:
+RFQ_Clarifications.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+25 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
+India HIV/AIDS Alliance (Alliance India)
+Location:
+Manipur
+Apply by:
+27 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Development of Sports Ground with Multi Game Court in CGIC ,Tikri,Va...</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Plan India | Tikri,Varanasi, Uttar Pradesh
+RFP - Development of Sports Ground with Multi Game Court in CGIC ,Tikri,Varanasi ,UP, Plan India(Tikri,Varanasi) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regis ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Bid Submission Deadline:
+25
+th
+September 2026.
+• How to apply : send proposal to Plan India in the Big /one envelope:
+• Bid Submission Address *
+only sealed bids with subject line
+a) Technical Proposal (in BOQ attached along with the Documents )
+b) Financial Proposal
+Procurement Department
+Plan International (India Chapter)
+1, Zamrudpur Community Centre, Kailash Colony
+New Delhi – 110048
+Email for Clarifications:
+procurement@planindia.org
+• Plan India reserves the rights to alter the terms &amp; conditions and alteration on Scope of Work.
+Plan India reserves the right to accept/ reject the quotation without assigning the reason whatsoever.
+Issued By
+Plan International (India Chapter)
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+RFP -Developing Sports Ground Tikri -Varanasi -UP ..doc
+Download Attachment:
+BOQ-Tikri School Multisport Game Court (1).xls
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+25 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
+India HIV/AIDS Alliance (Alliance India)
+Location:
+Manipur
+Apply by:
+27 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303695</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303760</t>
         </is>
       </c>
     </row>
@@ -3584,6 +3495,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -3620,12 +3537,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -3647,54 +3558,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3736,7 +3647,7 @@
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -3753,498 +3664,10 @@
       <c r="B22" s="1" t="inlineStr"/>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>RFP - Development of Sports Ground with Multi Game Court in CGIC ,Tikri,Va...</t>
+          <t>RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Proj...</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Plan India | Tikri,Varanasi, Uttar Pradesh
-RFP - Development of Sports Ground with Multi Game Court in CGIC ,Tikri,Varanasi ,UP, Plan India(Tikri,Varanasi) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>• Bid Submission Deadline:
-25
-th
-September 2026.
-• How to apply : send proposal to Plan India in the Big /one envelope:
-• Bid Submission Address *
-only sealed bids with subject line
-a) Technical Proposal (in BOQ attached along with the Documents )
-b) Financial Proposal
-Procurement Department
-Plan International (India Chapter)
-1, Zamrudpur Community Centre, Kailash Colony
-New Delhi – 110048
-Email for Clarifications:
-procurement@planindia.org
-• Plan India reserves the rights to alter the terms &amp; conditions and alteration on Scope of Work.
-Plan India reserves the right to accept/ reject the quotation without assigning the reason whatsoever.
-Issued By
-Plan International (India Chapter)
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-RFP -Developing Sports Ground Tikri -Varanasi -UP ..doc
-Download Attachment:
-BOQ-Tikri School Multisport Game Court (1).xls
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-25 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303760</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
-RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Se ... Read More</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>• SCOPE OF WORK
-• The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
-TAF will facilitate access to the baseline survey tool, the January 2025 baseline report, the deidentified baseline dataset, and government permissions; these materials, along with any other tools and de-identified datasets, will be shared only with the selected study partner. The study partner will be responsible for adapting the instruments, and for fielding, analysing, and reporting the endline round.
-Key deliverables
-will include an inception report, IRB approval documentation, cleaned quantitative and qualitative datasets, a draft endline report, a final endline report, and a presentation of findings to TAF (see Annex 1, Section VI).
-SUBMISSION
-All proposals and queries should be sent to
-TAF_MnE@antarafoundation.org
-and cc to
-puneet.naithani@antarafoundation.org
-with the subject line
-"Damoh Endline Evaluation proposal || Organisation name".
-Queries will be accepted until the deadline stated on the cover page; responses to queries (RFQ) will be shared with all prospective applicants by the date indicated.
-For detailed information, please check the complete version of the RFP attached below
-Download Attachment:
-Damoh_Endline_RFP_TAF.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-25 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Program Manager – ITI and Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-Resource Person – Bangalore
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-Manager - Programs – Persons with Disability
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-18 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
-Location:
-Jharkhand
-Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
-India HIV/AIDS Alliance (Alliance India)
-Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>25 September 2026</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Proj...</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Aga Khan Foundation (India) | Bihar
 RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Project Dhenu Dhara – Foraging pathways to improving livestock health and dairy , Aga Khan Foundation (India)() | DevNetJobsIndia
@@ -4257,7 +3680,7 @@
 Broadcast Re ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• Bidders may alter or withdraw their bids by written notification prior to the stated deadline for submission of bids. No bids may be altered after this deadline. Withdrawals must be unconditional and will end all participation in the bid procedure.
 6. Opening of bid
@@ -4335,6 +3758,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -4371,12 +3800,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -4398,54 +3821,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4476,38 +3899,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>28-09-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303730</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>RFP - for Final Evaluation of Support Micro/Small entrepreneurs among part...</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe e.V | India
 RFP - for Final Evaluation of Support Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans, Deutsche Welthungerhilfe e.V() | DevNetJobsIndia
@@ -4522,7 +3945,7 @@
 Searc ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION ANDCONTEXT
 Country:
@@ -4580,6 +4003,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -4616,12 +4045,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -4643,54 +4066,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4721,22 +4144,157 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 29 September 2026</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>29 September 2026</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>29 September 2026</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
+        </is>
+      </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
+          <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -4753,17 +4311,17 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+          <t>Giving Joy Microgrant 2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -4773,7 +4331,7 @@
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>29 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
@@ -4781,7 +4339,7 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
         </is>
       </c>
     </row>
@@ -4798,27 +4356,27 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 29 September 2026</t>
+          <t>The application deadline is30 September 2026</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>29 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
@@ -4826,7 +4384,7 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
+          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
         </is>
       </c>
     </row>
@@ -4843,17 +4401,17 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Green Box Artist in Residency Program</t>
+          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -4867,11 +4425,11 @@
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
+          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
         </is>
       </c>
     </row>
@@ -4888,17 +4446,17 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Giving Joy Microgrant 2026</t>
+          <t>Apply for Greenprint GET Breakthrough Innovation Award 2027 for Indian Startups</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent policy research institution working on energy, environment, climate and sustainable development issues in India and beyond. CEEW brings together research, policy engagement and partnerships to support evidence-based solutions for ... Read More</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
+          <t>Eligible startups should apply through the Greenprint Awards application process before the closing date. Applicants should select the GET Breakthrough Innovation category and provide accurate information about their organisation, innovation, impact and contribution to the green economy. Supporting evidence should clearly demonstrate the systemic significance of the solution. Applicants should review the category requirements and terms before submitting. Only one category may be selected by each applicant. There is no entry fee for the Greenprint Awards.</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -4912,11 +4470,11 @@
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
+          <t>https://andpurpose.world/apply-for-greenprint-get-breakthrough-innovation-award/</t>
         </is>
       </c>
     </row>
@@ -4933,22 +4491,22 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
+          <t>Apply for Greenprint Art and Culture Award 2027 for Climate Storytellers</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
+          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
@@ -4957,11 +4515,11 @@
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
+          <t>https://andpurpose.world/apply-for-greenprint-art-and-culture-award-2027-for-climate-storytellers/</t>
         </is>
       </c>
     </row>
@@ -4978,22 +4536,22 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
+          <t>Applications Open for Green Box Artist in Residency Program</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
+          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is30 September 2026</t>
+          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
@@ -5002,117 +4560,27 @@
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
+          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
+          <t>ToR - Consultant for an Evidence-Based Research Study on Forest Rights Act...</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 01 October 2026</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>01 October 2026</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Consultant for an Evidence-Based Research Study on Forest Rights Act...</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Development Agency for Poor and Tribal Awakening (DAPTA) | Odisha
 ToR - Consultant for an Evidence-Based Research Study on Forest Rights Act (FRA) Implementation in Odisha, Development Agency for Poor and Tribal Awakening (DAPTA)() | DevNetJobsIndia
@@ -5124,7 +4592,7 @@
 Value Membershi ... Read More</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>• 5. Scope of Work
 The consultant will undertake the following:
@@ -5205,6 +4673,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -5241,12 +4715,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -5268,54 +4736,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5346,14 +4814,104 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>01-10-2026</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303803</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 01 October 2026</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>01 October 2026</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Apply for AMBSO Impact Research Initiative 2026: Up to USD 10,000 in Health Research Grants</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Africa Medical and Behavioral Sciences Organization (AMBSO) TheAfrica Medical and Behavioral Sciences Organization (AMBSO)is a research and health-focused organization working to advance clinical, epidemiological, social, and behavioral research across Africa. Its work includes clinical trials, popu ... Read More</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>TheAMBSO Impact Research Initiative 2026is open to eligible researchers, academic institutions, research organizations, community-based organizations, and other entities whose proposed work aligns with the initiative’s public health objectives. Doctoral students are encouraged to apply as members of research teams led by a faculty Principal Investigator. Independent researchers may apply when affiliated with an academic or research institution. Applications can come from anywhere in the world, with no geographical restriction stated by AMBSO. Proposed projects should focus on eligible priority health areas, generate useful evidence, and be feasible within the 18-month funding period. For-profit entities, political organizations, lobbying groups, and organizations primarily engaged in political advocacy are not eligible.</t>
+        </is>
+      </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>01-10-2026</t>
+          <t>2 October 2026</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -5361,113 +4919,23 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303803</t>
+          <t>https://andpurpose.world/apply-for-ambso-impact-research-initiative/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>RFAs: Expanding Global Health Security Through Local Partnerships (Ethiopia)</t>
+          <t>RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme i...</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Centers for Disease Control and Prevention (CDC) TheU.S. Centers for Disease Control and Prevention (CDC)is a leading public health agency dedicated to protecting communities from health threats through research, disease prevention, surveillance, and emergency response. Working closely with gov ... Read More</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Review the official funding announcement and verify your organization’s eligibility. Prepare a technical proposal aligned with one or more program priorities, including implementation plans, monitoring strategies, and a realistic budget. Demonstrate organizational capacity, sustainable partnerships, and measurable public health outcomes. Submit the completed application with all required supporting documents through the official application system before the closing deadline.</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>02 October 2026</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/rfas-expanding-global-health-security-through-local-partnerships-ethiopia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>Apply for AMBSO Impact Research Initiative 2026: Up to USD 10,000 in Health Research Grants</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Africa Medical and Behavioral Sciences Organization (AMBSO) TheAfrica Medical and Behavioral Sciences Organization (AMBSO)is a research and health-focused organization working to advance clinical, epidemiological, social, and behavioral research across Africa. Its work includes clinical trials, popu ... Read More</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>TheAMBSO Impact Research Initiative 2026is open to eligible researchers, academic institutions, research organizations, community-based organizations, and other entities whose proposed work aligns with the initiative’s public health objectives. Doctoral students are encouraged to apply as members of research teams led by a faculty Principal Investigator. Independent researchers may apply when affiliated with an academic or research institution. Applications can come from anywhere in the world, with no geographical restriction stated by AMBSO. Proposed projects should focus on eligible priority health areas, generate useful evidence, and be feasible within the 18-month funding period. For-profit entities, political organizations, lobbying groups, and organizations primarily engaged in political advocacy are not eligible.</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>2 October 2026</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-ambso-impact-research-initiative/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme i...</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>World Resources Institute India (WRI India) | Karnataka
 RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme in Karnataka, World Resources Institute India (WRI India)() | DevNetJobsIndia
@@ -5482,7 +4950,7 @@
 Search Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 Aprajita.Verma(at)wri.org
@@ -5498,6 +4966,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
 Lead Consultant PHEOC
 The Voluntary Health Services (VHS)
 Location:
@@ -5534,12 +5008,6 @@
 Maharashtra
 Apply by:
 30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
 Director / Associate Director: Corporate Fundrais...
 India HIV/ AIDS Alliance (Alliance India)
 Location:
@@ -5561,54 +5029,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Senior Lead, IDTS
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-District Lead
-Room to Read India
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
 Location:
 Jharkhand
 Apply by:
-16 Oct 2026
-Officer, Learning and Innovations
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-Senior Lead, Data and Evaluation
-Room to Read India
-Location:
-Delhi
-Apply by:
-16 Oct 2026
-ToR - Consultant for an Evidence-Based Research S...
-Development Agency for Poor and Tribal Awakening ...
-Location:
-Odisha
-Apply by:
-01 Oct 2026
-Selection Camp - Multiple Vacancies
-Transforming Rural India (TRI)
-Location:
-India
-Apply by:
-16 Oct 2026
-RFP - Procurement of IT Equipment and Accessories
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
 India HIV/AIDS Alliance (Alliance India)
 Location:
-India
-Apply by:
-21 Sep 2026
-District Enablers
-Illumine Knowledge Resources
-Location:
-Maharashtra
-Apply by:
-10 Oct 2026
+Manipur
+Apply by:
+27 Sep 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5639,14 +5107,104 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Electropreneur Park 2.0 Open Challenge Programme in India</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Software Technology Parks of India (STPI) is an autonomous society under theMinistry of Electronics and Information Technology (MeitY), Government of India. STPI works to strengthen India’s technology ecosystem through infrastructure, incubation, entrepreneurship and support for technology businesse ... Read More</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>TheElectropreneur Park 2.0 Open Challenge Programmeis open to students, budding entrepreneurs and startups developing innovative solutions in ESDM or cognitive computing and social sensing. Eligible applicants may include individuals at the ideation stage requiring prototype-development support, early or pre-revenue startups, prototype-stage ventures and startups with breakthrough technologies. Relevant areas include MedTech, EdTech, automotive electronics, strategic electronics, EVs, defence, drones and other ESDM applications. The programme particularly supports innovators who need access to prototyping facilities, technical mentoring, incubation, market support and funding or investment opportunities.</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-electropreneur-park-2-0-open-challenge-programme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+        </is>
+      </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>6 October 2026</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
@@ -5654,7 +5212,7 @@
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
+          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
         </is>
       </c>
     </row>
@@ -5671,27 +5229,27 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+          <t>Apply for MNRE Concentrating Solar Thermal Technology Grant 2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, d ... Read More</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, development, demonstration and deployment of renewable energy technologies through dedicated programmes. Its Renewable Energy Research and Technology Development Programme supports technology development and practical applications of renewable energy. Through this current call, MNRE is encouraging the development and deployment of concentrating solar thermal technology for Indian industries, particularly solutions capable of providing clean heat for industrial processes.</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>7 October 2026</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
@@ -5699,7 +5257,7 @@
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
+          <t>https://andpurpose.world/apply-for-prip-pharma-medtech-innovation-scheme/</t>
         </is>
       </c>
     </row>
@@ -5716,35 +5274,35 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Funding Opportunity for Civil Society Organisations to Countering Disinformation in Poland</t>
+          <t>Pfizer HRRm Testing Education Grant 2026: Apply for Up to $100,000</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>TheEEA Civil Society Fundsupports civil society organisations working to strengthen democracy, human rights, public participation, and social inclusion across eligible European countries. Through targeted funding programmes, the Fund empowers non-profit organisations to address emerging societal cha ... Read More</t>
+          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombinati ... Read More</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should prepare a proposal outlining the disinformation challenge, project objectives, planned activities, expected outcomes, implementation strategy, organisational experience, and budget. Applications should demonstrate measurable impact, sustainability, and community benefit. Ensure all legal and eligibility requirements are met before submitting the proposal according to the programme guidelines before the closing date.</t>
+          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombination Repair mutation (HRRm) testingfor metastatic prostate cancer. Through this funding opportunity, Pfizer supports practical educational initiatives that help multidisciplinary healthcare teams apply guideline-based testing approaches in clinical practice. The programme particularly emphasizes education covering pre-analytical considerations, testing-related decision-making, interpretation of results, and communication of testing information throughout the patient care pathway.</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>06 October 2026</t>
+          <t>08 October 2026</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/funding-opportunity-for-civil-society-organisations-to-countering-disinformation-in-poland/</t>
+          <t>https://andpurpose.world/pfizer-hrrm-testing-education-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -5761,17 +5319,17 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Apply for Electropreneur Park 2.0 Open Challenge Programme in India</t>
+          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Software Technology Parks of India (STPI) is an autonomous society under theMinistry of Electronics and Information Technology (MeitY), Government of India. STPI works to strengthen India’s technology ecosystem through infrastructure, incubation, entrepreneurship and support for technology businesse ... Read More</t>
+          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>TheElectropreneur Park 2.0 Open Challenge Programmeis open to students, budding entrepreneurs and startups developing innovative solutions in ESDM or cognitive computing and social sensing. Eligible applicants may include individuals at the ideation stage requiring prototype-development support, early or pre-revenue startups, prototype-stage ventures and startups with breakthrough technologies. Relevant areas include MedTech, EdTech, automotive electronics, strategic electronics, EVs, defence, drones and other ESDM applications. The programme particularly supports innovators who need access to prototyping facilities, technical mentoring, incubation, market support and funding or investment opportunities.</t>
+          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -5781,15 +5339,15 @@
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>09 October 2026</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-electropreneur-park-2-0-open-challenge-programme/</t>
+          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -5806,35 +5364,35 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Pfizer HRRm Testing Education Grant 2026: Apply for Up to $100,000</t>
+          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombinati ... Read More</t>
+          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombination Repair mutation (HRRm) testingfor metastatic prostate cancer. Through this funding opportunity, Pfizer supports practical educational initiatives that help multidisciplinary healthcare teams apply guideline-based testing approaches in clinical practice. The programme particularly emphasizes education covering pre-analytical considerations, testing-related decision-making, interpretation of results, and communication of testing information throughout the patient care pathway.</t>
+          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>08 October 2026</t>
+          <t>13 October 2026</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/pfizer-hrrm-testing-education-grant-2026/</t>
+          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -5851,17 +5409,17 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
+          <t>Applications Open for Realization of Short Animation Grant</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
+          <t>TheNetherlands Film Fundis the national agency responsible for supporting professional film production and film-related activities in the Netherlands. The Fund provides financial contributions for film development, production, distribution, and other activities within the Dutch film sector. It suppo ... Read More</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
+          <t>Applications are open to eligibleindependent production companiesthat are legal entities and have been established for at least two years in the Netherlands, an EU member state, EEA country, or Switzerland. The company must continuously produce and exploit films or other audiovisual productions. For films up to 10 minutes, the producer must have experience as the majority producer responsible for realizing and releasing at least one qualifying independent film. For films from 10 minutes onward, the producer must have experience with at least two qualifying independent animation productions. The producer cannot also be the film’s director or screenwriter.</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
@@ -5871,15 +5429,15 @@
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>09 October 2026</t>
+          <t>13 October 2026</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
+          <t>https://andpurpose.world/applications-open-for-realization-of-short-animation-grant/</t>
         </is>
       </c>
     </row>
@@ -5896,17 +5454,17 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Realization of Short Animation Grant</t>
+          <t>Applications Invited for WUN Research Development Fund 2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>TheNetherlands Film Fundis the national agency responsible for supporting professional film production and film-related activities in the Netherlands. The Fund provides financial contributions for film development, production, distribution, and other activities within the Dutch film sector. It suppo ... Read More</t>
+          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Applications are open to eligibleindependent production companiesthat are legal entities and have been established for at least two years in the Netherlands, an EU member state, EEA country, or Switzerland. The company must continuously produce and exploit films or other audiovisual productions. For films up to 10 minutes, the producer must have experience as the majority producer responsible for realizing and releasing at least one qualifying independent film. For films from 10 minutes onward, the producer must have experience with at least two qualifying independent animation productions. The producer cannot also be the film’s director or screenwriter.</t>
+          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -5916,15 +5474,15 @@
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>13 October 2026</t>
+          <t>15 October 2026</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-realization-of-short-animation-grant/</t>
+          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -5941,17 +5499,17 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
+          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
+          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
+          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -5961,52 +5519,254 @@
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>13 October 2026</t>
+          <t>15 October 2026</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
+          <t>RFP For Impact Assessment For FLN Program</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
+          <t>Centre For Microfinance &amp; Livelihood (Cml) | Goalpara, Bongaigaon and Baksa District., Assam
+RFP For Impact Assessment For FLN Program, Centre For Microfinance &amp; Livelihood (Cml)(Goalpara, Bongaigaon and Baksa District.) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
+          <t>• 3. Eligibility of bidder:
+a. The bidder can either be a propriety or partnership firm, company or any
+other institution registered in India.
+b. The bidding organisation is required to have multiple years of experience in dealing with issues pertaining to education, advocacy, etc. Prior experience in carrying out similar assignments in the North-East is an added advantage.
+4.         Procedure for submitting Bids:
+The Bid shall be in two separate documents, Technical Bid &amp; Financial Bid
+Technical Bids shall consist of the following:
+Proposal detailing approach and methodology
+Plan of work including timelines
+Functionalities covered as per Scope
+Financial Bid:
+The Bidder shall provide the Financial Bid in the following format.
+Particulars                   Unit                             Unit cost (Rs.)                          Total (Rs.)
+Bidder shall quote price that is all-inclusive except GST. No separate fees/charges whosoever will be paid for any other expenses.
+GST shall be shown separately.
+Incomplete Bids will be summarily rejected and will not be considered for further evaluation and shortlisting.
+5. Evaluation of the Bids: The Procurement Committee duly constituted by CML authority will evaluate the proposal / technical bid and financial bid and recommend successful bidder / firm for award of work.
+6. Validity: The bids shall have to remain valid for minimum 180 days and an undertaking must be submitted to this effect.
+7. The successful bidder shall have to complete the work within the stipulated completion period as stated in the RFP document. The completion period will be counted from the date of issue of work order.
+8. The bids should be sealed in one envelope addressed to the Executive Director, Centre for Microfinance &amp; Livelihood; Guwahati, Assam and the name of the work intended for should be clearly written and underlined on top of the envelope. Soft copies of the bids could be sent via email to the following email id: procurement@cmlnortheast.com
+9. The bids shall be signed by the authorized signatory or a person duly authorized by him or her.
+10. Extension of deadline: CML Authority reserves the right to extend, as necessary, the deadline for submission of quotations.
+11. Language: The bid of the bidder, as well as all documents attached to bid by the bidder and all correspondence relating to the bid exchanged by the Bidder and CML shall be written in English language.
+12. Documents to be submitted along with the bids:
+a. Signed statement mentioning the legal status, place of registration and principal place of business of the bidder (individual firm, company or partnership), complete address of the registered office and address for correspondences with Phone number/cell number/Fax number and E-mail ID
+b. Registration Certificate – Firm/Society/DIC/SSI etc.
+c. Audit Report for last 3 years.
+d. A copy of passport size photograph of the signatory of the bid.
+e. Authorization of the Signatory by the head of the Firm/Company.
+f. PAN Card
+g. GST Registration.
+h. Financial capability certificate from competent authority
+i. Experience certificate.
+13. Payment:
+a. 20% payment will be made on receipt of counter-signed work order
+b. 30% on completion of data collection and field work
+c. 30% on analysis and submission of draft report
+d. Balance 20% on Submission and Acceptance of Final Report
+14. Taxes and Duties: The bidder shall be entirely responsible for and bear all taxes – GST and any other tax, royalty, license fees, permits, etc., paid during the execution of the work and submit clearance certificate(s) to CML.
+15. CML will not deduct such taxes – GST and any other tax, royalty, license fees, permits, etc.; but at the same time will not release the final bill unless proof of payment of such taxes – GST and any other tax, royalty, license fees, permits, etc. to the concerned Govt. authority is submitted to CML authority. CML will scrutinize such documents and shall release final payment only after satisfying itself.
+Executive Director
+Centre for Microfinance &amp; Livelihood
+Guwahati, Assam.
+For detailed information, please check the complete version of the RFP at the link below or can also contact the following email:
+• Job Email ID:
+procurement@cmlnortheast.com
+Attachment Link:
+https://drive.google.com/file/d/19uZ8Rf6Xq_CQhfJ-XbABp5_tAC7AKTSD/view?usp=sharing
+• Job Email ID:
+procurement(at)cmlnortheast.com
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+16 Oct 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Program Manager – ITI and Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+Resource Person – Bangalore
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+Manager - Programs – Persons with Disability
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+18 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Project Officer
+(Value Members only)
+Location:
+West Bengal
+Apply by:
+23 Sep 2026
+Program Coordinator
+Gramin Adiwasi Samaj Vikas Sansthan
+Location:
+Madhya Pradesh
+Apply by:
+30 Sep 2026
+Digital Literacy Trainer
+South Kolkata Hamari Muskan
+Location:
+West Bengal
+Apply by:
+30 Sep 2026
+Accountant
+Sarv Mangal Gramin Vikas Sansthan (SMGVS)
+Location:
+Rajasthan
+Apply by:
+30 Sep 2026
+Veterinary Consultant
+Yuva Vikas Kendra
+Location:
+Jharkhand
+Apply by:
+25 Sep 2026
+Project Lead
+(Value Members only)
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+Male ANM &amp; Male Outreach Worker
+Rewa Network of Poeple Living with HIV/AIDS Socie...
+Location:
+Madhya Pradesh
+Apply by:
+25 Sep 2026
+State Programme Manager
+India HIV/AIDS Alliance (Alliance India)
+Location:
+Manipur
+Apply by:
+27 Sep 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance, Learning</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>15 October 2026</t>
+          <t>16-10-2026</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
@@ -6014,7 +5774,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303842</t>
         </is>
       </c>
     </row>
@@ -6031,27 +5791,27 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for WUN Research Development Fund 2026</t>
+          <t>Request for Applications: Research in Health Systems (South Africa)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
+          <t>TheSouth African Medical Research Council (SAMRC)is a national research organisation dedicated to improving health and quality of life through research, innovation and technology transfer. SAMRC supports health and medical research across South Africa and works with academic institutions, researcher ... Read More</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
+          <t>The opportunity is open to eligible researchers employed by recognised South African research institutions whose primary purpose includes research and postgraduate training. Eligible host institutions includeSouth African public universities, public research entities, science councils, national facilities and other recognised research institutions. The Principal Investigator must be aSouth African citizen or permanent residentand employed by an eligible institution. NGOs, nonprofit organisations and private companies whose primary purpose is not research and postgraduate training cannot apply as lead applicants, although they may participate as collaborators where permitted. International organisations and researchers may also collaborate where allowed. Applicants must demonstrate appropriate research capacity, institutional support, scientific expertise and implementation potential.</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>15 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
@@ -6059,7 +5819,7 @@
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
+          <t>https://andpurpose.world/request-for-applications-research-in-health-systems-south-africa/</t>
         </is>
       </c>
     </row>
@@ -6076,22 +5836,22 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Request for Applications: Research in Health Systems (South Africa)</t>
+          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TheSouth African Medical Research Council (SAMRC)is a national research organisation dedicated to improving health and quality of life through research, innovation and technology transfer. SAMRC supports health and medical research across South Africa and works with academic institutions, researcher ... Read More</t>
+          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>The opportunity is open to eligible researchers employed by recognised South African research institutions whose primary purpose includes research and postgraduate training. Eligible host institutions includeSouth African public universities, public research entities, science councils, national facilities and other recognised research institutions. The Principal Investigator must be aSouth African citizen or permanent residentand employed by an eligible institution. NGOs, nonprofit organisations and private companies whose primary purpose is not research and postgraduate training cannot apply as lead applicants, although they may participate as collaborators where permitted. International organisations and researchers may also collaborate where allowed. Applicants must demonstrate appropriate research capacity, institutional support, scientific expertise and implementation potential.</t>
+          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -6100,11 +5860,11 @@
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/request-for-applications-research-in-health-systems-south-africa/</t>
+          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
         </is>
       </c>
     </row>
@@ -6121,22 +5881,22 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
+          <t>North Midlands Drought Resilience Community Grant 2026 – Apply by 16 October</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
+          <t>TheAustralian Government’s Future Drought Fundand theWestern Australian Governmentjointly support the Regional Drought Resilience Planning Program. The programme helps regional communities strengthen their ability to prepare for and manage drought and prolonged dry seasons. Through regional planning ... Read More</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
+          <t>Eligible applicants must have a currentAustralian Business Number (ABN)or be auspiced by an incorporated organisation with an ABN. Applicants must have an account with an Australian financial institution and meet GST registration requirements where applicable. They must demonstrate sufficient organisational capacity, resources, partnerships, and arrangements to successfully deliver the proposed project. Projects must contribute to drought resilience and demonstrate alignment with the Mid West Regional Drought Resilience Plan. Applicants must also be able to manage project expenditure, monitor outcomes, deliver approved activities, and meet reporting and accountability requirements. These eligibility conditions apply to organisations seeking Future Drought Fund grants through this programme.</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
@@ -6145,11 +5905,11 @@
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
+          <t>https://andpurpose.world/north-midlands-drought-resilience-community-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -6166,17 +5926,17 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>North Midlands Drought Resilience Community Grant 2026 – Apply by 16 October</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TheAustralian Government’s Future Drought Fundand theWestern Australian Governmentjointly support the Regional Drought Resilience Planning Program. The programme helps regional communities strengthen their ability to prepare for and manage drought and prolonged dry seasons. Through regional planning ... Read More</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants must have a currentAustralian Business Number (ABN)or be auspiced by an incorporated organisation with an ABN. Applicants must have an account with an Australian financial institution and meet GST registration requirements where applicable. They must demonstrate sufficient organisational capacity, resources, partnerships, and arrangements to successfully deliver the proposed project. Projects must contribute to drought resilience and demonstrate alignment with the Mid West Regional Drought Resilience Plan. Applicants must also be able to manage project expenditure, monitor outcomes, deliver approved activities, and meet reporting and accountability requirements. These eligibility conditions apply to organisations seeking Future Drought Fund grants through this programme.</t>
+          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -6186,15 +5946,15 @@
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/north-midlands-drought-resilience-community-grant-2026/</t>
+          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
         </is>
       </c>
     </row>
@@ -6211,17 +5971,17 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
+          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
+          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
+          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -6235,11 +5995,11 @@
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
+          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
         </is>
       </c>
     </row>
@@ -6256,17 +6016,17 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
+          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
+          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
+          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
@@ -6276,15 +6036,15 @@
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>26 October 2026</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
+          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
         </is>
       </c>
     </row>
@@ -6301,17 +6061,17 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
+          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
+          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
+          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -6321,15 +6081,15 @@
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>26 October 2026</t>
+          <t>28 October 2026</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
+          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
         </is>
       </c>
     </row>
@@ -6346,17 +6106,17 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
+          <t>Whitley Award 2027</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
+          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
+          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -6366,15 +6126,15 @@
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>28 October 2026</t>
+          <t>30 October 2026</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
+          <t>https://andpurpose.world/whitley-award-2027/</t>
         </is>
       </c>
     </row>
@@ -6391,35 +6151,35 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Whitley Award 2027</t>
+          <t>National Indian Health Outreach and Education Program 2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
+          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
+          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>30 October 2026</t>
+          <t>2 November 2026</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/whitley-award-2027/</t>
+          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
         </is>
       </c>
     </row>
@@ -6436,35 +6196,35 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>National Indian Health Outreach and Education Program 2026</t>
+          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
+          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
+          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>2 November 2026</t>
+          <t>4 November 2026</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
         </is>
       </c>
     </row>
@@ -6481,27 +6241,27 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
+          <t>CFAs: U.S. Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
+          <t>TheCenters for Disease Control and Prevention (CDC)is a U.S. public health agency responsible for protecting communities from diseases, health threats, and other public health risks. The agency conducts research, develops evidence-based guidance, monitors health trends, and supports public health pr ... Read More</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
+          <t>TheTravel Health Research Grants 2026opportunity supports initiatives that improve health protection for U.S. residents traveling internationally. The program focuses on four connected areas: travel preparation information, health information collection and surveillance, research into emerging health threats, and travel medicine education for primary care providers. Projects may use electronic medical records, websites, mobile applications, and other digital health technologies to collect information before, during, and after international travel. The estimated total program funding isUS$5 million, with individual awards ranging fromUS$750,000 to US$1 million. The initiative aims to strengthen evidence-based travel health information and public health research.</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>4 November 2026</t>
+          <t>05 November 2026</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
@@ -6509,7 +6269,7 @@
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
+          <t>https://andpurpose.world/cfas-u-s-travelers-health-research-surveillance-communication-and-outreach-network/</t>
         </is>
       </c>
     </row>
@@ -6526,27 +6286,27 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>CFAs: U.S. Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
+          <t>Applications Invited for World Food Day Poster Contest 2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>TheCenters for Disease Control and Prevention (CDC)is a U.S. public health agency responsible for protecting communities from diseases, health threats, and other public health risks. The agency conducts research, develops evidence-based guidance, monitors health trends, and supports public health pr ... Read More</t>
+          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>TheTravel Health Research Grants 2026opportunity supports initiatives that improve health protection for U.S. residents traveling internationally. The program focuses on four connected areas: travel preparation information, health information collection and surveillance, research into emerging health threats, and travel medicine education for primary care providers. Projects may use electronic medical records, websites, mobile applications, and other digital health technologies to collect information before, during, and after international travel. The estimated total program funding isUS$5 million, with individual awards ranging fromUS$750,000 to US$1 million. The initiative aims to strengthen evidence-based travel health information and public health research.</t>
+          <t>The application deadline is 6 November 2026</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>05 November 2026</t>
+          <t>6 November 2026</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
@@ -6554,7 +6314,7 @@
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/cfas-u-s-travelers-health-research-surveillance-communication-and-outreach-network/</t>
+          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
         </is>
       </c>
     </row>
@@ -6571,17 +6331,17 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for World Food Day Poster Contest 2026</t>
+          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
+          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 6 November 2026</t>
+          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -6591,15 +6351,15 @@
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>6 November 2026</t>
+          <t>9 November 2026</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
+          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
         </is>
       </c>
     </row>
@@ -6616,17 +6376,17 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
+          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
+          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
+          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -6636,15 +6396,15 @@
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>9 November 2026</t>
+          <t>15 November 2026</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
+          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
         </is>
       </c>
     </row>
@@ -6661,17 +6421,17 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
+          <t>Apply Now for Skills Development Grants for Creative Industries in Toronto</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
+          <t>TheCity of Torontois Canada’s largest municipal government and supports initiatives that strengthen the city’s economy, communities, culture, and workforce. Through its creative industries funding programs, the City supports film, television, music, and creative technology sectors. Its funding initi ... Read More</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
+          <t>Applications are open to eligibleCanadian not-for-profit and charitable organizations, urban off-reserve Indigenous-led organizations, and community centres that are part of the Association of Community Centres. Applicants must be located in Toronto or deliver the proposed funded services to Toronto-based individuals or entities. Organizations must not owe money to the City of Toronto or be in default of existing City agreements. Projects should focus on practical workforce development, employment readiness, and technical skills connected to Toronto’s creative industries. Eligible initiatives may include training in post-production, VFX, animation, digital workflows, trades, crafts, and other high-demand technical roles.</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -6685,11 +6445,11 @@
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
+          <t>https://andpurpose.world/apply-now-for-skills-development-grants-for-creative-industries-in-toronto/</t>
         </is>
       </c>
     </row>
@@ -6706,17 +6466,17 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for Skills Development Grants for Creative Industries in Toronto</t>
+          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TheCity of Torontois Canada’s largest municipal government and supports initiatives that strengthen the city’s economy, communities, culture, and workforce. Through its creative industries funding programs, the City supports film, television, music, and creative technology sectors. Its funding initi ... Read More</t>
+          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Applications are open to eligibleCanadian not-for-profit and charitable organizations, urban off-reserve Indigenous-led organizations, and community centres that are part of the Association of Community Centres. Applicants must be located in Toronto or deliver the proposed funded services to Toronto-based individuals or entities. Organizations must not owe money to the City of Toronto or be in default of existing City agreements. Projects should focus on practical workforce development, employment readiness, and technical skills connected to Toronto’s creative industries. Eligible initiatives may include training in post-production, VFX, animation, digital workflows, trades, crafts, and other high-demand technical roles.</t>
+          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -6726,7 +6486,7 @@
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>15 November 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
@@ -6734,7 +6494,7 @@
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-skills-development-grants-for-creative-industries-in-toronto/</t>
+          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6535,7 @@
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
@@ -6796,17 +6556,17 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
+          <t>Applications Open for CRI Technology Impact Award Grant</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -6820,11 +6580,11 @@
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
+          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
         </is>
       </c>
     </row>
@@ -6841,35 +6601,35 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for CRI Technology Impact Award Grant</t>
+          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
+          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
+          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
+          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
         </is>
       </c>
     </row>
@@ -6886,22 +6646,22 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
+          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
+          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
+          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
@@ -6910,11 +6670,11 @@
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
+          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
         </is>
       </c>
     </row>
@@ -6931,17 +6691,17 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
+          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
+          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
+          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -6955,11 +6715,11 @@
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
+          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
         </is>
       </c>
     </row>
@@ -6976,17 +6736,17 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
+          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
+          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
+          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -7000,11 +6760,11 @@
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
+          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
         </is>
       </c>
     </row>
@@ -7021,17 +6781,17 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
+          <t>Collections Stewardship Program Grant – National Endowment for the Humanities</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
+          <t>TheNational Endowment for the Humanities (NEH)is an independent federal agency of the United States that supports research, education, preservation and public programs in the humanities. Through its Division of Collections &amp; Infrastructure, NEH supports organizations working to preserve physical and ... Read More</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
+          <t>TheNEH Collections Stewardship Programprovides funding for projects that preserve and improve access to physical and digital collections important to humanities research, teaching and public engagement. Supported activities include conservation, preservation planning, collection storage and care, archival arrangement and description, cataloguing, digitization, transcription, indexing, digital preservation and enhancement of established digital humanities resources. The program can also support preservation services and education or training for students and professionals working with humanities collections. Awards range from$50,000 to $500,000, with single organizations eligible for up to $350,000 and consortium applications eligible for up to $500,000.</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -7041,15 +6801,15 @@
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>15 December 2026</t>
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
+          <t>https://andpurpose.world/collections-stewardship-program-grant-national-endowment-for-the-humanities/</t>
         </is>
       </c>
     </row>
@@ -7066,17 +6826,17 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Collections Stewardship Program Grant – National Endowment for the Humanities</t>
+          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>TheNational Endowment for the Humanities (NEH)is an independent federal agency of the United States that supports research, education, preservation and public programs in the humanities. Through its Division of Collections &amp; Infrastructure, NEH supports organizations working to preserve physical and ... Read More</t>
+          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>TheNEH Collections Stewardship Programprovides funding for projects that preserve and improve access to physical and digital collections important to humanities research, teaching and public engagement. Supported activities include conservation, preservation planning, collection storage and care, archival arrangement and description, cataloguing, digitization, transcription, indexing, digital preservation and enhancement of established digital humanities resources. The program can also support preservation services and education or training for students and professionals working with humanities collections. Awards range from$50,000 to $500,000, with single organizations eligible for up to $350,000 and consortium applications eligible for up to $500,000.</t>
+          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
@@ -7086,15 +6846,15 @@
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>15 December 2026</t>
+          <t>20 December 2026</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/collections-stewardship-program-grant-national-endowment-for-the-humanities/</t>
+          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -7111,17 +6871,17 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
+          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
+          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
+          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
@@ -7131,15 +6891,15 @@
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>20 December 2026</t>
+          <t>14 January 2027</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
         </is>
       </c>
     </row>
@@ -7156,27 +6916,27 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
+          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
+          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
+          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>14 January 2027</t>
+          <t>15 January 2027</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
@@ -7184,7 +6944,7 @@
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
+          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
         </is>
       </c>
     </row>
@@ -7201,35 +6961,35 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
+          <t>J. N. Derbyshire Trust Grants UK: Apply for Up to £10,000</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
+          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, ... Read More</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
+          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, advancing education, and relieving poverty, distress and sickness. The Trust primarily supports community and voluntary organisations through project funding. It operates as a grant-making charity and reviews applications through two annual grant rounds. The Trust prioritises organisations delivering meaningful benefits within Nottingham and Nottinghamshire.</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>15 January 2027</t>
+          <t>31 January 2027</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
+          <t>https://andpurpose.world/j-n-derbyshire-trust-grants/</t>
         </is>
       </c>
     </row>
@@ -7246,17 +7006,17 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>J. N. Derbyshire Trust Grants UK: Apply for Up to £10,000</t>
+          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, ... Read More</t>
+          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, advancing education, and relieving poverty, distress and sickness. The Trust primarily supports community and voluntary organisations through project funding. It operates as a grant-making charity and reviews applications through two annual grant rounds. The Trust prioritises organisations delivering meaningful benefits within Nottingham and Nottinghamshire.</t>
+          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
@@ -7266,15 +7026,15 @@
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>31 January 2027</t>
+          <t>15 February 2027</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/j-n-derbyshire-trust-grants/</t>
+          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
         </is>
       </c>
     </row>
@@ -7291,17 +7051,17 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
+          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
+          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
+          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
@@ -7311,15 +7071,15 @@
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>15 February 2027</t>
+          <t>8 March 2027</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
+          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
         </is>
       </c>
     </row>
@@ -7336,17 +7096,17 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
+          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
+          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
+          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
@@ -7356,60 +7116,42 @@
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>8 March 2027</t>
+          <t>30 June 2027</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>173</v>
+        <v>286</v>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
+          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr"/>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
-        </is>
-      </c>
+          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>30 June 2027</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="n">
-        <v>287</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr"/>
+      <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7164,7 @@
       <c r="B78" s="1" t="inlineStr"/>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -7436,7 +7178,7 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7191,7 @@
       <c r="B79" s="1" t="inlineStr"/>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -7463,7 +7205,7 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7218,8 @@
       <c r="B80" s="1" t="inlineStr"/>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
+          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
+                    here</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -7490,7 +7233,7 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -7503,22 +7246,21 @@
       <c r="B81" s="1" t="inlineStr"/>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
-                    here</t>
+          <t>RFP for Women Entrepreneurship Programme - Click here</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -7531,21 +7273,21 @@
       <c r="B82" s="1" t="inlineStr"/>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>RFP for Women Entrepreneurship Programme - Click here</t>
+          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7300,8 @@
       <c r="B83" s="1" t="inlineStr"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+                    here</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -7572,7 +7315,7 @@
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7328,8 @@
       <c r="B84" s="1" t="inlineStr"/>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+          <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
+                India Pvt. Ltd - Click here | Click
                     here</t>
         </is>
       </c>
@@ -7593,14 +7337,14 @@
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -7613,23 +7357,21 @@
       <c r="B85" s="1" t="inlineStr"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
-                India Pvt. Ltd - Click here | Click
-                    here</t>
+          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
         </is>
       </c>
     </row>
@@ -7642,21 +7384,21 @@
       <c r="B86" s="1" t="inlineStr"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
+          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
         </is>
       </c>
     </row>
@@ -7669,21 +7411,21 @@
       <c r="B87" s="1" t="inlineStr"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
+          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
         </is>
       </c>
     </row>
@@ -7696,21 +7438,21 @@
       <c r="B88" s="1" t="inlineStr"/>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
+          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7465,8 @@
       <c r="B89" s="1" t="inlineStr"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
+          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
+                    here</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -7737,7 +7480,7 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7750,22 +7493,21 @@
       <c r="B90" s="1" t="inlineStr"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
-                    here</t>
+          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7520,7 @@
       <c r="B91" s="1" t="inlineStr"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -7792,7 +7534,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7805,21 +7547,21 @@
       <c r="B92" s="1" t="inlineStr"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7832,21 +7574,21 @@
       <c r="B93" s="1" t="inlineStr"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7859,21 +7601,21 @@
       <c r="B94" s="1" t="inlineStr"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7886,21 +7628,21 @@
       <c r="B95" s="1" t="inlineStr"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7655,7 @@
       <c r="B96" s="1" t="inlineStr"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -7927,7 +7669,7 @@
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7682,7 @@
       <c r="B97" s="1" t="inlineStr"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -7954,7 +7696,7 @@
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7709,7 @@
       <c r="B98" s="1" t="inlineStr"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -7981,7 +7723,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7994,21 +7736,22 @@
       <c r="B99" s="1" t="inlineStr"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
+                education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -8021,8 +7764,7 @@
       <c r="B100" s="1" t="inlineStr"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
-                education in STEM courses - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -8036,7 +7778,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -8049,7 +7791,7 @@
       <c r="B101" s="1" t="inlineStr"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
@@ -8063,7 +7805,7 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -8076,21 +7818,22 @@
       <c r="B102" s="1" t="inlineStr"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
+                and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -8103,22 +7846,22 @@
       <c r="B103" s="1" t="inlineStr"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
-                and Financial Management - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
+                    here</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -8131,8 +7874,8 @@
       <c r="B104" s="1" t="inlineStr"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
-                    here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -8146,7 +7889,7 @@
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -8160,7 +7903,7 @@
       <c r="C105" s="1" t="inlineStr">
         <is>
           <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -8174,7 +7917,7 @@
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -8187,8 +7930,7 @@
       <c r="B106" s="1" t="inlineStr"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -8202,7 +7944,7 @@
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -8215,7 +7957,7 @@
       <c r="B107" s="1" t="inlineStr"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -8229,7 +7971,7 @@
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -8242,21 +7984,21 @@
       <c r="B108" s="1" t="inlineStr"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -8269,34 +8011,38 @@
       <c r="B109" s="1" t="inlineStr"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -8306,11 +8052,15 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G110" s="1" t="inlineStr"/>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>31st Aug, 2026</t>
+        </is>
+      </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
         </is>
       </c>
     </row>
@@ -8327,25 +8077,25 @@
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
+          <t>Senior Programme Officer - Uday</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>31st Aug, 2026</t>
+          <t>15th Aug, 2026</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8112,7 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Senior Programme Officer - Uday</t>
+          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -8374,13 +8124,13 @@
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>15th Aug, 2026</t>
+          <t>29th Jun, 2026</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
         </is>
       </c>
     </row>
@@ -8397,25 +8147,25 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>29th Jun, 2026</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8182,7 @@
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -8450,7 +8200,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -8467,25 +8217,25 @@
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -8502,25 +8252,25 @@
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -8537,25 +8287,25 @@
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -8572,25 +8322,25 @@
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -8607,60 +8357,52 @@
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>EOI for Onboarding of Partner Institutes for LCCM.pdf</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI%20for%20Onboarding%20of%20Partner%20Institutes%20for%20LCCM.pdf</t>
         </is>
       </c>
     </row>
@@ -9285,87 +9027,6 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>Draft RFP UHI_4.pdf</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="1" t="inlineStr"/>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Draft%20RFP%20UHI_4.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-9289662.pdf</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr"/>
-      <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9289662.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum_USI.pdf</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_USI.pdf</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,43 +489,48 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFQ - for Guest Rooms &amp; Conference Facilities – October26</t>
+          <t>RFP - Digital Commerce, Brand Identity &amp; Social Media Enablement — Bhoomga...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>WaterAid India | Delhi
-RFQ - for Guest Rooms &amp; Conference Facilities – October26, WaterAid India() | DevNetJobsIndia
+          <t>Development Support Centre (DSC) | Dantewada, Chhattisgarh
+RFP - Digital Commerce, Brand Identity &amp; Social Media Enablement — Bhoomgaadi Organic Farmers Producer Company Ltd, Dantewada, Chhattisgarh, Development Support Centre (DSC)(Dantewada) | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ID:
-303893
-R ... Read More</t>
+Val ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• Job Email ID:
-WAIP2P-Delhi(at)wateraid.org
+          <t>• 2. Eligibility
+—
+pass/fail gate
+Valid GST registration and a registered office address anywhere in India, with documentary proof. There is no state restriction on who may apply.
+Minimum 3 years in digital marketing, branding or e-commerce enablement, with a portfolio — mandatory.
+At least one live e-commerce website built or managed by the applicant (URL), and three published reels (links).
+Named individuals who will do the work, with CVs. Hindi essential; Halbi or Gondi an advantage. FPO, agri or organic experience preferred, not mandatory. Applicants able to reach Dantewada easily, or with a presence in Chhattisgarh or a nearby state, get additional preference at evaluation — but this is a preference, not a condition. DSC wants a compact, agile team, not a large agency.
+• How to Apply
+One email, all attachments, by the deadline. Incomplete submissions may be rejected without correspondence.
+Profile with GST certificate and registered office proof. (2) Portfolio — at least one live e-commerce URL and three reel links. (3) Methodology and execution plan, including the approach to field visits and to farmer, Millet Sisters and ecopreneur stories. (4) CVs of the people who will do the work. (5) Financial proposal as a separate document, workstream-wise, field visit cost shown separately, with the inclusions and exclusions statement. (6) Proposed monthly targets for the two accountable measures in Section 8. (7) Signed acceptance of the mandatory conditions in Section 4.
+Submissions
+dscmiraclemillet@gmail.com
+(cc:
+dsc@dscindia.org
+)
+Subject line
+RFP Response –   Digital Marketing – Dantewada, Chhattisgarh
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+DSC_RFP_Digital_Marketing_Dantewada.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-24 Sep 2026
+25 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -594,54 +599,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -679,7 +684,7 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -687,7 +692,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303893</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303818</t>
         </is>
       </c>
     </row>
@@ -700,43 +705,60 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>RFP - Digital Commerce, Brand Identity &amp; Social Media Enablement — Bhoomga...</t>
+          <t>RFP - Hiring of professional agency for video documentation of best pract...</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Development Support Centre (DSC) | Dantewada, Chhattisgarh
-RFP - Digital Commerce, Brand Identity &amp; Social Media Enablement — Bhoomgaadi Organic Farmers Producer Company Ltd, Dantewada, Chhattisgarh, Development Support Centre (DSC)(Dantewada) | DevNetJobsIndia
+          <t>People’s Rural Education Movement (PREM) | Odisha
+RFP -  Hiring of professional agency for video documentation of best practices, case studies, process documentation on roll out of subdermal..., People’s Rural Education Movement (PREM)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Val ... Read More</t>
+Value Mem ... Read More</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• 2. Eligibility
-—
-pass/fail gate
-Valid GST registration and a registered office address anywhere in India, with documentary proof. There is no state restriction on who may apply.
-Minimum 3 years in digital marketing, branding or e-commerce enablement, with a portfolio — mandatory.
-At least one live e-commerce website built or managed by the applicant (URL), and three published reels (links).
-Named individuals who will do the work, with CVs. Hindi essential; Halbi or Gondi an advantage. FPO, agri or organic experience preferred, not mandatory. Applicants able to reach Dantewada easily, or with a presence in Chhattisgarh or a nearby state, get additional preference at evaluation — but this is a preference, not a condition. DSC wants a compact, agile team, not a large agency.
-• How to Apply
-One email, all attachments, by the deadline. Incomplete submissions may be rejected without correspondence.
-Profile with GST certificate and registered office proof. (2) Portfolio — at least one live e-commerce URL and three reel links. (3) Methodology and execution plan, including the approach to field visits and to farmer, Millet Sisters and ecopreneur stories. (4) CVs of the people who will do the work. (5) Financial proposal as a separate document, workstream-wise, field visit cost shown separately, with the inclusions and exclusions statement. (6) Proposed monthly targets for the two accountable measures in Section 8. (7) Signed acceptance of the mandatory conditions in Section 4.
-Submissions
-dscmiraclemillet@gmail.com
-(cc:
-dsc@dscindia.org
-)
-Subject line
-RFP Response –   Digital Marketing – Dantewada, Chhattisgarh
+          <t>• As part of the introduction of newer contraceptive choices, subdermal contraceptive implants and Subcutaneous being introduced in facilities of selected districts. The subdermal implant service is being implemented in Medical Colleges and District Headquarters Hospitals in
+Ganjam, Kataka, Khordha and Sundargarh
+districts where as the Subcutaneous MPA is being rolled out in the districts of
+Gajapati, Balasore, Bhadrak, Boudh and Mayurbhanj
+.
+The initiative provides an opportunity to document the experience of service providers, programme managers and, most importantly, real beneficiaries/clients who have voluntarily accessed the implant service. Such documentation will help capture the human story behind the programme, demonstrate good practices, understand the service delivery process, identify innovations and lessons learned, and provide replicable examples for strengthening and scaling up the service.
+The proposed documentation will therefore focus on producing
+Five
+short
+,
+high-quality documentary-style videos (In odia with sub-titles in English), each of approximately
+2–3 minutes duration
+, covering real-life beneficiary and service-provider experiences from
+Kataka, Ganjam, Gajapati and Mayurbhanj districts
+.
+The videos should go beyond conventional promotional content and should present authentic, evidence-based and human-centred stories, while maintaining the dignity, privacy, confidentiality and informed consent of all participants.
+2. Objective:
+The purpose of this assignment is to engage an experienced professional agency/production house to conceptualize, research, script, shoot, edit and produce five high-quality short documentary/case-study videos, each of approximately 2–3 minutes, showcasing:
+Real-life stories and experiences of beneficiaries/clients who have voluntarily opted for the contraceptive implant.
+Experiences of trained service providers delivering implant services.
+The counselling and decision-making process preceding service uptake.
+The service delivery pathway and client experience.
+Good practices and innovations adopted by health facilities and providers.
+The role of health system personnel in generating awareness, counselling, referral and follow-up.
+Key learnings that can potentially be replicated in other facilities/districts.
+The overall journey from awareness and counselling to service provision and follow-up.
+Submission Instructions:
+The Agency should have to submit Technical Proposal (must include supporting documents to justify the Required Criteria for the Bidder) and Financial Proposal (In the provided Template only) in separate email to
+premoffice.hr@gmail.com
+with the Mandatory Subject line of the e-mail as
+e.g. “
+Hiring of professional agency for video documentation of best practices, case studies, process documentation on roll out of subdermal contraceptive implant and subcutaneous services under the family planning programme in pilot districts of Odisha
+&amp;quot; by 25rd Sep 2026, 23:59 Hrs.
+Note: Technical &amp;amp; Financial Proposal to be submitted in separate email.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-DSC_RFP_Digital_Marketing_Dantewada.pdf
+PREM-RFP_for video documentation- FP (1) (2).doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -810,54 +832,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -899,11 +921,11 @@
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303818</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303819</t>
         </is>
       </c>
     </row>
@@ -1038,54 +1060,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1127,7 +1149,7 @@
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -1411,54 +1433,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1500,7 +1522,7 @@
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -1517,60 +1539,44 @@
       <c r="B6" s="1" t="inlineStr"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>RFP - Hiring of professional agency for video documentation of best pract...</t>
+          <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>People’s Rural Education Movement (PREM) | Odisha
-RFP -  Hiring of professional agency for video documentation of best practices, case studies, process documentation on roll out of subdermal..., People’s Rural Education Movement (PREM)() | DevNetJobsIndia
+          <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
+RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Value Mem ... Read More</t>
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Se ... Read More</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>• As part of the introduction of newer contraceptive choices, subdermal contraceptive implants and Subcutaneous being introduced in facilities of selected districts. The subdermal implant service is being implemented in Medical Colleges and District Headquarters Hospitals in
-Ganjam, Kataka, Khordha and Sundargarh
-districts where as the Subcutaneous MPA is being rolled out in the districts of
-Gajapati, Balasore, Bhadrak, Boudh and Mayurbhanj
-.
-The initiative provides an opportunity to document the experience of service providers, programme managers and, most importantly, real beneficiaries/clients who have voluntarily accessed the implant service. Such documentation will help capture the human story behind the programme, demonstrate good practices, understand the service delivery process, identify innovations and lessons learned, and provide replicable examples for strengthening and scaling up the service.
-The proposed documentation will therefore focus on producing
-Five
-short
-,
-high-quality documentary-style videos (In odia with sub-titles in English), each of approximately
-2–3 minutes duration
-, covering real-life beneficiary and service-provider experiences from
-Kataka, Ganjam, Gajapati and Mayurbhanj districts
-.
-The videos should go beyond conventional promotional content and should present authentic, evidence-based and human-centred stories, while maintaining the dignity, privacy, confidentiality and informed consent of all participants.
-2. Objective:
-The purpose of this assignment is to engage an experienced professional agency/production house to conceptualize, research, script, shoot, edit and produce five high-quality short documentary/case-study videos, each of approximately 2–3 minutes, showcasing:
-Real-life stories and experiences of beneficiaries/clients who have voluntarily opted for the contraceptive implant.
-Experiences of trained service providers delivering implant services.
-The counselling and decision-making process preceding service uptake.
-The service delivery pathway and client experience.
-Good practices and innovations adopted by health facilities and providers.
-The role of health system personnel in generating awareness, counselling, referral and follow-up.
-Key learnings that can potentially be replicated in other facilities/districts.
-The overall journey from awareness and counselling to service provision and follow-up.
-Submission Instructions:
-The Agency should have to submit Technical Proposal (must include supporting documents to justify the Required Criteria for the Bidder) and Financial Proposal (In the provided Template only) in separate email to
-premoffice.hr@gmail.com
-with the Mandatory Subject line of the e-mail as
-e.g. “
-Hiring of professional agency for video documentation of best practices, case studies, process documentation on roll out of subdermal contraceptive implant and subcutaneous services under the family planning programme in pilot districts of Odisha
-&amp;quot; by 25rd Sep 2026, 23:59 Hrs.
-Note: Technical &amp;amp; Financial Proposal to be submitted in separate email.
-For detailed information, please check the complete version of the RFP attached below.
+          <t>• SCOPE OF WORK
+• The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
+TAF will facilitate access to the baseline survey tool, the January 2025 baseline report, the deidentified baseline dataset, and government permissions; these materials, along with any other tools and de-identified datasets, will be shared only with the selected study partner. The study partner will be responsible for adapting the instruments, and for fielding, analysing, and reporting the endline round.
+Key deliverables
+will include an inception report, IRB approval documentation, cleaned quantitative and qualitative datasets, a draft endline report, a final endline report, and a presentation of findings to TAF (see Annex 1, Section VI).
+SUBMISSION
+All proposals and queries should be sent to
+TAF_MnE@antarafoundation.org
+and cc to
+puneet.naithani@antarafoundation.org
+with the subject line
+"Damoh Endline Evaluation proposal || Organisation name".
+Queries will be accepted until the deadline stated on the cover page; responses to queries (RFQ) will be shared with all prospective applicants by the date indicated.
+For detailed information, please check the complete version of the RFP attached below
 Download Attachment:
-PREM-RFP_for video documentation- FP (1) (2).doc
+Damoh_Endline_RFP_TAF.pdf
+Download Attachment:
+RFQ_Clarifications.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1644,54 +1650,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1724,7 +1730,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -1733,11 +1739,11 @@
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303819</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
         </is>
       </c>
     </row>
@@ -1750,741 +1756,10 @@
       <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>RFP - Hotel Selection for Training of Sub National Verification (SNV)</t>
+          <t>RFP - Empanelment of development &amp; implementation partners for CSR, commu...</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>TCI Foundation | Rishikesh/Dehradun, Uttarakhand
-RFP - Hotel Selection for Training of Sub National Verification (SNV), TCI Foundation(Rishikesh/Dehradun) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Regist ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• Payment Terms and Conditions:
-50% payment would be made by TCI Foundation as advance.
-Billing for the program to be done on “Bill to Company” basis and balance payment will be released within 7 days of completion of the event and on submission of GST Bill.
-The GST bills raised by the Hotel shall clearly mention the billing components (basic tariff, taxes etc) Check-in, and Check-out details of guest(s).
-Billing: TCI Foundation, Gurugram-122001
-• General Terms and Conditions:
-Availability of minimum required rooms (mixed category accommodating all participants) and conference hall is a non-negotiable condition to qualify in the technical bid. Non-availability of minimum number of rooms and conference hall disqualifies the hotel in the technical evaluation process.
-TCI Foundation will pay only for the boarding and lodging for the participants on APAI basis (inclusive of breakfast, lunch, dinner and all taxes). Any personal expense of participants would be borne by the individuals only and to be collected directly by the Hotel/Resort.
-. Regular updates on room requirements will be provided to the contact person of the Hotel by TCI Foundation in advance to avoid retention charges
-Separately mention of rates for the charges for extra breakfast, lunch &amp; dinner for non- residential participants.
-Complimentary use of facilities in Hotel like Gym, Swimming Pool etc. should be provided as complimentary services.
-The Hotel accommodation will have facility to provide first aid and doctor on call facility for medical emergencies.
-The selected hotel may be empaneled with TCI Foundation for conducting residential training and meeting programs within the
-country till
-31
-st
-March 2027.
-Instructions to Hotels
-The Hotel shall provide necessary information/details as per the format provided: a. Bank details (Form I),
-Technical Proposal (Form II)
-Financial Proposal (Form III)
-The Hotel shall submit its Technical documents in pdf format through email to
-rfp@tcifindia.org
-Mention the dimensions, name and photographs of the conference hall
-• The eligibility of hotels for considering the financial Proposals will be decided after evaluation of the technical proposal. Only those hotels that are found eligible as per technical evaluation will be considered for financial evaluation.
-IMPORTANT
-The “FINANCIAL PROPOSAL” must be sent in a “PASSWORD PROTECTED pdf format” through email on
-rfp@tcifindia.org
-Only technically qualified bidders shall be asked to share the password to open the encrypted financial bids received through email.
-The Hotel shall provide a signed and scanned copy of the valid registration certificate for PAN, TAN &amp; GST. The applicable GST rates must be mentioned for each service provided clearly.
-TCI Foundation has the right to cancel the Proposals at any time, extend or postpone the last date for submission of the Proposal, information for which will be sent to all concerned in advance. TCI Foundation has the right to reject any offers that are found to be incomplete and not having enough details for the technical evaluation.
-TCI Foundation reserves the right to further negotiate the financial terms / other facilities with the Hotels as per the specific requirements.
-Each page of the forms submitted should be signed with name of the signatory and stamped with date
-CRITICAL DATES
-Published Date
-14-09-2026
-Submission Start Date &amp; Time
-18-09-2026, 12.00 am
-Submission End Date &amp; Time
-25-09-2026, 5.30 pm
-Technical Bid Opening Date &amp; Time
-26-09-2026, 3.00 pm
-Financial Bid Opening Date &amp; Time
-26-09-2026. 4.00 pm
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-rfp(at)tcifindia.org
-Download Attachment:
-RFQ-SNV-2026-27 Rishikesh.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-25 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
-Trickle Up India Foundation
-Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
-Apply by:
-08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303891</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>25 September 2026</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RPF-for Development of a Module on Social Media Marketing, Customer Engage...</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>People’s Rural Education Movement (PREM) | Odisha
-RPF-for Development of a Module on Social Media Marketing, Customer Engagement and Business Strategy for (WSHG) Members of Mission Shakti, People’s Rural Education Movement (PREM)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membershi ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-The assignment will comprise the following stages.
-4.1
-Review and Design of the Module
-The agency shall:
-Review the existing Social Media Training Module and Social Media Skilling Framework.
-Map existing competencies against the proposed business and marketing competencies to ensure complementarity and avoid duplication.
-Identify key gaps and barriers in translating social media presence and engagement into business outcomes.
-Develop the overall framework, learning architecture and outline for the second module.
-Ensure relevance to WSHG members with varying levels of digital literacy and enterprise experience.
-Submission Instructions:
-The Agency should have to submit Technical Proposal (must include supporting documents to justify the Required Criteria for the Bidder) and Financial Proposal (In the provided Template only) in separate email to
-procurement.prem@gmail.com
-with the Mandatory Subject line of the e-mail as e.g. “Technical Proposal–Bidder Name- RFP NO/RFP/2026/004- "Development of a Module on Social Media Marketing" by 25th Sep 2026, 23:59 Hrs.
-Note: Technical &amp; Financial Proposal to be submitted in separate email.
-• # Bids that do not contain the correct email subject line, contain Technical &amp; Financial Proposal in a single email, Any Financial Quote in the Technical proposal or submission of bid post to the above timelines may not be considered for further processing.
-# Any Bid submitted will be regarded as an offer by the bidder and does not constitute or imply the acceptance of any quotation by PREM. PREM is under no obligation to award a contract to any bidder as a result of this RFP.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-PREM-RFQ_Module on Social Media Marketing-MS (1) (1).doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-25 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
-Trickle Up India Foundation
-Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
-Apply by:
-08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303781</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>RFP -for an Endline evaluation of the Akshita Program's integrated model...</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>The Antara Foundation (TAF) | Damoh District, Madhya Pradesh
-RFP -for an  Endline evaluation of the Akshita  Program's integrated model – Damoh District, The Antara Foundation (TAF)(Damoh District) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Se ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>• SCOPE OF WORK
-• The study partner is expected to execute the endline round consistent with the baseline's evaluation design (see Annex 1, Sections II–IV for detailed objectives, evaluation design, scope of work, and measurement domains), flagging any deviations required by changed ground conditions.
-TAF will facilitate access to the baseline survey tool, the January 2025 baseline report, the deidentified baseline dataset, and government permissions; these materials, along with any other tools and de-identified datasets, will be shared only with the selected study partner. The study partner will be responsible for adapting the instruments, and for fielding, analysing, and reporting the endline round.
-Key deliverables
-will include an inception report, IRB approval documentation, cleaned quantitative and qualitative datasets, a draft endline report, a final endline report, and a presentation of findings to TAF (see Annex 1, Section VI).
-SUBMISSION
-All proposals and queries should be sent to
-TAF_MnE@antarafoundation.org
-and cc to
-puneet.naithani@antarafoundation.org
-with the subject line
-"Damoh Endline Evaluation proposal || Organisation name".
-Queries will be accepted until the deadline stated on the cover page; responses to queries (RFQ) will be shared with all prospective applicants by the date indicated.
-For detailed information, please check the complete version of the RFP attached below
-Download Attachment:
-Damoh_Endline_RFP_TAF.pdf
-Download Attachment:
-RFQ_Clarifications.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-25 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
-Trickle Up India Foundation
-Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
-Apply by:
-08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>25-09-2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303449</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Empanelment of development &amp; implementation partners for CSR, commu...</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AROH Foundation | India
 RFP - Empanelment of development &amp; implementation partners  for CSR, community development &amp; infrastructure projects across India, AROH Foundation() | DevNetJobsIndia
@@ -2501,7 +1776,7 @@
 Jobseeke ... Read More</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• 1. INTRODUCTION AND BACKGROUND
 AROH Foundation invites proposals from experienced, technically competent and financially sound development agencies, implementation partners, contractors, service providers and vendors for empanelment to undertake CSR, community development, infrastructure, renewable energy, water conservation, natural resource management and allied
@@ -2675,54 +1950,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2753,72 +2028,121 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>25-09-2026</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=302836</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Open Call: SMART Capital Equipment Fund (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>TheWelsh Governmentis the devolved government responsible for a wide range of public policy and investment programmes across Wales. It works to support economic development, innovation, businesses, research, skills, sustainability and improvements in public services. Through funding programmes such ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Identify the productivity or resource-efficiency challenge your organisation faces and select the capital equipment needed to address it. Explain why the investment goes beyond routine replacement and quantify expected benefits such as increased output, reduced waste or improved labour productivity. Prepare an eligible capital budget, demonstrate project readiness and confirm that assets will be located in Wales. Complete the required application and comply with subsidy-control and due-diligence requirements.</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>25 September 2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/open-call-smart-capital-equipment-fund-united-kingdom/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Consultant for Content Development for Gender Resource Centre</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Breakthrough | India
-ToR - Consultant for Content Development for Gender Resource Centre, Breakthrough() | DevNetJobsIndia
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>RPF-for Development of a Module on Social Media Marketing, Customer Engage...</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>People’s Rural Education Movement (PREM) | Odisha
+RPF-for Development of a Module on Social Media Marketing, Customer Engagement and Business Strategy for (WSHG) Members of Mission Shakti, People’s Rural Education Movement (PREM)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ID:
-30 ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-rfp(at)inbreakthrough.org
+Value Membershi ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• Scope of Work
+The assignment will comprise the following stages.
+4.1
+Review and Design of the Module
+The agency shall:
+Review the existing Social Media Training Module and Social Media Skilling Framework.
+Map existing competencies against the proposed business and marketing competencies to ensure complementarity and avoid duplication.
+Identify key gaps and barriers in translating social media presence and engagement into business outcomes.
+Develop the overall framework, learning architecture and outline for the second module.
+Ensure relevance to WSHG members with varying levels of digital literacy and enterprise experience.
+Submission Instructions:
+The Agency should have to submit Technical Proposal (must include supporting documents to justify the Required Criteria for the Bidder) and Financial Proposal (In the provided Template only) in separate email to
+procurement.prem@gmail.com
+with the Mandatory Subject line of the e-mail as e.g. “Technical Proposal–Bidder Name- RFP NO/RFP/2026/004- "Development of a Module on Social Media Marketing" by 25th Sep 2026, 23:59 Hrs.
+Note: Technical &amp; Financial Proposal to be submitted in separate email.
+• # Bids that do not contain the correct email subject line, contain Technical &amp; Financial Proposal in a single email, Any Financial Quote in the Technical proposal or submission of bid post to the above timelines may not be considered for further processing.
+# Any Bid submitted will be regarded as an offer by the bidder and does not constitute or imply the acceptance of any quotation by PREM. PREM is under no obligation to award a contract to any bidder as a result of this RFP.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-• Scope of work- GRC.pdf
+PREM-RFQ_Module on Social Media Marketing-MS (1) (1).doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-27 Sep 2026
+25 Sep 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -2887,54 +2211,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2965,38 +2289,250 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303781</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Consultant for Content Development for Gender Resource Centre</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Breakthrough | India
+ToR - Consultant for Content Development for Gender Resource Centre, Breakthrough() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Register
+Job ID:
+30 ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+rfp(at)inbreakthrough.org
+Download Attachment:
+• Scope of work- GRC.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+27 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
+Trickle Up India Foundation
+Location:
+West Bengal
+Apply by:
+08 Oct 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>27-09-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304041</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RFP - Design and Delivery of Street Play (Nukkad Natak), Puppet Theatre, a...</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Centre for Catalyzing Change (C3) | Rajasthan
 RFP - Design and Delivery of Street Play (Nukkad Natak), Puppet Theatre, and Theatre-Based Workshops on Gender Equity in Selected Districts..., Centre for Catalyzing Change (C3)() | DevNetJobsIndia
@@ -3009,7 +2545,7 @@
 Broa ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Introduction &amp; Organizational Context
 The Centre for Catalyzing Change (C3) is a leading national non-profit organization dedicated to empowering women and adolescent girls through innovative, evidence-based programmes. For over 30 years, C3 has worked to advance education, health, safety, life skills, and economic opportunities by strengthening systems and influencing public policy.
@@ -3113,54 +2649,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3191,521 +2727,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Climate, Safety</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>27-09-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303890</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>Tender notice for Installation of 2 Nos ARU Bahraich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Bahraich, Uttar Pradesh
-Tender notice for  Installation of 2 Nos ARU Bahraich, WaterAid India(Bahraich) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Reg ... Read More</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>• Interested Bidders are required to submit their complete proposal on their letter heads along with all terms and conditions to email id:
-WAIProcurementUP@wateraid.org
-by 28
-th
-September 2026 w
-hich should necessarily include:
-For any queries pertaining to the tender, please write to
-me before 25
-th
-September,2026
-.
-Profile of the organization, given as per the below –
-1.
-Profile of Bidder-
-Name of Organization:
-Registration Certificate:
-GST Certificate
-Last three years Balance sheet
-MSME Certificate (if registered) 6. 3 years Tax return File (attached)
-Address for correspondence:
-Office Phone:
-Mobile Phones of corresponding officials:
-Email for correspondence:
-Locations of operations (Head office and Branch offices):
-All certificates must be attached.
-• Terms and Conditions:
-Submit Quotations with subject line Items –
-Quotation for Installation of 2 Nos ARU Bahraich
-Without subject quotation will not consider for further process
-Pproposal’s should  be addressed to Jal Seva Charitable Foundation,
-2/92,
-Vishal Khand Gomti Nagar Lucknow 226010
-The Proposal must be on the company letter head with date, signature and company seal. (It is to be signed by the authorized person).
-Proposals must be submitted to Procurement Email ID:
-WAIProcurementUP@wateraid.org
-Any proposal submitted to any other email id will not be considered.
-The Proposal to be submitted as
-two separate attachment
-– 1. Technical proposal as per the BOQ and Financial proposal in non-editable PDF Format.
-The proposal must have the subject mentioning the village name given in the table below of point
-12.
-THE PROPOSAL MUST BE SUBMITTED AS A SEPARATE ATTACHMENT FOR EACH VILLAGE (four attachments). Kindly refer the BOQ given.
-Proposals received after due date will not be considered.
-Financial proposals must be submitted inclusive of applicable taxes and mentioning the validity of the quoted rate.
-• All terms and conditions must be clearly mentioned in the proposals.
-Incomplete proposals shall not be considered
-The work shall be completed on or before 30 October 2026
-Payment shall be released based on the actual work completed and verified.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Tender notice for  Installation of 2 Nos ARU Bahraich.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-28 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
-Trickle Up India Foundation
-Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
-Apply by:
-08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304070</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Video documentation of change stories on Ground water replenishment ...</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Hyderabad and Sanga Reddy, Telangana
-RFP - Video documentation of change stories on Ground water replenishment in Hyderabad and Sanga Reddy locations, WaterAid India(Hyderabad and Sanga Reddy) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFP ... Read More</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>• In this context, Jal Seva Charitable Foundation (JSCF) seeks to engage a consultant for ‘Video Documentation of Change Stories’ as outlined in the following terms and conditions.
-Objective of the contract:
-The objective of this assignment is to capture and document post-intervention activities of ground water replenishment in Sherlingampally Zone in Hyderabad and in Sangareddy district through video documentation.
-Scope of assignment &amp; expected outcome:
-This assignment involves producing a 6-minute video capturing real-life change stories resulting from water-harvesting interventions.
-The assignment includes the following deliverables:
-1.
-A 6-minute, high-resolution video showcasing the impact of water-harvesting infrastructure through community testimonials. It will include interviews, relevant field visuals and a clear storyline highlighting the changes brought about by the interventions. The video will effectively capture community experiences, benefits, and key outcomes.
-Duration of the
-• contract: The Consultancy Agreement will be effective for a period of 20 days from the date of signing and is expected to be completed by 30 October 2026, unless extended in writing by JSCF. Any extension will be subject to additional or revised terms and conditions as mutually agreed upon in writing between the Consultant and JSCF.
-Reporting point and Progress Report
-For matters covered by the TORs and this agreement, you will report directly to Mr Pachimadla Krishna, Program Coordinator, Telangana, JSCF, and submit reports as specified in the TORs.
-Payment Schedule
-Condition for   Payment
-20%
-40%
-40%
-Upon signing of the Contract
-Upon submission of 6 Minutes of Drafted Video
-Upon   completion of Assignment
-Contact
-For submission of Proposal, queries and clarifications
-Please mail to this email i.d.
-WAIProcurementAP@wateraid.org
-Experience in strategic communications, digital storytelling and social media management.
-Strong photography, videography and content development skills.
-• Job Email ID:
-WAIProcurementAP(at)wateraid.org
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-28 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
-Trickle Up India Foundation
-Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
-Apply by:
-08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303896</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>RFP - for Final Evaluation of Support Micro/Small entrepreneurs among part...</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe e.V | India
 RFP - for Final Evaluation of Support Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans, Deutsche Welthungerhilfe e.V() | DevNetJobsIndia
@@ -3720,7 +2773,7 @@
 Searc ... Read More</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION ANDCONTEXT
 Country:
@@ -3841,54 +2894,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3919,38 +2972,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>28-09-2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Proj...</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Aga Khan Foundation (India) | Bihar
 RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Project Dhenu Dhara – Foraging pathways to improving livestock health and dairy , Aga Khan Foundation (India)() | DevNetJobsIndia
@@ -3963,7 +3016,7 @@
 Broadcast Re ... Read More</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• Bidders may alter or withdraw their bids by written notification prior to the stated deadline for submission of bids. No bids may be altered after this deadline. Withdrawals must be unconditional and will end all participation in the bid procedure.
 6. Opening of bid
@@ -4104,54 +3157,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4182,14 +3235,587 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303730</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Tender notice for Installation of 2 Nos ARU Bahraich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | Bahraich, Uttar Pradesh
+Tender notice for  Installation of 2 Nos ARU Bahraich, WaterAid India(Bahraich) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Reg ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• Interested Bidders are required to submit their complete proposal on their letter heads along with all terms and conditions to email id:
+WAIProcurementUP@wateraid.org
+by 28
+th
+September 2026 w
+hich should necessarily include:
+For any queries pertaining to the tender, please write to
+me before 25
+th
+September,2026
+.
+Profile of the organization, given as per the below –
+1.
+Profile of Bidder-
+Name of Organization:
+Registration Certificate:
+GST Certificate
+Last three years Balance sheet
+MSME Certificate (if registered) 6. 3 years Tax return File (attached)
+Address for correspondence:
+Office Phone:
+Mobile Phones of corresponding officials:
+Email for correspondence:
+Locations of operations (Head office and Branch offices):
+All certificates must be attached.
+• Terms and Conditions:
+Submit Quotations with subject line Items –
+Quotation for Installation of 2 Nos ARU Bahraich
+Without subject quotation will not consider for further process
+Pproposal’s should  be addressed to Jal Seva Charitable Foundation,
+2/92,
+Vishal Khand Gomti Nagar Lucknow 226010
+The Proposal must be on the company letter head with date, signature and company seal. (It is to be signed by the authorized person).
+Proposals must be submitted to Procurement Email ID:
+WAIProcurementUP@wateraid.org
+Any proposal submitted to any other email id will not be considered.
+The Proposal to be submitted as
+two separate attachment
+– 1. Technical proposal as per the BOQ and Financial proposal in non-editable PDF Format.
+The proposal must have the subject mentioning the village name given in the table below of point
+12.
+THE PROPOSAL MUST BE SUBMITTED AS A SEPARATE ATTACHMENT FOR EACH VILLAGE (four attachments). Kindly refer the BOQ given.
+Proposals received after due date will not be considered.
+Financial proposals must be submitted inclusive of applicable taxes and mentioning the validity of the quoted rate.
+• All terms and conditions must be clearly mentioned in the proposals.
+Incomplete proposals shall not be considered
+The work shall be completed on or before 30 October 2026
+Payment shall be released based on the actual work completed and verified.
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+Tender notice for  Installation of 2 Nos ARU Bahraich.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+28 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
+Trickle Up India Foundation
+Location:
+West Bengal
+Apply by:
+08 Oct 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304070</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Video documentation of change stories on Ground water replenishment ...</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | Hyderabad and Sanga Reddy, Telangana
+RFP - Video documentation of change stories on Ground water replenishment in Hyderabad and Sanga Reddy locations, WaterAid India(Hyderabad and Sanga Reddy) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFP ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>• In this context, Jal Seva Charitable Foundation (JSCF) seeks to engage a consultant for ‘Video Documentation of Change Stories’ as outlined in the following terms and conditions.
+Objective of the contract:
+The objective of this assignment is to capture and document post-intervention activities of ground water replenishment in Sherlingampally Zone in Hyderabad and in Sangareddy district through video documentation.
+Scope of assignment &amp; expected outcome:
+This assignment involves producing a 6-minute video capturing real-life change stories resulting from water-harvesting interventions.
+The assignment includes the following deliverables:
+1.
+A 6-minute, high-resolution video showcasing the impact of water-harvesting infrastructure through community testimonials. It will include interviews, relevant field visuals and a clear storyline highlighting the changes brought about by the interventions. The video will effectively capture community experiences, benefits, and key outcomes.
+Duration of the
+• contract: The Consultancy Agreement will be effective for a period of 20 days from the date of signing and is expected to be completed by 30 October 2026, unless extended in writing by JSCF. Any extension will be subject to additional or revised terms and conditions as mutually agreed upon in writing between the Consultant and JSCF.
+Reporting point and Progress Report
+For matters covered by the TORs and this agreement, you will report directly to Mr Pachimadla Krishna, Program Coordinator, Telangana, JSCF, and submit reports as specified in the TORs.
+Payment Schedule
+Condition for   Payment
+20%
+40%
+40%
+Upon signing of the Contract
+Upon submission of 6 Minutes of Drafted Video
+Upon   completion of Assignment
+Contact
+For submission of Proposal, queries and clarifications
+Please mail to this email i.d.
+WAIProcurementAP@wateraid.org
+Experience in strategic communications, digital storytelling and social media management.
+Strong photography, videography and content development skills.
+• Job Email ID:
+WAIProcurementAP(at)wateraid.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+28 Sep 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
+Trickle Up India Foundation
+Location:
+West Bengal
+Apply by:
+08 Oct 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303896</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>29 September 2026</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 29 September 2026</t>
+        </is>
+      </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="H17" s="1" t="n">
@@ -4197,7 +3823,7 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303730</t>
+          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
         </is>
       </c>
     </row>
@@ -4214,27 +3840,27 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+          <t>The application deadline is30 September 2026</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>29 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H18" s="1" t="n">
@@ -4242,7 +3868,7 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
         </is>
       </c>
     </row>
@@ -4259,17 +3885,17 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+          <t>Applications Open for Green Box Artist in Residency Program</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 29 September 2026</t>
+          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -4279,7 +3905,7 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>29 September 2026</t>
+          <t>30 September 2026</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
@@ -4287,7 +3913,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
+          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
         </is>
       </c>
     </row>
@@ -4304,17 +3930,17 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
+          <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
+          <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
+          <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -4328,11 +3954,11 @@
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
+          <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -4373,7 +3999,7 @@
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -4394,22 +4020,22 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Apply for Giving Joy Microgrant 2026 – Up to US$500 for Women Entrepreneurs</t>
+          <t>Giving Joy Microgrant 2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Giving Joy is a nonprofit organisation that supports women entrepreneurs and changemakers by providing small grants, mentorship and practical support. The organisation focuses on helping women develop ideas that create positive economic or social impact in their communities. Its global grant program ... Read More</t>
+          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>The Giving Joy Microgrant 2026 provides small-scale financial support to women entrepreneurs and changemakers worldwide. The Fall 2026 grant cycle is designed to help applicants start or expand a business, nonprofit organisation or community project that generates positive economic or social benefits for women, girls and families. Selected applicants can receive a one-time microgrant of up to US$500, along with mentorship and participation in the Giving Joy community. The grant can support practical activities and project expenses during a six-month implementation period. Applications for the Fall 2026 cycle are open from 1 September through 30 September 2026.</t>
+          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -4418,11 +4044,11 @@
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-giving-joy-microgrant-2026/</t>
+          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
         </is>
       </c>
     </row>
@@ -4439,17 +4065,17 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Apply for RAFT AI for Transformative Social Impact Grant 2026 – Up to ₹50 Lakh</t>
+          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI ... Read More</t>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI at the core of their solutions and can demonstrate meaningful, measurable and responsible impact. The initiative focuses particularly on agriculture, healthcare, disability inclusion and frontline support. RAFT indicates a preference for organisations operating in Maharashtra and is interested in solutions with potential for scale and longer-term impact. The initiative is designed for organisations that are already applying AI to real-world social challenges.</t>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -4463,56 +4089,60 @@
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/raft-ai-transformative-social-impact-grant-2026/</t>
+          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr"/>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
+          <t>RFQ - for Solar Home Lightning Procurement for SAHAS Project</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
+          <t>Development Support Centre (DSC) | Dhadgaon Block, Nandurbar District, Maharashtra
+RFQ -  for Solar Home Lightning Procurement for SAHAS Project, Development Support Centre (DSC)(Dhadgaon Block, Nandurbar District) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resum ... Read More</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is30 September 2026</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304229</t>
         </is>
       </c>
     </row>
@@ -4529,22 +4159,22 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Green Box Artist in Residency Program</t>
+          <t>Apply for Giving Joy Microgrant 2026 – Up to US$500 for Women Entrepreneurs</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
+          <t>Giving Joy is a nonprofit organisation that supports women entrepreneurs and changemakers by providing small grants, mentorship and practical support. The organisation focuses on helping women develop ideas that create positive economic or social impact in their communities. Its global grant program ... Read More</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
+          <t>The Giving Joy Microgrant 2026 provides small-scale financial support to women entrepreneurs and changemakers worldwide. The Fall 2026 grant cycle is designed to help applicants start or expand a business, nonprofit organisation or community project that generates positive economic or social benefits for women, girls and families. Selected applicants can receive a one-time microgrant of up to US$500, along with mentorship and participation in the Giving Joy community. The grant can support practical activities and project expenses during a six-month implementation period. Applications for the Fall 2026 cycle are open from 1 September through 30 September 2026.</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
@@ -4553,11 +4183,11 @@
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
+          <t>https://andpurpose.world/apply-for-giving-joy-microgrant-2026/</t>
         </is>
       </c>
     </row>
@@ -4574,17 +4204,17 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Giving Joy Microgrant 2026</t>
+          <t>Apply for RAFT AI for Transformative Social Impact Grant 2026 – Up to ₹50 Lakh</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
+          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI ... Read More</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
+          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI at the core of their solutions and can demonstrate meaningful, measurable and responsible impact. The initiative focuses particularly on agriculture, healthcare, disability inclusion and frontline support. RAFT indicates a preference for organisations operating in Maharashtra and is interested in solutions with potential for scale and longer-term impact. The initiative is designed for organisations that are already applying AI to real-world social challenges.</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -4598,11 +4228,11 @@
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
+          <t>https://andpurpose.world/raft-ai-transformative-social-impact-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -4619,17 +4249,17 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
+          <t>Apply for European Youth Foundation Grants 2027 – Up to €60,000</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
+          <t>The European Youth Foundation (EYF) is a funding body of the Council of Europe supporting youth organisations and initiatives that promote human rights, democracy, peace, intercultural dialogue and youth participation. EYF grants support international youth cooperation and projects that help young p ... Read More</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
+          <t>Eligible applicants are youth non-governmental organisations and networks registered with the European Youth Foundation. Organisations must satisfy the EYF’s registration and eligibility criteria before applying. The projects must involve young people and contribute to the Foundation’s thematic priorities. Applicants should ensure their organisation has been validated before the deadline because EYF registration can take time. Projects should have an international youth cooperation dimension and demonstrate clear objectives, activities, expected outcomes and appropriate budgeting. Individuals cannot apply independently for these organisational grants.</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -4639,7 +4269,7 @@
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>30 September 2026</t>
+          <t>1 October 2026</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
@@ -4647,7 +4277,7 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
+          <t>https://andpurpose.world/apply-for-european-youth-foundation-grants-2027/</t>
         </is>
       </c>
     </row>
@@ -4819,54 +4449,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4908,7 +4538,7 @@
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -4919,22 +4549,112 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 01 October 2026</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>01 October 2026</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Mumbai Ekatra Going Green 2026 – Grants Up to ₹1 Lakh</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>The Kshirsagar Apte Foundation is an Indian family foundation established in 2013 that supports initiatives across education and employability, gender, environment and sustainability, arts and culture, disabilities and health. One of its programmes focuses on citizen-led initiatives addressing civic ... Read More</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai Ekatra – Going Green is open to community groups, institutions and organisations proposing citizen-led projects focused on environmental sustainability in Mumbai. Applicants should present a clear idea that addresses a relevant urban environmental challenge and demonstrates community participation. Projects may relate to areas including water conservation, urban agriculture, green roofing, recycling, waste management and other sustainability initiatives. Organisations and groups should review the programme’s official requirements and application instructions before submitting their proposals. The opportunity is geographically focused on Mumbai rather than being an India-wide grant.</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>1 October 2026</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-mumbai-ekatra-going-green-2026-grants-up/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar ...</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society (CECOEDECON) | Jaisalmer, Jodhpur, Barmer Districts, Rajasthan
 RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar PV Systems – 2 kW, 3 kW and 5 kW, Centre For Community Economics And Development Consultants So ... Read More</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>• 5. Scope of Work
 The selected bidder shall provide complete turnkey services, including but not limited to:
@@ -5114,54 +4834,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5192,176 +4912,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>01-10-2026</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="H31" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304105</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 01 October 2026</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>01 October 2026</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Apply for European Youth Foundation Grants 2027 – Up to €60,000</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>The European Youth Foundation (EYF) is a funding body of the Council of Europe supporting youth organisations and initiatives that promote human rights, democracy, peace, intercultural dialogue and youth participation. EYF grants support international youth cooperation and projects that help young p ... Read More</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants are youth non-governmental organisations and networks registered with the European Youth Foundation. Organisations must satisfy the EYF’s registration and eligibility criteria before applying. The projects must involve young people and contribute to the Foundation’s thematic priorities. Applicants should ensure their organisation has been validated before the deadline because EYF registration can take time. Projects should have an international youth cooperation dimension and demonstrate clear objectives, activities, expected outcomes and appropriate budgeting. Individuals cannot apply independently for these organisational grants.</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>1 October 2026</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-european-youth-foundation-grants-2027/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Apply for Mumbai Ekatra Going Green 2026 – Grants Up to ₹1 Lakh</t>
+          <t>RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>The Kshirsagar Apte Foundation is an Indian family foundation established in 2013 that supports initiatives across education and employability, gender, environment and sustainability, arts and culture, disabilities and health. One of its programmes focuses on citizen-led initiatives addressing civic ... Read More</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Mumbai Ekatra – Going Green is open to community groups, institutions and organisations proposing citizen-led projects focused on environmental sustainability in Mumbai. Applicants should present a clear idea that addresses a relevant urban environmental challenge and demonstrates community participation. Projects may relate to areas including water conservation, urban agriculture, green roofing, recycling, waste management and other sustainability initiatives. Organisations and groups should review the programme’s official requirements and application instructions before submitting their proposals. The opportunity is geographically focused on Mumbai rather than being an India-wide grant.</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>1 October 2026</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-mumbai-ekatra-going-green-2026-grants-up/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>RFP - English Annotation of Student Voice Recordings from Uttarakhand</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
           <t>Lords Education and Health Society (LEHS) | Uttarakhand
-RFP - English Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -5372,31 +4957,25 @@
 RFPs/Tenders
 Search Jobs
 Events
-Jobseekers ... Read More</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+Jobseekers: ... Read More</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 All proposals to this RFP must be received no later than
-&lt;Oct 2nd 2026&gt;
+&lt;October 2nd 2026&gt;.
+The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP:
+Hindi Transcriptions of Student Voice Recordings of Reading - Uttarakhand (Name of the partner)
 .
-The
-proposal should be submitted only through e-mail in PDF format addressed to The
-Procurement Team at the below-given e-mail id:
-rfp.lehs@wadhwaniai.org
-. The
-email's subject line must contain the reference number and title of the RFP:
-English
-Transcriptions of Student Voice Recordings of Reading - Uttarakhand (Name
-of the partner).
-Any proposals received by Wadhwani-AI after the deadline for submission of proposals
-prescribed in the timeline of this document are liable to be rejected.
+Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
 For detailed information, please check the complete version of the RFP attached below.
 • Job Email ID:
 rfp.lehs(at)wadhwaniai.org
 Download Attachment:
-RFP - Uttrakhand Data Annotation I Grades 1-8 English RFP.pdf
+RFP - Uttarakhand Data Annotation I Grades 1-8 Hindi RFP.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -5470,54 +5049,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5548,41 +5127,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>02-10-2026</t>
         </is>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304049</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="H32" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304050</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | Uttarakhand
-RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hotel Selection for Training of Sub National Verification (SNV)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>TCI Foundation | Rishikesh/Dehradun, Uttarakhand
+RFP - Hotel Selection for Training of Sub National Verification (SNV), TCI Foundation(Rishikesh/Dehradun) | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -5593,25 +5172,63 @@
 RFPs/Tenders
 Search Jobs
 Events
-Jobseekers: ... Read More</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>• Submission Details
-All proposals to this RFP must be received no later than
-&lt;October 2nd 2026&gt;.
-The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP:
-Hindi Transcriptions of Student Voice Recordings of Reading - Uttarakhand (Name of the partner)
-.
-Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
+Jobseekers:
+Login
+|
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>• Payment Terms and Conditions:
+50% payment would be made by TCI Foundation as advance.
+Billing for the program to be done on “Bill to Company” basis and balance payment will be released within 7 days of completion of the event and on submission of GST Bill.
+The GST bills raised by the Hotel shall clearly mention the billing components (basic tariff, taxes etc) Check-in, and Check-out details of guest(s).
+Billing: TCI Foundation, Gurugram-122001
+• General Terms and Conditions:
+Availability of minimum required rooms (mixed category accommodating all participants) and conference hall is a non-negotiable condition to qualify in the technical bid. Non-availability of minimum number of rooms and conference hall disqualifies the hotel in the technical evaluation process.
+TCI Foundation will pay only for the boarding and lodging for the participants on APAI basis (inclusive of breakfast, lunch, dinner and all taxes). Any personal expense of participants would be borne by the individuals only and to be collected directly by the Hotel/Resort.
+. Regular updates on room requirements will be provided to the contact person of the Hotel by TCI Foundation in advance to avoid retention charges
+Separately mention of rates for the charges for extra breakfast, lunch &amp; dinner for non- residential participants.
+Complimentary use of facilities in Hotel like Gym, Swimming Pool etc. should be provided as complimentary services.
+The Hotel accommodation will have facility to provide first aid and doctor on call facility for medical emergencies.
+The selected hotel may be empaneled with TCI Foundation for conducting residential training and meeting programs within the
+country till
+31
+st
+March 2027.
+Instructions to Hotels
+The Hotel shall provide necessary information/details as per the format provided: a. Bank details (Form I),
+Technical Proposal (Form II)
+Financial Proposal (Form III)
+The Hotel shall submit its Technical documents in pdf format through email to
+rfp@tcifindia.org
+Mention the dimensions, name and photographs of the conference hall
+• The eligibility of hotels for considering the financial Proposals will be decided after evaluation of the technical proposal. Only those hotels that are found eligible as per technical evaluation will be considered for financial evaluation.
+IMPORTANT
+The “FINANCIAL PROPOSAL” must be sent in a “PASSWORD PROTECTED pdf format” through email on
+rfp@tcifindia.org
+Only technically qualified bidders shall be asked to share the password to open the encrypted financial bids received through email.
+The Hotel shall provide a signed and scanned copy of the valid registration certificate for PAN, TAN &amp; GST. The applicable GST rates must be mentioned for each service provided clearly.
+TCI Foundation has the right to cancel the Proposals at any time, extend or postpone the last date for submission of the Proposal, information for which will be sent to all concerned in advance. TCI Foundation has the right to reject any offers that are found to be incomplete and not having enough details for the technical evaluation.
+TCI Foundation reserves the right to further negotiate the financial terms / other facilities with the Hotels as per the specific requirements.
+Each page of the forms submitted should be signed with name of the signatory and stamped with date
+CRITICAL DATES
+Published Date
+14-09-2026
+Submission Start Date &amp; Time
+18-09-2026, 12.00 am
+Submission End Date &amp; Time
+02-10-2026, 5.30 pm
+Technical Bid Opening Date &amp; Time
+26-09-2026, 3.00 pm
+Financial Bid Opening Date &amp; Time
+26-09-2026. 4.00 pm
 For detailed information, please check the complete version of the RFP attached below.
 • Job Email ID:
-rfp.lehs(at)wadhwaniai.org
+rfp(at)tcifindia.org
 Download Attachment:
-RFP - Uttarakhand Data Annotation I Grades 1-8 Hindi RFP.pdf
+RFQ-SNV-2026-27 Rishikesh.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -5685,54 +5302,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5763,6 +5380,227 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303891</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>RFP - English Annotation of Student Voice Recordings from Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Uttarakhand
+RFP - English Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers ... Read More</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>• Submission Details
+All proposals to this RFP must be received no later than
+&lt;Oct 2nd 2026&gt;
+.
+The
+proposal should be submitted only through e-mail in PDF format addressed to The
+Procurement Team at the below-given e-mail id:
+rfp.lehs@wadhwaniai.org
+. The
+email's subject line must contain the reference number and title of the RFP:
+English
+Transcriptions of Student Voice Recordings of Reading - Uttarakhand (Name
+of the partner).
+Any proposals received by Wadhwani-AI after the deadline for submission of proposals
+prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP - Uttrakhand Data Annotation I Grades 1-8 English RFP.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+02 Oct 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Resource Person – Vocational Education
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Director / Associate Director: Corporate Fundrais...
+India HIV/ AIDS Alliance (Alliance India)
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
+Trickle Up India Foundation
+Location:
+West Bengal
+Apply by:
+08 Oct 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
@@ -5774,11 +5612,11 @@
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304050</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304049</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5657,7 @@
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
@@ -5864,7 +5702,7 @@
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -6016,54 +5854,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6105,7 +5943,7 @@
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
@@ -6219,54 +6057,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6308,7 +6146,7 @@
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
@@ -6353,7 +6191,7 @@
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
@@ -6398,7 +6236,7 @@
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
@@ -6443,7 +6281,7 @@
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
@@ -6488,7 +6326,7 @@
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
@@ -6533,7 +6371,7 @@
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
@@ -6578,7 +6416,7 @@
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
@@ -6599,17 +6437,17 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
+          <t>2026 CSO Call for Expressions of Project Intentions – AFD</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
+          <t>Agence Française de Développement (AFD) is France’s public development agency working to finance and support projects that contribute to sustainable development, poverty reduction, climate action, biodiversity, social inclusion and international solidarity. Through its CSO Initiatives mechanism, AFD ... Read More</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
+          <t>Eligible CSOs should prepare a project intention describing the proposed project, objectives, expected outcomes, target communities and implementation approach. Applications must be submitted through AFD’s OSCar platform using the relevant project-intention documentation. Organisations without an OSCar account were required to request account creation by 15 September 2026. Complete project intentions must be submitted online by the final deadline. Applicants should carefully review the eligibility and documentation requirements before submission.</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -6619,15 +6457,15 @@
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>09 October 2026</t>
+          <t>9 October 2026</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
+          <t>https://andpurpose.world/2026-cso-call-for-expressions-of-project-intentions-afd/</t>
         </is>
       </c>
     </row>
@@ -6644,35 +6482,35 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Apply for Samhita-CGF Catalytic Grant 2026 – Up to ₹1 Crore for Education</t>
+          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Samhita–Collective Good Foundation works with organisations and partners seeking practical solutions to social and development challenges in India. Its grantmaking supports initiatives that improve access to essential services, strengthen systems and create sustainable opportunities for underserved ... Read More</t>
+          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Interested organisations should review Samhita-CGF’s programme information and eligibility requirements and submit an Expression of Interest through the designated application form. Applicants should clearly explain their education programme, target communities, expected outcomes, organisational experience and proposed use of funding. Samhita has also announced an applicant webinar for September 25, 2026. The EOI deadline is October 9, 2026.</t>
+          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>09 October 2026</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-samhita-cgf-catalytic-grant/</t>
+          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -6689,35 +6527,35 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Apply for Resilience Fund for Women in Global Value Chains 2026 – Up to US$50,000</t>
+          <t>Apply for Samhita-CGF Catalytic Grant 2026 – Up to ₹1 Crore for Education</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>The Resilience Fund for Women in Global Value Chains The Resilience Fund for Women in Global Value Chains is a philanthropic initiative supporting women-led and community-based organisations working with women connected to global supply chains. The fund promotes locally led solutions addressing wome ... Read More</t>
+          <t>Samhita–Collective Good Foundation works with organisations and partners seeking practical solutions to social and development challenges in India. Its grantmaking supports initiatives that improve access to essential services, strengthen systems and create sustainable opportunities for underserved ... Read More</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>The Resilience Fund for Women in Global Value Chains 2026 provides flexible, unrestricted grants to women-led, community-based organisations in India, Bangladesh, Cambodia and Vietnam. Selected organisations can receive between US$15,000 and US$50,000 over two years. The fund supports work connected to women’s health and safety, economic resilience, climate adaptation and the rights and wellbeing of women workers in global value chains. Funding is designed to give local organisations greater flexibility in responding to community priorities rather than restricting every grant dollar to narrowly defined activities. Applications for the current round opened on September 18, 2026.</t>
+          <t>Interested organisations should review Samhita-CGF’s programme information and eligibility requirements and submit an Expression of Interest through the designated application form. Applicants should clearly explain their education programme, target communities, expected outcomes, organisational experience and proposed use of funding. Samhita has also announced an applicant webinar for September 25, 2026. The EOI deadline is October 9, 2026.</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>12 October 2026</t>
+          <t>9 October 2026</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-resilience-fund-for-women-in-global-value-chains-2026/</t>
+          <t>https://andpurpose.world/apply-for-samhita-cgf-catalytic-grant/</t>
         </is>
       </c>
     </row>
@@ -6734,17 +6572,17 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
+          <t>Technology Support Programme 2026</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
+          <t>The Technology Support Programme for Small NGOs and Grassroots Organisations is designed to strengthen the digital and technological capacity of smaller civil society organisations. The programme focuses on helping organisations use technology to improve their operations, programme implementation, m ... Read More</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
+          <t>The programme is intended for small NGOs, grassroots organisations, community-based organisations and other eligible civil society groups requiring technology or digital-capacity support. Applicants should have a clearly identified organisational technology need and demonstrate how the proposed assistance could improve their work. Eligible organisations should be able to explain their existing technology challenges and the practical solution required. Applicants may need to provide relevant organisational documentation and information about their programmes. Organisations applying for technology grants India should ensure that their proposed requirement is connected to genuine operational, programme management, data, communication or monitoring needs.</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -6754,15 +6592,15 @@
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>13 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
+          <t>https://andpurpose.world/technology-support-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -6779,35 +6617,35 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
+          <t>Apply for Resilience Fund for Women in Global Value Chains 2026 – Up to US$50,000</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
+          <t>The Resilience Fund for Women in Global Value Chains The Resilience Fund for Women in Global Value Chains is a philanthropic initiative supporting women-led and community-based organisations working with women connected to global supply chains. The fund promotes locally led solutions addressing wome ... Read More</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
+          <t>The Resilience Fund for Women in Global Value Chains 2026 provides flexible, unrestricted grants to women-led, community-based organisations in India, Bangladesh, Cambodia and Vietnam. Selected organisations can receive between US$15,000 and US$50,000 over two years. The fund supports work connected to women’s health and safety, economic resilience, climate adaptation and the rights and wellbeing of women workers in global value chains. Funding is designed to give local organisations greater flexibility in responding to community priorities rather than restricting every grant dollar to narrowly defined activities. Applications for the current round opened on September 18, 2026.</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>15 October 2026</t>
+          <t>12 October 2026</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
+          <t>https://andpurpose.world/apply-for-resilience-fund-for-women-in-global-value-chains-2026/</t>
         </is>
       </c>
     </row>
@@ -6824,17 +6662,17 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for WUN Research Development Fund 2026</t>
+          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
+          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
+          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -6844,31 +6682,211 @@
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>15 October 2026</t>
+          <t>13 October 2026</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
+          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Mohamed bin Zayed Species Conservation Fund 2026</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>The Mohamed bin Zayed Species Conservation Fund is an international conservation initiative supporting practical efforts to protect threatened species around the world. The fund provides financial assistance to conservationists working to prevent species extinction and improve the conservation statu ... Read More</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>The Mohamed bin Zayed Species Conservation Fund provides grants for practical, field-based projects focused on threatened species conservation. The programme supports work involving endangered and critically endangered species and can also consider Data Deficient species where strong conservation needs are demonstrated. Funding may support activities such as field research, population monitoring, habitat protection, conservation planning and community-based species protection. For organisations and individuals searching for wildlife conservation grants, biodiversity funding and endangered species grants, the programme provides an opportunity to finance targeted conservation actions. The December 2026 funding cycle is currently accepting applications until October 2026.</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>15 October 2026</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/mohamed-bin-zayed-species-conservation-fund-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>15 October 2026</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for WUN Research Development Fund 2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>15 October 2026</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Greenprint GET Breakthrough Innovation Award 2027 for Indian Startups</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent policy research institution working on energy, environment, climate and sustainable development issues in India and beyond. CEEW brings together research, policy engagement and partnerships to support evidence-based solutions for ... Read More</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Eligible startups should apply through the Greenprint Awards application process before the closing date. Applicants should select the GET Breakthrough Innovation category and provide accurate information about their organisation, innovation, impact and contribution to the green economy. Supporting evidence should clearly demonstrate the systemic significance of the solution. Applicants should review the category requirements and terms before submitting. Only one category may be selected by each applicant. There is no entry fee for the Greenprint Awards.</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>16 October 2026</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-greenprint-get-breakthrough-innovation-award/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>RFP For Impact Assessment For FLN Program</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Centre For Microfinance &amp; Livelihood (Cml) | Goalpara, Bongaigaon and Baksa District., Assam
 RFP For Impact Assessment For FLN Program, Centre For Microfinance &amp; Livelihood (Cml)(Goalpara, Bongaigaon and Baksa District.) | DevNetJobsIndia
@@ -6881,7 +6899,7 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>• 3. Eligibility of bidder:
 a. The bidder can either be a propriety or partnership firm, company or any
@@ -7006,54 +7024,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -7084,202 +7102,22 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>16-10-2026</t>
         </is>
       </c>
-      <c r="H51" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I51" s="1" t="inlineStr">
+      <c r="H55" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303842</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>North Midlands Drought Resilience Community Grant 2026 – Apply by 16 October</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>TheAustralian Government’s Future Drought Fundand theWestern Australian Governmentjointly support the Regional Drought Resilience Planning Program. The programme helps regional communities strengthen their ability to prepare for and manage drought and prolonged dry seasons. Through regional planning ... Read More</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants must have a currentAustralian Business Number (ABN)or be auspiced by an incorporated organisation with an ABN. Applicants must have an account with an Australian financial institution and meet GST registration requirements where applicable. They must demonstrate sufficient organisational capacity, resources, partnerships, and arrangements to successfully deliver the proposed project. Projects must contribute to drought resilience and demonstrate alignment with the Mid West Regional Drought Resilience Plan. Applicants must also be able to manage project expenditure, monitor outcomes, deliver approved activities, and meet reporting and accountability requirements. These eligibility conditions apply to organisations seeking Future Drought Fund grants through this programme.</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>16 October 2026</t>
-        </is>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/north-midlands-drought-resilience-community-grant-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>16 October 2026</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>Apply for Greenprint Art and Culture Award 2027 for Climate Storytellers</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>16 October 2026</t>
-        </is>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I54" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-greenprint-art-and-culture-award-2027-for-climate-storytellers/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>Apply for Greenprint Rising Star Award 2027 for Women Climate Leaders</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.centered stories.</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>16 October 2026</t>
-        </is>
-      </c>
-      <c r="H55" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-greenprint-rising-star-award-2027/</t>
         </is>
       </c>
     </row>
@@ -7296,22 +7134,22 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>Apply for Greenprint GET Breakthrough Innovation Award 2027 for Indian Startups</t>
+          <t>Apply for Greenprint Art and Culture Award 2027 for Climate Storytellers</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>The Council on Energy, Environment and Water (CEEW) is an independent policy research institution working on energy, environment, climate and sustainable development issues in India and beyond. CEEW brings together research, policy engagement and partnerships to support evidence-based solutions for ... Read More</t>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Eligible startups should apply through the Greenprint Awards application process before the closing date. Applicants should select the GET Breakthrough Innovation category and provide accurate information about their organisation, innovation, impact and contribution to the green economy. Supporting evidence should clearly demonstrate the systemic significance of the solution. Applicants should review the category requirements and terms before submitting. Only one category may be selected by each applicant. There is no entry fee for the Greenprint Awards.</t>
+          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
@@ -7320,11 +7158,11 @@
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-greenprint-get-breakthrough-innovation-award/</t>
+          <t>https://andpurpose.world/apply-for-greenprint-art-and-culture-award-2027-for-climate-storytellers/</t>
         </is>
       </c>
     </row>
@@ -7341,35 +7179,35 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
+          <t>Apply for Greenprint Rising Star Award 2027 for Women Climate Leaders</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
+          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.centered stories.</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
+          <t>https://andpurpose.world/apply-for-greenprint-rising-star-award-2027/</t>
         </is>
       </c>
     </row>
@@ -7386,35 +7224,35 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Apply for Re-Alliance Upscaling &amp; Integrating Regeneration Grant 2026 – £13,625</t>
+          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscal ... Read More</t>
+          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscaling and Integrating Regeneration Grant, Re-Alliance is providing funding to a grassroots organisation in a Global South country to develop a new regenerative project. The grant also supports knowledge sharing with influential regional organisations or government bodies and collaboration to produce educational materials. The initiative particularly encourages applications from organisations working in Asia and the MENA region and those led by displaced people, refugees, women or affected communities. contemporary global issues.</t>
+          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-re-alliance-upscaling-integrating-regeneration-grant-2026-13625/</t>
+          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
         </is>
       </c>
     </row>
@@ -7431,17 +7269,17 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
+          <t>North Midlands Drought Resilience Community Grant 2026 – Apply by 16 October</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
+          <t>TheAustralian Government’s Future Drought Fundand theWestern Australian Governmentjointly support the Regional Drought Resilience Planning Program. The programme helps regional communities strengthen their ability to prepare for and manage drought and prolonged dry seasons. Through regional planning ... Read More</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
+          <t>Eligible applicants must have a currentAustralian Business Number (ABN)or be auspiced by an incorporated organisation with an ABN. Applicants must have an account with an Australian financial institution and meet GST registration requirements where applicable. They must demonstrate sufficient organisational capacity, resources, partnerships, and arrangements to successfully deliver the proposed project. Projects must contribute to drought resilience and demonstrate alignment with the Mid West Regional Drought Resilience Plan. Applicants must also be able to manage project expenditure, monitor outcomes, deliver approved activities, and meet reporting and accountability requirements. These eligibility conditions apply to organisations seeking Future Drought Fund grants through this programme.</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -7451,15 +7289,15 @@
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
+          <t>https://andpurpose.world/north-midlands-drought-resilience-community-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -7476,17 +7314,17 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Apply for Aidsfonds ActHIVate Fund 2026 – €2 Million Funding Pool</t>
+          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Aidsfonds is an international organisation working to end AIDS and improve access to HIV prevention, treatment, care and rights-based services. The organisation supports community-led responses and works with affected communities, civil society organisations and partners to address barriers to HIV s ... Read More</t>
+          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants are community-led, not-for-profit civil society organisations that are led by and primarily serve men who have sex with men and trans communities. Applicants must demonstrate experience in HIV-related health programming and advocacy. The current call covers organisations working in Uganda, Nigeria, Morocco, Egypt, Lebanon, Ukraine, Kazakhstan, Kyrgyzstan and Moldova. Organisations must be able to implement the proposed project during the specified 2027–2028 period and submit their application in English through the Aidsfonds Good Grants platform.</t>
+          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -7496,15 +7334,15 @@
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>25 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-aidsfonds-acthivate-fund-2026-e2-million-funding-pool/</t>
+          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
         </is>
       </c>
     </row>
@@ -7521,17 +7359,17 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Apply for WRF PFAS Contributions to Agricultural Systems Grant – US$400,000</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>The Water Research Foundation (WRF) is a research organisation supporting scientific studies and innovation related to water quality, water management and emerging environmental challenges. Through its Research Priority Program, WRF funds research addressing practical issues relevant to water and en ... Read More</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official WRF 2026 Research Priority Program guidelines and the RFP-5413 documentation before preparing their proposal. Required materials include the relevant certification and assurance documentation, co-funding support information, current and pending forms and project budget materials. Proposals must address the stated PFAS agricultural research objectives and follow WRF’s submission requirements. Applications are submitted through the WRF grant portal using an eligible organisation account.</t>
+          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -7541,15 +7379,15 @@
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>26 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-wrf-pfas-contributions-to-agricultural-systems/</t>
+          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
         </is>
       </c>
     </row>
@@ -7566,17 +7404,17 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
+          <t>Apply for Re-Alliance Upscaling &amp; Integrating Regeneration Grant 2026 – £13,625</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
+          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscal ... Read More</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
+          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscaling and Integrating Regeneration Grant, Re-Alliance is providing funding to a grassroots organisation in a Global South country to develop a new regenerative project. The grant also supports knowledge sharing with influential regional organisations or government bodies and collaboration to produce educational materials. The initiative particularly encourages applications from organisations working in Asia and the MENA region and those led by displaced people, refugees, women or affected communities. contemporary global issues.</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -7586,15 +7424,15 @@
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>26 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
+          <t>https://andpurpose.world/apply-for-re-alliance-upscaling-integrating-regeneration-grant-2026-13625/</t>
         </is>
       </c>
     </row>
@@ -7611,17 +7449,17 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
+          <t>National Geographic Ocean Exploration and Discovery Grant 2026</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
+          <t>The National Geographic Society is a global nonprofit organisation dedicated to exploring and understanding our world through science, research, education and storytelling. It supports scientists, conservationists, educators and explorers working on projects that advance knowledge and protect the pl ... Read More</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
+          <t>Applicants should review the Ocean Exploration and Discovery programme requirements and confirm their eligibility before preparing an application. The proposal should clearly explain the research objectives, methodology, expected outcomes and relevance to ocean exploration. Applicants must submit the required information and supporting materials through the designated application process before the closing date. Early preparation is recommended to ensure all required scientific and administrative information is complete.</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
@@ -7631,15 +7469,15 @@
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>28 October 2026</t>
+          <t>21 October 2026</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
+          <t>https://andpurpose.world/national-geographic-ocean-exploration-and-discovery-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -7656,17 +7494,17 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>Whitley Award 2027</t>
+          <t>Apply for Aidsfonds ActHIVate Fund 2026 – €2 Million Funding Pool</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
+          <t>Aidsfonds is an international organisation working to end AIDS and improve access to HIV prevention, treatment, care and rights-based services. The organisation supports community-led responses and works with affected communities, civil society organisations and partners to address barriers to HIV s ... Read More</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
+          <t>Eligible applicants are community-led, not-for-profit civil society organisations that are led by and primarily serve men who have sex with men and trans communities. Applicants must demonstrate experience in HIV-related health programming and advocacy. The current call covers organisations working in Uganda, Nigeria, Morocco, Egypt, Lebanon, Ukraine, Kazakhstan, Kyrgyzstan and Moldova. Organisations must be able to implement the proposed project during the specified 2027–2028 period and submit their application in English through the Aidsfonds Good Grants platform.</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -7676,31 +7514,211 @@
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>30 October 2026</t>
+          <t>25 October 2026</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/whitley-award-2027/</t>
+          <t>https://andpurpose.world/apply-for-aidsfonds-acthivate-fund-2026-e2-million-funding-pool/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>26 October 2026</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Apply for WRF PFAS Contributions to Agricultural Systems Grant – US$400,000</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>The Water Research Foundation (WRF) is a research organisation supporting scientific studies and innovation related to water quality, water management and emerging environmental challenges. Through its Research Priority Program, WRF funds research addressing practical issues relevant to water and en ... Read More</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should review the official WRF 2026 Research Priority Program guidelines and the RFP-5413 documentation before preparing their proposal. Required materials include the relevant certification and assurance documentation, co-funding support information, current and pending forms and project budget materials. Proposals must address the stated PFAS agricultural research objectives and follow WRF’s submission requirements. Applications are submitted through the WRF grant portal using an eligible organisation account.</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>26 October 2026</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-wrf-pfas-contributions-to-agricultural-systems/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>28 October 2026</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>Whitley Award 2027</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>30 October 2026</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/whitley-award-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="B69" s="1" t="inlineStr"/>
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>RFP - For the Empanelment of agencies to support the development, validati...</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS) | India
 RFP - For the Empanelment of agencies to support the development, validation, deployment, and scaling of AI-enabled agriculture solutions, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
@@ -7712,7 +7730,7 @@
 Value Membersh ... Read More</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 rfp.lehs(at)wadhwaniai.org
@@ -7791,54 +7809,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coaching &amp; Capacity Building Specialist
+National Program Officer- Adolescent and Maternal...
+Nutrition International
+Location:
+Delhi
+Apply by:
+30 Sep 2026
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+28 Sep 2026
+RFP - Hotel Selection for Training of Sub Nationa...
+TCI Foundation
+Location:
+Uttarakhand
+Apply by:
+02 Oct 2026
+SBC &amp; Creative Communication Expert
+IPE Global Limited
+Location:
+Delhi
+Apply by:
+25 Oct 2026
+ToR - Third-Party Auditor for FSS Assessment — Co...
+Deutsche Welthungerhilfe e.V
+Location:
+Uttarakhand
+Apply by:
+10 Oct 2026
+RFQ - Solar Powered Village (60 kWp Off-Grid Sola...
+Partnering Hope Into Action Foundation (PHIA)
+Location:
+Ladakh
+Apply by:
+14 Oct 2026
+RFP - Engagement of a Technical Consultant/Agency...
 Trickle Up India Foundation
 Location:
-Chhattisgarh
-Apply by:
-04 Oct 2026
-Training Consultants
-Project Concern International India (PCI India )
-Location:
-Chhattisgarh, Maharashtra
-Apply by:
-24 Oct 2026
-RFP - For Appointment of Resource Mobilization Ag...
-Deutsche Welthungerhilfe e.V
-Location:
-India
-Apply by:
-30 Sep 2026
-Pramukh Sewak (Principal)
-NGO Sapna / Sapna IT College
-Location:
-Rajasthan
-Apply by:
-24 Oct 2026
-Humanitarian Affairs and Institutional Advocacy L...
-Doctors Without Borders/ Médecins Sans Frontières...
-Location:
-India
-Apply by:
-16 Oct 2026
-Program Lead – Gig and platform component
-Jan Sahas Foundation
-Location:
-Maharashtra, Delhi
-Apply by:
-10 Oct 2026
-Consultant
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+West Bengal
 Apply by:
 08 Oct 2026
-RFP - Hiring an Hotel to Conference / workshop 5-...
-Jhpiego
-Location:
-Delhi
-Apply by:
-27 Sep 2026
+Consultant – Officer, Logistics
+ChildFund India
+Location:
+Tamil Nadu
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -7869,202 +7887,22 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
+      <c r="F69" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>31-10-2026</t>
         </is>
       </c>
-      <c r="H65" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="I65" s="1" t="inlineStr">
+      <c r="H69" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I69" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304046</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>Apply for TEEEM Foundation Community Impact Grant 2026 – Up to $30,000</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>The TEEEM Foundation supports nonprofit and charitable organisations working to improve lives and strengthen communities around the world. Its Community Impact Grant Program focuses on locally informed, sustainable solutions developed with communities rather than simply for them. The Foundation supp ... Read More</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>The grant is intended for nonprofit and charitable organisations working to improve communities around the world. Suitable applicants should have strong leadership and financial stewardship and demonstrate a clear understanding of the communities they serve. Projects should be community-centred and have measurable outcomes and a pathway toward sustainable impact. TEEEM identifies education and youth development, health and essential needs, equality and empowerment, entrepreneurship and economic opportunity, community infrastructure and sustainable community initiatives among its funding areas. Applicants should review the official application for the complete eligibility requirements and required documentation before applying.</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>1 November 2026</t>
-        </is>
-      </c>
-      <c r="H66" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-teeem-foundation-community-impact-grant-2026-up-to-30000/</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>National Indian Health Outreach and Education Program 2026</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>2 November 2026</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>4 November 2026</t>
-        </is>
-      </c>
-      <c r="H68" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for World Food Day Poster Contest 2026</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 6 November 2026</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>6 November 2026</t>
-        </is>
-      </c>
-      <c r="H69" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
         </is>
       </c>
     </row>
@@ -8081,17 +7919,17 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
+          <t>Apply for TEEEM Foundation Community Impact Grant 2026 – Up to $30,000</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
+          <t>The TEEEM Foundation supports nonprofit and charitable organisations working to improve lives and strengthen communities around the world. Its Community Impact Grant Program focuses on locally informed, sustainable solutions developed with communities rather than simply for them. The Foundation supp ... Read More</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
+          <t>The grant is intended for nonprofit and charitable organisations working to improve communities around the world. Suitable applicants should have strong leadership and financial stewardship and demonstrate a clear understanding of the communities they serve. Projects should be community-centred and have measurable outcomes and a pathway toward sustainable impact. TEEEM identifies education and youth development, health and essential needs, equality and empowerment, entrepreneurship and economic opportunity, community infrastructure and sustainable community initiatives among its funding areas. Applicants should review the official application for the complete eligibility requirements and required documentation before applying.</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
@@ -8101,15 +7939,15 @@
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>9 November 2026</t>
+          <t>1 November 2026</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
+          <t>https://andpurpose.world/apply-for-teeem-foundation-community-impact-grant-2026-up-to-30000/</t>
         </is>
       </c>
     </row>
@@ -8126,35 +7964,35 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
+          <t>National Indian Health Outreach and Education Program 2026</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
+          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
+          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>15 November 2026</t>
+          <t>2 November 2026</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
+          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
         </is>
       </c>
     </row>
@@ -8171,17 +8009,17 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for CRI Technology Impact Award Grant</t>
+          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
+          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
+          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
@@ -8191,15 +8029,15 @@
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>4 November 2026</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
+          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
         </is>
       </c>
     </row>
@@ -8216,17 +8054,17 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
+          <t>Applications Invited for World Food Day Poster Contest 2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
+          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
+          <t>The application deadline is 6 November 2026</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
@@ -8236,15 +8074,15 @@
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>6 November 2026</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
+          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
         </is>
       </c>
     </row>
@@ -8261,17 +8099,17 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
+          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
+          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
+          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
@@ -8281,15 +8119,15 @@
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>9 November 2026</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
+          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
         </is>
       </c>
     </row>
@@ -8306,17 +8144,17 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
+          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
+          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
+          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
@@ -8326,15 +8164,15 @@
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>15 November 2026</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
+          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
         </is>
       </c>
     </row>
@@ -8351,17 +8189,17 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
+          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
+          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
+          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
@@ -8371,15 +8209,15 @@
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
+          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
         </is>
       </c>
     </row>
@@ -8396,17 +8234,17 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
+          <t>Applications Open for CRI Technology Impact Award Grant</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research ... Read More</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
+          <t>TheCancer Research Institute (CRI)is a nonprofit organization dedicated to advancing cancer immunotherapy research and accelerating the development of innovative approaches to cancer treatment. CRI supports researchers working across cancer immunology, technology development, translational research and clinical applications. Through competitive funding programmes, the organization invests in scientists developing new ways to understand, detect and treat cancer by harnessing the immune system. Its Technology Impact Award focuses specifically on high-risk, high-reward technological innovation that could overcome important barriers in cancer immunotherapy. CRI aims to accelerate discoveries that can generate new biological insights, enable better therapeutic development and ultimately contribute to improved outcomes for cancer patients.</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
@@ -8416,15 +8254,15 @@
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
+          <t>https://andpurpose.world/applications-open-for-cri-technology-impact-award-grant/</t>
         </is>
       </c>
     </row>
@@ -8441,35 +8279,35 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
+          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
+          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
+          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
+          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
         </is>
       </c>
     </row>
@@ -8486,35 +8324,35 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
+          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
+          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
+          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>20 December 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
         </is>
       </c>
     </row>
@@ -8531,17 +8369,17 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Apply for Ernest Solvay Fund 2026 – Up to €10,000</t>
+          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>The Ernest Solvay Fund supports non-commercial initiatives that contribute to scientific education, environmental sustainability and community wellbeing. The fund focuses on three broad areas: STEM education, Planet Progress and Better Life. It supports organisations developing practical projects re ... Read More</t>
+          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>The fund is open to organisations implementing eligible non-commercial projects. Proposed initiatives must fall under STEM education, Planet Progress or Better Life and must be implemented within 100 kilometres of an eligible Solvay industrial, R&amp;D or administrative site. Commercial sites do not qualify for the geographic requirement. Relevant projects can involve science and technology education, biodiversity, environmental protection, energy, water and air quality or community wellbeing. Applicants should verify that their project location meets the distance requirement before preparing their application.</t>
+          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
@@ -8551,15 +8389,15 @@
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>30 December 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-ernest-solvay-fund-2026/</t>
+          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8414,17 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Apply for FIER·ES Ukraine Psychosocial &amp; Emergency Support 2026 – Up to €2,300</t>
+          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ERIM is an international nonprofit organisation working to strengthen human rights, independent media and civil society. Through programmes supporting civil society organisations and activists, ERIM provides capacity building, grants and other assistance to organisations and individuals facing diffi ... Read More</t>
+          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>The FIER·ES Programme provides two forms of support in Ukraine. Eligible applicants can receive up to€500 for psychosocial and wellbeing supportand up to€2,300 in emergency assistancefor eligible needs such as legal aid, security measures, medical expenses and relocation assistance. The programme aims to strengthen the resilience and safety of LGBTQIA+ activists and civil society actors while helping organisations and individuals continue their human rights and inclusion work. Applications remain open on a continuing basis through the published deadline, subject to programme requirements and available support.</t>
+          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
@@ -8596,15 +8434,15 @@
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>31 December 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-fier%c2%b7es-ukraine-psychosocial-emergency-support/</t>
+          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
         </is>
       </c>
     </row>
@@ -8621,17 +8459,17 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
+          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
+          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
+          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
@@ -8641,15 +8479,15 @@
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>14 January 2027</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
+          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
         </is>
       </c>
     </row>
@@ -8666,35 +8504,35 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
+          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
+          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
+          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>15 January 2027</t>
+          <t>20 December 2026</t>
         </is>
       </c>
       <c r="H83" s="1" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
+          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -8711,17 +8549,17 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>J. N. Derbyshire Trust Grants UK: Apply for Up to £10,000</t>
+          <t>Apply for Ernest Solvay Fund 2026 – Up to €10,000</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, ... Read More</t>
+          <t>The Ernest Solvay Fund supports non-commercial initiatives that contribute to scientific education, environmental sustainability and community wellbeing. The fund focuses on three broad areas: STEM education, Planet Progress and Better Life. It supports organisations developing practical projects re ... Read More</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, advancing education, and relieving poverty, distress and sickness. The Trust primarily supports community and voluntary organisations through project funding. It operates as a grant-making charity and reviews applications through two annual grant rounds. The Trust prioritises organisations delivering meaningful benefits within Nottingham and Nottinghamshire.</t>
+          <t>The fund is open to organisations implementing eligible non-commercial projects. Proposed initiatives must fall under STEM education, Planet Progress or Better Life and must be implemented within 100 kilometres of an eligible Solvay industrial, R&amp;D or administrative site. Commercial sites do not qualify for the geographic requirement. Relevant projects can involve science and technology education, biodiversity, environmental protection, energy, water and air quality or community wellbeing. Applicants should verify that their project location meets the distance requirement before preparing their application.</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
@@ -8731,15 +8569,15 @@
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>31 January 2027</t>
+          <t>30 December 2026</t>
         </is>
       </c>
       <c r="H84" s="1" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/j-n-derbyshire-trust-grants/</t>
+          <t>https://andpurpose.world/apply-for-ernest-solvay-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -8756,17 +8594,17 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
+          <t>Apply for FIER·ES Ukraine Psychosocial &amp; Emergency Support 2026 – Up to €2,300</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
+          <t>ERIM is an international nonprofit organisation working to strengthen human rights, independent media and civil society. Through programmes supporting civil society organisations and activists, ERIM provides capacity building, grants and other assistance to organisations and individuals facing diffi ... Read More</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
+          <t>The FIER·ES Programme provides two forms of support in Ukraine. Eligible applicants can receive up to€500 for psychosocial and wellbeing supportand up to€2,300 in emergency assistancefor eligible needs such as legal aid, security measures, medical expenses and relocation assistance. The programme aims to strengthen the resilience and safety of LGBTQIA+ activists and civil society actors while helping organisations and individuals continue their human rights and inclusion work. Applications remain open on a continuing basis through the published deadline, subject to programme requirements and available support.</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
@@ -8776,15 +8614,15 @@
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>15 February 2027</t>
+          <t>31 December 2026</t>
         </is>
       </c>
       <c r="H85" s="1" t="n">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
+          <t>https://andpurpose.world/apply-for-fier%c2%b7es-ukraine-psychosocial-emergency-support/</t>
         </is>
       </c>
     </row>
@@ -8801,17 +8639,17 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
+          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
+          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
+          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
@@ -8821,15 +8659,15 @@
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>8 March 2027</t>
+          <t>14 January 2027</t>
         </is>
       </c>
       <c r="H86" s="1" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
+          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
         </is>
       </c>
     </row>
@@ -8846,144 +8684,215 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
+          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
+          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
+          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>30 June 2027</t>
+          <t>15 January 2027</t>
         </is>
       </c>
       <c r="H87" s="1" t="n">
-        <v>279</v>
+        <v>112</v>
       </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
+          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B88" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>RFP for Turnkey Set-up of Rohini Skilling Centre Click
-                    here</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr"/>
+          <t>J. N. Derbyshire Trust Grants UK: Apply for Up to £10,000</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, ... Read More</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, advancing education, and relieving poverty, distress and sickness. The Trust primarily supports community and voluntary organisations through project funding. It operates as a grant-making charity and reviews applications through two annual grant rounds. The Trust prioritises organisations delivering meaningful benefits within Nottingham and Nottinghamshire.</t>
+        </is>
+      </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>31 January 2027</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>128</v>
+      </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/RFP_Turnkey_Setup_Rohini_Skilling_Centre_Branded.pdf</t>
+          <t>https://andpurpose.world/j-n-derbyshire-trust-grants/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B89" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="inlineStr"/>
+          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
+        </is>
+      </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>15 February 2027</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>143</v>
+      </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
+          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B90" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr"/>
+          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
+        </is>
+      </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>8 March 2027</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>164</v>
+      </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
+          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B91" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
+        </is>
+      </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>30 June 2027</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>278</v>
+      </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
+          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8905,7 @@
       <c r="B92" s="1" t="inlineStr"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
+          <t>RFP for Turnkey Set-up of Rohini Skilling Centre Click
                     here</t>
         </is>
       </c>
@@ -9011,7 +8920,7 @@
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/RFP_Turnkey_Setup_Rohini_Skilling_Centre_Branded.pdf</t>
         </is>
       </c>
     </row>
@@ -9024,21 +8933,21 @@
       <c r="B93" s="1" t="inlineStr"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>RFP for Women Entrepreneurship Programme - Click here</t>
+          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -9051,21 +8960,21 @@
       <c r="B94" s="1" t="inlineStr"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -9078,22 +8987,21 @@
       <c r="B95" s="1" t="inlineStr"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
-                    here</t>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -9105,120 +9013,122 @@
       </c>
       <c r="B96" s="1" t="inlineStr"/>
       <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
+                    here</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr"/>
+      <c r="H96" s="1" t="inlineStr"/>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr"/>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Women Entrepreneurship Programme - Click here</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr"/>
+      <c r="H97" s="1" t="inlineStr"/>
+      <c r="I97" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr"/>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr"/>
+      <c r="H98" s="1" t="inlineStr"/>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr"/>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+                    here</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="inlineStr"/>
+      <c r="H99" s="1" t="inlineStr"/>
+      <c r="I99" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr"/>
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
                 India Pvt. Ltd - Click here | Click
                     here</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr"/>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="inlineStr"/>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B99" s="1" t="inlineStr"/>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B100" s="1" t="inlineStr"/>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
-        </is>
-      </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
@@ -9230,7 +9140,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -9243,22 +9153,21 @@
       <c r="B101" s="1" t="inlineStr"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
-                    here</t>
+          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
         </is>
       </c>
     </row>
@@ -9271,21 +9180,21 @@
       <c r="B102" s="1" t="inlineStr"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
+          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9207,7 @@
       <c r="B103" s="1" t="inlineStr"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
@@ -9312,7 +9221,7 @@
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9234,7 @@
       <c r="B104" s="1" t="inlineStr"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -9339,7 +9248,7 @@
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
         </is>
       </c>
     </row>
@@ -9352,21 +9261,22 @@
       <c r="B105" s="1" t="inlineStr"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
+                    here</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
         </is>
       </c>
     </row>
@@ -9379,21 +9289,21 @@
       <c r="B106" s="1" t="inlineStr"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9316,7 @@
       <c r="B107" s="1" t="inlineStr"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -9420,7 +9330,7 @@
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
@@ -9433,21 +9343,21 @@
       <c r="B108" s="1" t="inlineStr"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9370,7 @@
       <c r="B109" s="1" t="inlineStr"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -9474,7 +9384,7 @@
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -9487,21 +9397,21 @@
       <c r="B110" s="1" t="inlineStr"/>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -9514,22 +9424,21 @@
       <c r="B111" s="1" t="inlineStr"/>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
-                education in STEM courses - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -9542,21 +9451,21 @@
       <c r="B112" s="1" t="inlineStr"/>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -9569,21 +9478,21 @@
       <c r="B113" s="1" t="inlineStr"/>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -9596,8 +9505,7 @@
       <c r="B114" s="1" t="inlineStr"/>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
-                and Financial Management - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -9611,7 +9519,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -9624,8 +9532,8 @@
       <c r="B115" s="1" t="inlineStr"/>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
-                    here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
+                education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -9639,7 +9547,7 @@
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -9652,8 +9560,7 @@
       <c r="B116" s="1" t="inlineStr"/>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -9667,7 +9574,7 @@
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -9680,8 +9587,7 @@
       <c r="B117" s="1" t="inlineStr"/>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
@@ -9695,7 +9601,7 @@
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -9708,21 +9614,22 @@
       <c r="B118" s="1" t="inlineStr"/>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
+                and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9642,8 @@
       <c r="B119" s="1" t="inlineStr"/>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
+                    here</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
@@ -9749,7 +9657,7 @@
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -9762,21 +9670,22 @@
       <c r="B120" s="1" t="inlineStr"/>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9698,8 @@
       <c r="B121" s="1" t="inlineStr"/>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
@@ -9803,24 +9713,20 @@
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr"/>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
@@ -9830,120 +9736,92 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>31st Aug, 2026</t>
-        </is>
-      </c>
+      <c r="G122" s="1" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr"/>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Senior Programme Officer - Uday</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>15th Aug, 2026</t>
-        </is>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr"/>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr"/>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>29th Jun, 2026</t>
-        </is>
-      </c>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr"/>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr"/>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>10th Feb, 2026</t>
-        </is>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
@@ -9960,25 +9838,25 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>31st Aug, 2026</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
         </is>
       </c>
     </row>
@@ -9995,25 +9873,25 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>Senior Programme Officer - Uday</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>15th Aug, 2026</t>
         </is>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -10030,25 +9908,25 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>29th Jun, 2026</t>
         </is>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
         </is>
       </c>
     </row>
@@ -10065,25 +9943,25 @@
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
@@ -10100,25 +9978,25 @@
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -10135,133 +10013,165 @@
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>15th May, 2025</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9937006.pdf</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="1" t="inlineStr"/>
-      <c r="G132" s="1" t="inlineStr"/>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>10th Nov, 2025</t>
+        </is>
+      </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9937006.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>EOI FOR INTEGRATING WOMEN ENTREPRENEURS INTO CIRCULAR ECONOMY VALUE CHAINS A ROADMAP FOR CITIES.pdf</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="1" t="inlineStr"/>
-      <c r="G133" s="1" t="inlineStr"/>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>31st Oct, 2025</t>
+        </is>
+      </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20INTEGRATING%20WOMEN%20ENTREPRENEURS%20INTO%20CIRCULAR%20ECONOMY%20VALUE%20CHAINS%20A%20ROADMAP%20FOR%20CITIES.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>EOI for Onboarding of Partner Institutes for LCCM.pdf</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="1" t="inlineStr"/>
-      <c r="G134" s="1" t="inlineStr"/>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>21st May, 2025</t>
+        </is>
+      </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI%20for%20Onboarding%20of%20Partner%20Institutes%20for%20LCCM.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>RFP_Technical_Assistance_SAM_Final.pdf</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="1" t="inlineStr"/>
-      <c r="G135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Technical_Assistance_SAM_Final.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10188,7 @@
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9891532.pdf</t>
+          <t>GeM-Bidding-9937006.pdf</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
@@ -10288,7 +10198,7 @@
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9891532.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9937006.pdf</t>
         </is>
       </c>
     </row>
@@ -10305,7 +10215,7 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
+          <t>EOI FOR INTEGRATING WOMEN ENTREPRENEURS INTO CIRCULAR ECONOMY VALUE CHAINS A ROADMAP FOR CITIES.pdf</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
@@ -10315,7 +10225,7 @@
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20INTEGRATING%20WOMEN%20ENTREPRENEURS%20INTO%20CIRCULAR%20ECONOMY%20VALUE%20CHAINS%20A%20ROADMAP%20FOR%20CITIES.pdf</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10242,7 @@
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
+          <t>EOI for Onboarding of Partner Institutes for LCCM.pdf</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
@@ -10342,7 +10252,7 @@
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI%20for%20Onboarding%20of%20Partner%20Institutes%20for%20LCCM.pdf</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10269,7 @@
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
+          <t>RFP_Technical_Assistance_SAM_Final.pdf</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
@@ -10369,7 +10279,7 @@
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_Technical_Assistance_SAM_Final.pdf</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10296,7 @@
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
+          <t>GeM-Bidding-9891532.pdf</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -10396,7 +10306,7 @@
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9891532.pdf</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10323,7 @@
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
+          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -10423,7 +10333,7 @@
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10350,7 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>UHI_RFP_Formatted_10072026.pdf</t>
+          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -10450,7 +10360,7 @@
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10467,7 +10377,7 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9590033.pdf</t>
+          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr"/>
@@ -10477,7 +10387,7 @@
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10404,7 @@
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
+          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr"/>
@@ -10504,7 +10414,7 @@
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10431,7 @@
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
+          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr"/>
@@ -10531,7 +10441,7 @@
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10458,7 @@
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
+          <t>UHI_RFP_Formatted_10072026.pdf</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr"/>
@@ -10558,7 +10468,7 @@
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP_CORRIGENDUM%20I_150726.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10485,7 @@
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>05.06.2026_EOI-RFP_Kedarnath and Amarnath Yatra.pdf</t>
+          <t>GeM-Bidding-9590033.pdf</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr"/>
@@ -10585,7 +10495,7 @@
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/05.06.2026_EOI-RFP_Kedarnath%20and%20Amarnath%20Yatra.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10512,7 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>SOP_Kedarnath and Amarnath_corrigendum_1.pdf</t>
+          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -10612,7 +10522,7 @@
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP_Kedarnath%20and%20Amarnath_corrigendum_1.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10539,7 @@
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>SOP-Kedarnath Amarnath_PRe-bid queries.pdf</t>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr"/>
@@ -10639,6 +10549,114 @@
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
         <is>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="1" t="inlineStr"/>
+      <c r="G150" s="1" t="inlineStr"/>
+      <c r="H150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP_CORRIGENDUM%20I_150726.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>05.06.2026_EOI-RFP_Kedarnath and Amarnath Yatra.pdf</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="1" t="inlineStr"/>
+      <c r="G151" s="1" t="inlineStr"/>
+      <c r="H151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/05.06.2026_EOI-RFP_Kedarnath%20and%20Amarnath%20Yatra.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>SOP_Kedarnath and Amarnath_corrigendum_1.pdf</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="1" t="inlineStr"/>
+      <c r="G152" s="1" t="inlineStr"/>
+      <c r="H152" s="1" t="inlineStr"/>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/SOP_Kedarnath%20and%20Amarnath_corrigendum_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>SOP-Kedarnath Amarnath_PRe-bid queries.pdf</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="1" t="inlineStr"/>
+      <c r="G153" s="1" t="inlineStr"/>
+      <c r="H153" s="1" t="inlineStr"/>
+      <c r="I153" s="1" t="inlineStr">
+        <is>
           <t>https://niua.in/sites/default/files/tenders/SOP-Kedarnath%20Amarnath_PRe-bid%20queries.pdf</t>
         </is>
       </c>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -609,54 +609,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -821,54 +821,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -1078,54 +1078,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -1304,54 +1304,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -1549,54 +1549,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
@@ -1812,54 +1812,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="H14" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -2606,54 +2606,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
@@ -3006,54 +3006,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -3227,54 +3227,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -3480,54 +3480,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -3695,54 +3695,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -4116,54 +4116,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
@@ -4364,54 +4364,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" s="1" t="inlineStr">
         <is>
@@ -5376,54 +5376,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
@@ -6161,54 +6161,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Cluster Coordinators
+Account Person
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+HR Coordinator
 (Value Members only)
 Location:
-Rajasthan, Gujarat, Maharashtra
+Assam
+Apply by:
+09 Oct 2026
+Counselor
+Asian Minority Action Network
+Location:
+Jharkhand
 Apply by:
 10 Oct 2026
-Computer Instructor
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Project Associate
+Master Trainer
 (Value Members only)
 Location:
-Maharashtra
+Gujarat
+Apply by:
+10 Oct 2026
+MIS Executive - DDU-GKY Project
+Nifa India
+Location:
+West Bengal
+Apply by:
+24 Oct 2026
+Fundraising Executive / Manager
+(Value Members only)
+Location:
+Karnataka
 Apply by:
 07 Oct 2026
-Field Coordinator
-Adhwana Kerala Forum of Partners in Functional Vo...
-Location:
-Kerala
-Apply by:
-30 Sep 2026
-Chief Executive Officer
+Community Outreach Workers
+Sangini
+Location:
+Madhya Pradesh
+Apply by:
+05 Oct 2026
+Senior Program Manager, Assistant Project Manager...
 (Value Members only)
 Location:
-Delhi
-Apply by:
-06 Oct 2026
-Support Teacher
-Help for Children in Need Foundation
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Program Manager
-(Value Members only)
-Location:
-West Bengal
-Apply by:
-30 Sep 2026
-Counsellor
-Aditya Information Management Society
-Location:
-Madhya Pradesh
-Apply by:
-30 Sep 2026
+Haryana
+Apply by:
+10 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="H83" s="1" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="H84" s="1" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="H85" s="1" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I85" s="1" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="H86" s="1" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I86" s="1" t="inlineStr">
         <is>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -483,218 +483,37 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - Design and Delivery of Street Play (Nukkad Natak), Puppet Theatre, a...</t>
+          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Centre for Catalyzing Change (C3) | Rajasthan
-RFP - Design and Delivery of Street Play (Nukkad Natak), Puppet Theatre, and Theatre-Based Workshops on Gender Equity in Selected Districts..., Centre for Catalyzing Change (C3)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broa ... Read More</t>
+          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• Introduction &amp; Organizational Context
-The Centre for Catalyzing Change (C3) is a leading national non-profit organization dedicated to empowering women and adolescent girls through innovative, evidence-based programmes. For over 30 years, C3 has worked to advance education, health, safety, life skills, and economic opportunities by strengthening systems and influencing public policy.
-In Rajasthan, C3 partners with the Rajasthan State Rural Livelihood Mission to carry gender-equity messaging directly into communities through accessible, participatory formats, complementing the initiative's curriculum and training-based interventions with men, boys, and young women.
-Project Goals and Objectives
-Goal
-To use street play, puppet theatre, and theatre-based workshops as an engaging, participatory medium to build community awareness on gender equity, positive masculinities, and safety in selected districts of Rajasthan, while building local capacity to sustain such community engagement beyond the assignment.
-Objectives
-Design and deliver street play (Nukkad Natak) performances on gender equity, contextualized to villages and Gram Panchayats across the target districts.
-Deliver puppet theatre performances as a complementary medium, particularly suited to engaging children and younger audiences.
-Conduct a 2-day theatre-based workshop in each target district to build a local cadre of community facilitators skilled in participatory theatre techniques.
-Document performance reach, audience engagement, and key learnings to inform future community engagement strategy.
-Submission Instructions
-Submit to:
-procurement@c3india.org
-Subject line: "Proposal for Street Theatre
-–
-[Agency Name]"
-Deadline: 27
-th
-September 2026, 5:00 PM IST. Proposals received after this deadline will not be considered.
-Queries: Written questions only, submitted by 22
-nd
-September 2026 to the e-mail address above. Responses will be circulated to all agencies who have expressed interest, to keep the process fair and transparent.
-Contact for this assignment: State Head
-–
-Centre for Catalyzing Change (C3), Jaipur, Rajasthan.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-C3_RFP_Street_Play_Puppet_Theatre_Workshop_Rajasthan.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-27 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Account Person
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
-Location:
-Haryana
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
+          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Climate, Safety</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>27-09-2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -702,211 +521,44 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303890</t>
+          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>ToR - Consultant for Content Development for Gender Resource Centre</t>
+          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Breakthrough | India
-ToR - Consultant for Content Development for Gender Resource Centre, Breakthrough() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ID:
-30 ... Read More</t>
+          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• Job Email ID:
-rfp(at)inbreakthrough.org
-Download Attachment:
-• Scope of work- GRC.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-27 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Account Person
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
-Location:
-Haryana
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
+          <t>The application deadline is 29 September 2026</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>27-09-2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
@@ -914,7 +566,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304041</t>
+          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
         </is>
       </c>
     </row>
@@ -927,1361 +579,10 @@
       <c r="B4" s="1" t="inlineStr"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Tender notice for Installation of 2 Nos ARU Bahraich</t>
+          <t>RFQ - for Solar Home Lightning Procurement for SAHAS Project</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Bahraich, Uttar Pradesh
-Tender notice for  Installation of 2 Nos ARU Bahraich, WaterAid India(Bahraich) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Reg ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• Interested Bidders are required to submit their complete proposal on their letter heads along with all terms and conditions to email id:
-WAIProcurementUP@wateraid.org
-by 28
-th
-September 2026 w
-hich should necessarily include:
-For any queries pertaining to the tender, please write to
-me before 25
-th
-September,2026
-.
-Profile of the organization, given as per the below –
-1.
-Profile of Bidder-
-Name of Organization:
-Registration Certificate:
-GST Certificate
-Last three years Balance sheet
-MSME Certificate (if registered) 6. 3 years Tax return File (attached)
-Address for correspondence:
-Office Phone:
-Mobile Phones of corresponding officials:
-Email for correspondence:
-Locations of operations (Head office and Branch offices):
-All certificates must be attached.
-• Terms and Conditions:
-Submit Quotations with subject line Items –
-Quotation for Installation of 2 Nos ARU Bahraich
-Without subject quotation will not consider for further process
-Pproposal’s should  be addressed to Jal Seva Charitable Foundation,
-2/92,
-Vishal Khand Gomti Nagar Lucknow 226010
-The Proposal must be on the company letter head with date, signature and company seal. (It is to be signed by the authorized person).
-Proposals must be submitted to Procurement Email ID:
-WAIProcurementUP@wateraid.org
-Any proposal submitted to any other email id will not be considered.
-The Proposal to be submitted as
-two separate attachment
-– 1. Technical proposal as per the BOQ and Financial proposal in non-editable PDF Format.
-The proposal must have the subject mentioning the village name given in the table below of point
-12.
-THE PROPOSAL MUST BE SUBMITTED AS A SEPARATE ATTACHMENT FOR EACH VILLAGE (four attachments). Kindly refer the BOQ given.
-Proposals received after due date will not be considered.
-Financial proposals must be submitted inclusive of applicable taxes and mentioning the validity of the quoted rate.
-• All terms and conditions must be clearly mentioned in the proposals.
-Incomplete proposals shall not be considered
-The work shall be completed on or before 30 October 2026
-Payment shall be released based on the actual work completed and verified.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Tender notice for  Installation of 2 Nos ARU Bahraich.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-28 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Account Person
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
-Location:
-Haryana
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304070</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Video documentation of change stories on Ground water replenishment ...</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Hyderabad and Sanga Reddy, Telangana
-RFP - Video documentation of change stories on Ground water replenishment in Hyderabad and Sanga Reddy locations, WaterAid India(Hyderabad and Sanga Reddy) | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFP ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• In this context, Jal Seva Charitable Foundation (JSCF) seeks to engage a consultant for ‘Video Documentation of Change Stories’ as outlined in the following terms and conditions.
-Objective of the contract:
-The objective of this assignment is to capture and document post-intervention activities of ground water replenishment in Sherlingampally Zone in Hyderabad and in Sangareddy district through video documentation.
-Scope of assignment &amp; expected outcome:
-This assignment involves producing a 6-minute video capturing real-life change stories resulting from water-harvesting interventions.
-The assignment includes the following deliverables:
-1.
-A 6-minute, high-resolution video showcasing the impact of water-harvesting infrastructure through community testimonials. It will include interviews, relevant field visuals and a clear storyline highlighting the changes brought about by the interventions. The video will effectively capture community experiences, benefits, and key outcomes.
-Duration of the
-• contract: The Consultancy Agreement will be effective for a period of 20 days from the date of signing and is expected to be completed by 30 October 2026, unless extended in writing by JSCF. Any extension will be subject to additional or revised terms and conditions as mutually agreed upon in writing between the Consultant and JSCF.
-Reporting point and Progress Report
-For matters covered by the TORs and this agreement, you will report directly to Mr Pachimadla Krishna, Program Coordinator, Telangana, JSCF, and submit reports as specified in the TORs.
-Payment Schedule
-Condition for   Payment
-20%
-40%
-40%
-Upon signing of the Contract
-Upon submission of 6 Minutes of Drafted Video
-Upon   completion of Assignment
-Contact
-For submission of Proposal, queries and clarifications
-Please mail to this email i.d.
-WAIProcurementAP@wateraid.org
-Experience in strategic communications, digital storytelling and social media management.
-Strong photography, videography and content development skills.
-• Job Email ID:
-WAIProcurementAP(at)wateraid.org
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-28 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Account Person
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
-Location:
-Haryana
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303896</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Final Evaluation of Support Micro/Small entrepreneurs among part...</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Deutsche Welthungerhilfe e.V | India
-RFP - for Final Evaluation of Support Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans, Deutsche Welthungerhilfe e.V() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Searc ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• INTRODUCTION ANDCONTEXT
-Country:
-India
-Project   title:
-Support   Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans
-Project   no.:
-1409-23
-Project   holder:
-Welthungerhilfe
-Project   budget:
-500000 USD
-Co-financer   (line):
-SPF
-Project   period:
-01/07/2023 - 30/11/2026
-Deutsche Welthungerhilfe e. V.
-is one of the largest non-governmental organization’s in Germany operating in the humanitarian assistance and development fields. It was established in 1962, as the German section of the “Freedom from Hunger Campaign”, one of the world’s first initiatives aimed at the eradication of hunger. Welthungerhilfe’s work is still dedicated to the following vision: All people have a right to a self-determined life in dignity and justice, free from hunger and poverty.
-WHH India operated as the Regional Office for India, Nepal, Sri Lanka, and Bangladesh between 2007 and 2013. Since 2014, it has been functioning as the India Country Office.
-Welthungerhilfe
-India today works in priority regions across 10 states, engaging with grassroots organizations, local governments, and strategic actors at regional, national, and global levels.
-The
-focus is on integrated and scalable approaches in food systems transformation, WASH (water, sanitation and hygiene), and green skilling, with rural youth and women at the heart of everything we do.
-The Ramakrishna Mission Ashrama, Narendrapur, through its specialized development wing, Lokasiksha Parishad, has been actively engaged in community development across South Bengal for over five decades. Operating through a structured rural development framework, the Parishad currently collaborates with more than 300 grassroots organizations spanning 12 districts. The primary mission of the Parishad is the holistic advancement of marginalized communities. Its core interventions encompass informal and value-based education, mother and child development, environmental promotion, healthcare and basic sanitation, livelihood enhancement, income-generation programs and vocational, distressed relief and technical skill development for the youth.
-About the Project
-Sundarbans is a part of the tidally active delta where the land building process is still incomplete with Ganges-Brahmaputra River system carries suspended sediment load through numerous interlacing channels, intervening islands with the elevation of less than 3 meters above msl. Agriculture forms the backbone of the economy of Sundarban, where the entire area is dependent on a single crop, the rain-fed (mostly high yielding varieties) paddy. Sundarbans, is threatened by various biophysical and social barriers, emerges as a unique case where the most vulnerable population lives in an extremely vulnerable situation with high risk of hazards which is characterized by a low level of development and lack of infrastructure, prevalence of extreme poverty and lack of health facilities. It is also under the threat of severe coastal erosion due to relative sea level rise, increase in surface air temperatures and increased intensity of cyclone.
-For the project titled “Support Micro/Small entrepreneurs among particularly vulnerable   communities in the Sundarbans”, Welthungerhilfe Country Office India with the funding support from SPF and an earlier phase supported by Oak Foundation and through its implementation partner Ramakrishna Mission Ashrama, Narendrapur seeks to empower socially, economically, and ecologically vulnerable communities in Sundarbans by creating a diversified basket of opportunities through supporting microenterprises in collaboration with grassroots CSOs. Through this project, in Sundarbans, a total of 1200 members from these vulnerable communities with special focus on youth and women are being trained on location specific and climate resilient trades (agri-allied and non-farm both) coupled with business and soft skills. The potential trainees will be further supported to set up micro enterprises by establishing backward and forward linkages. Based on local resources and interest of the communities, two value chains will be established and the value chain actors and communities will be further collectivized in two sustainable and resilient microenterprises in the form of registered community institutions or Farmer Producer Companies to achieve economies of scale and self-sufficiency. Overall, the project will ensure transition of targeted communities from subsistence-level livelihoods to sustainable microenterprises.
-Project Participants:
-1200 community members from ecologically/socially vulnerable communities, especially women who will be trained on at least 5 trades.
-Two Farmer Producer Organizations will be created with at least 200 community members.
-Geographical outreach of project, participants profile and other details: List of the Blocks, Panchayats in Annex-1
-Objectives:
-Strengthen value chains, based on local resources to increase income of the targeted communities.
-Facilitate the transition of targeted communities from subsistence-level livelihoods to sustainable microenterprises.
-Establish an informal collaborative of grassroots CSOs to identify and foster value chains, promoting sustainable economic development in the region.
-The interested agencies/Agency/Consultants can share the proposals to
-gagan.mehta@welthungerhilfe.de
-with a copy to
-poonam.mishra@welthungerhilfe.de
-rahul.jain@welthungerhilfe.de
-or before
-28
-th
-September 2026 (5 PM IST).
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Final ToR for Final Evaluation-1409-23.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-28 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Account Person
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
-Location:
-Haryana
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303597</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Proj...</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Aga Khan Foundation (India) | Bihar
-RFP - Onboarding a consulting agency to Conduct a Baseline Study for “Project Dhenu Dhara – Foraging pathways to improving livestock health and dairy , Aga Khan Foundation (India)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Re ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• Bidders may alter or withdraw their bids by written notification prior to the stated deadline for submission of bids. No bids may be altered after this deadline. Withdrawals must be unconditional and will end all participation in the bid procedure.
-6. Opening of bid
-The bid will be opened by the Aga Khan Foundation within
-15 days
-from the deadline for the submission of the bid.
-Any attempt by a bidder to influence the evaluation committee in the process of examination, clarification, evaluation and comparison of bids, to obtain information on how the procedure is progressing or to influence the contracting authority in its decision concerning the award of the contract will result in immediate rejection of its bid.
-• 7. Submission of bids
-The bid has to be submitted in the prescribed format on or before
-Monday,
-28
-th
-September
-202
-6
-by 5 p.m.
-Indian
-Standard Time to
-akfindia.helpdesk@akdn.org
-Technical and financial proposals should be
-submitted simultaneously, but in separate emails
-, with the RFP reference and the clear description of the proposal (technical or financial) by the date and time stipulated in this document. If the emails and email attachments are not marked as instructed, AKF will assume no responsibility for the misplacement or premature opening of the proposals submitted.
-Both email text bodies should indicate the name and address of the bidder and the description of the proposal (technical or financial). The technical email should not contain any pricing information, nor should the financial email contain any component of the technical proposal.
-Technical proposals should be submitted in one (1) email accompanied by the forms prescribed in this
-RFP, clearly marked as “technical proposal”
-- in the email subject line and corresponding attachment should read: (RFP Reference No.)
-–
-(name of bidder)
-–
-TECHNICAL PROPOSAL
-The technical proposal should not contain any details of the financial proposal / budget.
-Any financial information contained in the technical proposal will invalidate the proposal.
-Financial proposals should be submitted in one (1) email with the email subject line as ‘FINANCIAL PROPOSAL’ and corresponding email attachment should read: (RFP Reference No.) –
-(name of bidder)
-–
-FINANCIAL PROPOSAL.
-The
-Financial Proposal should contain the budget in a password protected file (excel and/or pdf), which can be opened only with the password. The bidder should not mention any financial amounts in the email text body, or the password.
-Passwords should be made available only at a later date, when requested for by AKF.
-Proposals should be received by the date, time and means of submission stipulated in this RFP. Bidders are responsible for ensuring that AKF receives their proposal by the due date and time. Proposals received by AKF after the due date and time may be rejected. When receiving proposals by email (as is required for the RFP), the receipt time stamp shall be the date and time when the submission has been received in the dedicated AKF inbox. AKF shall not be responsible for any delays caused by network problems, etc. It is the sole responsibility of bidders to ensure that their proposal is received by AKF in the dedicated inbox on or before the prescribed RFP deadline.
-Proposals following a Consortium Model for undertaking the given assignment are encouraged to
-apply
-.
-8. Request for Clarification
-All questions regarding the preparation of proposals must be submitted in writing (by e-mail) to
-akfindia.helpdesk@akdn.org
-by
-Thursday
-,
-24
-th
-September
-202
-6
-. Responses will be provided to all interested organizations by
-Friday,
-25
-th
-September
-202
-6
-, through email. Aga Khan Foundation is under no obligation to consider or respond to questions that are not received in a timely manner.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-akfindia.helpdesk(at)akdn.org
-Download Attachment:
-RFP_Dhenu Dhara Project Baseline.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-28 Sep 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Field Coordinator - Village Institutions
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Program Manager
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Project Coordinator -NRM / Watershed
-Basudeo Kanoria Seva Sansthan
-Location:
-Rajasthan
-Apply by:
-12 Oct 2026
-Lead Consultant PHEOC
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Consultant - Emergency Management (PHEOC)
-The Voluntary Health Services (VHS)
-Location:
-Delhi
-Apply by:
-29 Sep 2026
-Field Research Executive
-Academy of Management Studies (AMS)
-Location:
-Maharashtra
-Apply by:
-30 Sep 2026
-Manager – Program Finance
-Wipro Foundation
-Location:
-Karnataka
-Apply by:
-09 Oct 2026
-Resource Person — ITI Engagement
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Account Person
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
-Location:
-Haryana
-Apply by:
-10 Oct 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-©
-2026
-M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>28-09-2026</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303730</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 29 September 2026</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>29 September 2026</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>29 September 2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Apply for Giving Joy Microgrant 2026 – Up to US$500 for Women Entrepreneurs</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Giving Joy is a nonprofit organisation that supports women entrepreneurs and changemakers by providing small grants, mentorship and practical support. The organisation focuses on helping women develop ideas that create positive economic or social impact in their communities. Its global grant program ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>The Giving Joy Microgrant 2026 provides small-scale financial support to women entrepreneurs and changemakers worldwide. The Fall 2026 grant cycle is designed to help applicants start or expand a business, nonprofit organisation or community project that generates positive economic or social benefits for women, girls and families. Selected applicants can receive a one-time microgrant of up to US$500, along with mentorship and participation in the Giving Joy community. The grant can support practical activities and project expenses during a six-month implementation period. Applications for the Fall 2026 cycle are open from 1 September through 30 September 2026.</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Women &amp; Gender</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-giving-joy-microgrant-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is30 September 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Giving Joy Microgrant 2026</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>Applications Open for Green Box Artist in Residency Program</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>Apply for RAFT AI for Transformative Social Impact Grant 2026 – Up to ₹50 Lakh</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI ... Read More</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI at the core of their solutions and can demonstrate meaningful, measurable and responsible impact. The initiative focuses particularly on agriculture, healthcare, disability inclusion and frontline support. RAFT indicates a preference for organisations operating in Maharashtra and is interested in solutions with potential for scale and longer-term impact. The initiative is designed for organisations that are already applying AI to real-world social challenges.</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>30 September 2026</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/raft-ai-transformative-social-impact-grant-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for Solar Home Lightning Procurement for SAHAS Project</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Development Support Centre (DSC) | Dhadgaon Block, Nandurbar District, Maharashtra
 RFQ -  for Solar Home Lightning Procurement for SAHAS Project, Development Support Centre (DSC)(Dhadgaon Block, Nandurbar District) | DevNetJobsIndia
@@ -2294,139 +595,499 @@
 Broadcast Resum ... Read More</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>30-09-2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304229</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Applications Open for Green Box Artist in Residency Program</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Apply for RAFT AI for Transformative Social Impact Grant 2026 – Up to ₹50 Lakh</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI ... Read More</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI at the core of their solutions and can demonstrate meaningful, measurable and responsible impact. The initiative focuses particularly on agriculture, healthcare, disability inclusion and frontline support. RAFT indicates a preference for organisations operating in Maharashtra and is interested in solutions with potential for scale and longer-term impact. The initiative is designed for organisations that are already applying AI to real-world social challenges.</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/raft-ai-transformative-social-impact-grant-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Giving Joy Microgrant 2026 – Up to US$500 for Women Entrepreneurs</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Giving Joy is a nonprofit organisation that supports women entrepreneurs and changemakers by providing small grants, mentorship and practical support. The organisation focuses on helping women develop ideas that create positive economic or social impact in their communities. Its global grant program ... Read More</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The Giving Joy Microgrant 2026 provides small-scale financial support to women entrepreneurs and changemakers worldwide. The Fall 2026 grant cycle is designed to help applicants start or expand a business, nonprofit organisation or community project that generates positive economic or social benefits for women, girls and families. Selected applicants can receive a one-time microgrant of up to US$500, along with mentorship and participation in the Giving Joy community. The grant can support practical activities and project expenses during a six-month implementation period. Applications for the Fall 2026 cycle are open from 1 September through 30 September 2026.</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Women &amp; Gender</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-giving-joy-microgrant-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is30 September 2026</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Giving Joy Microgrant 2026</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>30 September 2026</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>AndPurpose</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>Apply for India-Finland Joint Innovation Call 2026</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>The Technology Development Board (TDB), operating under India’s Department of Science and Technology, supports the development and commercialization of indigenous technologies. For the India-Finland Joint Innovation Call 2026, TDB is implementing the programme on behalf of DST in partnership with Bu ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>The India-Finland Joint Innovation Call 2026 supports collaborative R&amp;D projects between eligible Indian and Finnish partners. Priority areas include sustainable energy, renewable energy, hydrogen technologies, smart cities, waste management, waste-to-energy, electric vehicles, carbon capture, energy storage, advanced digital technologies, artificial intelligence, 5G/6G, MEMS and sensors. Projects can run for a maximum of 24 months, with up to six projects expected to receive support. Successful proposals should demonstrate innovation, market potential, commercialization prospects and strong joint project-management capacity. Both Indian and Finnish partners must submit applications to their respective national funding agencies.</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>30 September 2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://andpurpose.world/grants-india-finland-joint-innovation-call-2026/</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Apply for European Youth Foundation Grants 2027 – Up to €60,000</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>The European Youth Foundation (EYF) is a funding body of the Council of Europe supporting youth organisations and initiatives that promote human rights, democracy, peace, intercultural dialogue and youth participation. EYF grants support international youth cooperation and projects that help young p ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Eligible applicants are youth non-governmental organisations and networks registered with the European Youth Foundation. Organisations must satisfy the EYF’s registration and eligibility criteria before applying. The projects must involve young people and contribute to the Foundation’s thematic priorities. Applicants should ensure their organisation has been validated before the deadline because EYF registration can take time. Projects should have an international youth cooperation dimension and demonstrate clear objectives, activities, expected outcomes and appropriate budgeting. Individuals cannot apply independently for these organisational grants.</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>1 October 2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-european-youth-foundation-grants-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 01 October 2026</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>01 October 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar ...</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society (CECOEDECON) | Jaisalmer, Jodhpur, Barmer Districts, Rajasthan
 RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar PV Systems – 2 kW, 3 kW and 5 kW, Centre For Community Economics And Development Consultants So ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>• 5. Scope of Work
 The selected bidder shall provide complete turnkey services, including but not limited to:
@@ -2543,6 +1204,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -2591,69 +1264,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2684,173 +1345,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>01-10-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304105</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Apply for European Youth Foundation Grants 2027 – Up to €60,000</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>The European Youth Foundation (EYF) is a funding body of the Council of Europe supporting youth organisations and initiatives that promote human rights, democracy, peace, intercultural dialogue and youth participation. EYF grants support international youth cooperation and projects that help young p ... Read More</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants are youth non-governmental organisations and networks registered with the European Youth Foundation. Organisations must satisfy the EYF’s registration and eligibility criteria before applying. The projects must involve young people and contribute to the Foundation’s thematic priorities. Applicants should ensure their organisation has been validated before the deadline because EYF registration can take time. Projects should have an international youth cooperation dimension and demonstrate clear objectives, activities, expected outcomes and appropriate budgeting. Individuals cannot apply independently for these organisational grants.</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>1 October 2026</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-european-youth-foundation-grants-2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 01 October 2026</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>01 October 2026</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>Apply for Mumbai Ekatra Going Green 2026 – Grants Up to ₹1 Lakh</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>The Kshirsagar Apte Foundation is an Indian family foundation established in 2013 that supports initiatives across education and employability, gender, environment and sustainability, arts and culture, disabilities and health. One of its programmes focuses on citizen-led initiatives addressing civic ... Read More</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Mumbai Ekatra – Going Green is open to community groups, institutions and organisations proposing citizen-led projects focused on environmental sustainability in Mumbai. Applicants should present a clear idea that addresses a relevant urban environmental challenge and demonstrates community participation. Projects may relate to areas including water conservation, urban agriculture, green roofing, recycling, waste management and other sustainability initiatives. Organisations and groups should review the programme’s official requirements and application instructions before submitting their proposals. The opportunity is geographically focused on Mumbai rather than being an India-wide grant.</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>1 October 2026</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-mumbai-ekatra-going-green-2026-grants-up/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>ToR - Consultant for an Evidence-Based Research Study on Forest Rights Act...</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Development Agency for Poor and Tribal Awakening (DAPTA) | Odisha
 ToR - Consultant for an Evidence-Based Research Study on Forest Rights Act (FRA) Implementation in Odisha, Development Agency for Poor and Tribal Awakening (DAPTA)() | DevNetJobsIndia
@@ -2862,7 +1388,7 @@
 Value Membershi ... Read More</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• 5. Scope of Work
 The consultant will undertake the following:
@@ -2943,6 +1469,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -2991,69 +1529,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3084,38 +1610,83 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>01-10-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303803</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Mumbai Ekatra Going Green 2026 – Grants Up to ₹1 Lakh</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>The Kshirsagar Apte Foundation is an Indian family foundation established in 2013 that supports initiatives across education and employability, gender, environment and sustainability, arts and culture, disabilities and health. One of its programmes focuses on citizen-led initiatives addressing civic ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai Ekatra – Going Green is open to community groups, institutions and organisations proposing citizen-led projects focused on environmental sustainability in Mumbai. Applicants should present a clear idea that addresses a relevant urban environmental challenge and demonstrates community participation. Projects may relate to areas including water conservation, urban agriculture, green roofing, recycling, waste management and other sustainability initiatives. Organisations and groups should review the programme’s official requirements and application instructions before submitting their proposals. The opportunity is geographically focused on Mumbai rather than being an India-wide grant.</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>1 October 2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-mumbai-ekatra-going-green-2026-grants-up/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - English Annotation of Student Voice Recordings from Uttarakhand</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS) | Uttarakhand
 RFP - English Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
@@ -3132,7 +1703,7 @@
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 All proposals to this RFP must be received no later than
@@ -3164,6 +1735,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -3212,69 +1795,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3305,38 +1876,298 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>02-10-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304049</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Apply for AMBSO Impact Research Initiative 2026: Up to USD 10,000 in Health Research Grants</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Africa Medical and Behavioral Sciences Organization (AMBSO) TheAfrica Medical and Behavioral Sciences Organization (AMBSO)is a research and health-focused organization working to advance clinical, epidemiological, social, and behavioral research across Africa. Its work includes clinical trials, popu ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>TheAMBSO Impact Research Initiative 2026is open to eligible researchers, academic institutions, research organizations, community-based organizations, and other entities whose proposed work aligns with the initiative’s public health objectives. Doctoral students are encouraged to apply as members of research teams led by a faculty Principal Investigator. Independent researchers may apply when affiliated with an academic or research institution. Applications can come from anywhere in the world, with no geographical restriction stated by AMBSO. Proposed projects should focus on eligible priority health areas, generate useful evidence, and be feasible within the 18-month funding period. For-profit entities, political organizations, lobbying groups, and organizations primarily engaged in political advocacy are not eligible.</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-ambso-impact-research-initiative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Uttarakhand
+RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers: ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Submission Details
+All proposals to this RFP must be received no later than
+&lt;October 2nd 2026&gt;.
+The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP:
+Hindi Transcriptions of Student Voice Recordings of Reading - Uttarakhand (Name of the partner)
+.
+Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP - Uttarakhand Data Annotation I Grades 1-8 Hindi RFP.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+02 Oct 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
+Location:
+Madhya Pradesh
+Apply by:
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304050</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - Hotel Selection for Training of Sub National Verification (SNV)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>TCI Foundation | Rishikesh/Dehradun, Uttarakhand
 RFP - Hotel Selection for Training of Sub National Verification (SNV), TCI Foundation(Rishikesh/Dehradun) | DevNetJobsIndia
@@ -3356,7 +2187,7 @@
 Regist ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• Payment Terms and Conditions:
 50% payment would be made by TCI Foundation as advance.
@@ -3417,6 +2248,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -3465,69 +2308,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3558,80 +2389,236 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>02-10-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="H21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303891</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Apply for GEF Small Grants Programme Ghana 2026 – Up to US$50,000</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>The Global Environment Facility Small Grants Programme is implemented by the United Nations Development Programme and supports locally led environmental and community-development initiatives. In Ghana, the programme’s ICCA-GSI Phase II call focuses on territories and areas conserved by Indigenous Pe ... Read More</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should review the official UNDP Ghana call and prepare their proposal using the relevant application template. Proposals should describe the environmental challenge, communities involved, activities, expected results and sustainability benefits. Completed applications and required documents must be submitted electronically to the designated UNDP Ghana email address before the deadline. A proposal workshop was also scheduled for September 22, 2026.</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>3 October 2026</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-gef-small-grants-programme-ghana-2026-up-to-us50000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Assam Startup Call for Grant Applications 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>The Department of Innovation, Incubation and Start-ups (DIIS) The Department of Innovation, Incubation and Start-ups (DIIS) is the Government of Assam’s nodal department responsible for developing the state’s startup and innovation ecosystem. The department coordinates startup policy, recognition, f ... Read More</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The Assam Startup Call for Grant Applications 2026 provides grant support to eligible startups at the idea and prototype or MVP stages. The programme is designed to help startups develop, validate and scale innovative solutions under Assam’s startup policy. Applicants select the funding category corresponding to their development stage and provide information about their product, market validation, business model, funding requirement, expected employment and impact. The opportunity is relevant for entrepreneurs seeking startup grants India, prototype funding India and government-backed innovation support. Applications under the current call are reviewed by the Assam Innovation &amp; Startup Foundation, with funding provided to selected eligible startups.</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>3 October 2026</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/assam-startup-call-for-grant-applications-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>French Republic Human Rights Prize 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>The National Consultative Commission on Human Rights (CNCDH) The National Consultative Commission on Human Rights (CNCDH) is France’s independent national human rights institution responsible for advising public authorities and promoting the protection of human rights and fundamental freedoms. It al ... Read More</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should prepare a complete application describing their organisation or initiative, human-rights objectives, activities, beneficiaries and expected outcomes. The proposal should clearly demonstrate how the project protects the rights of refugees, asylum seekers or displaced persons. Applicants must complete the prescribed application form and submit the required documents before the closing date. Applications should clearly explain the project’s human-rights approach and practical impact.</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>4 October 2026</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303891</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/french-republic-human-rights-prize-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | Uttarakhand
-RFP - Hindi Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Design, Digitization and Pilot Roll-Out of a Curriculum on TFGBV, Di...</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Centre for Catalyzing Change (C3) | Jaipur, Rajasthan
+RFP - Design, Digitization and Pilot Roll-Out of a Curriculum on TFGBV, Digital and Financial Literacy for Young Women (18–30 years) in Rajasthan, Centre for Catalyzing Change (C3)(Jaipur) | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers: ... Read More</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>• Submission Details
-All proposals to this RFP must be received no later than
-&lt;October 2nd 2026&gt;.
-The proposal should be submitted only through e-mail in PDF format addressed to The Procurement Team at the below-given e-mail id:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP:
-Hindi Transcriptions of Student Voice Recordings of Reading - Uttarakhand (Name of the partner)
-.
-Any proposals received by Wadhwani-AI after the deadline for submission of proposals prescribed in the timeline of this document are liable to be rejected.
+Valu ... Read More</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>• Introduction &amp; Organizational Context
+The Centre for Catalyzing Change (C3) is a leading national non-profit organization dedicated to empowering women and adolescent girls through innovative, evidence-based programmes. For over 30 years, C3 has worked to advance education, health, safety, life skills, and economic opportunities by strengthening systems and influencing public policy.
+In Rajasthan, C3 partners with the Rajasthan State Rural Livelihood Mission to strengthen the safety, digital confidence, and financial capability of young women engaged with community institutions, enabling them to participate more fully and safely in digital and economic life.
+Project Goals and Objectives
+Goal
+To equip young women aged 18–30 across selected districts of Rajasthan with the knowledge and skills to recognize and respond to technology-facilitated gender-based violence, and to safely and confidently use digital and financial tools and services.
+Objectives
+Develop a curriculum on TFGBV, digital literacy, and financial literacy tailored to young women aged 18–30 in Rajasthan.
+Digitize the curriculum to enable flexible, scalable delivery.
+Conduct a training of trainers (ToT) to build a cadre of facilitators.
+Conduct pilot training of young women across 4 districts of Rajasthan (Alwar, Dausa, Kota, Rajsamand).
+• Scope of Work / Services Required
+Agencies are expected to propose a methodology that addresses all of the following components:
+Curriculum Development
+Formative research/consultations with young women, SRLM field cadre, and relevant subject experts to ground the curriculum in local realities and common TFGBV risks (e.g., online harassment, image-based abuse, financial fraud/scams).
+Design of an integrated curriculum covering TFGBV awareness, prevention and response (including referral pathways), safe digital practices, and foundational financial literacy (savings, digital payments, access to financial services, fraud prevention).
+Development of a facilitator guide, participant handbook, and supporting IEC materials in Hindi.
+Submission Instructions
+Submit to:
+procurement@c3india.org
+Subject line: "Proposal for Young Women Digital and Financial Literacy – [Agency Name]"
+Deadline: 4th October 2026,
+5:00 PM IST. Proposals received after this deadline will not be considered.
+Queries: Written questions only, submitted by 29th September 2026 to the e-mail address above. Responses will be circulated to all agencies who have expressed interest, to keep the process fair and transparent.
+Contact for this assignment: State Head – Centre for Catalyzing Change (C3), Jaipur, Rajasthan.
 For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-rfp.lehs(at)wadhwaniai.org
 Download Attachment:
-RFP - Uttarakhand Data Annotation I Grades 1-8 Hindi RFP.pdf
+RFP_Young Women TFGBV and Digital Financial Literacy_Rajasthan.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-02 Oct 2026
+04 Oct 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -3680,69 +2667,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3773,6 +2748,231 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>04-10-2026</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304274</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Design and Roll-Out of a Curriculum on Positive Masculinities for Co...</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Centre for Catalyzing Change (C3) | Jaipur, Rajasthan
+RFP - Design and Roll-Out of a Curriculum on Positive Masculinities for Community  Members and Participatory Community Safety Audits..., Centre for Catalyzing Change (C3)(Jaipur) | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membersh ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>• Introduction &amp; Organizational Context
+The Centre for Catalyzing Change (C3) is a leading national non-profit organization dedicated to empowering women and adolescent girls through innovative, evidence-based programmes. For over 30 years, C3 has worked to advance education, health, safety, life skills, and economic opportunities by strengthening systems and influencing public policy.
+In Rajasthan, C3 partners with the Rajasthan State Rural Livelihood Mission to engage men and boys as partners in advancing gender equality, and to strengthen community-level systems, including women's collectives supported by Rajasthan SRLM, that can identify and respond to safety risks faced by women and girls in public and private spaces.
+Project Goals and Objectives
+Goal
+To engage men and boys across selected districts of Rajasthan in adopting positive, equitable, and nonviolent masculinities, and to build the capacity of community members to identify, document, and act on gender safety risks through participatory community safety audits.
+Objectives
+Develop a curriculum on positive masculinities contextualized to the social and cultural context of Rajasthan.
+Design training strategies and roll out training for men and boys using this curriculum.
+Develop a participatory community safety audit curriculum suited to rural and peri-urban Rajasthan.
+Train community members on gender safety audits and roll out audits across target communities.
+• Scope of Work / Services Required
+Agencies are expected to propose a methodology that addresses all of the following components:
+Curriculum Development — Positive Masculinities
+Formative consultations with men, boys, adolescent boys, and community stakeholders to ground the curriculum in local realities.
+Design of a curriculum contextualized to Rajasthan, covering gender norms and socialization, power and privilege, consent, prevention of violence against women and girls, caregiving and shared domestic responsibility, and allyship.
+Development of a facilitator guide, session plans, and IEC/audio-visual materials in Hindi (and local dialects where relevant).
+Submission Instructions
+Submit to:
+procurement@c3india.org
+Subject line: "
+Proposal for Masculinities and Rural Safety Audits – [Agency Name]"
+Deadline: 5th October 2026, 5:00 PM IST
+. Proposals received after this deadline will not be considered.
+Queries: Written questions only, submitted by 29th September 2026 to the e-mail address above. Responses will be circulated to all agencies who have expressed interest, to keep the process fair and transparent.
+Contact for this assignment: State Head – Centre for Catalyzing Change (C3), Jaipur, Rajasthan.
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+RFP_Positive Masculinities Safety Audits_Rajasthan.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Oct 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
+Location:
+Madhya Pradesh
+Apply by:
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
@@ -3780,15 +2980,15 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>02-10-2026</t>
+          <t>05-10-2026</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304050</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304275</t>
         </is>
       </c>
     </row>
@@ -3805,186 +3005,51 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Apply for AMBSO Impact Research Initiative 2026: Up to USD 10,000 in Health Research Grants</t>
+          <t>Poshan Vatika Grant 2026 – National Medicinal Plants Board</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Africa Medical and Behavioral Sciences Organization (AMBSO) TheAfrica Medical and Behavioral Sciences Organization (AMBSO)is a research and health-focused organization working to advance clinical, epidemiological, social, and behavioral research across Africa. Its work includes clinical trials, popu ... Read More</t>
+          <t>The National Medicinal Plants Board (NMPB), under the Ministry of AYUSH, Government of India, works to promote the cultivation, conservation and sustainable use of medicinal plants. Its programmes support medicinal plant development, awareness, cultivation and related activities across India. The Bo ... Read More</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>TheAMBSO Impact Research Initiative 2026is open to eligible researchers, academic institutions, research organizations, community-based organizations, and other entities whose proposed work aligns with the initiative’s public health objectives. Doctoral students are encouraged to apply as members of research teams led by a faculty Principal Investigator. Independent researchers may apply when affiliated with an academic or research institution. Applications can come from anywhere in the world, with no geographical restriction stated by AMBSO. Proposed projects should focus on eligible priority health areas, generate useful evidence, and be feasible within the 18-month funding period. For-profit entities, political organizations, lobbying groups, and organizations primarily engaged in political advocacy are not eligible.</t>
+          <t>Eligible applicants include government organisations, NGOs and voluntary organisations with demonstrated experience relevant to the proposed Poshan Vatika project. Applicants should be capable of establishing and maintaining a nutrition garden within an eligible Eklavya Model Residential School. The proposed site should have suitable cultivable land and the necessary conditions for plantation and maintenance, including appropriate irrigation and arrangements for ongoing upkeep. Projects should include at least 30 suitable plant species and activities such as training, awareness and educational support. Organisations applying for government grants for NGOs should demonstrate the capacity to implement, monitor and maintain the garden for the full project period.</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>2 October 2026</t>
+          <t>5 October 2026</t>
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-ambso-impact-research-initiative/</t>
+          <t>https://andpurpose.world/poshan-vatika-grant-2026-national-medicinal-plants-board/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Apply for GEF Small Grants Programme Ghana 2026 – Up to US$50,000</t>
+          <t>EoI - Selection of Skilled Bamboo Craft / Construction Team for Design, Fa...</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>The Global Environment Facility Small Grants Programme is implemented by the United Nations Development Programme and supports locally led environmental and community-development initiatives. In Ghana, the programme’s ICCA-GSI Phase II call focuses on territories and areas conserved by Indigenous Pe ... Read More</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should review the official UNDP Ghana call and prepare their proposal using the relevant application template. Proposals should describe the environmental challenge, communities involved, activities, expected results and sustainability benefits. Completed applications and required documents must be submitted electronically to the designated UNDP Ghana email address before the deadline. A proposal workshop was also scheduled for September 22, 2026.</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>3 October 2026</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-gef-small-grants-programme-ghana-2026-up-to-us50000/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>Assam Startup Call for Grant Applications 2026</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>The Department of Innovation, Incubation and Start-ups (DIIS) The Department of Innovation, Incubation and Start-ups (DIIS) is the Government of Assam’s nodal department responsible for developing the state’s startup and innovation ecosystem. The department coordinates startup policy, recognition, f ... Read More</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>The Assam Startup Call for Grant Applications 2026 provides grant support to eligible startups at the idea and prototype or MVP stages. The programme is designed to help startups develop, validate and scale innovative solutions under Assam’s startup policy. Applicants select the funding category corresponding to their development stage and provide information about their product, market validation, business model, funding requirement, expected employment and impact. The opportunity is relevant for entrepreneurs seeking startup grants India, prototype funding India and government-backed innovation support. Applications under the current call are reviewed by the Assam Innovation &amp; Startup Foundation, with funding provided to selected eligible startups.</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>3 October 2026</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/assam-startup-call-for-grant-applications-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>French Republic Human Rights Prize 2026</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>The National Consultative Commission on Human Rights (CNCDH) The National Consultative Commission on Human Rights (CNCDH) is France’s independent national human rights institution responsible for advising public authorities and promoting the protection of human rights and fundamental freedoms. It al ... Read More</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should prepare a complete application describing their organisation or initiative, human-rights objectives, activities, beneficiaries and expected outcomes. The proposal should clearly demonstrate how the project protects the rights of refugees, asylum seekers or displaced persons. Applicants must complete the prescribed application form and submit the required documents before the closing date. Applications should clearly explain the project’s human-rights approach and practical impact.</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>4 October 2026</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/french-republic-human-rights-prize-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>EoI - Selection of Skilled Bamboo Craft / Construction Team for Design, Fa...</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>NEEDS | Jharkhand
 EoI - Selection of Skilled Bamboo Craft / Construction Team for Design, Fabrication and Erection of a Bamboo Innovation Centre, NEEDS() | DevNetJobsIndia
@@ -4004,7 +3069,7 @@
 Registe ... Read More</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work of the Selected Bamboo Team:
 The selected team will preferably undertake the following activities.
@@ -4053,6 +3118,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -4101,69 +3178,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4194,83 +3259,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>05-10-2026</t>
         </is>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
+      <c r="H28" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303948</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Poshan Vatika Grant 2026 – National Medicinal Plants Board</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>The National Medicinal Plants Board (NMPB), under the Ministry of AYUSH, Government of India, works to promote the cultivation, conservation and sustainable use of medicinal plants. Its programmes support medicinal plant development, awareness, cultivation and related activities across India. The Bo ... Read More</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants include government organisations, NGOs and voluntary organisations with demonstrated experience relevant to the proposed Poshan Vatika project. Applicants should be capable of establishing and maintaining a nutrition garden within an eligible Eklavya Model Residential School. The proposed site should have suitable cultivable land and the necessary conditions for plantation and maintenance, including appropriate irrigation and arrangements for ongoing upkeep. Projects should include at least 30 suitable plant species and activities such as training, awareness and educational support. Organisations applying for government grants for NGOs should demonstrate the capacity to implement, monitor and maintain the garden for the full project period.</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>5 October 2026</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/poshan-vatika-grant-2026-national-medicinal-plants-board/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme i...</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>World Resources Institute India (WRI India) | Karnataka
 RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme in Karnataka, World Resources Institute India (WRI India)() | DevNetJobsIndia
@@ -4285,7 +3305,7 @@
 Search Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 Aprajita.Verma(at)wri.org
@@ -4301,6 +3321,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -4349,69 +3381,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -4442,14 +3462,194 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Electropreneur Park 2.0 Open Challenge Programme in India</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Software Technology Parks of India (STPI) is an autonomous society under theMinistry of Electronics and Information Technology (MeitY), Government of India. STPI works to strengthen India’s technology ecosystem through infrastructure, incubation, entrepreneurship and support for technology businesse ... Read More</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>TheElectropreneur Park 2.0 Open Challenge Programmeis open to students, budding entrepreneurs and startups developing innovative solutions in ESDM or cognitive computing and social sensing. Eligible applicants may include individuals at the ideation stage requiring prototype-development support, early or pre-revenue startups, prototype-stage ventures and startups with breakthrough technologies. Relevant areas include MedTech, EdTech, automotive electronics, strategic electronics, EVs, defence, drones and other ESDM applications. The programme particularly supports innovators who need access to prototyping facilities, technical mentoring, incubation, market support and funding or investment opportunities.</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-electropreneur-park-2-0-open-challenge-programme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Citi Foundation Global Innovation Challenge 2026 – $500,000 Grant</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>The Citi Foundation works with community organisations addressing social and economic challenges affecting low-income communities around the world. Through its Global Innovation Challenge, the Foundation provides philanthropic funding to organisations developing innovative solutions that can be pilo ... Read More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>The opportunity is intended for eligible community organisations working with low-income young people. Applicants should have an innovative solution addressing the changing employment landscape and helping youth develop skills needed in an AI-shaped economy. Relevant activities include AI and digital skills, critical thinking, problem-solving, employment connections, shared technology access, AI integration into existing youth employment programmes and cross-sector partnerships. The official RFP contains the complete eligibility criteria and target geographies, so organisations should review those requirements before submitting an application. Citi Foundation operates internationally across more than 80 countries and territories, but applicants must meet the specific geographic and organisational requirements of the current challenge.</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-citi-foundation-global-innovation-challenge-2026-500000-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Apply for GFF × CIVIC VOICES Funding 2026 – US$3.35 Million Funding Pool</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>The GFF × CIVIC VOICES initiative brings together the Global Financing Facility and the VOICES consortium to strengthen civil society participation in health decision-making across participating African countries. The programme is implemented through partners including PATH, the African Institute fo ... Read More</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should review the official GFF × CIVIC VOICES call materials, technical proposal template, budgeting template and frequently asked questions before preparing their submission. Partnerships must meet the required organisation composition and geographic eligibility criteria. Applications should be submitted according to the official instructions provided by the VOICES consortium. The programme also provides advocacy training, budget-analysis assistance and mentorship to selected partnerships.</t>
+        </is>
+      </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>05-10-2026</t>
+          <t>7 October 2026</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
@@ -4457,7 +3657,7 @@
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
+          <t>https://andpurpose.world/apply-for-gff-x-civic-voices-funding-2026-us3-35-million-funding-pool/</t>
         </is>
       </c>
     </row>
@@ -4474,35 +3674,35 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+          <t>Apply for MNRE Concentrating Solar Thermal Technology Grant 2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, d ... Read More</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, development, demonstration and deployment of renewable energy technologies through dedicated programmes. Its Renewable Energy Research and Technology Development Programme supports technology development and practical applications of renewable energy. Through this current call, MNRE is encouraging the development and deployment of concentrating solar thermal technology for Indian industries, particularly solutions capable of providing clean heat for industrial processes.</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>7 October 2026</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
+          <t>https://andpurpose.world/apply-for-prip-pharma-medtech-innovation-scheme/</t>
         </is>
       </c>
     </row>
@@ -4519,27 +3719,27 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Apply for Citi Foundation Global Innovation Challenge 2026 – $500,000 Grant</t>
+          <t>Pfizer HRRm Testing Education Grant 2026: Apply for Up to $100,000</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>The Citi Foundation works with community organisations addressing social and economic challenges affecting low-income communities around the world. Through its Global Innovation Challenge, the Foundation provides philanthropic funding to organisations developing innovative solutions that can be pilo ... Read More</t>
+          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombinati ... Read More</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>The opportunity is intended for eligible community organisations working with low-income young people. Applicants should have an innovative solution addressing the changing employment landscape and helping youth develop skills needed in an AI-shaped economy. Relevant activities include AI and digital skills, critical thinking, problem-solving, employment connections, shared technology access, AI integration into existing youth employment programmes and cross-sector partnerships. The official RFP contains the complete eligibility criteria and target geographies, so organisations should review those requirements before submitting an application. Citi Foundation operates internationally across more than 80 countries and territories, but applicants must meet the specific geographic and organisational requirements of the current challenge.</t>
+          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombination Repair mutation (HRRm) testingfor metastatic prostate cancer. Through this funding opportunity, Pfizer supports practical educational initiatives that help multidisciplinary healthcare teams apply guideline-based testing approaches in clinical practice. The programme particularly emphasizes education covering pre-analytical considerations, testing-related decision-making, interpretation of results, and communication of testing information throughout the patient care pathway.</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>08 October 2026</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -4547,7 +3747,7 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-citi-foundation-global-innovation-challenge-2026-500000-grant/</t>
+          <t>https://andpurpose.world/pfizer-hrrm-testing-education-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -4564,17 +3764,17 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Apply for Electropreneur Park 2.0 Open Challenge Programme in India</t>
+          <t>WHO/IBP Network SPARK Grants 2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Software Technology Parks of India (STPI) is an autonomous society under theMinistry of Electronics and Information Technology (MeitY), Government of India. STPI works to strengthen India’s technology ecosystem through infrastructure, incubation, entrepreneurship and support for technology businesse ... Read More</t>
+          <t>The World Health Organization (WHO) works globally to promote health, prevent disease and strengthen health systems, while the IBP Network brings together organisations and partners working to translate WHO guidance into effective health programmes. The network supports evidence-based approaches to ... Read More</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>TheElectropreneur Park 2.0 Open Challenge Programmeis open to students, budding entrepreneurs and startups developing innovative solutions in ESDM or cognitive computing and social sensing. Eligible applicants may include individuals at the ideation stage requiring prototype-development support, early or pre-revenue startups, prototype-stage ventures and startups with breakthrough technologies. Relevant areas include MedTech, EdTech, automotive electronics, strategic electronics, EVs, defence, drones and other ESDM applications. The programme particularly supports innovators who need access to prototyping facilities, technical mentoring, incubation, market support and funding or investment opportunities.</t>
+          <t>The WHO/IBP Network SPARK Grants 2026 support youth-led, women-led and Indigenous-led community-based organisations applying WHO guidance in innovative, locally grounded ways. Selected organisations can receive funding for one-year projects addressing sexual and reproductive health, maternal health, newborn health, child health and adolescent health and rights. Alongside financial assistance, grantees receive technical support, opportunities for peer learning and connections with the wider IBP Network. The programme is designed to strengthen locally driven approaches and help community organisations translate evidence and global health guidance into practical interventions. These global health grants provide an opportunity for organisations to strengthen community-level health outcomes.</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -4584,15 +3784,15 @@
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>6 October 2026</t>
+          <t>9 October 2026</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-electropreneur-park-2-0-open-challenge-programme/</t>
+          <t>https://andpurpose.world/who-ibp-network-spark-grants-2026/</t>
         </is>
       </c>
     </row>
@@ -4609,17 +3809,17 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Apply for GFF × CIVIC VOICES Funding 2026 – US$3.35 Million Funding Pool</t>
+          <t>2026 CSO Call for Expressions of Project Intentions – AFD</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>The GFF × CIVIC VOICES initiative brings together the Global Financing Facility and the VOICES consortium to strengthen civil society participation in health decision-making across participating African countries. The programme is implemented through partners including PATH, the African Institute fo ... Read More</t>
+          <t>Agence Française de Développement (AFD) is France’s public development agency working to finance and support projects that contribute to sustainable development, poverty reduction, climate action, biodiversity, social inclusion and international solidarity. Through its CSO Initiatives mechanism, AFD ... Read More</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official GFF × CIVIC VOICES call materials, technical proposal template, budgeting template and frequently asked questions before preparing their submission. Partnerships must meet the required organisation composition and geographic eligibility criteria. Applications should be submitted according to the official instructions provided by the VOICES consortium. The programme also provides advocacy training, budget-analysis assistance and mentorship to selected partnerships.</t>
+          <t>Eligible CSOs should prepare a project intention describing the proposed project, objectives, expected outcomes, target communities and implementation approach. Applications must be submitted through AFD’s OSCar platform using the relevant project-intention documentation. Organisations without an OSCar account were required to request account creation by 15 September 2026. Complete project intentions must be submitted online by the final deadline. Applicants should carefully review the eligibility and documentation requirements before submission.</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
@@ -4629,7 +3829,7 @@
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>7 October 2026</t>
+          <t>9 October 2026</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
@@ -4637,7 +3837,7 @@
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-gff-x-civic-voices-funding-2026-us3-35-million-funding-pool/</t>
+          <t>https://andpurpose.world/2026-cso-call-for-expressions-of-project-intentions-afd/</t>
         </is>
       </c>
     </row>
@@ -4654,27 +3854,27 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Apply for MNRE Concentrating Solar Thermal Technology Grant 2026</t>
+          <t>Apply for Samhita-CGF Catalytic Grant 2026 – Up to ₹1 Crore for Education</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, d ... Read More</t>
+          <t>Samhita–Collective Good Foundation works with organisations and partners seeking practical solutions to social and development challenges in India. Its grantmaking supports initiatives that improve access to essential services, strengthen systems and create sustainable opportunities for underserved ... Read More</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, development, demonstration and deployment of renewable energy technologies through dedicated programmes. Its Renewable Energy Research and Technology Development Programme supports technology development and practical applications of renewable energy. Through this current call, MNRE is encouraging the development and deployment of concentrating solar thermal technology for Indian industries, particularly solutions capable of providing clean heat for industrial processes.</t>
+          <t>Interested organisations should review Samhita-CGF’s programme information and eligibility requirements and submit an Expression of Interest through the designated application form. Applicants should clearly explain their education programme, target communities, expected outcomes, organisational experience and proposed use of funding. Samhita has also announced an applicant webinar for September 25, 2026. The EOI deadline is October 9, 2026.</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>7 October 2026</t>
+          <t>9 October 2026</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
@@ -4682,7 +3882,7 @@
       </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-prip-pharma-medtech-innovation-scheme/</t>
+          <t>https://andpurpose.world/apply-for-samhita-cgf-catalytic-grant/</t>
         </is>
       </c>
     </row>
@@ -4699,35 +3899,35 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Pfizer HRRm Testing Education Grant 2026: Apply for Up to $100,000</t>
+          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombinati ... Read More</t>
+          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombination Repair mutation (HRRm) testingfor metastatic prostate cancer. Through this funding opportunity, Pfizer supports practical educational initiatives that help multidisciplinary healthcare teams apply guideline-based testing approaches in clinical practice. The programme particularly emphasizes education covering pre-analytical considerations, testing-related decision-making, interpretation of results, and communication of testing information throughout the patient care pathway.</t>
+          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>08 October 2026</t>
+          <t>09 October 2026</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/pfizer-hrrm-testing-education-grant-2026/</t>
+          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
         </is>
       </c>
     </row>
@@ -4744,17 +3944,17 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>WHO/IBP Network SPARK Grants 2026</t>
+          <t>Technology Support Programme 2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) works globally to promote health, prevent disease and strengthen health systems, while the IBP Network brings together organisations and partners working to translate WHO guidance into effective health programmes. The network supports evidence-based approaches to ... Read More</t>
+          <t>The Technology Support Programme for Small NGOs and Grassroots Organisations is designed to strengthen the digital and technological capacity of smaller civil society organisations. The programme focuses on helping organisations use technology to improve their operations, programme implementation, m ... Read More</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>The WHO/IBP Network SPARK Grants 2026 support youth-led, women-led and Indigenous-led community-based organisations applying WHO guidance in innovative, locally grounded ways. Selected organisations can receive funding for one-year projects addressing sexual and reproductive health, maternal health, newborn health, child health and adolescent health and rights. Alongside financial assistance, grantees receive technical support, opportunities for peer learning and connections with the wider IBP Network. The programme is designed to strengthen locally driven approaches and help community organisations translate evidence and global health guidance into practical interventions. These global health grants provide an opportunity for organisations to strengthen community-level health outcomes.</t>
+          <t>The programme is intended for small NGOs, grassroots organisations, community-based organisations and other eligible civil society groups requiring technology or digital-capacity support. Applicants should have a clearly identified organisational technology need and demonstrate how the proposed assistance could improve their work. Eligible organisations should be able to explain their existing technology challenges and the practical solution required. Applicants may need to provide relevant organisational documentation and information about their programmes. Organisations applying for technology grants India should ensure that their proposed requirement is connected to genuine operational, programme management, data, communication or monitoring needs.</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -4764,15 +3964,15 @@
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/who-ibp-network-spark-grants-2026/</t>
+          <t>https://andpurpose.world/technology-support-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -4789,35 +3989,35 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>2026 CSO Call for Expressions of Project Intentions – AFD</t>
+          <t>Apply for Resilience Fund for Women in Global Value Chains 2026 – Up to US$50,000</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Agence Française de Développement (AFD) is France’s public development agency working to finance and support projects that contribute to sustainable development, poverty reduction, climate action, biodiversity, social inclusion and international solidarity. Through its CSO Initiatives mechanism, AFD ... Read More</t>
+          <t>The Resilience Fund for Women in Global Value Chains The Resilience Fund for Women in Global Value Chains is a philanthropic initiative supporting women-led and community-based organisations working with women connected to global supply chains. The fund promotes locally led solutions addressing wome ... Read More</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Eligible CSOs should prepare a project intention describing the proposed project, objectives, expected outcomes, target communities and implementation approach. Applications must be submitted through AFD’s OSCar platform using the relevant project-intention documentation. Organisations without an OSCar account were required to request account creation by 15 September 2026. Complete project intentions must be submitted online by the final deadline. Applicants should carefully review the eligibility and documentation requirements before submission.</t>
+          <t>The Resilience Fund for Women in Global Value Chains 2026 provides flexible, unrestricted grants to women-led, community-based organisations in India, Bangladesh, Cambodia and Vietnam. Selected organisations can receive between US$15,000 and US$50,000 over two years. The fund supports work connected to women’s health and safety, economic resilience, climate adaptation and the rights and wellbeing of women workers in global value chains. Funding is designed to give local organisations greater flexibility in responding to community priorities rather than restricting every grant dollar to narrowly defined activities. Applications for the current round opened on September 18, 2026.</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>12 October 2026</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2026-cso-call-for-expressions-of-project-intentions-afd/</t>
+          <t>https://andpurpose.world/apply-for-resilience-fund-for-women-in-global-value-chains-2026/</t>
         </is>
       </c>
     </row>
@@ -4834,35 +4034,35 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Apply for Samhita-CGF Catalytic Grant 2026 – Up to ₹1 Crore for Education</t>
+          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Samhita–Collective Good Foundation works with organisations and partners seeking practical solutions to social and development challenges in India. Its grantmaking supports initiatives that improve access to essential services, strengthen systems and create sustainable opportunities for underserved ... Read More</t>
+          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Interested organisations should review Samhita-CGF’s programme information and eligibility requirements and submit an Expression of Interest through the designated application form. Applicants should clearly explain their education programme, target communities, expected outcomes, organisational experience and proposed use of funding. Samhita has also announced an applicant webinar for September 25, 2026. The EOI deadline is October 9, 2026.</t>
+          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>13 October 2026</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-samhita-cgf-catalytic-grant/</t>
+          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -4879,17 +4079,17 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
+          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
+          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
+          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
@@ -4899,15 +4099,15 @@
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>09 October 2026</t>
+          <t>15 October 2026</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
+          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
         </is>
       </c>
     </row>
@@ -4924,17 +4124,17 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Technology Support Programme 2026</t>
+          <t>Applications Invited for WUN Research Development Fund 2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>The Technology Support Programme for Small NGOs and Grassroots Organisations is designed to strengthen the digital and technological capacity of smaller civil society organisations. The programme focuses on helping organisations use technology to improve their operations, programme implementation, m ... Read More</t>
+          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>The programme is intended for small NGOs, grassroots organisations, community-based organisations and other eligible civil society groups requiring technology or digital-capacity support. Applicants should have a clearly identified organisational technology need and demonstrate how the proposed assistance could improve their work. Eligible organisations should be able to explain their existing technology challenges and the practical solution required. Applicants may need to provide relevant organisational documentation and information about their programmes. Organisations applying for technology grants India should ensure that their proposed requirement is connected to genuine operational, programme management, data, communication or monitoring needs.</t>
+          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -4944,15 +4144,15 @@
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>15 October 2026</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/technology-support-programme-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -4969,35 +4169,35 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Apply for Resilience Fund for Women in Global Value Chains 2026 – Up to US$50,000</t>
+          <t>Mohamed bin Zayed Species Conservation Fund 2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>The Resilience Fund for Women in Global Value Chains The Resilience Fund for Women in Global Value Chains is a philanthropic initiative supporting women-led and community-based organisations working with women connected to global supply chains. The fund promotes locally led solutions addressing wome ... Read More</t>
+          <t>The Mohamed bin Zayed Species Conservation Fund is an international conservation initiative supporting practical efforts to protect threatened species around the world. The fund provides financial assistance to conservationists working to prevent species extinction and improve the conservation statu ... Read More</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>The Resilience Fund for Women in Global Value Chains 2026 provides flexible, unrestricted grants to women-led, community-based organisations in India, Bangladesh, Cambodia and Vietnam. Selected organisations can receive between US$15,000 and US$50,000 over two years. The fund supports work connected to women’s health and safety, economic resilience, climate adaptation and the rights and wellbeing of women workers in global value chains. Funding is designed to give local organisations greater flexibility in responding to community priorities rather than restricting every grant dollar to narrowly defined activities. Applications for the current round opened on September 18, 2026.</t>
+          <t>The Mohamed bin Zayed Species Conservation Fund provides grants for practical, field-based projects focused on threatened species conservation. The programme supports work involving endangered and critically endangered species and can also consider Data Deficient species where strong conservation needs are demonstrated. Funding may support activities such as field research, population monitoring, habitat protection, conservation planning and community-based species protection. For organisations and individuals searching for wildlife conservation grants, biodiversity funding and endangered species grants, the programme provides an opportunity to finance targeted conservation actions. The December 2026 funding cycle is currently accepting applications until October 2026.</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>12 October 2026</t>
+          <t>15 October 2026</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-resilience-fund-for-women-in-global-value-chains-2026/</t>
+          <t>https://andpurpose.world/mohamed-bin-zayed-species-conservation-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -5014,231 +4214,51 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
+          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
+          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
+          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>13 October 2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Jack Kimmel International Grant Program 2026</t>
+          <t>RFP For Impact Assessment For FLN Program</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Tree Research and Education Endowment Fund (TREE Fund) TheTree Research and Education Endowment Fund (TREE Fund)is a nonprofit organisation dedicated to supporting scientific research and the dissemination of knowledge in arboriculture and urban forestry. Established in 2002, TREE Fund supports rese ... Read More</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should follow the TREE Fund research grant process and submit the required Letter of Intent (LOI) during the designated LOI period. Applicants whose concepts advance can proceed with the full submission. The 2026 Jack Kimmel programme opened on 1 August 2026, and the official TREE Fund page lists 15 October 2026 as the full submission deadline. Researchers should review the programme requirements and application instructions before submitting.</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>15 October 2026</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="I47" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-jack-kimmel-international-grant-program-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for WUN Research Development Fund 2026</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>TheWorldwide Universities Network (WUN)is an international partnership of research-intensive universities working together on major global challenges. WUN uses the geographic, cultural and academic diversity of its member institutions to develop collaborative research and education initiatives. Its ... Read More</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>TheWUN Research Development Fund (RDF) 2026provides grants of up to£10,000to researchers at WUN member universities. The fund is designed to encourage collaborative research across the network and help researchers develop projects that can lead to larger research programmes, publications and future external funding. The 2026 round is being operated as a transition towards WUN’s future research-support approach and will fund a smaller number of projects than previous rounds. A maximum of one application may be submitted by each lead member university, while member universities can participate as co-investigators in other proposals.</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>15 October 2026</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-wun-research-development-fund-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>Mohamed bin Zayed Species Conservation Fund 2026</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>The Mohamed bin Zayed Species Conservation Fund is an international conservation initiative supporting practical efforts to protect threatened species around the world. The fund provides financial assistance to conservationists working to prevent species extinction and improve the conservation statu ... Read More</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>The Mohamed bin Zayed Species Conservation Fund provides grants for practical, field-based projects focused on threatened species conservation. The programme supports work involving endangered and critically endangered species and can also consider Data Deficient species where strong conservation needs are demonstrated. Funding may support activities such as field research, population monitoring, habitat protection, conservation planning and community-based species protection. For organisations and individuals searching for wildlife conservation grants, biodiversity funding and endangered species grants, the programme provides an opportunity to finance targeted conservation actions. The December 2026 funding cycle is currently accepting applications until October 2026.</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>15 October 2026</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/mohamed-bin-zayed-species-conservation-fund-2026/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>Applications Invited for Blue Action Fund Grant Call: Mangroves, Blue Carbon Markets and 30×30 in Asia</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Blue Action Fundis a German foundation focused on conserving marine and coastal biodiversity while improving livelihoods in coastal communities. Its Grant Programme supports NGOs implementing marine protected areas, Other Effective Area-Based Conservation Measures (OECMs) and sustainable livelihood ... Read More</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Applicants must complete the official Blue Action Fund Grant Application template and submit it electronically in Word or PDF format, under 5 MB. Applications should be emailed to grants@blueactionfund.org with the subject line “[your organisation] Grant Application”. The process has two stages: a competitive Grant Application stage followed by Full Proposal Development for shortlisted applicants.</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>16 October 2026</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="I50" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/applications-invited-for-blue-action-fund-grant-call-mangroves-blue-carbon-markets-and-30x30-in-asia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Impact Assessment For FLN Program</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Centre For Microfinance &amp; Livelihood (Cml) | Goalpara, Bongaigaon and Baksa District., Assam
 RFP For Impact Assessment For FLN Program, Centre For Microfinance &amp; Livelihood (Cml)(Goalpara, Bongaigaon and Baksa District.) | DevNetJobsIndia
@@ -5251,7 +4271,7 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>• 3. Eligibility of bidder:
 a. The bidder can either be a propriety or partnership firm, company or any
@@ -5313,6 +4333,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -5361,69 +4393,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -5454,22 +4474,202 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303842</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Greenprint GET Breakthrough Innovation Award 2027 for Indian Startups</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent policy research institution working on energy, environment, climate and sustainable development issues in India and beyond. CEEW brings together research, policy engagement and partnerships to support evidence-based solutions for ... Read More</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Eligible startups should apply through the Greenprint Awards application process before the closing date. Applicants should select the GET Breakthrough Innovation category and provide accurate information about their organisation, innovation, impact and contribution to the green economy. Supporting evidence should clearly demonstrate the systemic significance of the solution. Applicants should review the category requirements and terms before submitting. Only one category may be selected by each applicant. There is no entry fee for the Greenprint Awards.</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>16 October 2026</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-greenprint-get-breakthrough-innovation-award/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>North Midlands Drought Resilience Community Grant 2026 – Apply by 16 October</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>TheAustralian Government’s Future Drought Fundand theWestern Australian Governmentjointly support the Regional Drought Resilience Planning Program. The programme helps regional communities strengthen their ability to prepare for and manage drought and prolonged dry seasons. Through regional planning ... Read More</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Eligible applicants must have a currentAustralian Business Number (ABN)or be auspiced by an incorporated organisation with an ABN. Applicants must have an account with an Australian financial institution and meet GST registration requirements where applicable. They must demonstrate sufficient organisational capacity, resources, partnerships, and arrangements to successfully deliver the proposed project. Projects must contribute to drought resilience and demonstrate alignment with the Mid West Regional Drought Resilience Plan. Applicants must also be able to manage project expenditure, monitor outcomes, deliver approved activities, and meet reporting and accountability requirements. These eligibility conditions apply to organisations seeking Future Drought Fund grants through this programme.</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>16 October 2026</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/north-midlands-drought-resilience-community-grant-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Greenprint Rising Star Award 2027 for Women Climate Leaders</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.centered stories.</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>16 October 2026</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-greenprint-rising-star-award-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Greenprint Art and Culture Award 2027 for Climate Storytellers</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.</t>
+        </is>
+      </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>Governance, Learning</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>16-10-2026</t>
+          <t>16 October 2026</t>
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303842</t>
+          <t>https://andpurpose.world/apply-for-greenprint-art-and-culture-award-2027-for-climate-storytellers/</t>
         </is>
       </c>
     </row>
@@ -5486,17 +4686,17 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Apply for Greenprint GET Breakthrough Innovation Award 2027 for Indian Startups</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>The Council on Energy, Environment and Water (CEEW) is an independent policy research institution working on energy, environment, climate and sustainable development issues in India and beyond. CEEW brings together research, policy engagement and partnerships to support evidence-based solutions for ... Read More</t>
+          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Eligible startups should apply through the Greenprint Awards application process before the closing date. Applicants should select the GET Breakthrough Innovation category and provide accurate information about their organisation, innovation, impact and contribution to the green economy. Supporting evidence should clearly demonstrate the systemic significance of the solution. Applicants should review the category requirements and terms before submitting. Only one category may be selected by each applicant. There is no entry fee for the Greenprint Awards.</t>
+          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
@@ -5506,15 +4706,15 @@
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-greenprint-get-breakthrough-innovation-award/</t>
+          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
         </is>
       </c>
     </row>
@@ -5531,17 +4731,17 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>North Midlands Drought Resilience Community Grant 2026 – Apply by 16 October</t>
+          <t>Apply for Re-Alliance Upscaling &amp; Integrating Regeneration Grant 2026 – £13,625</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>TheAustralian Government’s Future Drought Fundand theWestern Australian Governmentjointly support the Regional Drought Resilience Planning Program. The programme helps regional communities strengthen their ability to prepare for and manage drought and prolonged dry seasons. Through regional planning ... Read More</t>
+          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscal ... Read More</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants must have a currentAustralian Business Number (ABN)or be auspiced by an incorporated organisation with an ABN. Applicants must have an account with an Australian financial institution and meet GST registration requirements where applicable. They must demonstrate sufficient organisational capacity, resources, partnerships, and arrangements to successfully deliver the proposed project. Projects must contribute to drought resilience and demonstrate alignment with the Mid West Regional Drought Resilience Plan. Applicants must also be able to manage project expenditure, monitor outcomes, deliver approved activities, and meet reporting and accountability requirements. These eligibility conditions apply to organisations seeking Future Drought Fund grants through this programme.</t>
+          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscaling and Integrating Regeneration Grant, Re-Alliance is providing funding to a grassroots organisation in a Global South country to develop a new regenerative project. The grant also supports knowledge sharing with influential regional organisations or government bodies and collaboration to produce educational materials. The initiative particularly encourages applications from organisations working in Asia and the MENA region and those led by displaced people, refugees, women or affected communities. contemporary global issues.</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -5551,15 +4751,15 @@
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/north-midlands-drought-resilience-community-grant-2026/</t>
+          <t>https://andpurpose.world/apply-for-re-alliance-upscaling-integrating-regeneration-grant-2026-13625/</t>
         </is>
       </c>
     </row>
@@ -5576,35 +4776,35 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Apply for Greenprint Rising Star Award 2027 for Women Climate Leaders</t>
+          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
+          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.centered stories.</t>
+          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>20 October 2026</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-greenprint-rising-star-award-2027/</t>
+          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
         </is>
       </c>
     </row>
@@ -5621,35 +4821,35 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Apply for Greenprint Art and Culture Award 2027 for Climate Storytellers</t>
+          <t>National Geographic Ocean Exploration and Discovery Grant 2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>The Council on Energy, Environment and Water (CEEW) is an independent research institution working on energy, environment, climate and sustainable development. Its work connects evidence-based research with policy and practical solutions for environmental and social challenges. CEEW organises The Gr ... Read More</t>
+          <t>The National Geographic Society is a global nonprofit organisation dedicated to exploring and understanding our world through science, research, education and storytelling. It supports scientists, conservationists, educators and explorers working on projects that advance knowledge and protect the pl ... Read More</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The award is open to an individual or organisation based in India that has used creative storytelling to communicate climate change and sustainability issues. Eligible creative formats include film, literature, photography, sculpture, installations, paintings, digital media and other relevant forms of artistic expression. The work should make climate change more accessible, relatable and action-oriented or contribute meaningfully to public understanding. Importantly, the applicant must be a woman associated with the production in a key manner. Applicants must satisfy the category-specific requirements and can submit an application under only one Greenprint Awards category.</t>
+          <t>Applicants should review the Ocean Exploration and Discovery programme requirements and confirm their eligibility before preparing an application. The proposal should clearly explain the research objectives, methodology, expected outcomes and relevance to ocean exploration. Applicants must submit the required information and supporting materials through the designated application process before the closing date. Early preparation is recommended to ensure all required scientific and administrative information is complete.</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>16 October 2026</t>
+          <t>21 October 2026</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-greenprint-art-and-culture-award-2027-for-climate-storytellers/</t>
+          <t>https://andpurpose.world/national-geographic-ocean-exploration-and-discovery-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -5666,17 +4866,17 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States)</t>
+          <t>Apply for Aidsfonds ActHIVate Fund 2026 – €2 Million Funding Pool</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2027 AmeriCorps Seniors RSVP Competition (United States) AmeriCorpsis a U.S. federal agency that brings people together through national and community service to address important challenges across the United States. Its programmes support volunteerism, civic engagement and community-based service w ... Read More</t>
+          <t>Aidsfonds is an international organisation working to end AIDS and improve access to HIV prevention, treatment, care and rights-based services. The organisation supports community-led responses and works with affected communities, civil society organisations and partners to address barriers to HIV s ... Read More</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants can includefederally recognized Native American tribal governments, county governments, city or township governments, special district governments, tribal organizations, state governments, nonprofit organizations and public or private institutions of higher education. Nonprofits do not necessarily need to hold501(c)(3)status to be eligible. Applicants should have the organizational capacity to recruit, train, manage, supervise and support volunteers aged 55 and older. Organizations should also demonstrate their ability to identify meaningful community needs, establish appropriate volunteer roles, track volunteer contributions and measure outcomes. Applicants must meet all additional requirements contained in the official competition notice and application instructions.</t>
+          <t>Eligible applicants are community-led, not-for-profit civil society organisations that are led by and primarily serve men who have sex with men and trans communities. Applicants must demonstrate experience in HIV-related health programming and advocacy. The current call covers organisations working in Uganda, Nigeria, Morocco, Egypt, Lebanon, Ukraine, Kazakhstan, Kyrgyzstan and Moldova. Organisations must be able to implement the proposed project during the specified 2027–2028 period and submit their application in English through the Aidsfonds Good Grants platform.</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -5686,15 +4886,15 @@
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>25 October 2026</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2027-americorps-seniors-rsvp-competition-united-states/</t>
+          <t>https://andpurpose.world/apply-for-aidsfonds-acthivate-fund-2026-e2-million-funding-pool/</t>
         </is>
       </c>
     </row>
@@ -5711,17 +4911,17 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Apply for Re-Alliance Upscaling &amp; Integrating Regeneration Grant 2026 – £13,625</t>
+          <t>Apply for WRF PFAS Contributions to Agricultural Systems Grant – US$400,000</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscal ... Read More</t>
+          <t>The Water Research Foundation (WRF) is a research organisation supporting scientific studies and innovation related to water quality, water management and emerging environmental challenges. Through its Research Priority Program, WRF funds research addressing practical issues relevant to water and en ... Read More</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Re-Alliance is a network focused on regenerative humanitarian responses and approaches that go beyond conventional sustainability models. Its work supports community-led approaches in displacement settings and seeks to strengthen the agency of communities affected by displacement. Through its Upscaling and Integrating Regeneration Grant, Re-Alliance is providing funding to a grassroots organisation in a Global South country to develop a new regenerative project. The grant also supports knowledge sharing with influential regional organisations or government bodies and collaboration to produce educational materials. The initiative particularly encourages applications from organisations working in Asia and the MENA region and those led by displaced people, refugees, women or affected communities. contemporary global issues.</t>
+          <t>Applicants should review the official WRF 2026 Research Priority Program guidelines and the RFP-5413 documentation before preparing their proposal. Required materials include the relevant certification and assurance documentation, co-funding support information, current and pending forms and project budget materials. Proposals must address the stated PFAS agricultural research objectives and follow WRF’s submission requirements. Applications are submitted through the WRF grant portal using an eligible organisation account.</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -5731,15 +4931,15 @@
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>26 October 2026</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-re-alliance-upscaling-integrating-regeneration-grant-2026-13625/</t>
+          <t>https://andpurpose.world/apply-for-wrf-pfas-contributions-to-agricultural-systems/</t>
         </is>
       </c>
     </row>
@@ -5756,17 +4956,17 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Apply for Sustainable Northern Operations Water and Waste Grant – Up to $5 Million</t>
+          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>The Department of National Defence (DND) and the Canadian Armed Forces (CAF) The Department of National Defence (DND) and the Canadian Armed Forces (CAF) are supporting innovation that can strengthen sustainable operations in Canada’s Arctic and sub-Arctic regions. Through the Innovation for Defence ... Read More</t>
+          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the challenge requirements and prepare a proposal describing their technology, development stage, technical approach, expected outcomes and ability to address northern operational requirements. Proposals must be submitted through the designated Government of Canada procurement process and follow the applicable solicitation requirements. Applicants should demonstrate how their solution integrates water purification, wastewater treatment and solid-waste management while operating reliably in Arctic conditions. The application should also explain the technology’s readiness level and development needs.</t>
+          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -5776,15 +4976,15 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>20 October 2026</t>
+          <t>26 October 2026</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-sustainable-northern-operations-water-and-waste-grant/</t>
+          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
         </is>
       </c>
     </row>
@@ -5801,17 +5001,17 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>National Geographic Ocean Exploration and Discovery Grant 2026</t>
+          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>The National Geographic Society is a global nonprofit organisation dedicated to exploring and understanding our world through science, research, education and storytelling. It supports scientists, conservationists, educators and explorers working on projects that advance knowledge and protect the pl ... Read More</t>
+          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the Ocean Exploration and Discovery programme requirements and confirm their eligibility before preparing an application. The proposal should clearly explain the research objectives, methodology, expected outcomes and relevance to ocean exploration. Applicants must submit the required information and supporting materials through the designated application process before the closing date. Early preparation is recommended to ensure all required scientific and administrative information is complete.</t>
+          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -5821,15 +5021,15 @@
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>21 October 2026</t>
+          <t>28 October 2026</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/national-geographic-ocean-exploration-and-discovery-grant-2026/</t>
+          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5046,17 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Apply for Aidsfonds ActHIVate Fund 2026 – €2 Million Funding Pool</t>
+          <t>Whitley Award 2027</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Aidsfonds is an international organisation working to end AIDS and improve access to HIV prevention, treatment, care and rights-based services. The organisation supports community-led responses and works with affected communities, civil society organisations and partners to address barriers to HIV s ... Read More</t>
+          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Eligible applicants are community-led, not-for-profit civil society organisations that are led by and primarily serve men who have sex with men and trans communities. Applicants must demonstrate experience in HIV-related health programming and advocacy. The current call covers organisations working in Uganda, Nigeria, Morocco, Egypt, Lebanon, Ukraine, Kazakhstan, Kyrgyzstan and Moldova. Organisations must be able to implement the proposed project during the specified 2027–2028 period and submit their application in English through the Aidsfonds Good Grants platform.</t>
+          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -5866,211 +5066,31 @@
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>25 October 2026</t>
+          <t>30 October 2026</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-aidsfonds-acthivate-fund-2026-e2-million-funding-pool/</t>
+          <t>https://andpurpose.world/whitley-award-2027/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr"/>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Apply for WRF PFAS Contributions to Agricultural Systems Grant – US$400,000</t>
+          <t>RFP - For the Empanelment of agencies to support the development, validati...</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>The Water Research Foundation (WRF) is a research organisation supporting scientific studies and innovation related to water quality, water management and emerging environmental challenges. Through its Research Priority Program, WRF funds research addressing practical issues relevant to water and en ... Read More</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should review the official WRF 2026 Research Priority Program guidelines and the RFP-5413 documentation before preparing their proposal. Required materials include the relevant certification and assurance documentation, co-funding support information, current and pending forms and project budget materials. Proposals must address the stated PFAS agricultural research objectives and follow WRF’s submission requirements. Applications are submitted through the WRF grant portal using an eligible organisation account.</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>26 October 2026</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-wrf-pfas-contributions-to-agricultural-systems/</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>WRF Adaptive BNR Control Grant 2026: Apply for Up to $300,000</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>TheWater Research Foundation (WRF)is a research-focused organisation that supports scientific and practical advances in water quality, wastewater treatment, and water management. Through research funding and collaboration, WRF helps utilities and the wider water sector address complex technical and ... Read More</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline for theWRF Adaptive BNR Control Grant 2026is26 October 2026. Applicants should complete their research proposal, budget, contribution plan, and supporting materials before the stated deadline.</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>26 October 2026</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/wrf-adaptive-bnr-control-grant-2026-apply-for-up-to-300000/</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>Apply for COST Open Call 2026 – Research Funding Up to €600,000</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>COST (European Cooperation in Science and Technology TheEuropean Cooperation in Science and Technology (COST)is a European research and innovation funding organisation that supports networking and collaboration among researchers and innovators. COST Actions bring together experts from different coun ... Read More</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should develop a bottom-up research-network idea addressing a relevant scientific, technological or societal challenge. Build a qualifying international network of proposers and ensure that the required geographic and young-researcher participation criteria are met. Proposals must be submitted online through the e-COST platform. The 2026 process uses a single-stage submission, with the Technical Annex integrated into the online application. Applicants should follow the current COST Open Call Announcement and Proposers’ Guidelines when preparing and submitting their proposal.</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>28 October 2026</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-cost-open-call-2026-research-funding-up-to-e600000/</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>Whitley Award 2027</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>TheWhitley Fund for Nature (WFN)is a UK-based charity that supports grassroots conservation leaders working to protect wildlife and biodiversity, particularly across the Global South. WFN provides funding, training, international recognition and professional support to conservationists implementing ... Read More</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>The Whitley Award is intended formid-career conservationists and grassroots conservation leaders working in the Global South. Applicants must be nationals of the country where they are carrying out their conservation work and should be leading an established project that has demonstrated results and would benefit from additional funding and international support. Projects must involvelocal communities at the grassroots leveland use practical conservation approaches founded on scientific evidence. Applicants should demonstrate that their work can be scaled up and deliver lasting benefits for people and nature.Applicants do not need to be invited or nominatedto apply for the award.</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>30 October 2026</t>
-        </is>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/whitley-award-2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>RFP - For the Empanelment of agencies to support the development, validati...</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS) | India
 RFP - For the Empanelment of agencies to support the development, validation, deployment, and scaling of AI-enabled agriculture solutions, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
@@ -6082,7 +5102,7 @@
 Value Membersh ... Read More</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 rfp.lehs(at)wadhwaniai.org
@@ -6098,6 +5118,18 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
 Field Coordinator - Village Institutions
 Basudeo Kanoria Seva Sansthan
 Location:
@@ -6146,69 +5178,57 @@
 Karnataka
 Apply by:
 05 Oct 2026
-Resource Person – Vocational Education
-Azim Premji Foundation
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Director / Associate Director: Corporate Fundrais...
-India HIV/ AIDS Alliance (Alliance India)
-Location:
-Delhi
-Apply by:
-30 Sep 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Account Person
-Sangini
+Social Worker
+Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+Location:
+Uttar Pradesh
+Apply by:
+30 Sep 2026
+Senior Associate - Social Media &amp; Comms
+(Value Members only)
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+Senior Coordinator, Strategy and Convergence
+Jan Sahas Foundation
 Location:
 Madhya Pradesh
 Apply by:
-05 Oct 2026
-HR Coordinator
-(Value Members only)
-Location:
-Assam
-Apply by:
-09 Oct 2026
-Counselor
-Asian Minority Action Network
-Location:
-Jharkhand
-Apply by:
-10 Oct 2026
-Master Trainer
-(Value Members only)
-Location:
-Gujarat
-Apply by:
-10 Oct 2026
-MIS Executive - DDU-GKY Project
-Nifa India
-Location:
-West Bengal
-Apply by:
-24 Oct 2026
-Fundraising Executive / Manager
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-07 Oct 2026
-Community Outreach Workers
-Sangini
-Location:
-Madhya Pradesh
-Apply by:
-05 Oct 2026
-Senior Program Manager, Assistant Project Manager...
-(Value Members only)
+20 Oct 2026
+Senior Field Consultant
+Soulace
+Location:
+India
+Apply by:
+28 Oct 2026
+Report Writer (Consultant)
+Soulace
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Community Coordinator
+Habitat for Humanity India
+Location:
+Maharashtra
+Apply by:
+28 Oct 2026
+Assistant Manager (Partnerships and Fundraising)
+PRAGYA
 Location:
 Haryana
 Apply by:
-10 Oct 2026
+28 Oct 2026
+Assistant Manager – MIS
+PRAGYA
+Location:
+Haryana
+Apply by:
+28 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -6239,22 +5259,202 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>31-10-2026</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304046</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>Apply for TEEEM Foundation Community Impact Grant 2026 – Up to $30,000</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>The TEEEM Foundation supports nonprofit and charitable organisations working to improve lives and strengthen communities around the world. Its Community Impact Grant Program focuses on locally informed, sustainable solutions developed with communities rather than simply for them. The Foundation supp ... Read More</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>The grant is intended for nonprofit and charitable organisations working to improve communities around the world. Suitable applicants should have strong leadership and financial stewardship and demonstrate a clear understanding of the communities they serve. Projects should be community-centred and have measurable outcomes and a pathway toward sustainable impact. TEEEM identifies education and youth development, health and essential needs, equality and empowerment, entrepreneurship and economic opportunity, community infrastructure and sustainable community initiatives among its funding areas. Applicants should review the official application for the complete eligibility requirements and required documentation before applying.</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>1 November 2026</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-teeem-foundation-community-impact-grant-2026-up-to-30000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>National Indian Health Outreach and Education Program 2026</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>2 November 2026</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>4 November 2026</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Applications Invited for World Food Day Poster Contest 2026</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 6 November 2026</t>
+        </is>
+      </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>31-10-2026</t>
+          <t>6 November 2026</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304046</t>
+          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
         </is>
       </c>
     </row>
@@ -6271,17 +5471,17 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Apply for TEEEM Foundation Community Impact Grant 2026 – Up to $30,000</t>
+          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>The TEEEM Foundation supports nonprofit and charitable organisations working to improve lives and strengthen communities around the world. Its Community Impact Grant Program focuses on locally informed, sustainable solutions developed with communities rather than simply for them. The Foundation supp ... Read More</t>
+          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>The grant is intended for nonprofit and charitable organisations working to improve communities around the world. Suitable applicants should have strong leadership and financial stewardship and demonstrate a clear understanding of the communities they serve. Projects should be community-centred and have measurable outcomes and a pathway toward sustainable impact. TEEEM identifies education and youth development, health and essential needs, equality and empowerment, entrepreneurship and economic opportunity, community infrastructure and sustainable community initiatives among its funding areas. Applicants should review the official application for the complete eligibility requirements and required documentation before applying.</t>
+          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -6291,15 +5491,15 @@
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>1 November 2026</t>
+          <t>9 November 2026</t>
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-teeem-foundation-community-impact-grant-2026-up-to-30000/</t>
+          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
         </is>
       </c>
     </row>
@@ -6316,35 +5516,35 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>National Indian Health Outreach and Education Program 2026</t>
+          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Indian Health Service (IHS), U.S. Department of Health and Human Services TheIndian Health Service (IHS)is an agency within the U.S. Department of Health and Human Services responsible for providing federal health services to American Indian and Alaska Native people. Its programmes support health ca ... Read More</t>
+          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Eligible organisations should review the official HHS-2026-IHS-NIHOE-0001 funding announcement and prepare an application addressing the programme’s outreach, education and technical assistance objectives. Applicants should demonstrate relevant organisational expertise and capacity to serve Tribal communities at a national level. The complete application must be submitted through the federal grant application system before the stated deadline.</t>
+          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>2 November 2026</t>
+          <t>15 November 2026</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/national-indian-health-outreach-and-education-program-2026/</t>
+          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
         </is>
       </c>
     </row>
@@ -6361,17 +5561,17 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIFAR Global Scholars Program 2027–2029 Cohort</t>
+          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>TheCanadian Institute for Advanced Research (CIFAR)is a Canada-based global research organisation that brings together researchers from different disciplines and countries to address major questions in science and society. Its model is built around long-term interdisciplinary collaboration, allowing ... Read More</t>
+          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>TheCIFAR Global Scholars Program 2027–2029is a two-year opportunity for early-career researchers to become members of a CIFAR interdisciplinary research programme. Scholars receiveCAD $100,000 in unrestricted research support, administered through their home institution, which can be used for research activities, teaching release, trainee support and conference travel. In addition to funding, the programme provides mentorship, international collaboration, leadership development, networking and opportunities to pursue high-risk, high-reward interdisciplinary research. Scholars can also apply for additional seed funding for collaborative projects.</t>
+          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -6381,15 +5581,15 @@
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>4 November 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cifar-global-scholars-program-2027-2029-cohort/</t>
+          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
         </is>
       </c>
     </row>
@@ -6406,17 +5606,17 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for World Food Day Poster Contest 2026</t>
+          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Food and Agriculture Organization of the United Nations (FAO) TheFood and Agriculture Organization of the United Nations (FAO)is a specialised UN agency working to eliminate hunger, improve nutrition and strengthen food security worldwide. FAO promotes sustainable agriculture, resilient food systems ... Read More</t>
+          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 6 November 2026</t>
+          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -6426,15 +5626,15 @@
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>6 November 2026</t>
+          <t>16 November 2026</t>
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-world-food-day-poster-contest-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
         </is>
       </c>
     </row>
@@ -6451,35 +5651,35 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Community Grant Scheme 2026 – Kingswood Town Council</t>
+          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Kingswood Town Councilsupports the development and wellbeing of the Kingswood community in the United Kingdom. Through its Community Grant Scheme, the Council provides financial assistance to local organisations delivering projects that benefit residents and contribute to the town’s future. The sche ... Read More</t>
+          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Local organisations should review the Community Grant Scheme guidance and identify the appropriate funding category for their project. Applicants should prepare details of the project, its benefits to Kingswood residents, proposed expenditure and alignment with the Council’s priorities. The application should clearly distinguish between revenue and capital costs where relevant and demonstrate how the project contributes to the future development of Kingswood.</t>
+          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>9 November 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/community-grant-scheme-2026-kingswood-town-council/</t>
+          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
         </is>
       </c>
     </row>
@@ -6496,17 +5696,17 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>IWRS Teaching Innovation Award for Insect and Invertebrate Biology</t>
+          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>TheInsect Welfare Research Society (IWRS)is an academic-led research society established in 2023 to advance evidence-based understanding of insect and invertebrate welfare. The organization supports the global insect welfare research community and promotes the integration of scientific evidence into ... Read More</t>
+          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Develop a teaching innovation focused on insect or invertebrate biology and clearly incorporate the 3Rs principles of Replacement, Reduction and Refinement. Identify the existing teaching practice and explain its welfare implications. Describe your proposed instructional materials or pedagogical approach, expected educational outcomes and welfare benefits. Explain how the approach can be implemented and potentially adopted more broadly. Submit the required application materials according to IWRS instructions before the deadline.</t>
+          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
@@ -6516,15 +5716,15 @@
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>15 November 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/iwrs-teaching-innovation-award-for-insect-and-invertebrate-biology/</t>
+          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
         </is>
       </c>
     </row>
@@ -6541,17 +5741,17 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Apply for DPS Social Commitment Programme UK – Grants Up to £7,000</t>
+          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>The School for Social Entrepreneurs (SSE) and The Deposit Protection Service (DPS) The School for Social Entrepreneurs (SSE), in partnership with The Deposit Protection Service (DPS), supports organisations and entrepreneurs developing solutions to important social challenges. Through learning progr ... Read More</t>
+          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Applicants must first register their interest in the DPS Social Commitment Programme. Following registration, eligible organisations receive information about the programme, guidance notes and access to the application form. Applicants should review the requirements carefully, prepare details about their organisation and explain how the grant and learning programme will strengthen their work addressing homelessness or housing insecurity. The completed application must be submitted through the online application process before the stated deadline.</t>
+          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
@@ -6561,15 +5761,15 @@
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-dps-social-commitment-programme-uk-grants/</t>
+          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
         </is>
       </c>
     </row>
@@ -6586,17 +5786,17 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Medium-Size Grants Call for Proposals – Global EbA Fund</t>
+          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Global EbA Fund, co-led by IUCN and UNEP and supported through Germany’s International Climate Initiative (IKI) TheGlobal EbA Fundis a funding mechanism designed to support catalytic, innovative and inclusive approaches toEcosystem-based Adaptation (EbA). It is co-led by the International Union for ... Read More</t>
+          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Applicants should prepare the required application package, including the Applicant Declaration, Co-applicant Mandate where applicable, Medium-Size Grants Application Form, Project Proposal Budget Template, and Due Diligence and Financial Capacity Questionnaire. Applications must be submitted in English through the online platform. The submission portal will become available from 12 October 2026 on the official Medium-Size Grants webpage. Applicants are encouraged to prepare their application offline before submitting it online.</t>
+          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
@@ -6606,15 +5806,15 @@
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>16 November 2026</t>
+          <t>1 December 2026</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-medium-size-grants-call-for-proposals-global-eba-fund/</t>
+          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
         </is>
       </c>
     </row>
@@ -6631,35 +5831,35 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for CIEIF Grant 2026 – Climate Intervention Environmental Impact Fund</t>
+          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Climate Intervention Environmental Impact Fund (CIEIF) TheClimate Intervention Environmental Impact Fund (CIEIF)is a philanthropic fund supporting innovative climate intervention investigators worldwide. Its funding is specifically focused on understanding the potential consequences of proposed smal ... Read More</t>
+          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>CIEIF considers applications fromqualified investigators and project teamsdeveloping innovative climate intervention technologies with potential for global-scale climate benefits. Priority is given to nonprofit institutions, including academic institutions, although private businesses preparing climate intervention field tests may also be considered. Individuals and student projects are not eligible. The proposed technology must be sufficiently ready for a small-scale field test and the application must focus on at least one of CIEIF’s three core areas: EIA, predictive impact modelling or stakeholder engagement. Applicants must also identify relevant permits, prior research and publications, consultants, other funding sources and potential insurance arrangements.</t>
+          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>20 December 2026</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-cieif-grant-2026-climate-intervention-environmental-impact-fund/</t>
+          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
         </is>
       </c>
     </row>
@@ -6676,17 +5876,17 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Apply Now for AISLS Dissertation Planning Grant (United States)</t>
+          <t>Apply for Ernest Solvay Fund 2026 – Up to €10,000</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>TheAmerican Institute for Sri Lankan Studies (AISLS)promotes research, teaching and scholarly exchange focused on Sri Lanka. Established in 1996, the institute works to strengthen connections between scholars and academic institutions in the United States and Sri Lanka. AISLS focuses particularly on ... Read More</t>
+          <t>The Ernest Solvay Fund supports non-commercial initiatives that contribute to scientific education, environmental sustainability and community wellbeing. The fund focuses on three broad areas: STEM education, Planet Progress and Better Life. It supports organisations developing practical projects re ... Read More</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Confirm your eligibility and prepare the required application materials, including the cover sheet, CV, graduate transcript, project narrative and one-page bibliography. Combine the application into a single Word or PDF file following AISLS formatting instructions. Ask your dissertation supervisor to send the confidential recommendation letter directly to AISLS US Director John Rogers. Submit the completed application by 1 December 2026.</t>
+          <t>The fund is open to organisations implementing eligible non-commercial projects. Proposed initiatives must fall under STEM education, Planet Progress or Better Life and must be implemented within 100 kilometres of an eligible Solvay industrial, R&amp;D or administrative site. Commercial sites do not qualify for the geographic requirement. Relevant projects can involve science and technology education, biodiversity, environmental protection, energy, water and air quality or community wellbeing. Applicants should verify that their project location meets the distance requirement before preparing their application.</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
@@ -6696,15 +5896,15 @@
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>30 December 2026</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-for-aisls-dissertation-planning-grant-united-states/</t>
+          <t>https://andpurpose.world/apply-for-ernest-solvay-fund-2026/</t>
         </is>
       </c>
     </row>
@@ -6721,17 +5921,17 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Apply Now: JF-JSA-ASEAN Fellowship Program 2027</t>
+          <t>Apply for FIER·ES Ukraine Psychosocial &amp; Emergency Support 2026 – Up to €2,300</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>The Japan Foundationis Japan’s only institution dedicated to comprehensive international cultural exchange. It operates programmes covering arts and cultural exchange, Japanese-language education, and Japanese studies and global partnerships. Through its Japanese Studies programmes, the Foundation s ... Read More</t>
+          <t>ERIM is an international nonprofit organisation working to strengthen human rights, independent media and civil society. Through programmes supporting civil society organisations and activists, ERIM provides capacity building, grants and other assistance to organisations and individuals facing diffi ... Read More</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The fellowship is open toPh.D. candidates at graduate schools in Southeast Asiaand researchers affiliated with institutions in Southeast Asia who are conducting research related to Japan, including comparative research. Doctoral candidates must have completed, or be expected to complete by the fellowship start, the necessary coursework. Researchers must hold aPh.D. or equivalent professional experience. Applicants must secure arrangements with advisors or research associates in Japan by the application deadline, be proficient in Japanese or English, and be able to stay continuously in Japan for the fellowship period.</t>
+          <t>The FIER·ES Programme provides two forms of support in Ukraine. Eligible applicants can receive up to€500 for psychosocial and wellbeing supportand up to€2,300 in emergency assistancefor eligible needs such as legal aid, security measures, medical expenses and relocation assistance. The programme aims to strengthen the resilience and safety of LGBTQIA+ activists and civil society actors while helping organisations and individuals continue their human rights and inclusion work. Applications remain open on a continuing basis through the published deadline, subject to programme requirements and available support.</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
@@ -6741,15 +5941,15 @@
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>31 December 2026</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-now-jf-jsa-asean-fellowship-program-2027/</t>
+          <t>https://andpurpose.world/apply-for-fier%c2%b7es-ukraine-psychosocial-emergency-support/</t>
         </is>
       </c>
     </row>
@@ -6766,17 +5966,17 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>ASPECT Funding Opportunity: $2M–$20M Grants for Emerging Chemical Technologies</t>
+          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>TheU.S. Department of Energy (DOE)is a federal government agency responsible for advancing America’s energy, science, technology, and national security priorities. Through research and funding programmes, DOE supports innovation in energy technologies, manufacturing, critical minerals, and sustainab ... Read More</t>
+          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>TheASPECT funding opportunityhas an application deadline of1 December 2026.</t>
+          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
@@ -6786,15 +5986,15 @@
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>1 December 2026</t>
+          <t>14 January 2027</t>
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/aspect-funding-opportunity-2m/</t>
+          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
         </is>
       </c>
     </row>
@@ -6811,35 +6011,35 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Oneness Revival Team ORT NGO Grant Programme 2026</t>
+          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Oneness Revival Team (ORT)is a non-governmental and philanthropic organisation focused on supporting grassroots nonprofits working towards social, economic and environmental development. ORT aims to help NGOs strengthen their organisational capacity, expand community programmes and improve long-term ... Read More</t>
+          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>The programme is open toregistered nonprofit organisations worldwide. Applicants must demonstrate a clear mission, measurable community impact and transparent financial management. The current official application page states that eligible NGOs must have anannual operating budget below USD 50,000. Applicants must also submit a detailed proposal explaining their activities, budget and expected outcomes. SEED is intended for organisations that have not previously received ORT funding, while THRIVE is for previously funded NGOs in good standing.</t>
+          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>20 December 2026</t>
+          <t>15 January 2027</t>
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-oneness-revival-team-ort-ngo-grant-programme-2026/</t>
+          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
         </is>
       </c>
     </row>
@@ -6856,17 +6056,17 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Apply for Ernest Solvay Fund 2026 – Up to €10,000</t>
+          <t>J. N. Derbyshire Trust Grants UK: Apply for Up to £10,000</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>The Ernest Solvay Fund supports non-commercial initiatives that contribute to scientific education, environmental sustainability and community wellbeing. The fund focuses on three broad areas: STEM education, Planet Progress and Better Life. It supports organisations developing practical projects re ... Read More</t>
+          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, ... Read More</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>The fund is open to organisations implementing eligible non-commercial projects. Proposed initiatives must fall under STEM education, Planet Progress or Better Life and must be implemented within 100 kilometres of an eligible Solvay industrial, R&amp;D or administrative site. Commercial sites do not qualify for the geographic requirement. Relevant projects can involve science and technology education, biodiversity, environmental protection, energy, water and air quality or community wellbeing. Applicants should verify that their project location meets the distance requirement before preparing their application.</t>
+          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, advancing education, and relieving poverty, distress and sickness. The Trust primarily supports community and voluntary organisations through project funding. It operates as a grant-making charity and reviews applications through two annual grant rounds. The Trust prioritises organisations delivering meaningful benefits within Nottingham and Nottinghamshire.</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
@@ -6876,15 +6076,15 @@
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>30 December 2026</t>
+          <t>31 January 2027</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-ernest-solvay-fund-2026/</t>
+          <t>https://andpurpose.world/j-n-derbyshire-trust-grants/</t>
         </is>
       </c>
     </row>
@@ -6901,17 +6101,17 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Apply for FIER·ES Ukraine Psychosocial &amp; Emergency Support 2026 – Up to €2,300</t>
+          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>ERIM is an international nonprofit organisation working to strengthen human rights, independent media and civil society. Through programmes supporting civil society organisations and activists, ERIM provides capacity building, grants and other assistance to organisations and individuals facing diffi ... Read More</t>
+          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>The FIER·ES Programme provides two forms of support in Ukraine. Eligible applicants can receive up to€500 for psychosocial and wellbeing supportand up to€2,300 in emergency assistancefor eligible needs such as legal aid, security measures, medical expenses and relocation assistance. The programme aims to strengthen the resilience and safety of LGBTQIA+ activists and civil society actors while helping organisations and individuals continue their human rights and inclusion work. Applications remain open on a continuing basis through the published deadline, subject to programme requirements and available support.</t>
+          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
@@ -6921,15 +6121,15 @@
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>31 December 2026</t>
+          <t>15 February 2027</t>
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-fier%c2%b7es-ukraine-psychosocial-emergency-support/</t>
+          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
         </is>
       </c>
     </row>
@@ -6946,17 +6146,17 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Strengthening EU Cybersecurity Capacities and Capabilities in Line with Legislative Requirements</t>
+          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>European Cybersecurity Industrial, Technology and Research Competence Centre (ECCC) / European Commission TheEuropean Cybersecurity Competence Centre (ECCC)is the EU body responsible for strengthening Europe’s cybersecurity ecosystem through investment, coordination and cooperation. Working with the ... Read More</t>
+          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official DIGITAL-ECCC-2027-DEPLOY-CYBER-11-EULEG call documentation and prepare their proposal around a clearly identified cybersecurity capacity or regulatory implementation need. Proposals should demonstrate practical European impact and explain how the project addresses relevant legislation, strengthens capabilities or improves cybersecurity processes. Applications are submitted through the EU Funding &amp; Tenders Portal under the Digital Europe Programme. The call follows a single-stage application process.</t>
+          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
@@ -6966,15 +6166,15 @@
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>14 January 2027</t>
+          <t>8 March 2027</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-strengthening-eu-cybersecurity-capacities-and-capabilities-in-line-with-legislative-requirements/</t>
+          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
         </is>
       </c>
     </row>
@@ -6991,215 +6191,144 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for Microbiota &amp; Women\’s Health International Call for Projects</t>
+          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>TheBiocodex Microbiota Foundation (BMF)is an international scientific foundation dedicated to advancing knowledge about the human microbiota and its role in health and disease. Through research funding, scientific initiatives and international collaborations, the Foundation supports researchers inve ... Read More</t>
+          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>The grant is open internationally to researchers holding anMD, PhD or Pharm-Dand working in relevant fields such as gynaecology, obstetrics, microbiology, infectious diseases, internal medicine or oncology. Applicants must be institutionally affiliated with a university, hospital or other eligible research setting because funding is awarded to institutions rather than directly to individuals. Principal investigators who previously received a BMF Women’s Health International Grant cannot reapply for three years. Members of the Women’s Health International Scientific Committee and their laboratory members are also excluded from applying as Principal Investigators.</t>
+          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>15 January 2027</t>
+          <t>30 June 2027</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>110</v>
+        <v>274</v>
       </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-microbiota-womens-health-international-call-for-projects/</t>
+          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>J. N. Derbyshire Trust Grants UK: Apply for Up to £10,000</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, ... Read More</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>TheJ. N. Derbyshire Trustis a UK charitable trust established in 1944 by Job Nightingale Derbyshire. The Trust provides charitable donations to organisations working for the benefit of people in Nottingham and Nottinghamshire. Its objectives include promoting health, supporting physical improvement, advancing education, and relieving poverty, distress and sickness. The Trust primarily supports community and voluntary organisations through project funding. It operates as a grant-making charity and reviews applications through two annual grant rounds. The Trust prioritises organisations delivering meaningful benefits within Nottingham and Nottinghamshire.</t>
-        </is>
-      </c>
+          <t>RFP for Turnkey Set-up of Rohini Skilling Centre Click
+                    here</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>31 January 2027</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="n">
-        <v>126</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr"/>
+      <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/j-n-derbyshire-trust-grants/</t>
+          <t>https://www.nasscomfoundation.org/pdf/RFP_Turnkey_Setup_Rohini_Skilling_Centre_Branded.pdf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr"/>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Applications Invited for 6th Annual Seeding The Future Global Food System Challenge</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Welthungerhilfe (WHH) / Seeding The Future Foundation Welthungerhilfe (WHH)is one of Germany’s largest private aid organizations and works toward creating a world without hunger. It supports initiatives addressing food security, nutrition, sustainable agriculture and resilient food systems, particul ... Read More</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants includenonprofits, NGOs, universities, academic and research institutions, early-stage companies and social enterprisesfrom eligible countries. Individuals cannot apply independently, although teams of students or researchers can participate through an eligible institution. Applicants must present an innovation that is practical, economically feasible and capable of producing significant benefits for people or the environment. Seed Grant applicants should have at least a prototype or initial proof of concept, while higher-level applicants require stronger evidence of feasibility, scalability and impact. For-profit applicants must meet the programme’s early-stage requirements. Applicants select the award level appropriate to their innovation’s development stage.</t>
-        </is>
-      </c>
+          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>15 February 2027</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="n">
-        <v>141</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr"/>
+      <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-invited-for-6th-annual-seeding-the-future-global-food-system-challenge/</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Apply for Kaikōura Community Initiatives Fund New Zealand – NZ$15,000</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>TheKaikōura District Councilis the local authority responsible for supporting the social, economic, cultural and environmental wellbeing of the Kaikōura community in New Zealand. Through its community grants programmes, the Council provides funding opportunities for local organisations, voluntary gr ... Read More</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Applicants should review the funding criteria and confirm that their organisation and proposed project meet the requirements. Prepare a clear description of the project, its local need, intended beneficiaries, activities, expected community benefits and alignment with Council objectives. Applicants should demonstrate consultation with the local hapori and include relevant supporting information. Quotes or price lists should be provided where appropriate to support the proposed budget. Complete the official application form and submit it before the relevant funding-round deadline.</t>
-        </is>
-      </c>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>8 March 2027</t>
-        </is>
-      </c>
-      <c r="H85" s="1" t="n">
-        <v>162</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr"/>
+      <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-kaikoura-community-initiatives-fund-new-zealand/</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Apply for Strengthening Our Culture Funding Pool Australia – Up to $100,000</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Preventive Health SA is responsible for supporting preventive health initiatives that improve health and wellbeing outcomes across South Australia. Through targeted programs and community partnerships, it works to address health inequalities and promote healthier communities. The Strengthening Our C ... Read More</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>The Strengthening Our Culture Funding Pool is primarily open toSouth Australian Aboriginal Community Controlled Organisations (ACCOs) and Aboriginal Community Controlled Health Organisations (ACCHOs)with an active ABN. Eligible organisations should be community controlled, not-for-profit and governed by a majority Aboriginal and/or Torres Strait Islander board. Applicants must operate in South Australia and provide services, programs or support to Aboriginal people. Joint applications may be submitted where an eligible Aboriginal organisation acts as the lead applicant. In limited rural or remote circumstances, other service providers may be considered where genuine partnerships and community support are demonstrated.</t>
-        </is>
-      </c>
+          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>30 June 2027</t>
-        </is>
-      </c>
-      <c r="H86" s="1" t="n">
-        <v>276</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr"/>
+      <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-strengthening-our-culture-funding-pool-australia/</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
         </is>
       </c>
     </row>
@@ -7212,7 +6341,7 @@
       <c r="B87" s="1" t="inlineStr"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>RFP for Turnkey Set-up of Rohini Skilling Centre Click
+          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
                     here</t>
         </is>
       </c>
@@ -7227,7 +6356,7 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/RFP_Turnkey_Setup_Rohini_Skilling_Centre_Branded.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
         </is>
       </c>
     </row>
@@ -7240,21 +6369,21 @@
       <c r="B88" s="1" t="inlineStr"/>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>RFP for Security Services — NF Skilling Centres, Dehradun &amp; Delhi - Click here</t>
+          <t>RFP for Women Entrepreneurship Programme - Click here</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-security-services-nf-skilling-centres-dehradun-delhi.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -7267,21 +6396,21 @@
       <c r="B89" s="1" t="inlineStr"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Dehradun - Click here</t>
+          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
         </is>
       </c>
     </row>
@@ -7294,21 +6423,22 @@
       <c r="B90" s="1" t="inlineStr"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>RFP for T-Shirts and Laptop Bags HDFC Bank Skilling Delhi - Click here</t>
+          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
+                    here</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-tshirts-and-laptop-bags-hdfc-bank-skilling-delhi.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
         </is>
       </c>
     </row>
@@ -7321,7 +6451,8 @@
       <c r="B91" s="1" t="inlineStr"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>RFP for Interior Partition &amp; Fit-Out of Skilling Center – Dehradun - Click
+          <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
+                India Pvt. Ltd - Click here | Click
                     here</t>
         </is>
       </c>
@@ -7336,7 +6467,7 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/interior-partition-and-fit-out-of-skilling-center-dehradun.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
         </is>
       </c>
     </row>
@@ -7349,21 +6480,21 @@
       <c r="B92" s="1" t="inlineStr"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>RFP for Women Entrepreneurship Programme - Click here</t>
+          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-entrepreneurship-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
         </is>
       </c>
     </row>
@@ -7376,21 +6507,21 @@
       <c r="B93" s="1" t="inlineStr"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>RFP for NF–DXC Technology Digital Literacy and E-Governance Project - Click here | Click here</t>
+          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/DXC_Evaluation_Cover_Letter.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
         </is>
       </c>
     </row>
@@ -7403,8 +6534,7 @@
       <c r="B94" s="1" t="inlineStr"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>RFP for Impact Assessment of the HDFC Ergo Neurodivergent Skilling Program - Click here | Click
-                    here</t>
+          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -7418,7 +6548,7 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-hdfc-ergo.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
         </is>
       </c>
     </row>
@@ -7431,9 +6561,7 @@
       <c r="B95" s="1" t="inlineStr"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>RFP for Baseline and Endline Study for STEM Education &amp; Tinkering Lab Programme – Applied Materials
-                India Pvt. Ltd - Click here | Click
-                    here</t>
+          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -7447,7 +6575,7 @@
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-stem-education-and-tinkering-lab-programme.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
         </is>
       </c>
     </row>
@@ -7460,21 +6588,22 @@
       <c r="B96" s="1" t="inlineStr"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>RFP for Training Curriculum development for E-Governance Empowerment Project - Click here | Click here</t>
+          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
+                    here</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-training-curriculum-development-for-e-governance-empowerment-project.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7487,21 +6616,21 @@
       <c r="B97" s="1" t="inlineStr"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>RFP for Empowering Growth and Development of Women Entrepreneurs - Click here | Click here</t>
+          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-empowering-growth-and-development-of-women-entrepreneurs.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7514,7 +6643,7 @@
       <c r="B98" s="1" t="inlineStr"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>RFP for Digital Literacy Program Evaluation - Click here | Click here</t>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -7528,7 +6657,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-digital-literacy-program-evaluation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7541,7 +6670,7 @@
       <c r="B99" s="1" t="inlineStr"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>RFP for Bootcamp Vendor | Scope of Work for Food Vendor - IBM Skillbuild Bootcamps - Click here | Click here</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
@@ -7555,7 +6684,7 @@
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-bootcamp-vendor.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7568,22 +6697,21 @@
       <c r="B100" s="1" t="inlineStr"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>RFP for Travel &amp; Transportation Services for Trainer Mobility - IBM SkillsBuild Bootcamps - Click
-                    here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-travel-and-transportation-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7596,21 +6724,21 @@
       <c r="B101" s="1" t="inlineStr"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Baseline and Evaluation Study - Coupa Digital Labs Program - Click here | Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-evaluation-study-coupa-digital-labs-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7623,7 +6751,7 @@
       <c r="B102" s="1" t="inlineStr"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -7637,7 +6765,7 @@
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -7650,21 +6778,21 @@
       <c r="B103" s="1" t="inlineStr"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7677,7 +6805,7 @@
       <c r="B104" s="1" t="inlineStr"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -7691,7 +6819,7 @@
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/cover-letter-baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -7704,21 +6832,21 @@
       <c r="B105" s="1" t="inlineStr"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7731,21 +6859,22 @@
       <c r="B106" s="1" t="inlineStr"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
+                education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -7758,21 +6887,21 @@
       <c r="B107" s="1" t="inlineStr"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -7785,21 +6914,21 @@
       <c r="B108" s="1" t="inlineStr"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7812,7 +6941,8 @@
       <c r="B109" s="1" t="inlineStr"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
+                and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -7826,7 +6956,7 @@
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -7839,8 +6969,8 @@
       <c r="B110" s="1" t="inlineStr"/>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher
-                education in STEM courses - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
+                    here</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -7854,7 +6984,7 @@
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -7867,7 +6997,8 @@
       <c r="B111" s="1" t="inlineStr"/>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
@@ -7881,7 +7012,7 @@
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7025,8 @@
       <c r="B112" s="1" t="inlineStr"/>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
+                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -7908,7 +7040,7 @@
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -7921,22 +7053,21 @@
       <c r="B113" s="1" t="inlineStr"/>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR
-                and Financial Management - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -7949,8 +7080,7 @@
       <c r="B114" s="1" t="inlineStr"/>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click
-                    here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -7964,7 +7094,7 @@
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -7977,22 +7107,21 @@
       <c r="B115" s="1" t="inlineStr"/>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr"/>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -8005,8 +7134,7 @@
       <c r="B116" s="1" t="inlineStr"/>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women
-                Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -8020,20 +7148,24 @@
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr"/>
@@ -8043,92 +7175,120 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G117" s="1" t="inlineStr"/>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>31st Aug, 2026</t>
+        </is>
+      </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Senior Programme Officer - Uday</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>15th Aug, 2026</t>
+        </is>
+      </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>29th Jun, 2026</t>
+        </is>
+      </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
@@ -8145,25 +7305,25 @@
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for Sports for Change under the flagship urban development programme – Uday</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr"/>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>31st Aug, 2026</t>
+          <t>10th Feb, 2026</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/RfP_SFC-Pune_Cochin.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -8180,25 +7340,25 @@
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>Senior Programme Officer - Uday</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>15th Aug, 2026</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-08/JD_Vijayawada_SPO%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -8215,25 +7375,25 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the post of Graphic Designer</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>29th Jun, 2026</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-06/HCLF_JD_Graphic%20Designer.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -8250,25 +7410,25 @@
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -8285,25 +7445,25 @@
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -8320,165 +7480,133 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>RFP for Development of Course Modules and Conducting Training of Trainers under CITIIS 2.0 LCCM Programme.pdf</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Climate</t>
-        </is>
-      </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>10th Nov, 2025</t>
-        </is>
-      </c>
+      <c r="F127" s="1" t="inlineStr"/>
+      <c r="G127" s="1" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP%20for%20Development%20of%20Course%20Modules%20and%20Conducting%20Training%20of%20Trainers%20under%20CITIIS%202.0%20LCCM%20Programme.pdf</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>GeM-Bidding-9937006.pdf</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>31st Oct, 2025</t>
-        </is>
-      </c>
+      <c r="F128" s="1" t="inlineStr"/>
+      <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9937006.pdf</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>EOI FOR INTEGRATING WOMEN ENTREPRENEURS INTO CIRCULAR ECONOMY VALUE CHAINS A ROADMAP FOR CITIES.pdf</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Climate</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>21st May, 2025</t>
-        </is>
-      </c>
+      <c r="F129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20INTEGRATING%20WOMEN%20ENTREPRENEURS%20INTO%20CIRCULAR%20ECONOMY%20VALUE%20CHAINS%20A%20ROADMAP%20FOR%20CITIES.pdf</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>EOI for Onboarding of Partner Institutes for LCCM.pdf</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr"/>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI%20for%20Onboarding%20of%20Partner%20Institutes%20for%20LCCM.pdf</t>
         </is>
       </c>
     </row>
@@ -8495,7 +7623,7 @@
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9937006.pdf</t>
+          <t>RFP_Technical_Assistance_SAM_Final.pdf</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr"/>
@@ -8505,7 +7633,7 @@
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9937006.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_Technical_Assistance_SAM_Final.pdf</t>
         </is>
       </c>
     </row>
@@ -8522,7 +7650,7 @@
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>EOI FOR INTEGRATING WOMEN ENTREPRENEURS INTO CIRCULAR ECONOMY VALUE CHAINS A ROADMAP FOR CITIES.pdf</t>
+          <t>GeM-Bidding-9891532.pdf</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr"/>
@@ -8532,7 +7660,7 @@
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI%20FOR%20INTEGRATING%20WOMEN%20ENTREPRENEURS%20INTO%20CIRCULAR%20ECONOMY%20VALUE%20CHAINS%20A%20ROADMAP%20FOR%20CITIES.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9891532.pdf</t>
         </is>
       </c>
     </row>
@@ -8549,7 +7677,7 @@
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>EOI for Onboarding of Partner Institutes for LCCM.pdf</t>
+          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr"/>
@@ -8559,7 +7687,7 @@
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI%20for%20Onboarding%20of%20Partner%20Institutes%20for%20LCCM.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
         </is>
       </c>
     </row>
@@ -8576,7 +7704,7 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>RFP_Technical_Assistance_SAM_Final.pdf</t>
+          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr"/>
@@ -8586,7 +7714,7 @@
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Technical_Assistance_SAM_Final.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -8603,7 +7731,7 @@
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9891532.pdf</t>
+          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr"/>
@@ -8613,7 +7741,7 @@
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9891532.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
         </is>
       </c>
     </row>
@@ -8630,7 +7758,7 @@
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>RFP_A CONSULTANCY FIRM FOR TRANSVERSAL EXPERTS.pdf</t>
+          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr"/>
@@ -8640,7 +7768,7 @@
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_A%20CONSULTANCY%20FIRM%20FOR%20TRANSVERSAL%20EXPERTS.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
         </is>
       </c>
     </row>
@@ -8657,7 +7785,7 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
+          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr"/>
@@ -8667,7 +7795,7 @@
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Request_for_Quotation_RfQ_Parvat_Manthan_2026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
         </is>
       </c>
     </row>
@@ -8684,7 +7812,7 @@
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Eligibility criteria and Submission Checklist for RfQ.pdf</t>
+          <t>UHI_RFP_Formatted_10072026.pdf</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr"/>
@@ -8694,7 +7822,7 @@
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Eligibility%20criteria%20and%20Submission%20Checklist%20for%20RfQ.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
         </is>
       </c>
     </row>
@@ -8711,7 +7839,7 @@
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>NIUA_RfP_Transit-influence and Station Area Mobility Plan_140826.pdf</t>
+          <t>GeM-Bidding-9590033.pdf</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr"/>
@@ -8721,7 +7849,7 @@
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Transit-influence%20and%20Station%20Area%20Mobility%20Plan_140826.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
         </is>
       </c>
     </row>
@@ -8738,7 +7866,7 @@
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>NIUA_RfP_Ti-SAMP Pune_Response to Pre-Bid Queries_270826.pdf</t>
+          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr"/>
@@ -8748,7 +7876,7 @@
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA_RfP_Ti-SAMP%20Pune_Response%20to%20Pre-Bid%20Queries_270826.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -8765,7 +7893,7 @@
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>UHI_RFP_Formatted_10072026.pdf</t>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr"/>
@@ -8775,7 +7903,7 @@
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/UHI_RFP_Formatted_10072026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
         </is>
       </c>
     </row>
@@ -8792,7 +7920,7 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-9590033.pdf</t>
+          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr"/>
@@ -8802,169 +7930,7 @@
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-9590033.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr"/>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="1" t="inlineStr"/>
-      <c r="G143" s="1" t="inlineStr"/>
-      <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_150726.pdf</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="1" t="inlineStr"/>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_150726.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr">
-        <is>
-          <t>NIUA-UrbanShift Country Project_RfP_IGMP_CORRIGENDUM I_150726.pdf</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr"/>
-      <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
           <t>https://niua.in/sites/default/files/tenders/NIUA-UrbanShift%20Country%20Project_RfP_IGMP_CORRIGENDUM%20I_150726.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>05.06.2026_EOI-RFP_Kedarnath and Amarnath Yatra.pdf</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/05.06.2026_EOI-RFP_Kedarnath%20and%20Amarnath%20Yatra.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr">
-        <is>
-          <t>SOP_Kedarnath and Amarnath_corrigendum_1.pdf</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="1" t="inlineStr"/>
-      <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP_Kedarnath%20and%20Amarnath_corrigendum_1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B148" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C148" s="1" t="inlineStr">
-        <is>
-          <t>SOP-Kedarnath Amarnath_PRe-bid queries.pdf</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="1" t="inlineStr"/>
-      <c r="G148" s="1" t="inlineStr"/>
-      <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/SOP-Kedarnath%20Amarnath_PRe-bid%20queries.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -493,17 +493,17 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
+          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
+          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
+          <t>The application deadline is 29 September 2026</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
+          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2026/27 Research and Development Projects Funding Scheme – Hong Kong</t>
+          <t>Call for Applications: ReCIPE Programme PhD Research Grants</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TheEnvironment and Conservation Fund (ECF)supports initiatives that contribute to environmental protection and conservation in Hong Kong. Through its Research and Development Projects Funding Scheme, the fund provides an opportunity for local non-profit organisations and educational institutions to ... Read More</t>
+          <t>TheReCIPE Programmesupports research examining the relationships between conflict, economic performance and development, particularly in countries affected by conflict, fragility and severe development challenges. The programme aims to generate high-quality evidence that can contribute to policy dis ... Read More</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is 29 September 2026</t>
+          <t>The programme primarily supports researchers undertakingPhD-level research. Principal investigators must hold aPhD or be enrolled in a PhD programme, although exceptions may be considered for applicants with strong academic or policy-relevant research records. PhD students must provide aletter of support from their PhD supervisor, submitted within two weeks of the application deadline. Multidisciplinary teams and collaboration between researchers from lower- and higher-income countries are encouraged. Projects should have clear relevance to ReCIPE Focus Countries. Researchers based atRussian institutions are not eligible. Applicants must also address ethical, safety and security considerations where relevant.</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/2026-27-research-and-development-projects-funding-scheme-hong-kong/</t>
+          <t>https://andpurpose.world/call-for-applications-recipe-programme-phd-research-grants/</t>
         </is>
       </c>
     </row>
@@ -632,22 +632,22 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Applications Open for Green Box Artist in Residency Program</t>
+          <t>Apply for Giving Joy Microgrant 2026 – Up to US$500 for Women Entrepreneurs</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
+          <t>Giving Joy is a nonprofit organisation that supports women entrepreneurs and changemakers by providing small grants, mentorship and practical support. The organisation focuses on helping women develop ideas that create positive economic or social impact in their communities. Its global grant program ... Read More</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
+          <t>The Giving Joy Microgrant 2026 provides small-scale financial support to women entrepreneurs and changemakers worldwide. The Fall 2026 grant cycle is designed to help applicants start or expand a business, nonprofit organisation or community project that generates positive economic or social benefits for women, girls and families. Selected applicants can receive a one-time microgrant of up to US$500, along with mentorship and participation in the Giving Joy community. The grant can support practical activities and project expenses during a six-month implementation period. Applications for the Fall 2026 cycle are open from 1 September through 30 September 2026.</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Women &amp; Gender</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
+          <t>https://andpurpose.world/apply-for-giving-joy-microgrant-2026/</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Apply for RAFT AI for Transformative Social Impact Grant 2026 – Up to ₹50 Lakh</t>
+          <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI ... Read More</t>
+          <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI at the core of their solutions and can demonstrate meaningful, measurable and responsible impact. The initiative focuses particularly on agriculture, healthcare, disability inclusion and frontline support. RAFT indicates a preference for organisations operating in Maharashtra and is interested in solutions with potential for scale and longer-term impact. The initiative is designed for organisations that are already applying AI to real-world social challenges.</t>
+          <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/raft-ai-transformative-social-impact-grant-2026/</t>
+          <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -722,22 +722,22 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Apply for Giving Joy Microgrant 2026 – Up to US$500 for Women Entrepreneurs</t>
+          <t>Giving Joy Microgrant 2026</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Giving Joy is a nonprofit organisation that supports women entrepreneurs and changemakers by providing small grants, mentorship and practical support. The organisation focuses on helping women develop ideas that create positive economic or social impact in their communities. Its global grant program ... Read More</t>
+          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>The Giving Joy Microgrant 2026 provides small-scale financial support to women entrepreneurs and changemakers worldwide. The Fall 2026 grant cycle is designed to help applicants start or expand a business, nonprofit organisation or community project that generates positive economic or social benefits for women, girls and families. Selected applicants can receive a one-time microgrant of up to US$500, along with mentorship and participation in the Giving Joy community. The grant can support practical activities and project expenses during a six-month implementation period. Applications for the Fall 2026 cycle are open from 1 September through 30 September 2026.</t>
+          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Women &amp; Gender</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-giving-joy-microgrant-2026/</t>
+          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
         </is>
       </c>
     </row>
@@ -767,22 +767,22 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
+          <t>Applications Open for Green Box Artist in Residency Program</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
+          <t>Green Box Artsis an arts incubator based in Green Mountain Falls, Colorado, at the foot of Pikes Peak in the Colorado Front Range. Its Artist in Residency Program provides artists with dedicated time, space and resources to focus on creative development and the creation of new work. The programme we ... Read More</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>The application deadline is30 September 2026</t>
+          <t>The residency welcomesartists from all disciplines and at all career stages. Emerging, mid-career and established artists, including artists of national and international stature, are encouraged to apply. There is no restriction to a particular creative discipline. Applicants should have clear artistic goals and a proposed project, new body of work, creative experiment or concept that would benefit from a dedicated residency period. Applicants are also expected to propose meaningful community engagement activities such as masterclasses, performances or open studios.</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
+          <t>https://andpurpose.world/applications-open-for-green-box-artist-in-residency-program/</t>
         </is>
       </c>
     </row>
@@ -812,17 +812,17 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Giving Joy Microgrant 2026</t>
+          <t>Apply for India-Finland Joint Innovation Call 2026</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Giving Joyis a US-based nonprofit organisation focused on strengthening and inspiring women’s entrepreneurship worldwide. Through microgrants and mentorship, the organisation helps women establish or improve businesses and community initiatives. Giving Joy supports women-led projects across differen ... Read More</t>
+          <t>The Technology Development Board (TDB), operating under India’s Department of Science and Technology, supports the development and commercialization of indigenous technologies. For the India-Finland Joint Innovation Call 2026, TDB is implementing the programme on behalf of DST in partnership with Bu ... Read More</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>The Giving Joy Microgrant is intended forwomen entrepreneurs worldwide. There is no specific sector restriction, allowing applicants to propose businesses or initiatives across different fields, trades, occupations and crafts. Strong applications should demonstrate an innovative or creative idea, initiative and potential for real community impact. Giving Joy particularly values proposals that generate clear economic and/or social benefits for women and girls. Applicants should ensure that their proposed activities can be implemented during the six-month grant period.</t>
+          <t>The India-Finland Joint Innovation Call 2026 supports collaborative R&amp;D projects between eligible Indian and Finnish partners. Priority areas include sustainable energy, renewable energy, hydrogen technologies, smart cities, waste management, waste-to-energy, electric vehicles, carbon capture, energy storage, advanced digital technologies, artificial intelligence, 5G/6G, MEMS and sensors. Projects can run for a maximum of 24 months, with up to six projects expected to receive support. Successful proposals should demonstrate innovation, market potential, commercialization prospects and strong joint project-management capacity. Both Indian and Finnish partners must submit applications to their respective national funding agencies.</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/giving-joy-microgrant-2026/</t>
+          <t>https://andpurpose.world/grants-india-finland-joint-innovation-call-2026/</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
+          <t>Apply for RAFT AI for Transformative Social Impact Grant 2026 – Up to ₹50 Lakh</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
+          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI ... Read More</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
+          <t>Rao Family Trust (RAFT) is supporting technology-driven solutions through its TechForGood initiative, with a focus on using artificial intelligence to address significant social challenges. Through its AI for Transformative Social Impact grant opportunity, RAFT is seeking organisations that have AI at the core of their solutions and can demonstrate meaningful, measurable and responsible impact. The initiative focuses particularly on agriculture, healthcare, disability inclusion and frontline support. RAFT indicates a preference for organisations operating in Maharashtra and is interested in solutions with potential for scale and longer-term impact. The initiative is designed for organisations that are already applying AI to real-world social challenges.</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
+          <t>https://andpurpose.world/raft-ai-transformative-social-impact-grant-2026/</t>
         </is>
       </c>
     </row>
@@ -902,17 +902,17 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>ICMR Intramural Ignition Grant 2026 – Apply for ₹30 Lakh</t>
+          <t>iDEX Open Challenge 2026: Apply for Defence Grants Up to ₹1.5 Crore</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TheIndian Council of Medical Research (ICMR)is India’s apex body for the formulation, coordination and promotion of biomedical research. It operates under the Department of Health Research, Ministry of Health and Family Welfare, Government of India. ICMR supports research addressing important medica ... Read More</t>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian d ... Read More</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Eligible ICMR scientists should develop a research proposal addressing a relevant priority topic and obtain the required institutional approval. The proposal must be reviewed and approved by the institution’s Scientific Advisory Committee before submission. Applicants should complete the required documentation and submit the proposal through the ICMR Intramural Electronic Project Management System (i-ePMS) during the active application period. Institutional authorities must verify the required documents and eligibility before the proposal is submitted.</t>
+          <t>Inovations for Defence Excellence (iDEX) is an initiative of theMinistry of Defence, Government of India, established to encourage innovation and technological development in the defence and aerospace sectors. The programme connects startups, innovators, MSMEs, research institutions and the Indian defence ecosystem to develop advanced solutions for military applications. Through funding, mentorship and institutional support, iDEX promotes indigenous defence technologies and strengthens India’s innovation capabilities. Its programmes provide opportunities for entrepreneurs and technology developers working on emerging solutions. By supporting home-grown innovation, iDEX contributes to the growth of India’s defence manufacturing ecosystem and creates opportunities for startups developing dual-use and specialised technologies.</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/icmr-intramural-ignition-grant-2026/</t>
+          <t>https://andpurpose.world/idex-open-challenge-2026/</t>
         </is>
       </c>
     </row>
@@ -947,22 +947,22 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Apply for India-Finland Joint Innovation Call 2026</t>
+          <t>Signals of Change: Shaping the Future of Sexual and Reproductive Health and Rights (SRHR)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The Technology Development Board (TDB), operating under India’s Department of Science and Technology, supports the development and commercialization of indigenous technologies. For the India-Finland Joint Innovation Call 2026, TDB is implementing the programme on behalf of DST in partnership with Bu ... Read More</t>
+          <t>TheWorld Health Organization (WHO)is the United Nations specialized agency responsible for international public health. Working with governments, health institutions and partners worldwide, WHO promotes health, protects populations from health threats and advances equitable access to healthcare. Its ... Read More</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>The India-Finland Joint Innovation Call 2026 supports collaborative R&amp;D projects between eligible Indian and Finnish partners. Priority areas include sustainable energy, renewable energy, hydrogen technologies, smart cities, waste management, waste-to-energy, electric vehicles, carbon capture, energy storage, advanced digital technologies, artificial intelligence, 5G/6G, MEMS and sensors. Projects can run for a maximum of 24 months, with up to six projects expected to receive support. Successful proposals should demonstrate innovation, market potential, commercialization prospects and strong joint project-management capacity. Both Indian and Finnish partners must submit applications to their respective national funding agencies.</t>
+          <t>The application deadline is30 September 2026</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
@@ -975,119 +975,29 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/grants-india-finland-joint-innovation-call-2026/</t>
+          <t>https://andpurpose.world/signals-of-change-shaping-the-future-of-sexual-and-reproductive-health-and-rights-srhr/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Apply for European Youth Foundation Grants 2027 – Up to €60,000</t>
+          <t>RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar ...</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>The European Youth Foundation (EYF) is a funding body of the Council of Europe supporting youth organisations and initiatives that promote human rights, democracy, peace, intercultural dialogue and youth participation. EYF grants support international youth cooperation and projects that help young p ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants are youth non-governmental organisations and networks registered with the European Youth Foundation. Organisations must satisfy the EYF’s registration and eligibility criteria before applying. The projects must involve young people and contribute to the Foundation’s thematic priorities. Applicants should ensure their organisation has been validated before the deadline because EYF registration can take time. Projects should have an international youth cooperation dimension and demonstrate clear objectives, activities, expected outcomes and appropriate budgeting. Individuals cannot apply independently for these organisational grants.</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>1 October 2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-european-youth-foundation-grants-2027/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>The application deadline is 01 October 2026</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>01 October 2026</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar ...</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society (CECOEDECON) | Jaisalmer, Jodhpur, Barmer Districts, Rajasthan
 RFP - Procurement, Supply, Installation, Testing &amp; Commissioning of Solar PV Systems – 2 kW, 3 kW and 5 kW, Centre For Community Economics And Development Consultants So ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• 5. Scope of Work
 The selected bidder shall provide complete turnkey services, including but not limited to:
@@ -1267,54 +1177,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1345,14 +1255,104 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>01-10-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304105</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Supporting Act Foundation Impact Grant 2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>The Supporting Act Foundation is a philanthropic organisation supporting emerging artists and nonprofit organisations working to create greater opportunities in the creative and cultural industries. Its programmes focus particularly on artists from underrepresented groups and communities facing syst ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The Supporting Act Foundation Impact Grant 2026 provides unrestricted funding to arts-focused nonprofit organisations that support underrepresented emerging artists through non-financial assistance. Ten organisations will receive €25,000 per year for two years, totalling €50,000 per organisation. The grant can help organisations strengthen their capacity and continue providing support to emerging artists facing barriers in the creative and cultural industries. The programme is open to eligible nonprofits based in selected European countries, while organisations registered elsewhere may apply through a qualifying fiscal host. The first grant instalment is scheduled for January 2027 following the application and review process.</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>1 October 2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/supporting-act-foundation-impact-grant-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>FOLUR Indonesia Low Value Grant: USD 450,000 for Sustainable Coffee and Palm Oil Value Chains</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>The United Nations Development Programme (UNDP) Indonesia The United Nations Development Programme (UNDP) Indonesia is implementing the FOLUR Indonesia Project to promote sustainable food systems, land use, and landscape restoration. The project is funded by the Global Environment Facility and imple ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The application deadline is 01 October 2026</t>
+        </is>
+      </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>01-10-2026</t>
+          <t>01 October 2026</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304105</t>
+          <t>https://andpurpose.world/folur-indonesia-low-value-grant-usd-450000-for-sustainable-coffee-and-palm-oil-value-chains/</t>
         </is>
       </c>
     </row>
@@ -1532,54 +1532,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1677,16 +1677,61 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Apply for European Youth Foundation Grants 2027 – Up to €60,000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>The European Youth Foundation (EYF) is a funding body of the Council of Europe supporting youth organisations and initiatives that promote human rights, democracy, peace, intercultural dialogue and youth participation. EYF grants support international youth cooperation and projects that help young p ... Read More</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Eligible applicants are youth non-governmental organisations and networks registered with the European Youth Foundation. Organisations must satisfy the EYF’s registration and eligibility criteria before applying. The projects must involve young people and contribute to the Foundation’s thematic priorities. Applicants should ensure their organisation has been validated before the deadline because EYF registration can take time. Projects should have an international youth cooperation dimension and demonstrate clear objectives, activities, expected outcomes and appropriate budgeting. Individuals cannot apply independently for these organisational grants.</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>1 October 2026</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-european-youth-foundation-grants-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>RFP - English Annotation of Student Voice Recordings from Uttarakhand</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS) | Uttarakhand
 RFP - English Annotation of Student Voice Recordings from Uttarakhand, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
@@ -1703,7 +1748,7 @@
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 All proposals to this RFP must be received no later than
@@ -1798,54 +1843,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1876,59 +1921,14 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>02-10-2026</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304049</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>Apply for AMBSO Impact Research Initiative 2026: Up to USD 10,000 in Health Research Grants</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Africa Medical and Behavioral Sciences Organization (AMBSO) TheAfrica Medical and Behavioral Sciences Organization (AMBSO)is a research and health-focused organization working to advance clinical, epidemiological, social, and behavioral research across Africa. Its work includes clinical trials, popu ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>TheAMBSO Impact Research Initiative 2026is open to eligible researchers, academic institutions, research organizations, community-based organizations, and other entities whose proposed work aligns with the initiative’s public health objectives. Doctoral students are encouraged to apply as members of research teams led by a faculty Principal Investigator. Independent researchers may apply when affiliated with an academic or research institution. Applications can come from anywhere in the world, with no geographical restriction stated by AMBSO. Proposed projects should focus on eligible priority health areas, generate useful evidence, and be feasible within the 18-month funding period. For-profit entities, political organizations, lobbying groups, and organizations primarily engaged in political advocacy are not eligible.</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>2 October 2026</t>
         </is>
       </c>
       <c r="H19" s="1" t="n">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-ambso-impact-research-initiative/</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304049</t>
         </is>
       </c>
     </row>
@@ -2058,54 +2058,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2311,54 +2311,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2421,35 +2421,35 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Apply for GEF Small Grants Programme Ghana 2026 – Up to US$50,000</t>
+          <t>Apply for AMBSO Impact Research Initiative 2026: Up to USD 10,000 in Health Research Grants</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>The Global Environment Facility Small Grants Programme is implemented by the United Nations Development Programme and supports locally led environmental and community-development initiatives. In Ghana, the programme’s ICCA-GSI Phase II call focuses on territories and areas conserved by Indigenous Pe ... Read More</t>
+          <t>Africa Medical and Behavioral Sciences Organization (AMBSO) TheAfrica Medical and Behavioral Sciences Organization (AMBSO)is a research and health-focused organization working to advance clinical, epidemiological, social, and behavioral research across Africa. Its work includes clinical trials, popu ... Read More</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Applicants should review the official UNDP Ghana call and prepare their proposal using the relevant application template. Proposals should describe the environmental challenge, communities involved, activities, expected results and sustainability benefits. Completed applications and required documents must be submitted electronically to the designated UNDP Ghana email address before the deadline. A proposal workshop was also scheduled for September 22, 2026.</t>
+          <t>TheAMBSO Impact Research Initiative 2026is open to eligible researchers, academic institutions, research organizations, community-based organizations, and other entities whose proposed work aligns with the initiative’s public health objectives. Doctoral students are encouraged to apply as members of research teams led by a faculty Principal Investigator. Independent researchers may apply when affiliated with an academic or research institution. Applications can come from anywhere in the world, with no geographical restriction stated by AMBSO. Proposed projects should focus on eligible priority health areas, generate useful evidence, and be feasible within the 18-month funding period. For-profit entities, political organizations, lobbying groups, and organizations primarily engaged in political advocacy are not eligible.</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>3 October 2026</t>
+          <t>2 October 2026</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/apply-for-gef-small-grants-programme-ghana-2026-up-to-us50000/</t>
+          <t>https://andpurpose.world/apply-for-ambso-impact-research-initiative/</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Assam Startup Call for Grant Applications 2026</t>
+          <t>Apply for GEF Small Grants Programme Ghana 2026 – Up to US$50,000</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>The Department of Innovation, Incubation and Start-ups (DIIS) The Department of Innovation, Incubation and Start-ups (DIIS) is the Government of Assam’s nodal department responsible for developing the state’s startup and innovation ecosystem. The department coordinates startup policy, recognition, f ... Read More</t>
+          <t>The Global Environment Facility Small Grants Programme is implemented by the United Nations Development Programme and supports locally led environmental and community-development initiatives. In Ghana, the programme’s ICCA-GSI Phase II call focuses on territories and areas conserved by Indigenous Pe ... Read More</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>The Assam Startup Call for Grant Applications 2026 provides grant support to eligible startups at the idea and prototype or MVP stages. The programme is designed to help startups develop, validate and scale innovative solutions under Assam’s startup policy. Applicants select the funding category corresponding to their development stage and provide information about their product, market validation, business model, funding requirement, expected employment and impact. The opportunity is relevant for entrepreneurs seeking startup grants India, prototype funding India and government-backed innovation support. Applications under the current call are reviewed by the Assam Innovation &amp; Startup Foundation, with funding provided to selected eligible startups.</t>
+          <t>Applicants should review the official UNDP Ghana call and prepare their proposal using the relevant application template. Proposals should describe the environmental challenge, communities involved, activities, expected results and sustainability benefits. Completed applications and required documents must be submitted electronically to the designated UNDP Ghana email address before the deadline. A proposal workshop was also scheduled for September 22, 2026.</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/assam-startup-call-for-grant-applications-2026/</t>
+          <t>https://andpurpose.world/apply-for-gef-small-grants-programme-ghana-2026-up-to-us50000/</t>
         </is>
       </c>
     </row>
@@ -2511,35 +2511,35 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>French Republic Human Rights Prize 2026</t>
+          <t>Assam Startup Call for Grant Applications 2026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>The National Consultative Commission on Human Rights (CNCDH) The National Consultative Commission on Human Rights (CNCDH) is France’s independent national human rights institution responsible for advising public authorities and promoting the protection of human rights and fundamental freedoms. It al ... Read More</t>
+          <t>The Department of Innovation, Incubation and Start-ups (DIIS) The Department of Innovation, Incubation and Start-ups (DIIS) is the Government of Assam’s nodal department responsible for developing the state’s startup and innovation ecosystem. The department coordinates startup policy, recognition, f ... Read More</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Applicants should prepare a complete application describing their organisation or initiative, human-rights objectives, activities, beneficiaries and expected outcomes. The proposal should clearly demonstrate how the project protects the rights of refugees, asylum seekers or displaced persons. Applicants must complete the prescribed application form and submit the required documents before the closing date. Applications should clearly explain the project’s human-rights approach and practical impact.</t>
+          <t>The Assam Startup Call for Grant Applications 2026 provides grant support to eligible startups at the idea and prototype or MVP stages. The programme is designed to help startups develop, validate and scale innovative solutions under Assam’s startup policy. Applicants select the funding category corresponding to their development stage and provide information about their product, market validation, business model, funding requirement, expected employment and impact. The opportunity is relevant for entrepreneurs seeking startup grants India, prototype funding India and government-backed innovation support. Applications under the current call are reviewed by the Assam Innovation &amp; Startup Foundation, with funding provided to selected eligible startups.</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>4 October 2026</t>
+          <t>3 October 2026</t>
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>https://andpurpose.world/french-republic-human-rights-prize-2026/</t>
+          <t>https://andpurpose.world/assam-startup-call-for-grant-applications-2026/</t>
         </is>
       </c>
     </row>
@@ -2670,54 +2670,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2770,16 +2770,264 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>French Republic Human Rights Prize 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>The National Consultative Commission on Human Rights (CNCDH) The National Consultative Commission on Human Rights (CNCDH) is France’s independent national human rights institution responsible for advising public authorities and promoting the protection of human rights and fundamental freedoms. It al ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should prepare a complete application describing their organisation or initiative, human-rights objectives, activities, beneficiaries and expected outcomes. The proposal should clearly demonstrate how the project protects the rights of refugees, asylum seekers or displaced persons. Applicants must complete the prescribed application form and submit the required documents before the closing date. Applications should clearly explain the project’s human-rights approach and practical impact.</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>4 October 2026</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/french-republic-human-rights-prize-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme i...</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>World Resources Institute India (WRI India) | Karnataka
+RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme in Karnataka, World Resources Institute India (WRI India)() | DevNetJobsIndia
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs ... Read More</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+Aprajita.Verma(at)wri.org
+Download Attachment:
+RFP- EV Skilling Programme in Karnataka.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Oct 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate Consultants
+Academy of Management Studies (AMS)
+Location:
+Delhi
+Apply by:
+28 Oct 2026
+Programme Manager
+Azim Premji Foundation
+Location:
+Madhya Pradesh, Karnataka
+Apply by:
+28 Oct 2026
+Field Coordinator - Village Institutions
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Program Manager
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Project Coordinator -NRM / Watershed
+Basudeo Kanoria Seva Sansthan
+Location:
+Rajasthan
+Apply by:
+12 Oct 2026
+Lead Consultant PHEOC
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Consultant - Emergency Management (PHEOC)
+The Voluntary Health Services (VHS)
+Location:
+Delhi
+Apply by:
+29 Sep 2026
+Field Research Executive
+Academy of Management Studies (AMS)
+Location:
+Maharashtra
+Apply by:
+30 Sep 2026
+Manager – Program Finance
+Wipro Foundation
+Location:
+Karnataka
+Apply by:
+09 Oct 2026
+Resource Person — ITI Engagement
+Azim Premji Foundation
+Location:
+Karnataka
+Apply by:
+05 Oct 2026
+View more featured non-profit jobs
+Latest NGO Jobs
+Post your highlighted jobs here
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
+Location:
+Uttar Pradesh
+Apply by:
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
+View all the latest non-profit jobs
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+©
+2026
+M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>05-10-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>RFP - Design and Roll-Out of a Curriculum on Positive Masculinities for Co...</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Centre for Catalyzing Change (C3) | Jaipur, Rajasthan
 RFP - Design and Roll-Out of a Curriculum on Positive Masculinities for Community  Members and Participatory Community Safety Audits..., Centre for Catalyzing Change (C3)(Jaipur) | DevNetJobsIndia
@@ -2791,7 +3039,7 @@
 Value Membersh ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Introduction &amp; Organizational Context
 The Centre for Catalyzing Change (C3) is a leading national non-profit organization dedicated to empowering women and adolescent girls through innovative, evidence-based programmes. For over 30 years, C3 has worked to advance education, health, safety, life skills, and economic opportunities by strengthening systems and influencing public policy.
@@ -2895,54 +3143,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2973,83 +3221,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>05-10-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H28" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=304275</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>Poshan Vatika Grant 2026 – National Medicinal Plants Board</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>The National Medicinal Plants Board (NMPB), under the Ministry of AYUSH, Government of India, works to promote the cultivation, conservation and sustainable use of medicinal plants. Its programmes support medicinal plant development, awareness, cultivation and related activities across India. The Bo ... Read More</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Eligible applicants include government organisations, NGOs and voluntary organisations with demonstrated experience relevant to the proposed Poshan Vatika project. Applicants should be capable of establishing and maintaining a nutrition garden within an eligible Eklavya Model Residential School. The proposed site should have suitable cultivable land and the necessary conditions for plantation and maintenance, including appropriate irrigation and arrangements for ongoing upkeep. Projects should include at least 30 suitable plant species and activities such as training, awareness and educational support. Organisations applying for government grants for NGOs should demonstrate the capacity to implement, monitor and maintain the garden for the full project period.</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>5 October 2026</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/poshan-vatika-grant-2026-national-medicinal-plants-board/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>EoI - Selection of Skilled Bamboo Craft / Construction Team for Design, Fa...</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>NEEDS | Jharkhand
 EoI - Selection of Skilled Bamboo Craft / Construction Team for Design, Fabrication and Erection of a Bamboo Innovation Centre, NEEDS() | DevNetJobsIndia
@@ -3069,7 +3272,7 @@
 Registe ... Read More</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work of the Selected Bamboo Team:
 The selected team will preferably undertake the following activities.
@@ -3181,54 +3384,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3259,63 +3462,954 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>05-10-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H29" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303948</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Poshan Vatika Grant 2026 – National Medicinal Plants Board</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>The National Medicinal Plants Board (NMPB), under the Ministry of AYUSH, Government of India, works to promote the cultivation, conservation and sustainable use of medicinal plants. Its programmes support medicinal plant development, awareness, cultivation and related activities across India. The Bo ... Read More</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Eligible applicants include government organisations, NGOs and voluntary organisations with demonstrated experience relevant to the proposed Poshan Vatika project. Applicants should be capable of establishing and maintaining a nutrition garden within an eligible Eklavya Model Residential School. The proposed site should have suitable cultivable land and the necessary conditions for plantation and maintenance, including appropriate irrigation and arrangements for ongoing upkeep. Projects should include at least 30 suitable plant species and activities such as training, awareness and educational support. Organisations applying for government grants for NGOs should demonstrate the capacity to implement, monitor and maintain the garden for the full project period.</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>5 October 2026</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/poshan-vatika-grant-2026-national-medicinal-plants-board/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Citi Foundation Global Innovation Challenge 2026 – $500,000 Grant</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>The Citi Foundation works with community organisations addressing social and economic challenges affecting low-income communities around the world. Through its Global Innovation Challenge, the Foundation provides philanthropic funding to organisations developing innovative solutions that can be pilo ... Read More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>The opportunity is intended for eligible community organisations working with low-income young people. Applicants should have an innovative solution addressing the changing employment landscape and helping youth develop skills needed in an AI-shaped economy. Relevant activities include AI and digital skills, critical thinking, problem-solving, employment connections, shared technology access, AI integration into existing youth employment programmes and cross-sector partnerships. The official RFP contains the complete eligibility criteria and target geographies, so organisations should review those requirements before submitting an application. Citi Foundation operates internationally across more than 80 countries and territories, but applicants must meet the specific geographic and organisational requirements of the current challenge.</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-citi-foundation-global-innovation-challenge-2026-500000-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Electropreneur Park 2.0 Open Challenge Programme in India</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Software Technology Parks of India (STPI) is an autonomous society under theMinistry of Electronics and Information Technology (MeitY), Government of India. STPI works to strengthen India’s technology ecosystem through infrastructure, incubation, entrepreneurship and support for technology businesse ... Read More</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>TheElectropreneur Park 2.0 Open Challenge Programmeis open to students, budding entrepreneurs and startups developing innovative solutions in ESDM or cognitive computing and social sensing. Eligible applicants may include individuals at the ideation stage requiring prototype-development support, early or pre-revenue startups, prototype-stage ventures and startups with breakthrough technologies. Relevant areas include MedTech, EdTech, automotive electronics, strategic electronics, EVs, defence, drones and other ESDM applications. The programme particularly supports innovators who need access to prototyping facilities, technical mentoring, incubation, market support and funding or investment opportunities.</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-electropreneur-park-2-0-open-challenge-programme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read More</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>TheChevening Scholarship for Hondurasprovides exceptional Honduran professionals with a fully funded opportunity to pursue aone-year taught master’s degree at an eligible UK university. The scholarship covers tuition fees, living expenses, travel and additional eligible allowances. Beyond financial support, scholars gain access to Chevening’s international community and professional network. Applicants are expected to demonstrate leadership potential, professional experience, networking ability and a clear vision for their future impact. A key condition is that successful scholars return toHonduras for at least two yearsafter completing their scholarship, allowing them to apply their knowledge and experience in their home country.</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>6 October 2026</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/submit-applications-for-chevening-scholarship-honduras/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Apply for GFF × CIVIC VOICES Funding 2026 – US$3.35 Million Funding Pool</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>The GFF × CIVIC VOICES initiative brings together the Global Financing Facility and the VOICES consortium to strengthen civil society participation in health decision-making across participating African countries. The programme is implemented through partners including PATH, the African Institute fo ... Read More</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should review the official GFF × CIVIC VOICES call materials, technical proposal template, budgeting template and frequently asked questions before preparing their submission. Partnerships must meet the required organisation composition and geographic eligibility criteria. Applications should be submitted according to the official instructions provided by the VOICES consortium. The programme also provides advocacy training, budget-analysis assistance and mentorship to selected partnerships.</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>7 October 2026</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-gff-x-civic-voices-funding-2026-us3-35-million-funding-pool/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>Apply for MNRE Concentrating Solar Thermal Technology Grant 2026</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, d ... Read More</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>The Ministry of New and Renewable Energy (MNRE), Government of India, is responsible for promoting renewable energy development and adoption across the country. The Ministry supports programmes covering solar, wind, bioenergy, hydrogen and other renewable technologies. MNRE also promotes research, development, demonstration and deployment of renewable energy technologies through dedicated programmes. Its Renewable Energy Research and Technology Development Programme supports technology development and practical applications of renewable energy. Through this current call, MNRE is encouraging the development and deployment of concentrating solar thermal technology for Indian industries, particularly solutions capable of providing clean heat for industrial processes.</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>7 October 2026</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-prip-pharma-medtech-innovation-scheme/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>Pfizer HRRm Testing Education Grant 2026: Apply for Up to $100,000</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombinati ... Read More</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Pfizeris the funder of this independent medical education grant programme, which supports organisations working in healthcare professional education and healthcare improvement. The programme focuses on strengthening healthcare professionals’ knowledge, skills, and confidence inHomologous Recombination Repair mutation (HRRm) testingfor metastatic prostate cancer. Through this funding opportunity, Pfizer supports practical educational initiatives that help multidisciplinary healthcare teams apply guideline-based testing approaches in clinical practice. The programme particularly emphasizes education covering pre-analytical considerations, testing-related decision-making, interpretation of results, and communication of testing information throughout the patient care pathway.</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>08 October 2026</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/pfizer-hrrm-testing-education-grant-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>2026 CSO Call for Expressions of Project Intentions – AFD</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Agence Française de Développement (AFD) is France’s public development agency working to finance and support projects that contribute to sustainable development, poverty reduction, climate action, biodiversity, social inclusion and international solidarity. Through its CSO Initiatives mechanism, AFD ... Read More</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Eligible CSOs should prepare a project intention describing the proposed project, objectives, expected outcomes, target communities and implementation approach. Applications must be submitted through AFD’s OSCar platform using the relevant project-intention documentation. Organisations without an OSCar account were required to request account creation by 15 September 2026. Complete project intentions must be submitted online by the final deadline. Applicants should carefully review the eligibility and documentation requirements before submission.</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>9 October 2026</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/2026-cso-call-for-expressions-of-project-intentions-afd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>WHO/IBP Network SPARK Grants 2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>The World Health Organization (WHO) works globally to promote health, prevent disease and strengthen health systems, while the IBP Network brings together organisations and partners working to translate WHO guidance into effective health programmes. The network supports evidence-based approaches to ... Read More</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>The WHO/IBP Network SPARK Grants 2026 support youth-led, women-led and Indigenous-led community-based organisations applying WHO guidance in innovative, locally grounded ways. Selected organisations can receive funding for one-year projects addressing sexual and reproductive health, maternal health, newborn health, child health and adolescent health and rights. Alongside financial assistance, grantees receive technical support, opportunities for peer learning and connections with the wider IBP Network. The programme is designed to strengthen locally driven approaches and help community organisations translate evidence and global health guidance into practical interventions. These global health grants provide an opportunity for organisations to strengthen community-level health outcomes.</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>9 October 2026</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/who-ibp-network-spark-grants-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Samhita-CGF Catalytic Grant 2026 – Up to ₹1 Crore for Education</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Samhita–Collective Good Foundation works with organisations and partners seeking practical solutions to social and development challenges in India. Its grantmaking supports initiatives that improve access to essential services, strengthen systems and create sustainable opportunities for underserved ... Read More</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Interested organisations should review Samhita-CGF’s programme information and eligibility requirements and submit an Expression of Interest through the designated application form. Applicants should clearly explain their education programme, target communities, expected outcomes, organisational experience and proposed use of funding. Samhita has also announced an applicant webinar for September 25, 2026. The EOI deadline is October 9, 2026.</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>9 October 2026</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-samhita-cgf-catalytic-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>Apply for GEF Small Grants in Sri Lanka – Up to $60,000 for Conservation Projects</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>TheGlobal Environment Facility (GEF)provides financial support for projects that address global environmental challenges while generating benefits for local communities. Through itsSmall Grants Programme (SGP), GEF supports community-based organisations and civil society groups implementing locally ... Read More</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should develop a project proposal that clearly explains the environmental challenge being addressed, proposed activities, expected results, community participation, and anticipated conservation benefits. Organisations should ensure that their proposed initiative meets the programme’s eligibility and thematic requirements. Applicants should follow the official GEF Small Grants Programme application process and submit the required information before the stated deadline. Project proposals should demonstrate practical, community-based approaches to conservation and sustainable environmental management.</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>09 October 2026</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-gef-small-grants-in-sri-lanka/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Technology Support Programme 2026</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>The Technology Support Programme for Small NGOs and Grassroots Organisations is designed to strengthen the digital and technological capacity of smaller civil society organisations. The programme focuses on helping organisations use technology to improve their operations, programme implementation, m ... Read More</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>The programme is intended for small NGOs, grassroots organisations, community-based organisations and other eligible civil society groups requiring technology or digital-capacity support. Applicants should have a clearly identified organisational technology need and demonstrate how the proposed assistance could improve their work. Eligible organisations should be able to explain their existing technology challenges and the practical solution required. Applicants may need to provide relevant organisational documentation and information about their programmes. Organisations applying for technology grants India should ensure that their proposed requirement is connected to genuine operational, programme management, data, communication or monitoring needs.</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>10 October 2026</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/technology-support-programme-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Apply for Resilience Fund for Women in Global Value Chains 2026 – Up to US$50,000</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>The Resilience Fund for Women in Global Value Chains The Resilience Fund for Women in Global Value Chains is a philanthropic initiative supporting women-led and community-based organisations working with women connected to global supply chains. The fund promotes locally led solutions addressing wome ... Read More</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>The Resilience Fund for Women in Global Value Chains 2026 provides flexible, unrestricted grants to women-led, community-based organisations in India, Bangladesh, Cambodia and Vietnam. Selected organisations can receive between US$15,000 and US$50,000 over two years. The fund supports work connected to women’s health and safety, economic resilience, climate adaptation and the rights and wellbeing of women workers in global value chains. Funding is designed to give local organisations greater flexibility in responding to community priorities rather than restricting every grant dollar to narrowly defined activities. Applications for the current round opened on September 18, 2026.</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>Women &amp; Gender</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>12 October 2026</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-resilience-fund-for-women-in-global-value-chains-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>AndPurpose</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Apply for the ServiceNow Community Solar Fund 2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ChangeXis an international non-profit community engagement platform that connects communities with proven ideas, funding and practical support. The organisation works with social innovators, companies and foundations to help communities implement projects addressing environmental, economic and socia ... Read More</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants should visit the official ChangeX fund page, review the available community solar project ideas and select the idea that best fits their organisation and community. Complete the online application by 13 October 2026 (IST) and provide the required organisational information and documentation. ChangeX will review applications after the deadline, with successful applicants expected to be notified by 3 December 2026.</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>13 October 2026</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>https://andpurpose.world/apply-for-the-servicenow-community-solar-fund-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme i...</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>World Resources Institute India (WRI India) | Karnataka
-RFP - Design and Delivery of an Electric Vehicle (EV) Skilling Programme in Karnataka, World Resources Institute India (WRI India)() | DevNetJobsIndia
+      <c r="B44" s="1" t="inlineStr"/>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Design, Development, Deployment &amp; Maintenance Of Drug Dispensing &amp; D...</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Society For Promotion Of Youth &amp; Masses (SPYM) | South Delhi, Delhi
+RFP - Design, Development, Deployment &amp; Maintenance Of Drug Dispensing &amp; Drug Database Management Software, Society For Promotion Of Youth &amp; Masses (SPYM)(South Delhi) | DevNetJobsIndia
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs ... Read More</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-Aprajita.Verma(at)wri.org
-Download Attachment:
-RFP- EV Skilling Programme in Karnataka.pdf
+Value Membe ... Read More</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>• SECTION 4: SCOPE OF WORK
+At this stage, the scope is limited to digitisation and management of medicine stock and dispensing records. The system shall be designed to accommodate future expansion without architectural rework.
+4.1 Drug Dispensing &amp; Inventory Management Module
+A. Central Stock Management
+•           Entry of medicines received from suppliers into the central stock register
+•           Batch-wise inventory capturing: Medicine name, Batch number, Manufacturing date, Expiry date, Quantity received, Supplier details, Invoice/reference details
+•           Automatic stock balance calculation with FEFO/FIFO inventory logic
+•           Prevention of issue of expired medicines; near-expiry alerts (configurable, default 60 days)
+•           Daily stock reconciliation and physical vs. digital stock variance reporting
+•           Buffer stock monitoring with alerts
+•           Drug master data including: Generic Name, Brand Names, Schedule Class, Therapeutic Category, Dosage Form, Strength, Unit of Measure, Controlled Substance Flag, Cold Chain Flag, Minimum Stock Level
+B. Stock Transfer to Dispensing Units
+•           Transfer of medicines from central stock to dispensing units with unit-wise stock ledgers
+•           Transfer acknowledgement workflow and audit logs
+•           Minimum buffer stock monitoring (minimum 15 days)
+•           Batch-wise stock transfer tracking
+C. Prescription-Based Dispensing
+Note:
+Bidders must clearly specify in their proposal whether the solution covers dispensing against existing prescriptions only, or also includes doctor consultation and e-prescription generation.
+•           Dispensing only against active, valid doctor prescriptions with mandatory linkage to patient treatment records
+•           Prescription validity checks and duplicate dispensing prevention
+•           Dosage validation controls and daily dose tracking
+•           Missed dose/non-collection tracking
+•           Emergency dispensing workflow with approval trail and override logging
+D. Digital Dispensing Register
+•           Patient-wise and medicine-wise dispensing records with automatic date/time stamping
+•           Unit-wise dispensing logs and daily dispensing summaries
+•           Medicine consumption analytics
+E. Beneficiary Acknowledgement
+•           Capture of beneficiary digital signature or thumb impression as confirmation of receipt
+•           Timestamped acknowledgement records
+•           Vendor must propose a cost-effective device/method for digital signature capture; fallback: supervisor witness counter-signature if device fails
+F. Verification &amp; Approval Workflow
+•           Nurse/Pharmacist: daily verification and digital countersignature of dispensing records
+•           Project In-charge: end-of-day review and approval with pending alerts and exception reporting
+•           Mandatory synchronisation before end-of-day approval workflow
+G. Patient Management
+Bidders must include the following minimum patient master features to prevent duplicate records and ensure data integrity.
+•           Unique Patient ID: auto-generated with optional Aadhaar and ABHA Card linkage
+•           Mandatory registration fields: Name, Age, Gender, Address, Emergency Contact, Admission Date, Primary Substance of Use, Treatment Type
+•           Deduplication check at registration: Name + Date of Birth + Phone
+•           Digital consent form capture at registration
+•           Allergy field mandatory with red alert on dispensing conflict
+•           Minor patients: guardian details mandatory, separate consent
+•           Deceased/discharged patients: archive view only (not deleted); data retention minimum 2 years post-discharge
+•           Patient data export in PDF for referral to other hospitals/other doctors – Customisable Fields
+•           Complete patient-wise medication history with cumulative dosage records (read-only archived records)
+H. Unit-wise Data Segregation
+•           Separate and independent management of records for AIIMS Community Clinic and SPYM DTC
+•           Both units operate within separate logical partitions under a common software platform
+•           Authorised administrators have oversight access across both units
+I. Document Management
+•           Upload and storage of scanned prescriptions and supporting documents / OCR Technology
+•           Searchable digital document archive with configurable document retention policy
+J. Notifications &amp; Alerts
+•           Configurable alerts for: Low stock, Near-expiry medicines, pending verification/approvals, Missed dispensing, Buffer stock shortages
+•           Future integration capability with SMS/email notification systems / 2 factor authentication
+4.2 Reports &amp; Dashboard Module
+The software shall include configurable dashboards and report generation with export options in PDF and Excel formats.
+A. Drug Dispensing Reports
+•           Unit-wise dispensing reports and period-wise summaries
+•           Medicine-wise dispensing trends
+B. Drug Stock Reports
+•           Real-time stock position and batch-wise inventory
+•           Expiry tracking: quantity received, quantity issued, current balance, near-expiry status, buffer stock
+C. Patient-wise Dispensing Summary
+•           Monthly dispensing summaries and period-based patient dispensing reports
+•           Patient medication history reports
+D. Audit Trail &amp; Activity Log
+•           Comprehensive audit trail capturing: User ID, Date &amp; timestamp, Activity performed, Before/after value tracking
+E. Exception &amp; Variance Reports
+•           Stock variance reports, missed dispensing reports, pending approvals, adjustment reports
+4.3 Administration &amp; User Management
+Role-Based Access Control (RBAC)
+Roles shall include at minimum:
+•           Medical Officer / Doctor
+•           Nurse / Pharmacist
+•           Project In-charge
+•           Medical Social Welfare Officer (MSWO)
+•           System Administrator
+Security Features
+•           Secure login with minimum password policy: 8 characters, uppercase, number, special character; 90-day expiry; no reuse of last 5 passwords
+•           Session auto-timeout: 10 minutes inactivity
+•           Two-factor authentication (2FA) mandatory for Doctor and Project In-charge roles
+•           Account lockout after 5 failed login attempts for 30 minutes; failed login tracking and admin activity monitoring
+•           User activity logging and IP/session logging
+•           Role-based permissions with unit-based data partitioning
+4.4 Technical Requirements
+A. Application Architecture
+•           Web-based application accessible via standard browsers; mobile-responsive interface preferred
+•           Centralised cloud-hosted system with browser-based access and centralised database
+•           Modular and scalable architecture, API-enabled for future integrations
+•           Multi-user concurrent access support: minimum 15–20 concurrent users across both units at go-live, architecture to scale to 50+ concurrent users as additional centres are added
+•           Target response time: page/screen load within 3 seconds and transaction save (e.g. dispensing entry) within 2 seconds under normal load
+•           Multi-centre scalability: configurable for deployment at new locations
+•           Minimum uptime target: 99.5%
+B. Offline Functionality
+Offline functionality is critical for this deployment and must be fully addressed in the technical proposal.
+•           Local offline transaction capture with queue-based synchronisation
+•           Offline data encrypted using device-level AES-256
+•           Automatic synchronisation on internet restoration with conflict resolution (last-write-wins with conflict log for review)
+•           Maximum recommended offline period: 24 hours
+•           Core features available offline: dispensing, stock view, prescriptions
+•           Online-only features: reports, admin, user management
+•           Sync priority order: dispensing &gt; stock &gt; signatures &gt; reports
+•           Visual sync status indicator: green = synced, amber = pending, red = failed
+•           Optimum internet bandwidth for sync operations: 512 kbps
+•           Synchronisation audit logs and data integrity validation during sync
+C. Hosting &amp; Infrastructure
+•           Cloud-hosted deployment preferably within India
+•           Daily automated backup and disaster recovery mechanism with backup restoration testing capability
+•           Data archival: minimum 7 years of data to be stored and available for reporting
+D. Security &amp; Compliance
+•           HTTPS/TLS 1.3 (minimum TLS 1.2) in transit; AES-256 encryption at rest
+•           Secure password hashing; OWASP Top 10 compliance
+•           Compliance with DPDP Act 2023, IT Act 2000, and NDPS Act 1985
+•           Vulnerability assessment and security audit before deployment; annual VAPT by certified agency
+E. Data Ownership &amp; Portability
+•           All data shall remain sole property of SPYM and NDDTC, AIIMS
+•           Vendor shall provide complete database export capability
+•           Vendor shall not retain or reuse patient data; no proprietary lock-in architecture
+F. Data Migration
+Bidders must clearly state in their proposal whether digitisation/migration of existing manual or paper records is: (a) included in scope, (b) partially included, or (c) out of scope with a separate cost indication.
+G. Training &amp; Change Management
+•           User and administrator training at Kotla Mubarakpur for staff of both units
+•           Training manuals, go-live support, and handholding support during implementation
+SECTION 5: KEY DELIVERABLES &amp; TIMELINES
+S.No.    Deliverable       Timeline (from Agreement)
+1          Requirement Study, Workflow Mapping &amp; SRS    60-90 Days
+2          System Architecture Document &amp; UI/UX Wireframes / Prototype for Approval
+3          Alpha Version of Application
+4          Beta Version for UAT at Kotla Mubarakpur (both units)
+5          UAT Feedback Incorporation &amp; Bug Fixes
+6          Production Deployment (both AIIMS Clinic and SPYM DTC)
+7          User Training &amp; Go-live Support
+8          Source Code, Technical Documentation &amp; Handover       After Completion of Development of the Software
+SECTION 6: MANDATORY DOCUMENTATION &amp; TESTING DELIVERABLES
+Vendor shall submit all of the following as part of the contract:
+•           Software Requirement Specification (SRS)
+•           System Architecture Document
+•           Database Schema Documentation
+•           API Documentation
+•           Deployment Manual
+•           User Manual (role-wise)
+•           Administrator Manual
+•           Backup &amp; Recovery SOP
+•           Security Architecture Documentation
+•           Test Cases &amp; Test Reports
+•           UAT Completion Report (with signoff process, acceptable defect levels, and production readiness approval criteria)
+•           Vulnerability Assessment Report
+•           Source Code Repository Access
+• SECTION 7: ELIGIBILITY CRITERIA
+• Proposals may be submitted by registered organisations as well as by individual professionals with relevant experience. Interested bidders must fulfil the minimum eligibility criteria applicable to their category, as set out below:
+A. Organisations (Company / LLP / Firm / NGO-Tech wing)
+•           Registered Company/LLP/Firm/NGO-Tech wing under applicable Indian laws
+•           Minimum 3 years of experience in software/application development
+•           Minimum 1 completed healthcare, hospital, pharmacy, dispensing management, or NGO management software project (mandatory; to be cited with client reference)
+•           Experience in multi-user, multi-location enterprise applications
+•           Prior work with government or social sector organisations is desirable
+•           Positive net worth during the last two financial years
+•           Not blacklisted by any government or institutional agency
+B. Individuals with Relevant Experience
+•           Individual professional / sole proprietor / freelance developer with a valid PAN and a valid government-issued photo ID and address proof
+•           Minimum 3 years of hands-on individual experience in software/application development, evidenced by a detailed CV
+•           Experience in designing or developing multi-user, multi-location applications
+•           Prior work with government or social sector organisations is desirable
+•           Income Tax Returns for the last two financial years demonstrating financial capacity to undertake the assignment (in place of the net worth requirement applicable to organisations)
+•           Not blacklisted by any government or institutional agency (self-declaration required)
+• Individual bidders shall be evaluated against the same criteria as organisations under Section 9 (Evaluation Criteria), without preference or prejudice on account of bidder category.
+• SECTION 8: PROPOSAL REQUIREMENTS
+8.1 Technical Proposal
+•           Company profile (organisations) or detailed individual profile/CV (individuals), and relevant project experience
+•           Understanding of SPYM requirements as described in this RFP
+•           Proposed system architecture and technology stack
+•           Project implementation methodology and detailed work plan with timelines
+•           Portfolio of minimum 2 relevant projects
+•           Details of team members/sub-contractors (if any) and continuity plan (mandatory for individual bidders)
+•           Clarification on prescription scope: dispensing-only vs. e-prescription generation
+•           Clarification on data migration scope: included / partial / out of scope
+•           Offline functionality architecture and approach
+•           Data security and privacy approach
+•           Training and change management plan
+•           Support and AMC approach with proposed SLA timelines
+8.2 Financial Proposal
+•           Item-wise costing for: requirement analysis, UI/UX design, software development, testing, deployment, cloud hosting (Year 1 &amp; 2), training, warranty support, AMC Year 1, AMC Year 2
+•           Payment terms proposed by the bidder
+•           Total cost of ownership for Year 1 and Year 2
+•           Price validity period
+8.3 Supporting Documents
+•           Certificate of incorporation/registration (organisations) or valid government photo ID and address proof (individuals)
+•           GST registration certificate (if applicable)
+•           PAN card of the entity/individual
+•           Audited financial statements for last 2 years (organisations) or Income Tax Returns for last 2 years (individuals)
+•           Client reference letters for at least 2 prior relevant projects
+•           Self-declaration regarding non-blacklisting
+•           Detailed CV highlighting relevant experience and qualifications (individuals)
+• SECTION 9: EVALUATION CRITERIA
+Proposals shall be evaluated on Quality-cum-Cost Based Selection (QCBS):
+S.No.    Evaluation Parameter    Weightage (%)
+1          Relevant healthcare/pharmacy/NGO software experience           25%
+2          Technical approach, architecture &amp; solution design          25%
+3          Security, scalability &amp; offline capability    15%
+4          Team qualifications &amp; project management plan 10%
+5          Training plan &amp; post-deployment support 5%
+6          Financial proposal (cost competitiveness)          20%
+TOTAL 100%
+Shortlisted bidders may be invited for a technical presentation and product demonstration.
+SECTION 10: PAYMENT TERMS
+Milestone          Payment (%)
+Requirement sign-off &amp; SRS approval    10%
+Prototype / Wireframe approval 15%
+Beta / UAT deployment 30%
+Final production deployment      30%
+Documentation &amp; source code handover 10%
+Post go-live stabilisation support (30 days)         5%
+Payments shall be released subject to milestone approval and submission of applicable invoices. SPYM typically releases payment within 30 working days of milestone approval.
+SECTION 11: WARRANTY, AMC &amp; SUPPORT
+11.1 Warranty
+•           Minimum 12 months warranty support from date of Go-live
+•           Warranty shall include: unlimited bug fixing, security patches, performance optimisation, and technical support
+11.2 AMC &amp; Support
+•           Vendor shall provide Annual Maintenance Contract (AMC) pricing after the warranty period
+•           AMC proposal must define: response time SLAs, issue resolution timelines by severity classification (Critical / High / Medium / Low)
+• •           Example SLA expectation: Critical (system down) — response within 2 hours, resolution within 8 hours; High (major feature failure) — response within 4 hours, resolution within 24 hours
+SECTION 12: SUBMISSION PROCESS &amp; TIMELINE
+Step     Activity Date
+1          RFP Issued      29.09.2026
+2          Last Date for Queries / Clarifications      01.10.2026
+3          Proposal Submission Deadline   14.10.2026
+Proposals submitted after the deadline will not be considered. SPYM reserves the right to modify the timeline with prior notice.
+SECTION 13: GENERAL TERMS &amp; CONDITIONS
+•           SPYM reserves the right to accept or reject any proposal, in whole or in part, without assigning reasons.
+•           Submission of a proposal does not guarantee award of contract.
+•           All costs incurred in preparing and submitting proposals shall be borne solely by the bidder.
+•           SPYM reserves the right to negotiate scope, timelines, and financial terms with the selected bidder.
+•           The selected vendor shall sign a Non-Disclosure Agreement (NDA) and a Data Protection &amp; Confidentiality Agreement prior to commencement of work.
+•           All patient and organisational data shall remain strictly confidential.
+13.1 Intellectual Property Rights
+All source code, documentation, database structures, APIs, workflows, and associated intellectual property developed under this assignment shall vest with SPYM upon full payment. Vendor shall provide complete source code, database scripts, technical documentation, deployment files, and administrative credentials.
+13.2 Data Protection &amp; Confidentiality
+Vendor shall maintain strict confidentiality of all patient and organisational data, not share or reuse data outside approved infrastructure, and comply with applicable data protection laws including the DPDP Act 2023 and IT Act 2000. Vendor shall remain liable for any breach arising due to negligence or non-compliance.
+13.3 Indemnity
+Vendor shall indemnify SPYM against data breaches, third-party claims, copyright and licensing violations, and negligence-related losses.
+13.4 Termination
+SPYM may terminate the contract for non-performance, breach of confidentiality, delayed delivery, or regulatory non-compliance. Upon termination, vendor shall provide transition support and complete data handover.
+13.5 Force Majeure
+Neither party shall be liable for delays caused by force majeure events beyond reasonable control.
+13.6 Governing Law &amp; Jurisdiction
+The contract shall be governed by the laws of India. Disputes shall first be attempted to be resolved amicably. Courts at New Delhi shall have jurisdiction.
+SECTION 14: CONTACT INFORMATION
+Field     Details
+Organisation    :
+Society for the Promotion of Youth &amp; Masses (SPYM)
+Contact Person
+: Aaditi Wahi, Research Assistant
+Phone
++91 8178693893
+Email
+aaditi@spym.org
+Alternate Email
+info@spym.org
+SECTION 15: ANNEXURES TO BE SUBMITTED WITH PROPOSAL
+•           Annexure A — Bidder Profile (Name, registered/residential address, year of establishment or start of professional practice, legal status — organisation or individual, key clients); individuals to attach a detailed CV
+•           Annexure B — Technical Proposal (as per Section 8.1)
+•           Annexure C — Financial Proposal (as per Section 8.2 — to be submitted in a separate sealed envelope or separate email)
+• •           Annexure D — Portfolio of Relevant Work (minimum 2 projects with client contact details)
+•           Annexure E — Declaration of Non-Conflict of Interest
+•           Annexure F — Copies of registration/identity proof, GST (if applicable), PAN, and audited financials/Income Tax Returns
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-05 Oct 2026
+14 Oct 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3384,54 +4478,54 @@
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Social Worker
-Smt Kaushilya Devi Purva Madhyamik Vidyalaya Sami...
+RFP - Hiring a service provider to provide infras...
+Project Concern International India (PCI India )
+Location:
+India
+Apply by:
+04 Oct 2026
+Project Manager (Health and Nutrition)
+TRIOs Development Support (P) Ltd
+Location:
+Delhi
+Apply by:
+19 Oct 2026
+RFP - Hiring a service provider to provide food/c...
+Project Concern International India (PCI India )
+Location:
+Odisha
+Apply by:
+01 Oct 2026
+District Project Coordinator-Wash Finance
+Inductus Limited
+Location:
+Odisha
+Apply by:
+05 Oct 2026
+RFP - Agency/Consultant for conducting a Comprehe...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Punjab
+Apply by:
+12 Oct 2026
+RFP - intends to engage a Consulting Agency to ca...
+Aga Khan Rural Support Programme (India)
+Location:
+Maharashtra
+Apply by:
+23 Oct 2026
+Field Coordinator
+Project Concern International India (PCI India )
 Location:
 Uttar Pradesh
 Apply by:
-30 Sep 2026
-Senior Associate - Social Media &amp; Comms
-(Value Members only)
-Location:
-Karnataka
-Apply by:
-05 Oct 2026
-Senior Coordinator, Strategy and Convergence
-Jan Sahas Foundation
-Location:
-Madhya Pradesh
-Apply by:
-20 Oct 2026
-Senior Field Consultant
-Soulace
-Location:
-India
-Apply by:
-28 Oct 2026
-Report Writer (Consultant)
-Soulace
-Location:
-Delhi
-Apply by:
-28 Oct 2026
-Community Coordinator
-Habitat for Humanity India
-Location:
-Maharashtra
-Apply by:
-28 Oct 2026
-Assistant Manager (Partnerships and Fundraising)
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
-Assistant Manager – MIS
-PRAGYA
-Location:
-Haryana
-Apply by:
-28 Oct 2026
+04 Oct 2026
+Field Officer, Programs (Grade-5)
+ChildFund India
+Location:
+Odisha
+Apply by:
+06 Oct 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3462,697 +4556,22 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>05-10-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=303753</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>Apply for Electropreneur Park 2.0 Open Challenge Programme in India</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Software Technology Parks of India (STPI) is an autonomous society under theMinistry of Electronics and Information Technology (MeitY), Government of India. STPI works to strengthen India’s technology ecosystem through infrastructure, incubation, entrepreneurship and support for technology businesse ... Read More</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>TheElectropreneur Park 2.0 Open Challenge Programmeis open to students, budding entrepreneurs and startups developing innovative solutions in ESDM or cognitive computing and social sensing. Eligible applicants may include individuals at the ideation stage requiring prototype-development support, early or pre-revenue startups, prototype-stage ventures and startups with breakthrough technologies. Relevant areas include MedTech, EdTech, automotive electronics, strategic electronics, EVs, defence, drones and other ESDM applications. The programme particularly supports innovators who need access to prototyping facilities, technical mentoring, incubation, market support and funding or investment opportunities.</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>6 October 2026</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-electropreneur-park-2-0-open-challenge-programme/</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Apply for Citi Foundation Global Innovation Challenge 2026 – $500,000 Grant</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>The Citi Foundation works with community organisations addressing social and economic challenges affecting low-income communities around the world. Through its Global Innovation Challenge, the Foundation provides philanthropic funding to organisations developing innovative solutions that can be pilo ... Read More</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>The opportunity is intended for eligible community organisations working with low-income young people. Applicants should have an innovative solution addressing the changing employment landscape and helping youth develop skills needed in an AI-shaped economy. Relevant activities include AI and digital skills, critical thinking, problem-solving, employment connections, shared technology access, AI integration into existing youth employment programmes and cross-sector partnerships. The official RFP contains the complete eligibility criteria and target geographies, so organisations should review those requirements before submitting an application. Citi Foundation operates internationally across more than 80 countries and territories, but applicants must meet the specific geographic and organisational requirements of the current challenge.</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>6 October 2026</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>https://andpurpose.world/apply-for-citi-foundation-global-innovation-challenge-2026-500000-grant/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>AndPurpose</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Submit Applications for Chevening Scholarship (Honduras)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Cheveningis the UK Government’s international scholarship programme for emerging and established leaders around the world. The programme provides talented professionals with the opportunity to pursue postgraduate education in the United Kingdom while developing their professional networks and leader ... Read Mo